--- a/DB Flotte ETR1000 Ver_1.8_PROVA.xlsx
+++ b/DB Flotte ETR1000 Ver_1.8_PROVA.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="Questa_cartella_di_lavoro"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="14400" yWindow="0" windowWidth="14400" windowHeight="15600" tabRatio="600" firstSheet="5" activeTab="8" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="600" firstSheet="5" activeTab="8" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issue" sheetId="1" state="visible" r:id="rId1"/>
@@ -22,7 +22,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Modifiche progettuali" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Requisiti'!$A$1:$K$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Requisiti'!$A$1:$K$57</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'PBS (TBD)'!$A$2:$J$86</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -34,7 +34,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-410]mmm\-yy;@"/>
   </numFmts>
-  <fonts count="37">
+  <fonts count="36">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -262,12 +262,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <b val="1"/>
-      <color rgb="FFBF8F00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
       <color rgb="FFBF8F00"/>
       <sz val="11"/>
     </font>
@@ -1486,7 +1480,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="525">
+  <cellXfs count="524">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2652,11 +2646,8 @@
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="57" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2862,10 +2853,10 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3829,8 +3820,8 @@
   <cols>
     <col width="10.85546875" customWidth="1" style="8" min="1" max="2"/>
     <col width="59" customWidth="1" style="8" min="3" max="3"/>
-    <col width="8.7109375" customWidth="1" style="8" min="4" max="12"/>
-    <col width="8.7109375" customWidth="1" style="8" min="13" max="16384"/>
+    <col width="8.7109375" customWidth="1" style="8" min="4" max="13"/>
+    <col width="8.7109375" customWidth="1" style="8" min="14" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" s="107">
@@ -3949,7 +3940,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K76"/>
+  <dimension ref="A1:K75"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="22.140625" bestFit="1" customWidth="1" style="62" min="1" max="1"/>
@@ -3960,8 +3951,8 @@
     <col width="14.85546875" customWidth="1" style="10" min="10" max="11"/>
     <col width="8.7109375" customWidth="1" style="59" min="12" max="12"/>
     <col width="33.140625" customWidth="1" style="59" min="13" max="13"/>
-    <col width="8.7109375" customWidth="1" style="59" min="14" max="16"/>
-    <col width="8.7109375" customWidth="1" style="59" min="17" max="16384"/>
+    <col width="8.7109375" customWidth="1" style="59" min="14" max="17"/>
+    <col width="8.7109375" customWidth="1" style="59" min="18" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" s="61">
@@ -3995,22 +3986,22 @@
           <t>VZI_New14</t>
         </is>
       </c>
-      <c r="G1" s="440" t="inlineStr">
+      <c r="G1" s="439" t="inlineStr">
         <is>
           <t>VZ_FR</t>
         </is>
       </c>
-      <c r="H1" s="440" t="inlineStr">
+      <c r="H1" s="439" t="inlineStr">
         <is>
           <t>VZ_ES</t>
         </is>
       </c>
-      <c r="I1" s="440" t="inlineStr">
+      <c r="I1" s="439" t="inlineStr">
         <is>
           <t>VZI-6_R1</t>
         </is>
       </c>
-      <c r="J1" s="440" t="inlineStr">
+      <c r="J1" s="439" t="inlineStr">
         <is>
           <t>VZI-4_R1</t>
         </is>
@@ -4042,7 +4033,7 @@
       <c r="J2" s="334" t="n"/>
       <c r="K2" s="335" t="n"/>
     </row>
-    <row r="3" ht="30" customHeight="1" s="479">
+    <row r="3" ht="30" customHeight="1" s="478">
       <c r="A3" s="347" t="inlineStr">
         <is>
           <t>LV_Country_code_selection</t>
@@ -4063,29 +4054,13 @@
       <c r="J3" s="350" t="n"/>
       <c r="K3" s="351" t="n"/>
     </row>
-    <row r="4" ht="30" customFormat="1" customHeight="1" s="8">
-      <c r="C4" s="428" t="n"/>
-      <c r="D4" s="421" t="n"/>
-    </row>
-    <row r="5" ht="45" customFormat="1" customHeight="1" s="8">
-      <c r="C5" s="428" t="n"/>
-      <c r="D5" s="421" t="n"/>
-    </row>
-    <row r="6" ht="30" customFormat="1" customHeight="1" s="8">
-      <c r="C6" s="426" t="n"/>
-      <c r="D6" s="421" t="n"/>
-    </row>
-    <row r="7" ht="45" customFormat="1" customHeight="1" s="8">
-      <c r="C7" s="426" t="n"/>
-      <c r="D7" s="428" t="n"/>
-    </row>
-    <row r="8" ht="30" customFormat="1" customHeight="1" s="8">
-      <c r="C8" s="524" t="inlineStr">
+    <row r="4" ht="45" customFormat="1" customHeight="1" s="8">
+      <c r="C4" s="523" t="inlineStr">
         <is>
           <t>2F_04.01.Zefiro-Europe.TRS.772</t>
         </is>
       </c>
-      <c r="D8" s="421" t="inlineStr">
+      <c r="D4" s="421" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4132,15 +4107,154 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="45" customFormat="1" customHeight="1" s="8">
+    <row r="5" ht="60" customFormat="1" customHeight="1" s="8">
+      <c r="C5" s="523" t="inlineStr">
+        <is>
+          <t>2F_04.01.Zefiro-</t>
+        </is>
+      </c>
+      <c r="D5" s="421" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00BF8F00"/>
+            </rPr>
+            <t>VZI-6_R1</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+            </rPr>
+            <t xml:space="preserve">, </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="001F4E79"/>
+            </rPr>
+            <t>VZI_Base</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+            </rPr>
+            <t xml:space="preserve">, </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="007030A0"/>
+            </rPr>
+            <t>VZ_ES</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+            </rPr>
+            <t xml:space="preserve">, </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="0000703C"/>
+            </rPr>
+            <t>VZ_FR</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customFormat="1" customHeight="1" s="8">
+      <c r="C6" s="523" t="inlineStr">
+        <is>
+          <t>4S_09.03.05.-.TCMS</t>
+        </is>
+      </c>
+      <c r="D6" s="421" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00BF8F00"/>
+            </rPr>
+            <t>VZI-6_R1</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+            </rPr>
+            <t xml:space="preserve">, </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="001F4E79"/>
+            </rPr>
+            <t>VZI_Base</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+            </rPr>
+            <t xml:space="preserve">, </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="007030A0"/>
+            </rPr>
+            <t>VZ_ES</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+            </rPr>
+            <t xml:space="preserve">, </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="0000703C"/>
+            </rPr>
+            <t>VZ_FR</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customFormat="1" customHeight="1" s="8">
+      <c r="C7" s="523" t="inlineStr">
+        <is>
+          <t>4S_04.-.Power</t>
+        </is>
+      </c>
+      <c r="D7" s="523" t="inlineStr">
+        <is>
+          <t>VZI-6_R1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="45" customFormat="1" customHeight="1" s="8">
+      <c r="A8" s="347" t="inlineStr">
+        <is>
+          <t>LV_Pantograph_Lifting</t>
+        </is>
+      </c>
+      <c r="B8" s="347" t="inlineStr">
+        <is>
+          <t>Comando di alzamento pantografo 1 o 2 sulla base di tensione di linea (switch) e paese (IDU) selezionati</t>
+        </is>
+      </c>
+      <c r="C8" s="303" t="n"/>
+      <c r="D8" s="303" t="n"/>
+      <c r="E8" s="350" t="n"/>
+      <c r="F8" s="350" t="n"/>
+      <c r="G8" s="350" t="n"/>
+      <c r="H8" s="350" t="n"/>
+      <c r="I8" s="350" t="n"/>
+      <c r="J8" s="350" t="n"/>
+      <c r="K8" s="351" t="n"/>
+    </row>
+    <row r="9" ht="30" customFormat="1" customHeight="1" s="8">
       <c r="A9" s="347" t="inlineStr">
         <is>
-          <t>LV_Pantograph_Lifting</t>
+          <t>LV_Pantograph_Lowering</t>
         </is>
       </c>
       <c r="B9" s="347" t="inlineStr">
         <is>
-          <t>Comando di alzamento pantografo 1 o 2 sulla base di tensione di linea (switch) e paese (IDU) selezionati</t>
+          <t>Comando di abbassamento pantografo manuale/automatico</t>
         </is>
       </c>
       <c r="C9" s="303" t="n"/>
@@ -4153,36 +4267,36 @@
       <c r="J9" s="350" t="n"/>
       <c r="K9" s="351" t="n"/>
     </row>
-    <row r="10" ht="60" customFormat="1" customHeight="1" s="8">
-      <c r="A10" s="347" t="inlineStr">
-        <is>
-          <t>LV_Pantograph_Lowering</t>
-        </is>
-      </c>
-      <c r="B10" s="347" t="inlineStr">
-        <is>
-          <t>Comando di abbassamento pantografo manuale/automatico</t>
-        </is>
-      </c>
-      <c r="C10" s="303" t="n"/>
-      <c r="D10" s="303" t="n"/>
-      <c r="E10" s="350" t="n"/>
-      <c r="F10" s="350" t="n"/>
-      <c r="G10" s="350" t="n"/>
-      <c r="H10" s="350" t="n"/>
-      <c r="I10" s="350" t="n"/>
-      <c r="J10" s="350" t="n"/>
-      <c r="K10" s="351" t="n"/>
+    <row r="10" ht="30" customFormat="1" customHeight="1" s="8">
+      <c r="A10" s="353" t="inlineStr">
+        <is>
+          <t>LV_Automatic_Dropping_Device_(ADD)</t>
+        </is>
+      </c>
+      <c r="B10" s="354" t="inlineStr">
+        <is>
+          <t>Dispositivo di abbassamento automatico del pantografo in caso di guasto</t>
+        </is>
+      </c>
+      <c r="C10" s="302" t="n"/>
+      <c r="D10" s="302" t="n"/>
+      <c r="E10" s="357" t="n"/>
+      <c r="F10" s="357" t="n"/>
+      <c r="G10" s="357" t="n"/>
+      <c r="H10" s="357" t="n"/>
+      <c r="I10" s="357" t="n"/>
+      <c r="J10" s="357" t="n"/>
+      <c r="K10" s="358" t="n"/>
     </row>
     <row r="11" ht="30" customFormat="1" customHeight="1" s="8">
       <c r="A11" s="353" t="inlineStr">
         <is>
-          <t>LV_Automatic_Dropping_Device_(ADD)</t>
-        </is>
-      </c>
-      <c r="B11" s="354" t="inlineStr">
-        <is>
-          <t>Dispositivo di abbassamento automatico del pantografo in caso di guasto</t>
+          <t>LV_Pantograph_Interlock</t>
+        </is>
+      </c>
+      <c r="B11" s="360" t="inlineStr">
+        <is>
+          <t>Interblocco automatico dei pantografi in caso di guasto rilevato. Il Pdc può bloccare anche manualmente un pantografo per impedirne la selezione</t>
         </is>
       </c>
       <c r="C11" s="302" t="n"/>
@@ -4198,12 +4312,12 @@
     <row r="12" ht="30" customFormat="1" customHeight="1" s="8">
       <c r="A12" s="353" t="inlineStr">
         <is>
-          <t>LV_Pantograph_Interlock</t>
+          <t>LV_Pantograph_Selection</t>
         </is>
       </c>
       <c r="B12" s="360" t="inlineStr">
         <is>
-          <t>Interblocco automatico dei pantografi in caso di guasto rilevato. Il Pdc può bloccare anche manualmente un pantografo per impedirne la selezione</t>
+          <t>Selezione del pantografo in base al paese (tipologia/dimensioni pantografo) e al sistema di alimentazione (AC/DC) selezionato</t>
         </is>
       </c>
       <c r="C12" s="302" t="n"/>
@@ -4216,15 +4330,15 @@
       <c r="J12" s="357" t="n"/>
       <c r="K12" s="358" t="n"/>
     </row>
-    <row r="13" ht="45" customFormat="1" customHeight="1" s="8">
+    <row r="13" ht="30" customFormat="1" customHeight="1" s="8">
       <c r="A13" s="353" t="inlineStr">
         <is>
-          <t>LV_Pantograph_Selection</t>
+          <t>LV_Pantograph_Control_of_Static_Contact_Force</t>
         </is>
       </c>
       <c r="B13" s="360" t="inlineStr">
         <is>
-          <t>Selezione del pantografo in base al paese (tipologia/dimensioni pantografo) e al sistema di alimentazione (AC/DC) selezionato</t>
+          <t>Controllo della forza statica/pressione del pantografo alzato in funzione del sistema di tensione, della velocità, della direzione di marcia e della posizione del pantografo stesso</t>
         </is>
       </c>
       <c r="C13" s="302" t="n"/>
@@ -4240,12 +4354,12 @@
     <row r="14" ht="30" customFormat="1" customHeight="1" s="8">
       <c r="A14" s="353" t="inlineStr">
         <is>
-          <t>LV_Pantograph_Control_of_Static_Contact_Force</t>
+          <t>LV_Line_Voltage_Supervision</t>
         </is>
       </c>
       <c r="B14" s="360" t="inlineStr">
         <is>
-          <t>Controllo della forza statica/pressione del pantografo alzato in funzione del sistema di tensione, della velocità, della direzione di marcia e della posizione del pantografo stesso</t>
+          <t>Controllo della tensione di linea tramite sensori di tensione letti dal sistema di propulsione</t>
         </is>
       </c>
       <c r="C14" s="302" t="n"/>
@@ -4261,12 +4375,12 @@
     <row r="15" ht="30" customFormat="1" customHeight="1" s="8">
       <c r="A15" s="353" t="inlineStr">
         <is>
-          <t>LV_Line_Voltage_Supervision</t>
+          <t>LV_Line_Current_Supervision</t>
         </is>
       </c>
       <c r="B15" s="360" t="inlineStr">
         <is>
-          <t>Controllo della tensione di linea tramite sensori di tensione letti dal sistema di propulsione</t>
+          <t>Controllo della corrente di linea</t>
         </is>
       </c>
       <c r="C15" s="302" t="n"/>
@@ -4282,12 +4396,12 @@
     <row r="16" ht="30" customFormat="1" customHeight="1" s="8">
       <c r="A16" s="353" t="inlineStr">
         <is>
-          <t>LV_Line_Current_Supervision</t>
+          <t>LV_Line_Interference_Monitor</t>
         </is>
       </c>
       <c r="B16" s="360" t="inlineStr">
         <is>
-          <t>Controllo della corrente di linea</t>
+          <t>Controllo correnti/interferenze indesiderate di linea</t>
         </is>
       </c>
       <c r="C16" s="302" t="n"/>
@@ -4303,12 +4417,12 @@
     <row r="17" ht="30" customFormat="1" customHeight="1" s="8">
       <c r="A17" s="353" t="inlineStr">
         <is>
-          <t>LV_Line_Interference_Monitor</t>
+          <t>LV_LIM_50Hz_protection_bypass</t>
         </is>
       </c>
       <c r="B17" s="360" t="inlineStr">
         <is>
-          <t>Controllo correnti/interferenze indesiderate di linea</t>
+          <t>Bypass della protezione LIM 50 Hz</t>
         </is>
       </c>
       <c r="C17" s="302" t="n"/>
@@ -4324,16 +4438,18 @@
     <row r="18" ht="30" customFormat="1" customHeight="1" s="8">
       <c r="A18" s="353" t="inlineStr">
         <is>
-          <t>LV_LIM_50Hz_protection_bypass</t>
+          <t>LV_Neutral_Section_Passing</t>
         </is>
       </c>
       <c r="B18" s="360" t="inlineStr">
         <is>
-          <t>Bypass della protezione LIM 50 Hz</t>
-        </is>
-      </c>
-      <c r="C18" s="302" t="n"/>
-      <c r="D18" s="302" t="n"/>
+          <t>Gestione del passaggio in sezione neutra:
+- automatica da ATP in caso di tratto neutro al cambio fase
+- inizializzata da ATP con selezione manuale deò PdC della tensione di linea, in caso di tratto neutro al cambio tensione</t>
+        </is>
+      </c>
+      <c r="C18" s="304" t="n"/>
+      <c r="D18" s="304" t="n"/>
       <c r="E18" s="357" t="n"/>
       <c r="F18" s="357" t="n"/>
       <c r="G18" s="357" t="n"/>
@@ -4345,14 +4461,12 @@
     <row r="19" ht="30" customFormat="1" customHeight="1" s="8">
       <c r="A19" s="353" t="inlineStr">
         <is>
-          <t>LV_Neutral_Section_Passing</t>
+          <t>LV_System_Selection</t>
         </is>
       </c>
       <c r="B19" s="360" t="inlineStr">
         <is>
-          <t>Gestione del passaggio in sezione neutra:
-- automatica da ATP in caso di tratto neutro al cambio fase
-- inizializzata da ATP con selezione manuale deò PdC della tensione di linea, in caso di tratto neutro al cambio tensione</t>
+          <t>Selezione tramite commutatore a 4 posizioni della tensione di linea (25 kV AC, 15 kV AC, 3 kV DC o 1,5 kV DC)</t>
         </is>
       </c>
       <c r="C19" s="304" t="n"/>
@@ -4368,12 +4482,12 @@
     <row r="20" ht="30" customFormat="1" customHeight="1" s="8">
       <c r="A20" s="353" t="inlineStr">
         <is>
-          <t>LV_System_Selection</t>
+          <t>LV_Line_Circuit_Breaker_Closing</t>
         </is>
       </c>
       <c r="B20" s="360" t="inlineStr">
         <is>
-          <t>Selezione tramite commutatore a 4 posizioni della tensione di linea (25 kV AC, 15 kV AC, 3 kV DC o 1,5 kV DC)</t>
+          <t>Chiusura dell’interruttore di linea (LCB) per collegare la tensione di linea al treno</t>
         </is>
       </c>
       <c r="C20" s="304" t="n"/>
@@ -4389,12 +4503,12 @@
     <row r="21" ht="30" customFormat="1" customHeight="1" s="8">
       <c r="A21" s="353" t="inlineStr">
         <is>
-          <t>LV_Line_Circuit_Breaker_Closing</t>
+          <t>LV_Line_Circuit_Breaker_Opening</t>
         </is>
       </c>
       <c r="B21" s="360" t="inlineStr">
         <is>
-          <t>Chiusura dell’interruttore di linea (LCB) per collegare la tensione di linea al treno</t>
+          <t>Apertura LCB su comando o per intervento protezione</t>
         </is>
       </c>
       <c r="C21" s="304" t="n"/>
@@ -4410,12 +4524,12 @@
     <row r="22" ht="30" customFormat="1" customHeight="1" s="8">
       <c r="A22" s="353" t="inlineStr">
         <is>
-          <t>LV_Line_Circuit_Breaker_Opening</t>
+          <t>LV_Isolate_High_Voltage</t>
         </is>
       </c>
       <c r="B22" s="360" t="inlineStr">
         <is>
-          <t>Apertura LCB su comando o per intervento protezione</t>
+          <t>Isolamento di sezioni HV guaste per mantenere disponibile parte della trazione</t>
         </is>
       </c>
       <c r="C22" s="304" t="n"/>
@@ -4431,12 +4545,12 @@
     <row r="23" ht="30" customFormat="1" customHeight="1" s="8">
       <c r="A23" s="353" t="inlineStr">
         <is>
-          <t>LV_Isolate_High_Voltage</t>
+          <t>LV_Main_Transformer_cooling_control</t>
         </is>
       </c>
       <c r="B23" s="360" t="inlineStr">
         <is>
-          <t>Isolamento di sezioni HV guaste per mantenere disponibile parte della trazione</t>
+          <t>Controllo da parte della PCU della velocità delle ventole del circuito di raffreddamento ad olio</t>
         </is>
       </c>
       <c r="C23" s="304" t="n"/>
@@ -4452,12 +4566,12 @@
     <row r="24" ht="30" customFormat="1" customHeight="1" s="8">
       <c r="A24" s="353" t="inlineStr">
         <is>
-          <t>LV_Main_Transformer_cooling_control</t>
+          <t>LV_Main_Transformer_Supervision</t>
         </is>
       </c>
       <c r="B24" s="360" t="inlineStr">
         <is>
-          <t>Controllo da parte della PCU della velocità delle ventole del circuito di raffreddamento ad olio</t>
+          <t>Controllo da parte della PCU della temperatura del trasformatore e degli induttori linea</t>
         </is>
       </c>
       <c r="C24" s="304" t="n"/>
@@ -4470,15 +4584,15 @@
       <c r="J24" s="357" t="n"/>
       <c r="K24" s="358" t="n"/>
     </row>
-    <row r="25" ht="30" customFormat="1" customHeight="1" s="8">
+    <row r="25">
       <c r="A25" s="353" t="inlineStr">
         <is>
-          <t>LV_Main_Transformer_Supervision</t>
+          <t>LV_Energy_Meter</t>
         </is>
       </c>
       <c r="B25" s="360" t="inlineStr">
         <is>
-          <t>Controllo da parte della PCU della temperatura del trasformatore e degli induttori linea</t>
+          <t>Sistema di lettura dell'evergia assorbita dal treno e invio a terra dei dati</t>
         </is>
       </c>
       <c r="C25" s="304" t="n"/>
@@ -4491,15 +4605,15 @@
       <c r="J25" s="357" t="n"/>
       <c r="K25" s="358" t="n"/>
     </row>
-    <row r="26" customFormat="1" s="8">
+    <row r="26">
       <c r="A26" s="353" t="inlineStr">
         <is>
-          <t>LV_Energy_Meter</t>
-        </is>
-      </c>
-      <c r="B26" s="360" t="inlineStr">
-        <is>
-          <t>Sistema di lettura dell'evergia assorbita dal treno e invio a terra dei dati</t>
+          <t>LV_Key_interlocking</t>
+        </is>
+      </c>
+      <c r="B26" s="364" t="inlineStr">
+        <is>
+          <t>Interblocco tramite giro chiavi del sistema alta tensione</t>
         </is>
       </c>
       <c r="C26" s="304" t="n"/>
@@ -4512,15 +4626,15 @@
       <c r="J26" s="357" t="n"/>
       <c r="K26" s="358" t="n"/>
     </row>
-    <row r="27" ht="30" customFormat="1" customHeight="1" s="8">
+    <row r="27">
       <c r="A27" s="353" t="inlineStr">
         <is>
-          <t>LV_Key_interlocking</t>
+          <t>LV_Function_Earthing_of_High_Voltage_Supply</t>
         </is>
       </c>
       <c r="B27" s="364" t="inlineStr">
         <is>
-          <t>Interblocco tramite giro chiavi del sistema alta tensione</t>
+          <t>Messa a terra dell'alta tensione per consentire la manutenzione in sicurezza</t>
         </is>
       </c>
       <c r="C27" s="304" t="n"/>
@@ -4533,15 +4647,15 @@
       <c r="J27" s="357" t="n"/>
       <c r="K27" s="358" t="n"/>
     </row>
-    <row r="28" ht="30" customFormat="1" customHeight="1" s="8">
+    <row r="28">
       <c r="A28" s="353" t="inlineStr">
         <is>
-          <t>LV_Function_Earthing_of_High_Voltage_Supply</t>
+          <t>LV_Function_Earthing_of_Converter_boxes</t>
         </is>
       </c>
       <c r="B28" s="364" t="inlineStr">
         <is>
-          <t>Messa a terra dell'alta tensione per consentire la manutenzione in sicurezza</t>
+          <t>Messa a terra dei box convertitori per consentire l’accesso e la manutenzione in sicurezza</t>
         </is>
       </c>
       <c r="C28" s="304" t="n"/>
@@ -4554,15 +4668,15 @@
       <c r="J28" s="357" t="n"/>
       <c r="K28" s="358" t="n"/>
     </row>
-    <row r="29" customFormat="1" s="8">
+    <row r="29">
       <c r="A29" s="353" t="inlineStr">
         <is>
-          <t>LV_Function_Earthing_of_Converter_boxes</t>
+          <t>LV_HVAC_pre-conditioning_on_DC_line</t>
         </is>
       </c>
       <c r="B29" s="364" t="inlineStr">
         <is>
-          <t>Messa a terra dei box convertitori per consentire l’accesso e la manutenzione in sicurezza</t>
+          <t>Funzione per alimentare gli HVAC senza superare i limiti di corrente</t>
         </is>
       </c>
       <c r="C29" s="304" t="n"/>
@@ -4578,14 +4692,10 @@
     <row r="30">
       <c r="A30" s="353" t="inlineStr">
         <is>
-          <t>LV_HVAC_pre-conditioning_on_DC_line</t>
-        </is>
-      </c>
-      <c r="B30" s="364" t="inlineStr">
-        <is>
-          <t>Funzione per alimentare gli HVAC senza superare i limiti di corrente</t>
-        </is>
-      </c>
+          <t>AUX_Function_General</t>
+        </is>
+      </c>
+      <c r="B30" s="360" t="n"/>
       <c r="C30" s="304" t="n"/>
       <c r="D30" s="304" t="n"/>
       <c r="E30" s="357" t="n"/>
@@ -4599,7 +4709,7 @@
     <row r="31">
       <c r="A31" s="353" t="inlineStr">
         <is>
-          <t>AUX_Function_General</t>
+          <t>AUX_Activation_and_Synchronisation_of_ACM</t>
         </is>
       </c>
       <c r="B31" s="360" t="n"/>
@@ -4616,7 +4726,7 @@
     <row r="32">
       <c r="A32" s="353" t="inlineStr">
         <is>
-          <t>AUX_Activation_and_Synchronisation_of_ACM</t>
+          <t>AUX_ACM_reset</t>
         </is>
       </c>
       <c r="B32" s="360" t="n"/>
@@ -4633,7 +4743,7 @@
     <row r="33">
       <c r="A33" s="353" t="inlineStr">
         <is>
-          <t>AUX_ACM_reset</t>
+          <t>AUX_AC_on_Board_Supply_System</t>
         </is>
       </c>
       <c r="B33" s="360" t="n"/>
@@ -4650,7 +4760,7 @@
     <row r="34">
       <c r="A34" s="353" t="inlineStr">
         <is>
-          <t>AUX_AC_on_Board_Supply_System</t>
+          <t>AUX_External_Power_Supply</t>
         </is>
       </c>
       <c r="B34" s="360" t="n"/>
@@ -4667,7 +4777,7 @@
     <row r="35">
       <c r="A35" s="353" t="inlineStr">
         <is>
-          <t>AUX_External_Power_Supply</t>
+          <t>AUX_Earthing_switch</t>
         </is>
       </c>
       <c r="B35" s="360" t="n"/>
@@ -4684,7 +4794,7 @@
     <row r="36">
       <c r="A36" s="353" t="inlineStr">
         <is>
-          <t>AUX_Earthing_switch</t>
+          <t>AUX_230V,_50Hz_Sockets</t>
         </is>
       </c>
       <c r="B36" s="360" t="n"/>
@@ -4701,7 +4811,7 @@
     <row r="37">
       <c r="A37" s="353" t="inlineStr">
         <is>
-          <t>AUX_230V,_50Hz_Sockets</t>
+          <t>AUX_Mini_Circuit_Breaker_Supervision</t>
         </is>
       </c>
       <c r="B37" s="360" t="n"/>
@@ -4716,26 +4826,26 @@
       <c r="K37" s="358" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="353" t="inlineStr">
-        <is>
-          <t>AUX_Mini_Circuit_Breaker_Supervision</t>
-        </is>
-      </c>
-      <c r="B38" s="360" t="n"/>
+      <c r="A38" s="181" t="inlineStr">
+        <is>
+          <t>BAT_Failure_cases_battery_system</t>
+        </is>
+      </c>
+      <c r="B38" s="367" t="n"/>
       <c r="C38" s="304" t="n"/>
       <c r="D38" s="304" t="n"/>
-      <c r="E38" s="357" t="n"/>
-      <c r="F38" s="357" t="n"/>
-      <c r="G38" s="357" t="n"/>
-      <c r="H38" s="357" t="n"/>
-      <c r="I38" s="357" t="n"/>
-      <c r="J38" s="357" t="n"/>
-      <c r="K38" s="358" t="n"/>
+      <c r="E38" s="163" t="n"/>
+      <c r="F38" s="163" t="n"/>
+      <c r="G38" s="163" t="n"/>
+      <c r="H38" s="163" t="n"/>
+      <c r="I38" s="163" t="n"/>
+      <c r="J38" s="163" t="n"/>
+      <c r="K38" s="164" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="181" t="inlineStr">
         <is>
-          <t>BAT_Failure_cases_battery_system</t>
+          <t>BAT_Function_Battery_Isolation</t>
         </is>
       </c>
       <c r="B39" s="367" t="n"/>
@@ -4752,7 +4862,7 @@
     <row r="40">
       <c r="A40" s="181" t="inlineStr">
         <is>
-          <t>BAT_Function_Battery_Isolation</t>
+          <t>BAT_Battery_Contactors</t>
         </is>
       </c>
       <c r="B40" s="367" t="n"/>
@@ -4769,7 +4879,7 @@
     <row r="41">
       <c r="A41" s="181" t="inlineStr">
         <is>
-          <t>BAT_Battery_Contactors</t>
+          <t>BAT_Load_Shed_Contactors</t>
         </is>
       </c>
       <c r="B41" s="367" t="n"/>
@@ -4786,7 +4896,7 @@
     <row r="42">
       <c r="A42" s="181" t="inlineStr">
         <is>
-          <t>BAT_Load_Shed_Contactors</t>
+          <t>BAT_DC_Busline_Distribution</t>
         </is>
       </c>
       <c r="B42" s="367" t="n"/>
@@ -4803,7 +4913,7 @@
     <row r="43">
       <c r="A43" s="181" t="inlineStr">
         <is>
-          <t>BAT_DC_Busline_Distribution</t>
+          <t>BAT_Battery_Charging</t>
         </is>
       </c>
       <c r="B43" s="367" t="n"/>
@@ -4820,7 +4930,7 @@
     <row r="44">
       <c r="A44" s="181" t="inlineStr">
         <is>
-          <t>BAT_Battery_Charging</t>
+          <t>AIR_Control_of_Main_Compressor</t>
         </is>
       </c>
       <c r="B44" s="367" t="n"/>
@@ -4837,7 +4947,7 @@
     <row r="45">
       <c r="A45" s="181" t="inlineStr">
         <is>
-          <t>AIR_Control_of_Main_Compressor</t>
+          <t>AIR_Monitoring_of_Main_Compressor</t>
         </is>
       </c>
       <c r="B45" s="367" t="n"/>
@@ -4854,7 +4964,7 @@
     <row r="46">
       <c r="A46" s="181" t="inlineStr">
         <is>
-          <t>AIR_Monitoring_of_Main_Compressor</t>
+          <t>AIR_Forcing_of_Main_compressor</t>
         </is>
       </c>
       <c r="B46" s="367" t="n"/>
@@ -4871,7 +4981,7 @@
     <row r="47">
       <c r="A47" s="181" t="inlineStr">
         <is>
-          <t>AIR_Forcing_of_Main_compressor</t>
+          <t>AIR_Air_Dryer</t>
         </is>
       </c>
       <c r="B47" s="367" t="n"/>
@@ -4888,7 +4998,7 @@
     <row r="48">
       <c r="A48" s="181" t="inlineStr">
         <is>
-          <t>AIR_Air_Dryer</t>
+          <t>AIR_External_Air_Supply</t>
         </is>
       </c>
       <c r="B48" s="367" t="n"/>
@@ -4905,7 +5015,7 @@
     <row r="49">
       <c r="A49" s="181" t="inlineStr">
         <is>
-          <t>AIR_External_Air_Supply</t>
+          <t>AIR_Control_of_Auxiliary_Compressor</t>
         </is>
       </c>
       <c r="B49" s="367" t="n"/>
@@ -4922,7 +5032,7 @@
     <row r="50">
       <c r="A50" s="181" t="inlineStr">
         <is>
-          <t>AIR_Control_of_Auxiliary_Compressor</t>
+          <t>AIR_Suspension_Supervision</t>
         </is>
       </c>
       <c r="B50" s="367" t="n"/>
@@ -4939,7 +5049,7 @@
     <row r="51">
       <c r="A51" s="181" t="inlineStr">
         <is>
-          <t>AIR_Suspension_Supervision</t>
+          <t>AIR_Provision_for_Tilt_system</t>
         </is>
       </c>
       <c r="B51" s="367" t="n"/>
@@ -4956,12 +5066,12 @@
     <row r="52">
       <c r="A52" s="181" t="inlineStr">
         <is>
-          <t>AIR_Provision_for_Tilt_system</t>
+          <t>BRK_Service_Brake_Direct_Electro-Pneumatic_Brake</t>
         </is>
       </c>
       <c r="B52" s="367" t="n"/>
-      <c r="C52" s="169" t="n"/>
-      <c r="D52" s="169" t="n"/>
+      <c r="C52" s="304" t="n"/>
+      <c r="D52" s="304" t="n"/>
       <c r="E52" s="163" t="n"/>
       <c r="F52" s="163" t="n"/>
       <c r="G52" s="163" t="n"/>
@@ -4973,10 +5083,12 @@
     <row r="53">
       <c r="A53" s="181" t="inlineStr">
         <is>
-          <t>BRK_Service_Brake_Direct_Electro-Pneumatic_Brake</t>
+          <t>BRK_Service_Brake_Indirect_Brake</t>
         </is>
       </c>
       <c r="B53" s="367" t="n"/>
+      <c r="C53" s="304" t="n"/>
+      <c r="D53" s="304" t="n"/>
       <c r="E53" s="163" t="n"/>
       <c r="F53" s="163" t="n"/>
       <c r="G53" s="163" t="n"/>
@@ -4988,10 +5100,12 @@
     <row r="54">
       <c r="A54" s="181" t="inlineStr">
         <is>
-          <t>BRK_Service_Brake_Indirect_Brake</t>
+          <t>BRK_Holding_Brake</t>
         </is>
       </c>
       <c r="B54" s="367" t="n"/>
+      <c r="C54" s="304" t="n"/>
+      <c r="D54" s="304" t="n"/>
       <c r="E54" s="163" t="n"/>
       <c r="F54" s="163" t="n"/>
       <c r="G54" s="163" t="n"/>
@@ -5003,10 +5117,12 @@
     <row r="55">
       <c r="A55" s="181" t="inlineStr">
         <is>
-          <t>BRK_Holding_Brake</t>
+          <t>BRK_Urgency_Brake_(Optional)</t>
         </is>
       </c>
       <c r="B55" s="367" t="n"/>
+      <c r="C55" s="304" t="n"/>
+      <c r="D55" s="304" t="n"/>
       <c r="E55" s="163" t="n"/>
       <c r="F55" s="163" t="n"/>
       <c r="G55" s="163" t="n"/>
@@ -5018,10 +5134,12 @@
     <row r="56">
       <c r="A56" s="181" t="inlineStr">
         <is>
-          <t>BRK_Urgency_Brake_(Optional)</t>
+          <t>BRK_Emergency_Brake</t>
         </is>
       </c>
       <c r="B56" s="367" t="n"/>
+      <c r="C56" s="304" t="n"/>
+      <c r="D56" s="304" t="n"/>
       <c r="E56" s="163" t="n"/>
       <c r="F56" s="163" t="n"/>
       <c r="G56" s="163" t="n"/>
@@ -5033,10 +5151,12 @@
     <row r="57">
       <c r="A57" s="181" t="inlineStr">
         <is>
-          <t>BRK_Emergency_Brake</t>
+          <t>BRK_Parking_Brake</t>
         </is>
       </c>
       <c r="B57" s="367" t="n"/>
+      <c r="C57" s="304" t="n"/>
+      <c r="D57" s="304" t="n"/>
       <c r="E57" s="163" t="n"/>
       <c r="F57" s="163" t="n"/>
       <c r="G57" s="163" t="n"/>
@@ -5048,10 +5168,12 @@
     <row r="58">
       <c r="A58" s="181" t="inlineStr">
         <is>
-          <t>BRK_Parking_Brake</t>
+          <t>BRK_Wheel_Slide_Protection</t>
         </is>
       </c>
       <c r="B58" s="367" t="n"/>
+      <c r="C58" s="304" t="n"/>
+      <c r="D58" s="304" t="n"/>
       <c r="E58" s="163" t="n"/>
       <c r="F58" s="163" t="n"/>
       <c r="G58" s="163" t="n"/>
@@ -5063,10 +5185,12 @@
     <row r="59">
       <c r="A59" s="181" t="inlineStr">
         <is>
-          <t>BRK_Wheel_Slide_Protection</t>
+          <t>BRK_Detection_of_Non-Rotating_Axle_(DNRA)</t>
         </is>
       </c>
       <c r="B59" s="367" t="n"/>
+      <c r="C59" s="304" t="n"/>
+      <c r="D59" s="304" t="n"/>
       <c r="E59" s="163" t="n"/>
       <c r="F59" s="163" t="n"/>
       <c r="G59" s="163" t="n"/>
@@ -5078,10 +5202,12 @@
     <row r="60">
       <c r="A60" s="181" t="inlineStr">
         <is>
-          <t>BRK_Detection_of_Non-Rotating_Axle_(DNRA)</t>
+          <t>BRK_Passenger_Emergency_Brake</t>
         </is>
       </c>
       <c r="B60" s="367" t="n"/>
+      <c r="C60" s="304" t="n"/>
+      <c r="D60" s="304" t="n"/>
       <c r="E60" s="163" t="n"/>
       <c r="F60" s="163" t="n"/>
       <c r="G60" s="163" t="n"/>
@@ -5093,10 +5219,12 @@
     <row r="61">
       <c r="A61" s="181" t="inlineStr">
         <is>
-          <t>BRK_Passenger_Emergency_Brake</t>
+          <t>BRK_Sanding</t>
         </is>
       </c>
       <c r="B61" s="367" t="n"/>
+      <c r="C61" s="304" t="n"/>
+      <c r="D61" s="304" t="n"/>
       <c r="E61" s="163" t="n"/>
       <c r="F61" s="163" t="n"/>
       <c r="G61" s="163" t="n"/>
@@ -5108,10 +5236,12 @@
     <row r="62">
       <c r="A62" s="181" t="inlineStr">
         <is>
-          <t>BRK_Sanding</t>
+          <t>BRK_Brake_Test</t>
         </is>
       </c>
       <c r="B62" s="367" t="n"/>
+      <c r="C62" s="304" t="n"/>
+      <c r="D62" s="304" t="n"/>
       <c r="E62" s="163" t="n"/>
       <c r="F62" s="163" t="n"/>
       <c r="G62" s="163" t="n"/>
@@ -5123,10 +5253,12 @@
     <row r="63">
       <c r="A63" s="181" t="inlineStr">
         <is>
-          <t>BRK_Brake_Test</t>
+          <t>BRK_Towing</t>
         </is>
       </c>
       <c r="B63" s="367" t="n"/>
+      <c r="C63" s="304" t="n"/>
+      <c r="D63" s="304" t="n"/>
       <c r="E63" s="163" t="n"/>
       <c r="F63" s="163" t="n"/>
       <c r="G63" s="163" t="n"/>
@@ -5138,10 +5270,12 @@
     <row r="64">
       <c r="A64" s="181" t="inlineStr">
         <is>
-          <t>BRK_Towing</t>
+          <t>BRK_Fire_Safety_&amp;_Running_Capability</t>
         </is>
       </c>
       <c r="B64" s="367" t="n"/>
+      <c r="C64" s="304" t="n"/>
+      <c r="D64" s="304" t="n"/>
       <c r="E64" s="163" t="n"/>
       <c r="F64" s="163" t="n"/>
       <c r="G64" s="163" t="n"/>
@@ -5153,10 +5287,12 @@
     <row r="65">
       <c r="A65" s="181" t="inlineStr">
         <is>
-          <t>BRK_Fire_Safety_&amp;_Running_Capability</t>
+          <t>BRK_Magnetic_Track_Brake_Optional</t>
         </is>
       </c>
       <c r="B65" s="367" t="n"/>
+      <c r="C65" s="304" t="n"/>
+      <c r="D65" s="304" t="n"/>
       <c r="E65" s="163" t="n"/>
       <c r="F65" s="163" t="n"/>
       <c r="G65" s="163" t="n"/>
@@ -5168,10 +5304,12 @@
     <row r="66">
       <c r="A66" s="181" t="inlineStr">
         <is>
-          <t>BRK_Magnetic_Track_Brake_Optional</t>
+          <t>BOG_Flange_Lubrication</t>
         </is>
       </c>
       <c r="B66" s="367" t="n"/>
+      <c r="C66" s="304" t="n"/>
+      <c r="D66" s="304" t="n"/>
       <c r="E66" s="163" t="n"/>
       <c r="F66" s="163" t="n"/>
       <c r="G66" s="163" t="n"/>
@@ -5183,10 +5321,12 @@
     <row r="67">
       <c r="A67" s="181" t="inlineStr">
         <is>
-          <t>BOG_Flange_Lubrication</t>
+          <t>BOG_Hotbox_Detection</t>
         </is>
       </c>
       <c r="B67" s="367" t="n"/>
+      <c r="C67" s="304" t="n"/>
+      <c r="D67" s="304" t="n"/>
       <c r="E67" s="163" t="n"/>
       <c r="F67" s="163" t="n"/>
       <c r="G67" s="163" t="n"/>
@@ -5198,10 +5338,12 @@
     <row r="68">
       <c r="A68" s="181" t="inlineStr">
         <is>
-          <t>BOG_Hotbox_Detection</t>
+          <t>BOG_Instability_Monitoring</t>
         </is>
       </c>
       <c r="B68" s="367" t="n"/>
+      <c r="C68" s="304" t="n"/>
+      <c r="D68" s="304" t="n"/>
       <c r="E68" s="163" t="n"/>
       <c r="F68" s="163" t="n"/>
       <c r="G68" s="163" t="n"/>
@@ -5213,10 +5355,12 @@
     <row r="69">
       <c r="A69" s="181" t="inlineStr">
         <is>
-          <t>BOG_Instability_Monitoring</t>
+          <t>BOG_Active_Lateral_Suspension_(ALS)</t>
         </is>
       </c>
       <c r="B69" s="367" t="n"/>
+      <c r="C69" s="304" t="n"/>
+      <c r="D69" s="304" t="n"/>
       <c r="E69" s="163" t="n"/>
       <c r="F69" s="163" t="n"/>
       <c r="G69" s="163" t="n"/>
@@ -5228,10 +5372,12 @@
     <row r="70">
       <c r="A70" s="181" t="inlineStr">
         <is>
-          <t>BOG_Active_Lateral_Suspension_(ALS)</t>
+          <t>BOG_Diagnostics_&amp;_CBM</t>
         </is>
       </c>
       <c r="B70" s="367" t="n"/>
+      <c r="C70" s="304" t="n"/>
+      <c r="D70" s="304" t="n"/>
       <c r="E70" s="163" t="n"/>
       <c r="F70" s="163" t="n"/>
       <c r="G70" s="163" t="n"/>
@@ -5241,165 +5387,46 @@
       <c r="K70" s="164" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="181" t="inlineStr">
-        <is>
-          <t>BOG_Diagnostics_&amp;_CBM</t>
-        </is>
-      </c>
-      <c r="B71" s="367" t="n"/>
-      <c r="E71" s="163" t="n"/>
-      <c r="F71" s="163" t="n"/>
-      <c r="G71" s="163" t="n"/>
-      <c r="H71" s="163" t="n"/>
-      <c r="I71" s="163" t="n"/>
-      <c r="J71" s="163" t="n"/>
-      <c r="K71" s="164" t="n"/>
+      <c r="B71" s="169" t="n"/>
+      <c r="E71" s="242" t="n"/>
+      <c r="F71" s="242" t="n"/>
+      <c r="G71" s="237" t="n"/>
+      <c r="H71" s="237" t="n"/>
+      <c r="I71" s="242" t="n"/>
+      <c r="J71" s="237" t="n"/>
+      <c r="K71" s="238" t="n"/>
     </row>
     <row r="72">
-      <c r="B72" s="169" t="n"/>
-      <c r="E72" s="242" t="n"/>
-      <c r="F72" s="242" t="n"/>
-      <c r="G72" s="237" t="n"/>
-      <c r="H72" s="237" t="n"/>
-      <c r="I72" s="242" t="n"/>
-      <c r="J72" s="237" t="n"/>
-      <c r="K72" s="238" t="n"/>
+      <c r="C72" s="420" t="n"/>
+      <c r="D72" s="421" t="n"/>
+      <c r="E72" s="422" t="n"/>
+      <c r="G72" s="423" t="n"/>
+      <c r="H72" s="424" t="n"/>
+      <c r="I72" s="425" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>LV_Country_code_selection</t>
-        </is>
-      </c>
-      <c r="C73" s="420" t="inlineStr">
-        <is>
-          <t>2F_04.01.Zefiro-Europe.TRS.772</t>
-        </is>
-      </c>
-      <c r="D73" s="421" t="inlineStr">
-        <is>
-          <t>VZI_Base, VZ_FR, VZ_ES, VZI-6_R1</t>
-        </is>
-      </c>
-      <c r="E73" s="422" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G73" s="423" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H73" s="424" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I73" s="425" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="C73" s="420" t="n"/>
+      <c r="D73" s="421" t="n"/>
+      <c r="E73" s="422" t="n"/>
+      <c r="G73" s="423" t="n"/>
+      <c r="H73" s="424" t="n"/>
+      <c r="I73" s="425" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>LV_Country_code_selection</t>
-        </is>
-      </c>
-      <c r="C74" s="420" t="inlineStr">
-        <is>
-          <t>2F_04.01.Zefiro-</t>
-        </is>
-      </c>
-      <c r="D74" s="421" t="inlineStr">
-        <is>
-          <t>VZI_Base, VZ_FR, VZ_ES, VZI-6_R1</t>
-        </is>
-      </c>
-      <c r="E74" s="422" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G74" s="423" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H74" s="424" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I74" s="425" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="C74" s="420" t="n"/>
+      <c r="D74" s="421" t="n"/>
+      <c r="E74" s="422" t="n"/>
+      <c r="G74" s="423" t="n"/>
+      <c r="H74" s="424" t="n"/>
+      <c r="I74" s="425" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>LV_Country_code_selection</t>
-        </is>
-      </c>
-      <c r="C75" s="420" t="inlineStr">
-        <is>
-          <t>4S_09.03.05.-.TCMS</t>
-        </is>
-      </c>
-      <c r="D75" s="421" t="inlineStr">
-        <is>
-          <t>VZI_Base, VZ_FR, VZ_ES, VZI-6_R1</t>
-        </is>
-      </c>
-      <c r="E75" s="422" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G75" s="423" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H75" s="424" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I75" s="425" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>LV_Country_code_selection</t>
-        </is>
-      </c>
-      <c r="C76" s="426" t="inlineStr">
-        <is>
-          <t>4S_04.-.Power</t>
-        </is>
-      </c>
-      <c r="D76" s="421" t="inlineStr">
-        <is>
-          <t>VZI-6_R1</t>
-        </is>
-      </c>
-      <c r="I76" s="425" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="C75" s="426" t="n"/>
+      <c r="D75" s="421" t="n"/>
+      <c r="I75" s="425" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K62"/>
+  <autoFilter ref="A1:K57"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5419,68 +5446,68 @@
     <col width="24.28515625" customWidth="1" style="10" min="3" max="3"/>
     <col width="18.7109375" bestFit="1" customWidth="1" style="10" min="4" max="4"/>
     <col width="16.5703125" customWidth="1" style="10" min="5" max="10"/>
-    <col width="8.7109375" customWidth="1" style="59" min="11" max="19"/>
-    <col width="8.7109375" customWidth="1" style="59" min="20" max="16384"/>
+    <col width="8.7109375" customWidth="1" style="59" min="11" max="20"/>
+    <col width="8.7109375" customWidth="1" style="59" min="21" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="31.5" customFormat="1" customHeight="1" s="61">
-      <c r="A1" s="459" t="inlineStr">
+      <c r="A1" s="458" t="inlineStr">
         <is>
           <t>Impianto</t>
         </is>
       </c>
-      <c r="B1" s="457" t="inlineStr">
+      <c r="B1" s="456" t="inlineStr">
         <is>
           <t>Gruppo/Componente</t>
         </is>
       </c>
-      <c r="C1" s="456" t="inlineStr">
+      <c r="C1" s="455" t="inlineStr">
         <is>
           <t>P/N</t>
         </is>
       </c>
-      <c r="D1" s="453" t="inlineStr">
+      <c r="D1" s="452" t="inlineStr">
         <is>
           <t>Applicabilità flotte</t>
         </is>
       </c>
-      <c r="E1" s="454" t="n"/>
-      <c r="F1" s="454" t="n"/>
-      <c r="G1" s="454" t="n"/>
-      <c r="H1" s="454" t="n"/>
-      <c r="I1" s="454" t="n"/>
-      <c r="J1" s="455" t="n"/>
+      <c r="E1" s="453" t="n"/>
+      <c r="F1" s="453" t="n"/>
+      <c r="G1" s="453" t="n"/>
+      <c r="H1" s="453" t="n"/>
+      <c r="I1" s="453" t="n"/>
+      <c r="J1" s="454" t="n"/>
     </row>
     <row r="2" ht="31.5" customFormat="1" customHeight="1" s="61">
-      <c r="A2" s="445" t="n"/>
-      <c r="B2" s="458" t="n"/>
-      <c r="C2" s="437" t="n"/>
+      <c r="A2" s="444" t="n"/>
+      <c r="B2" s="457" t="n"/>
+      <c r="C2" s="436" t="n"/>
       <c r="D2" s="330" t="inlineStr">
         <is>
           <t>VZI_Base</t>
         </is>
       </c>
-      <c r="E2" s="440" t="inlineStr">
+      <c r="E2" s="439" t="inlineStr">
         <is>
           <t>VZI_New14</t>
         </is>
       </c>
-      <c r="F2" s="440" t="inlineStr">
+      <c r="F2" s="439" t="inlineStr">
         <is>
           <t>VZ_FR</t>
         </is>
       </c>
-      <c r="G2" s="440" t="inlineStr">
+      <c r="G2" s="439" t="inlineStr">
         <is>
           <t>VZ_ES</t>
         </is>
       </c>
-      <c r="H2" s="440" t="inlineStr">
+      <c r="H2" s="439" t="inlineStr">
         <is>
           <t>VZI-6_R1</t>
         </is>
       </c>
-      <c r="I2" s="440" t="inlineStr">
+      <c r="I2" s="439" t="inlineStr">
         <is>
           <t>VZI-4_R1</t>
         </is>
@@ -5535,7 +5562,7 @@
         </is>
       </c>
     </row>
-    <row r="4" outlineLevel="1" s="479">
+    <row r="4" outlineLevel="1" s="478">
       <c r="A4" s="113" t="n"/>
       <c r="B4" s="69" t="inlineStr">
         <is>
@@ -5579,7 +5606,7 @@
         </is>
       </c>
     </row>
-    <row r="5" outlineLevel="2" s="479">
+    <row r="5" outlineLevel="2" s="478">
       <c r="A5" s="63" t="n"/>
       <c r="B5" s="64" t="inlineStr">
         <is>
@@ -5611,7 +5638,7 @@
       </c>
       <c r="J5" s="64" t="n"/>
     </row>
-    <row r="6" outlineLevel="2" s="479">
+    <row r="6" outlineLevel="2" s="478">
       <c r="A6" s="63" t="n"/>
       <c r="B6" s="64" t="inlineStr">
         <is>
@@ -5643,7 +5670,7 @@
       </c>
       <c r="J6" s="64" t="n"/>
     </row>
-    <row r="7" outlineLevel="2" s="479">
+    <row r="7" outlineLevel="2" s="478">
       <c r="A7" s="63" t="n"/>
       <c r="B7" s="64" t="inlineStr">
         <is>
@@ -5654,7 +5681,7 @@
       <c r="D7" s="63" t="n"/>
       <c r="J7" s="64" t="n"/>
     </row>
-    <row r="8" outlineLevel="1" s="479">
+    <row r="8" outlineLevel="1" s="478">
       <c r="A8" s="113" t="n"/>
       <c r="B8" s="69" t="inlineStr">
         <is>
@@ -5698,7 +5725,7 @@
         </is>
       </c>
     </row>
-    <row r="9" outlineLevel="2" s="479">
+    <row r="9" outlineLevel="2" s="478">
       <c r="A9" s="63" t="n"/>
       <c r="B9" s="73" t="inlineStr">
         <is>
@@ -5741,7 +5768,7 @@
       <c r="I10" s="78" t="n"/>
       <c r="J10" s="73" t="n"/>
     </row>
-    <row r="11" outlineLevel="2" s="479">
+    <row r="11" outlineLevel="2" s="478">
       <c r="A11" s="63" t="n"/>
       <c r="B11" s="115" t="inlineStr">
         <is>
@@ -5808,7 +5835,7 @@
         </is>
       </c>
     </row>
-    <row r="13" outlineLevel="1" s="479">
+    <row r="13" outlineLevel="1" s="478">
       <c r="A13" s="113" t="n"/>
       <c r="B13" s="69" t="inlineStr">
         <is>
@@ -5852,7 +5879,7 @@
         </is>
       </c>
     </row>
-    <row r="14" outlineLevel="2" s="479">
+    <row r="14" outlineLevel="2" s="478">
       <c r="A14" s="63" t="n"/>
       <c r="B14" s="73" t="inlineStr">
         <is>
@@ -5876,7 +5903,7 @@
       </c>
       <c r="J14" s="64" t="n"/>
     </row>
-    <row r="15" outlineLevel="2" s="479">
+    <row r="15" outlineLevel="2" s="478">
       <c r="A15" s="63" t="n"/>
       <c r="B15" s="73" t="inlineStr">
         <is>
@@ -5900,7 +5927,7 @@
       </c>
       <c r="J15" s="64" t="n"/>
     </row>
-    <row r="16" outlineLevel="2" s="479">
+    <row r="16" outlineLevel="2" s="478">
       <c r="A16" s="63" t="n"/>
       <c r="B16" s="73" t="inlineStr">
         <is>
@@ -5924,7 +5951,7 @@
       </c>
       <c r="J16" s="64" t="n"/>
     </row>
-    <row r="17" outlineLevel="2" s="479">
+    <row r="17" outlineLevel="2" s="478">
       <c r="A17" s="63" t="n"/>
       <c r="B17" s="73" t="inlineStr">
         <is>
@@ -5943,7 +5970,7 @@
       </c>
       <c r="J17" s="64" t="n"/>
     </row>
-    <row r="18" outlineLevel="2" s="479">
+    <row r="18" outlineLevel="2" s="478">
       <c r="A18" s="63" t="n"/>
       <c r="B18" s="74" t="inlineStr">
         <is>
@@ -5963,7 +5990,7 @@
       </c>
       <c r="J18" s="64" t="n"/>
     </row>
-    <row r="19" outlineLevel="2" s="479">
+    <row r="19" outlineLevel="2" s="478">
       <c r="A19" s="63" t="n"/>
       <c r="B19" s="73" t="inlineStr">
         <is>
@@ -5982,7 +6009,7 @@
       </c>
       <c r="J19" s="64" t="n"/>
     </row>
-    <row r="20" outlineLevel="2" s="479">
+    <row r="20" outlineLevel="2" s="478">
       <c r="A20" s="63" t="n"/>
       <c r="B20" s="74" t="inlineStr">
         <is>
@@ -6002,7 +6029,7 @@
       </c>
       <c r="J20" s="64" t="n"/>
     </row>
-    <row r="21" outlineLevel="2" s="479">
+    <row r="21" outlineLevel="2" s="478">
       <c r="A21" s="63" t="n"/>
       <c r="B21" s="73" t="inlineStr">
         <is>
@@ -6026,7 +6053,7 @@
       </c>
       <c r="J21" s="64" t="n"/>
     </row>
-    <row r="22" outlineLevel="2" s="479">
+    <row r="22" outlineLevel="2" s="478">
       <c r="A22" s="63" t="n"/>
       <c r="B22" s="64" t="inlineStr">
         <is>
@@ -6050,7 +6077,7 @@
       </c>
       <c r="J22" s="64" t="n"/>
     </row>
-    <row r="23" outlineLevel="2" s="479">
+    <row r="23" outlineLevel="2" s="478">
       <c r="A23" s="63" t="n"/>
       <c r="B23" s="64" t="inlineStr">
         <is>
@@ -6074,7 +6101,7 @@
       </c>
       <c r="J23" s="64" t="n"/>
     </row>
-    <row r="24" outlineLevel="2" s="479">
+    <row r="24" outlineLevel="2" s="478">
       <c r="A24" s="63" t="n"/>
       <c r="B24" s="64" t="inlineStr">
         <is>
@@ -6098,7 +6125,7 @@
       </c>
       <c r="J24" s="64" t="n"/>
     </row>
-    <row r="25" outlineLevel="2" s="479">
+    <row r="25" outlineLevel="2" s="478">
       <c r="A25" s="63" t="n"/>
       <c r="B25" s="115" t="inlineStr">
         <is>
@@ -6123,7 +6150,7 @@
       </c>
       <c r="J25" s="64" t="n"/>
     </row>
-    <row r="26" outlineLevel="2" s="479">
+    <row r="26" outlineLevel="2" s="478">
       <c r="A26" s="63" t="n"/>
       <c r="B26" s="115" t="inlineStr">
         <is>
@@ -6148,7 +6175,7 @@
       </c>
       <c r="J26" s="64" t="n"/>
     </row>
-    <row r="27" outlineLevel="2" s="479">
+    <row r="27" outlineLevel="2" s="478">
       <c r="A27" s="63" t="n"/>
       <c r="B27" s="115" t="inlineStr">
         <is>
@@ -6173,7 +6200,7 @@
       </c>
       <c r="J27" s="64" t="n"/>
     </row>
-    <row r="28" outlineLevel="2" s="479">
+    <row r="28" outlineLevel="2" s="478">
       <c r="A28" s="63" t="n"/>
       <c r="B28" s="115" t="inlineStr">
         <is>
@@ -6198,7 +6225,7 @@
       </c>
       <c r="J28" s="64" t="n"/>
     </row>
-    <row r="29" outlineLevel="2" s="479">
+    <row r="29" outlineLevel="2" s="478">
       <c r="A29" s="63" t="n"/>
       <c r="B29" s="115" t="inlineStr">
         <is>
@@ -6223,7 +6250,7 @@
       </c>
       <c r="J29" s="64" t="n"/>
     </row>
-    <row r="30" outlineLevel="2" s="479">
+    <row r="30" outlineLevel="2" s="478">
       <c r="A30" s="63" t="n"/>
       <c r="B30" s="115" t="inlineStr">
         <is>
@@ -6248,7 +6275,7 @@
       </c>
       <c r="J30" s="64" t="n"/>
     </row>
-    <row r="31" outlineLevel="2" s="479">
+    <row r="31" outlineLevel="2" s="478">
       <c r="A31" s="63" t="n"/>
       <c r="B31" s="115" t="inlineStr">
         <is>
@@ -6273,7 +6300,7 @@
       </c>
       <c r="J31" s="64" t="n"/>
     </row>
-    <row r="32" outlineLevel="2" s="479">
+    <row r="32" outlineLevel="2" s="478">
       <c r="A32" s="63" t="n"/>
       <c r="B32" s="115" t="inlineStr">
         <is>
@@ -6298,7 +6325,7 @@
       </c>
       <c r="J32" s="64" t="n"/>
     </row>
-    <row r="33" outlineLevel="2" s="479">
+    <row r="33" outlineLevel="2" s="478">
       <c r="A33" s="63" t="n"/>
       <c r="B33" s="115" t="inlineStr">
         <is>
@@ -6323,7 +6350,7 @@
       </c>
       <c r="J33" s="64" t="n"/>
     </row>
-    <row r="34" outlineLevel="2" s="479">
+    <row r="34" outlineLevel="2" s="478">
       <c r="A34" s="63" t="n"/>
       <c r="B34" s="115" t="inlineStr">
         <is>
@@ -6348,7 +6375,7 @@
       </c>
       <c r="J34" s="64" t="n"/>
     </row>
-    <row r="35" outlineLevel="2" ht="30" customHeight="1" s="479">
+    <row r="35" outlineLevel="2" ht="30" customHeight="1" s="478">
       <c r="A35" s="63" t="n"/>
       <c r="B35" s="115" t="inlineStr">
         <is>
@@ -6373,7 +6400,7 @@
       </c>
       <c r="J35" s="64" t="n"/>
     </row>
-    <row r="36" outlineLevel="2" s="479">
+    <row r="36" outlineLevel="2" s="478">
       <c r="A36" s="63" t="n"/>
       <c r="B36" s="115" t="inlineStr">
         <is>
@@ -6398,7 +6425,7 @@
       </c>
       <c r="J36" s="64" t="n"/>
     </row>
-    <row r="37" outlineLevel="1" s="479">
+    <row r="37" outlineLevel="1" s="478">
       <c r="A37" s="113" t="n"/>
       <c r="B37" s="69" t="inlineStr">
         <is>
@@ -6442,7 +6469,7 @@
         </is>
       </c>
     </row>
-    <row r="38" outlineLevel="2" s="479">
+    <row r="38" outlineLevel="2" s="478">
       <c r="A38" s="63" t="n"/>
       <c r="B38" s="73" t="inlineStr">
         <is>
@@ -6461,7 +6488,7 @@
       </c>
       <c r="J38" s="64" t="n"/>
     </row>
-    <row r="39" outlineLevel="2" s="479">
+    <row r="39" outlineLevel="2" s="478">
       <c r="A39" s="63" t="n"/>
       <c r="B39" s="74" t="inlineStr">
         <is>
@@ -6481,7 +6508,7 @@
       </c>
       <c r="J39" s="64" t="n"/>
     </row>
-    <row r="40" outlineLevel="2" s="479">
+    <row r="40" outlineLevel="2" s="478">
       <c r="A40" s="63" t="n"/>
       <c r="B40" s="73" t="inlineStr">
         <is>
@@ -6505,7 +6532,7 @@
       </c>
       <c r="J40" s="64" t="n"/>
     </row>
-    <row r="41" outlineLevel="2" s="479">
+    <row r="41" outlineLevel="2" s="478">
       <c r="A41" s="63" t="n"/>
       <c r="B41" s="115" t="inlineStr">
         <is>
@@ -6530,7 +6557,7 @@
       </c>
       <c r="J41" s="64" t="n"/>
     </row>
-    <row r="42" outlineLevel="1" s="479">
+    <row r="42" outlineLevel="1" s="478">
       <c r="A42" s="113" t="n"/>
       <c r="B42" s="69" t="inlineStr">
         <is>
@@ -6574,7 +6601,7 @@
         </is>
       </c>
     </row>
-    <row r="43" outlineLevel="2" s="479">
+    <row r="43" outlineLevel="2" s="478">
       <c r="A43" s="63" t="n"/>
       <c r="B43" s="64" t="inlineStr">
         <is>
@@ -6593,7 +6620,7 @@
       </c>
       <c r="J43" s="64" t="n"/>
     </row>
-    <row r="44" outlineLevel="2" s="479">
+    <row r="44" outlineLevel="2" s="478">
       <c r="A44" s="63" t="n"/>
       <c r="B44" s="74" t="inlineStr">
         <is>
@@ -6613,7 +6640,7 @@
       </c>
       <c r="J44" s="64" t="n"/>
     </row>
-    <row r="45" outlineLevel="2" s="479">
+    <row r="45" outlineLevel="2" s="478">
       <c r="A45" s="63" t="n"/>
       <c r="B45" s="64" t="inlineStr">
         <is>
@@ -6637,7 +6664,7 @@
       </c>
       <c r="J45" s="64" t="n"/>
     </row>
-    <row r="46" outlineLevel="2" s="479">
+    <row r="46" outlineLevel="2" s="478">
       <c r="A46" s="63" t="n"/>
       <c r="B46" s="73" t="inlineStr">
         <is>
@@ -6656,7 +6683,7 @@
       </c>
       <c r="J46" s="64" t="n"/>
     </row>
-    <row r="47" outlineLevel="2" s="479">
+    <row r="47" outlineLevel="2" s="478">
       <c r="A47" s="63" t="n"/>
       <c r="B47" s="74" t="inlineStr">
         <is>
@@ -6676,7 +6703,7 @@
       </c>
       <c r="J47" s="64" t="n"/>
     </row>
-    <row r="48" outlineLevel="2" s="479">
+    <row r="48" outlineLevel="2" s="478">
       <c r="A48" s="63" t="n"/>
       <c r="B48" s="73" t="inlineStr">
         <is>
@@ -6695,7 +6722,7 @@
       </c>
       <c r="J48" s="64" t="n"/>
     </row>
-    <row r="49" outlineLevel="2" s="479">
+    <row r="49" outlineLevel="2" s="478">
       <c r="A49" s="63" t="n"/>
       <c r="B49" s="72" t="inlineStr">
         <is>
@@ -6715,7 +6742,7 @@
       </c>
       <c r="J49" s="64" t="n"/>
     </row>
-    <row r="50" outlineLevel="2" s="479">
+    <row r="50" outlineLevel="2" s="478">
       <c r="A50" s="63" t="n"/>
       <c r="B50" s="73" t="inlineStr">
         <is>
@@ -6734,7 +6761,7 @@
       </c>
       <c r="J50" s="64" t="n"/>
     </row>
-    <row r="51" outlineLevel="2" s="479">
+    <row r="51" outlineLevel="2" s="478">
       <c r="A51" s="63" t="n"/>
       <c r="B51" s="74" t="inlineStr">
         <is>
@@ -6754,7 +6781,7 @@
       </c>
       <c r="J51" s="64" t="n"/>
     </row>
-    <row r="52" outlineLevel="2" s="479">
+    <row r="52" outlineLevel="2" s="478">
       <c r="A52" s="63" t="n"/>
       <c r="B52" s="74" t="inlineStr">
         <is>
@@ -6774,7 +6801,7 @@
       </c>
       <c r="J52" s="64" t="n"/>
     </row>
-    <row r="53" outlineLevel="2" s="479">
+    <row r="53" outlineLevel="2" s="478">
       <c r="A53" s="63" t="n"/>
       <c r="B53" s="64" t="inlineStr">
         <is>
@@ -6798,7 +6825,7 @@
       </c>
       <c r="J53" s="64" t="n"/>
     </row>
-    <row r="54" outlineLevel="2" ht="30" customHeight="1" s="479">
+    <row r="54" outlineLevel="2" ht="30" customHeight="1" s="478">
       <c r="A54" s="63" t="n"/>
       <c r="B54" s="115" t="inlineStr">
         <is>
@@ -6823,7 +6850,7 @@
       </c>
       <c r="J54" s="64" t="n"/>
     </row>
-    <row r="55" outlineLevel="2" ht="30" customHeight="1" s="479">
+    <row r="55" outlineLevel="2" ht="30" customHeight="1" s="478">
       <c r="A55" s="63" t="n"/>
       <c r="B55" s="115" t="inlineStr">
         <is>
@@ -6892,7 +6919,7 @@
         </is>
       </c>
     </row>
-    <row r="57" outlineLevel="1" s="479">
+    <row r="57" outlineLevel="1" s="478">
       <c r="A57" s="68" t="n"/>
       <c r="B57" s="69" t="inlineStr">
         <is>
@@ -6936,7 +6963,7 @@
         </is>
       </c>
     </row>
-    <row r="58" outlineLevel="2" ht="30" customHeight="1" s="479">
+    <row r="58" outlineLevel="2" ht="30" customHeight="1" s="478">
       <c r="A58" s="63" t="n"/>
       <c r="B58" s="64" t="inlineStr">
         <is>
@@ -6960,7 +6987,7 @@
       </c>
       <c r="J58" s="64" t="n"/>
     </row>
-    <row r="59" outlineLevel="3" ht="30" customHeight="1" s="479">
+    <row r="59" outlineLevel="3" ht="30" customHeight="1" s="478">
       <c r="A59" s="63" t="n"/>
       <c r="B59" s="64" t="inlineStr">
         <is>
@@ -6984,7 +7011,7 @@
       </c>
       <c r="J59" s="64" t="n"/>
     </row>
-    <row r="60" outlineLevel="3" ht="30" customHeight="1" s="479">
+    <row r="60" outlineLevel="3" ht="30" customHeight="1" s="478">
       <c r="A60" s="63" t="n"/>
       <c r="B60" s="64" t="inlineStr">
         <is>
@@ -7008,7 +7035,7 @@
       </c>
       <c r="J60" s="64" t="n"/>
     </row>
-    <row r="61" outlineLevel="2" s="479">
+    <row r="61" outlineLevel="2" s="478">
       <c r="A61" s="63" t="n"/>
       <c r="B61" s="115" t="inlineStr">
         <is>
@@ -7036,7 +7063,7 @@
       </c>
       <c r="J61" s="64" t="n"/>
     </row>
-    <row r="62" outlineLevel="3" s="479">
+    <row r="62" outlineLevel="3" s="478">
       <c r="A62" s="63" t="n"/>
       <c r="B62" s="115" t="inlineStr">
         <is>
@@ -7064,7 +7091,7 @@
       </c>
       <c r="J62" s="64" t="n"/>
     </row>
-    <row r="63" outlineLevel="3" collapsed="1" s="479">
+    <row r="63" outlineLevel="3" collapsed="1" s="478">
       <c r="A63" s="63" t="n"/>
       <c r="B63" s="115" t="inlineStr">
         <is>
@@ -7092,7 +7119,7 @@
       </c>
       <c r="J63" s="64" t="n"/>
     </row>
-    <row r="64" outlineLevel="1" s="479">
+    <row r="64" outlineLevel="1" s="478">
       <c r="A64" s="68" t="n"/>
       <c r="B64" s="69" t="inlineStr">
         <is>
@@ -7136,7 +7163,7 @@
         </is>
       </c>
     </row>
-    <row r="65" outlineLevel="2" ht="30" customHeight="1" s="479">
+    <row r="65" outlineLevel="2" ht="30" customHeight="1" s="478">
       <c r="A65" s="63" t="n"/>
       <c r="B65" s="64" t="inlineStr">
         <is>
@@ -7160,7 +7187,7 @@
       </c>
       <c r="J65" s="64" t="n"/>
     </row>
-    <row r="66" outlineLevel="3" ht="30" customHeight="1" s="479">
+    <row r="66" outlineLevel="3" ht="30" customHeight="1" s="478">
       <c r="A66" s="63" t="n"/>
       <c r="B66" s="64" t="inlineStr">
         <is>
@@ -7184,7 +7211,7 @@
       </c>
       <c r="J66" s="64" t="n"/>
     </row>
-    <row r="67" outlineLevel="3" ht="30" customHeight="1" s="479">
+    <row r="67" outlineLevel="3" ht="30" customHeight="1" s="478">
       <c r="A67" s="63" t="n"/>
       <c r="B67" s="64" t="inlineStr">
         <is>
@@ -7208,7 +7235,7 @@
       </c>
       <c r="J67" s="64" t="n"/>
     </row>
-    <row r="68" outlineLevel="2" s="479">
+    <row r="68" outlineLevel="2" s="478">
       <c r="A68" s="63" t="n"/>
       <c r="B68" s="115" t="inlineStr">
         <is>
@@ -7236,7 +7263,7 @@
       </c>
       <c r="J68" s="64" t="n"/>
     </row>
-    <row r="69" outlineLevel="3" s="479">
+    <row r="69" outlineLevel="3" s="478">
       <c r="A69" s="63" t="n"/>
       <c r="B69" s="71" t="inlineStr">
         <is>
@@ -7264,7 +7291,7 @@
       </c>
       <c r="J69" s="64" t="n"/>
     </row>
-    <row r="70" outlineLevel="3" collapsed="1" s="479">
+    <row r="70" outlineLevel="3" collapsed="1" s="478">
       <c r="A70" s="63" t="n"/>
       <c r="B70" s="115" t="inlineStr">
         <is>
@@ -7292,7 +7319,7 @@
       </c>
       <c r="J70" s="64" t="n"/>
     </row>
-    <row r="71" outlineLevel="1" s="479">
+    <row r="71" outlineLevel="1" s="478">
       <c r="A71" s="68" t="n"/>
       <c r="B71" s="69" t="inlineStr">
         <is>
@@ -7336,7 +7363,7 @@
         </is>
       </c>
     </row>
-    <row r="72" outlineLevel="2" ht="30" customHeight="1" s="479">
+    <row r="72" outlineLevel="2" ht="30" customHeight="1" s="478">
       <c r="A72" s="63" t="n"/>
       <c r="B72" s="64" t="inlineStr">
         <is>
@@ -7360,7 +7387,7 @@
       </c>
       <c r="J72" s="64" t="n"/>
     </row>
-    <row r="73" outlineLevel="3" ht="30" customHeight="1" s="479">
+    <row r="73" outlineLevel="3" ht="30" customHeight="1" s="478">
       <c r="A73" s="63" t="n"/>
       <c r="B73" s="64" t="inlineStr">
         <is>
@@ -7384,7 +7411,7 @@
       </c>
       <c r="J73" s="64" t="n"/>
     </row>
-    <row r="74" outlineLevel="3" ht="30" customHeight="1" s="479">
+    <row r="74" outlineLevel="3" ht="30" customHeight="1" s="478">
       <c r="A74" s="63" t="n"/>
       <c r="B74" s="64" t="inlineStr">
         <is>
@@ -7408,7 +7435,7 @@
       </c>
       <c r="J74" s="64" t="n"/>
     </row>
-    <row r="75" outlineLevel="2" s="479">
+    <row r="75" outlineLevel="2" s="478">
       <c r="A75" s="63" t="n"/>
       <c r="B75" s="115" t="inlineStr">
         <is>
@@ -7436,7 +7463,7 @@
       </c>
       <c r="J75" s="64" t="n"/>
     </row>
-    <row r="76" outlineLevel="3" s="479">
+    <row r="76" outlineLevel="3" s="478">
       <c r="A76" s="63" t="n"/>
       <c r="B76" s="115" t="inlineStr">
         <is>
@@ -7464,7 +7491,7 @@
       </c>
       <c r="J76" s="64" t="n"/>
     </row>
-    <row r="77" outlineLevel="3" collapsed="1" s="479">
+    <row r="77" outlineLevel="3" collapsed="1" s="478">
       <c r="A77" s="63" t="n"/>
       <c r="B77" s="115" t="inlineStr">
         <is>
@@ -7492,7 +7519,7 @@
       </c>
       <c r="J77" s="64" t="n"/>
     </row>
-    <row r="78" outlineLevel="1" s="479">
+    <row r="78" outlineLevel="1" s="478">
       <c r="A78" s="68" t="n"/>
       <c r="B78" s="69" t="inlineStr">
         <is>
@@ -7536,7 +7563,7 @@
         </is>
       </c>
     </row>
-    <row r="79" outlineLevel="2" ht="30" customHeight="1" s="479">
+    <row r="79" outlineLevel="2" ht="30" customHeight="1" s="478">
       <c r="A79" s="63" t="n"/>
       <c r="B79" s="64" t="inlineStr">
         <is>
@@ -7570,7 +7597,7 @@
       </c>
       <c r="J79" s="64" t="n"/>
     </row>
-    <row r="80" outlineLevel="1" s="479">
+    <row r="80" outlineLevel="1" s="478">
       <c r="A80" s="68" t="n"/>
       <c r="B80" s="69" t="inlineStr">
         <is>
@@ -7614,7 +7641,7 @@
         </is>
       </c>
     </row>
-    <row r="81" outlineLevel="2" ht="30" customHeight="1" s="479">
+    <row r="81" outlineLevel="2" ht="30" customHeight="1" s="478">
       <c r="A81" s="63" t="n"/>
       <c r="B81" s="64" t="inlineStr">
         <is>
@@ -7638,7 +7665,7 @@
       </c>
       <c r="J81" s="64" t="n"/>
     </row>
-    <row r="82" outlineLevel="3" ht="30" customHeight="1" s="479">
+    <row r="82" outlineLevel="3" ht="30" customHeight="1" s="478">
       <c r="A82" s="63" t="n"/>
       <c r="B82" s="64" t="inlineStr">
         <is>
@@ -7662,7 +7689,7 @@
       </c>
       <c r="J82" s="64" t="n"/>
     </row>
-    <row r="83" outlineLevel="3" ht="30" customHeight="1" s="479">
+    <row r="83" outlineLevel="3" ht="30" customHeight="1" s="478">
       <c r="A83" s="63" t="n"/>
       <c r="B83" s="64" t="inlineStr">
         <is>
@@ -7686,7 +7713,7 @@
       </c>
       <c r="J83" s="64" t="n"/>
     </row>
-    <row r="84" outlineLevel="2" s="479">
+    <row r="84" outlineLevel="2" s="478">
       <c r="A84" s="63" t="n"/>
       <c r="B84" s="115" t="inlineStr">
         <is>
@@ -7714,7 +7741,7 @@
       </c>
       <c r="J84" s="64" t="n"/>
     </row>
-    <row r="85" outlineLevel="3" s="479">
+    <row r="85" outlineLevel="3" s="478">
       <c r="A85" s="63" t="n"/>
       <c r="B85" s="71" t="inlineStr">
         <is>
@@ -7742,7 +7769,7 @@
       </c>
       <c r="J85" s="64" t="n"/>
     </row>
-    <row r="86" outlineLevel="3" collapsed="1" s="479">
+    <row r="86" outlineLevel="3" collapsed="1" s="478">
       <c r="A86" s="63" t="n"/>
       <c r="B86" s="71" t="inlineStr">
         <is>
@@ -7828,7 +7855,7 @@
       <c r="D92" s="63" t="n"/>
       <c r="J92" s="64" t="n"/>
     </row>
-    <row r="93" ht="30" customHeight="1" s="479">
+    <row r="93" ht="30" customHeight="1" s="478">
       <c r="A93" s="63" t="n"/>
       <c r="B93" s="64" t="inlineStr">
         <is>
@@ -7888,7 +7915,7 @@
       <c r="D96" s="63" t="n"/>
       <c r="J96" s="64" t="n"/>
     </row>
-    <row r="97" ht="30" customHeight="1" s="479">
+    <row r="97" ht="30" customHeight="1" s="478">
       <c r="A97" s="63" t="n"/>
       <c r="B97" s="64" t="inlineStr">
         <is>
@@ -7959,89 +7986,89 @@
   <dimension ref="A1:Z50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17.85546875" customWidth="1" style="479" min="1" max="1"/>
-    <col width="14.42578125" customWidth="1" style="479" min="2" max="2"/>
-    <col width="18.42578125" customWidth="1" style="479" min="3" max="3"/>
-    <col width="15.85546875" customWidth="1" style="479" min="4" max="4"/>
-    <col width="19.42578125" customWidth="1" style="479" min="5" max="6"/>
-    <col width="14.42578125" customWidth="1" style="479" min="7" max="7"/>
-    <col width="16.42578125" customWidth="1" style="479" min="8" max="8"/>
-    <col width="23.85546875" customWidth="1" style="479" min="9" max="9"/>
-    <col width="21.85546875" customWidth="1" style="479" min="10" max="10"/>
-    <col width="11.42578125" customWidth="1" style="479" min="11" max="11"/>
-    <col width="15.5703125" customWidth="1" style="479" min="12" max="12"/>
-    <col width="19.85546875" customWidth="1" style="479" min="13" max="13"/>
-    <col width="21.5703125" customWidth="1" style="479" min="14" max="14"/>
-    <col width="12.140625" customWidth="1" style="479" min="15" max="15"/>
-    <col width="15.5703125" customWidth="1" style="479" min="16" max="16"/>
-    <col width="24.5703125" customWidth="1" style="479" min="17" max="17"/>
-    <col width="26.85546875" customWidth="1" style="479" min="18" max="18"/>
-    <col width="15.140625" customWidth="1" style="479" min="20" max="20"/>
-    <col width="25.140625" customWidth="1" style="479" min="21" max="21"/>
-    <col width="20.140625" customWidth="1" style="479" min="22" max="22"/>
-    <col width="10" bestFit="1" customWidth="1" style="479" min="23" max="23"/>
-    <col width="15.42578125" customWidth="1" style="479" min="24" max="24"/>
-    <col width="20.42578125" customWidth="1" style="479" min="25" max="25"/>
-    <col width="25.85546875" customWidth="1" style="479" min="26" max="26"/>
+    <col width="17.85546875" customWidth="1" style="478" min="1" max="1"/>
+    <col width="14.42578125" customWidth="1" style="478" min="2" max="2"/>
+    <col width="18.42578125" customWidth="1" style="478" min="3" max="3"/>
+    <col width="15.85546875" customWidth="1" style="478" min="4" max="4"/>
+    <col width="19.42578125" customWidth="1" style="478" min="5" max="6"/>
+    <col width="14.42578125" customWidth="1" style="478" min="7" max="7"/>
+    <col width="16.42578125" customWidth="1" style="478" min="8" max="8"/>
+    <col width="23.85546875" customWidth="1" style="478" min="9" max="9"/>
+    <col width="21.85546875" customWidth="1" style="478" min="10" max="10"/>
+    <col width="11.42578125" customWidth="1" style="478" min="11" max="11"/>
+    <col width="15.5703125" customWidth="1" style="478" min="12" max="12"/>
+    <col width="19.85546875" customWidth="1" style="478" min="13" max="13"/>
+    <col width="21.5703125" customWidth="1" style="478" min="14" max="14"/>
+    <col width="12.140625" customWidth="1" style="478" min="15" max="15"/>
+    <col width="15.5703125" customWidth="1" style="478" min="16" max="16"/>
+    <col width="24.5703125" customWidth="1" style="478" min="17" max="17"/>
+    <col width="26.85546875" customWidth="1" style="478" min="18" max="18"/>
+    <col width="15.140625" customWidth="1" style="478" min="20" max="20"/>
+    <col width="25.140625" customWidth="1" style="478" min="21" max="21"/>
+    <col width="20.140625" customWidth="1" style="478" min="22" max="22"/>
+    <col width="10" bestFit="1" customWidth="1" style="478" min="23" max="23"/>
+    <col width="15.42578125" customWidth="1" style="478" min="24" max="24"/>
+    <col width="20.42578125" customWidth="1" style="478" min="25" max="25"/>
+    <col width="25.85546875" customWidth="1" style="478" min="26" max="26"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" s="479" thickBot="1">
-      <c r="C1" s="492" t="inlineStr">
+    <row r="1" ht="15.75" customHeight="1" s="478" thickBot="1">
+      <c r="C1" s="491" t="inlineStr">
         <is>
           <t>IT 50 treni (flotta base)</t>
         </is>
       </c>
-      <c r="D1" s="462" t="n"/>
-      <c r="E1" s="462" t="n"/>
-      <c r="F1" s="493" t="n"/>
-      <c r="G1" s="492" t="inlineStr">
+      <c r="D1" s="461" t="n"/>
+      <c r="E1" s="461" t="n"/>
+      <c r="F1" s="492" t="n"/>
+      <c r="G1" s="491" t="inlineStr">
         <is>
           <t>IT 8 treni (51-58)</t>
         </is>
       </c>
-      <c r="H1" s="462" t="n"/>
-      <c r="I1" s="462" t="n"/>
-      <c r="J1" s="493" t="n"/>
-      <c r="K1" s="492" t="inlineStr">
+      <c r="H1" s="461" t="n"/>
+      <c r="I1" s="461" t="n"/>
+      <c r="J1" s="492" t="n"/>
+      <c r="K1" s="491" t="inlineStr">
         <is>
           <t>IT 6+30 treni (101-136)</t>
         </is>
       </c>
-      <c r="L1" s="462" t="n"/>
-      <c r="M1" s="462" t="n"/>
-      <c r="N1" s="493" t="n"/>
-      <c r="O1" s="492" t="inlineStr">
+      <c r="L1" s="461" t="n"/>
+      <c r="M1" s="461" t="n"/>
+      <c r="N1" s="492" t="n"/>
+      <c r="O1" s="491" t="inlineStr">
         <is>
           <t>I-FR 9 treni</t>
         </is>
       </c>
-      <c r="P1" s="462" t="n"/>
-      <c r="Q1" s="462" t="n"/>
-      <c r="R1" s="493" t="n"/>
-      <c r="S1" s="492" t="inlineStr">
+      <c r="P1" s="461" t="n"/>
+      <c r="Q1" s="461" t="n"/>
+      <c r="R1" s="492" t="n"/>
+      <c r="S1" s="491" t="inlineStr">
         <is>
           <t>DAI 9 treni</t>
         </is>
       </c>
-      <c r="T1" s="462" t="n"/>
-      <c r="U1" s="462" t="n"/>
-      <c r="V1" s="493" t="n"/>
-      <c r="W1" s="492" t="inlineStr">
+      <c r="T1" s="461" t="n"/>
+      <c r="U1" s="461" t="n"/>
+      <c r="V1" s="492" t="n"/>
+      <c r="W1" s="491" t="inlineStr">
         <is>
           <t>ES 20 treni</t>
         </is>
       </c>
-      <c r="X1" s="462" t="n"/>
-      <c r="Y1" s="462" t="n"/>
-      <c r="Z1" s="493" t="n"/>
-    </row>
-    <row r="2" ht="15.75" customHeight="1" s="479" thickBot="1">
-      <c r="A2" s="504" t="inlineStr">
+      <c r="X1" s="461" t="n"/>
+      <c r="Y1" s="461" t="n"/>
+      <c r="Z1" s="492" t="n"/>
+    </row>
+    <row r="2" ht="15.75" customHeight="1" s="478" thickBot="1">
+      <c r="A2" s="503" t="inlineStr">
         <is>
           <t>Sottosistema</t>
         </is>
       </c>
-      <c r="B2" s="463" t="n"/>
+      <c r="B2" s="462" t="n"/>
       <c r="C2" s="12" t="inlineStr">
         <is>
           <t>P/N</t>
@@ -8163,18 +8190,18 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="286.5" customHeight="1" s="479">
-      <c r="A3" s="489" t="inlineStr">
+    <row r="3" ht="286.5" customHeight="1" s="478">
+      <c r="A3" s="488" t="inlineStr">
         <is>
           <t>Carrelli</t>
         </is>
       </c>
-      <c r="B3" s="486" t="inlineStr">
+      <c r="B3" s="485" t="inlineStr">
         <is>
           <t>Motori</t>
         </is>
       </c>
-      <c r="C3" s="464" t="inlineStr">
+      <c r="C3" s="463" t="inlineStr">
         <is>
           <t>100360301
 100360302
@@ -8199,7 +8226,7 @@
 Sala senza boccole: 100360064</t>
         </is>
       </c>
-      <c r="G3" s="464" t="inlineStr">
+      <c r="G3" s="463" t="inlineStr">
         <is>
           <t>100360301
 100360302
@@ -8224,7 +8251,7 @@
 Sala senza boccole: 100360064</t>
         </is>
       </c>
-      <c r="K3" s="502" t="inlineStr">
+      <c r="K3" s="501" t="inlineStr">
         <is>
           <t>100360301
 100360302
@@ -8249,7 +8276,7 @@
           <t>Sensoristica ERTMS-SCMT carrelli DM</t>
         </is>
       </c>
-      <c r="O3" s="464" t="inlineStr">
+      <c r="O3" s="463" t="inlineStr">
         <is>
           <t>100329688
 100329689
@@ -8262,7 +8289,7 @@
           <t>Sala Montata</t>
         </is>
       </c>
-      <c r="Q3" s="437" t="n"/>
+      <c r="Q3" s="436" t="n"/>
       <c r="R3" s="20" t="inlineStr">
         <is>
           <t>Sensoristica ERTMS-SCMT, Memor brush, ETCS antenna su carrelli ant. DM1/8
@@ -8271,7 +8298,7 @@
 Sala senza boccole: 100360064</t>
         </is>
       </c>
-      <c r="S3" s="472" t="n"/>
+      <c r="S3" s="471" t="n"/>
       <c r="T3" s="387" t="inlineStr">
         <is>
           <t>Sala Montata</t>
@@ -8283,7 +8310,7 @@
           <t>tbd sensori boccola DM</t>
         </is>
       </c>
-      <c r="W3" s="464" t="inlineStr">
+      <c r="W3" s="463" t="inlineStr">
         <is>
           <t>DM: 100437987
 100470644</t>
@@ -8294,7 +8321,7 @@
           <t>Sala Montata</t>
         </is>
       </c>
-      <c r="Y3" s="437" t="n"/>
+      <c r="Y3" s="436" t="n"/>
       <c r="Z3" s="17" t="inlineStr">
         <is>
           <t>Sensoristica ETCS-ASFA-LZB carrelli DM</t>
@@ -8302,8 +8329,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="468" t="n"/>
-      <c r="C4" s="465" t="n"/>
+      <c r="A4" s="467" t="n"/>
+      <c r="C4" s="464" t="n"/>
       <c r="D4" s="389" t="inlineStr">
         <is>
           <t>Riduttore</t>
@@ -8313,7 +8340,7 @@
         <v>13900244911</v>
       </c>
       <c r="F4" s="22" t="n"/>
-      <c r="G4" s="465" t="n"/>
+      <c r="G4" s="464" t="n"/>
       <c r="H4" s="389" t="inlineStr">
         <is>
           <t>Riduttore</t>
@@ -8323,7 +8350,7 @@
         <v>13900244911</v>
       </c>
       <c r="J4" s="22" t="n"/>
-      <c r="K4" s="465" t="n"/>
+      <c r="K4" s="464" t="n"/>
       <c r="L4" s="391" t="inlineStr">
         <is>
           <t>Riduttore</t>
@@ -8333,7 +8360,7 @@
         <v>13900244911</v>
       </c>
       <c r="N4" s="23" t="n"/>
-      <c r="O4" s="465" t="n"/>
+      <c r="O4" s="464" t="n"/>
       <c r="P4" s="389" t="inlineStr">
         <is>
           <t>Riduttore</t>
@@ -8343,7 +8370,7 @@
         <v>13900244911</v>
       </c>
       <c r="R4" s="22" t="n"/>
-      <c r="S4" s="465" t="n"/>
+      <c r="S4" s="464" t="n"/>
       <c r="T4" s="394" t="inlineStr">
         <is>
           <t>Riduttore</t>
@@ -8353,7 +8380,7 @@
         <v>13900244911</v>
       </c>
       <c r="V4" s="24" t="n"/>
-      <c r="W4" s="465" t="n"/>
+      <c r="W4" s="464" t="n"/>
       <c r="X4" s="389" t="inlineStr">
         <is>
           <t>Riduttore</t>
@@ -8363,8 +8390,8 @@
       <c r="Z4" s="22" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="468" t="n"/>
-      <c r="C5" s="465" t="n"/>
+      <c r="A5" s="467" t="n"/>
+      <c r="C5" s="464" t="n"/>
       <c r="D5" s="389" t="inlineStr">
         <is>
           <t>Motore</t>
@@ -8376,7 +8403,7 @@
         </is>
       </c>
       <c r="F5" s="22" t="n"/>
-      <c r="G5" s="465" t="n"/>
+      <c r="G5" s="464" t="n"/>
       <c r="H5" s="389" t="inlineStr">
         <is>
           <t>Motore</t>
@@ -8388,7 +8415,7 @@
         </is>
       </c>
       <c r="J5" s="22" t="n"/>
-      <c r="K5" s="465" t="n"/>
+      <c r="K5" s="464" t="n"/>
       <c r="L5" s="391" t="inlineStr">
         <is>
           <t>Motore</t>
@@ -8400,7 +8427,7 @@
         </is>
       </c>
       <c r="N5" s="23" t="n"/>
-      <c r="O5" s="465" t="n"/>
+      <c r="O5" s="464" t="n"/>
       <c r="P5" s="389" t="inlineStr">
         <is>
           <t>Motore</t>
@@ -8412,7 +8439,7 @@
         </is>
       </c>
       <c r="R5" s="22" t="n"/>
-      <c r="S5" s="465" t="n"/>
+      <c r="S5" s="464" t="n"/>
       <c r="T5" s="394" t="inlineStr">
         <is>
           <t>Motore</t>
@@ -8424,7 +8451,7 @@
         </is>
       </c>
       <c r="V5" s="24" t="n"/>
-      <c r="W5" s="465" t="n"/>
+      <c r="W5" s="464" t="n"/>
       <c r="X5" s="389" t="inlineStr">
         <is>
           <t>Motore</t>
@@ -8433,9 +8460,9 @@
       <c r="Y5" s="165" t="n"/>
       <c r="Z5" s="22" t="n"/>
     </row>
-    <row r="6" ht="87" customHeight="1" s="479">
-      <c r="A6" s="468" t="n"/>
-      <c r="C6" s="465" t="n"/>
+    <row r="6" ht="87" customHeight="1" s="478">
+      <c r="A6" s="467" t="n"/>
+      <c r="C6" s="464" t="n"/>
       <c r="D6" s="389" t="inlineStr">
         <is>
           <t>Cil.Freno</t>
@@ -8449,7 +8476,7 @@
         </is>
       </c>
       <c r="F6" s="22" t="n"/>
-      <c r="G6" s="465" t="n"/>
+      <c r="G6" s="464" t="n"/>
       <c r="H6" s="389" t="inlineStr">
         <is>
           <t>Cil.Freno</t>
@@ -8463,7 +8490,7 @@
         </is>
       </c>
       <c r="J6" s="22" t="n"/>
-      <c r="K6" s="465" t="n"/>
+      <c r="K6" s="464" t="n"/>
       <c r="L6" s="391" t="inlineStr">
         <is>
           <t>Cil.Freno</t>
@@ -8477,7 +8504,7 @@
         </is>
       </c>
       <c r="N6" s="23" t="n"/>
-      <c r="O6" s="465" t="n"/>
+      <c r="O6" s="464" t="n"/>
       <c r="P6" s="389" t="inlineStr">
         <is>
           <t>Cil.Freno</t>
@@ -8491,7 +8518,7 @@
         </is>
       </c>
       <c r="R6" s="22" t="n"/>
-      <c r="S6" s="465" t="n"/>
+      <c r="S6" s="464" t="n"/>
       <c r="T6" s="394" t="inlineStr">
         <is>
           <t>Cil.Freno</t>
@@ -8505,7 +8532,7 @@
         </is>
       </c>
       <c r="V6" s="24" t="n"/>
-      <c r="W6" s="465" t="n"/>
+      <c r="W6" s="464" t="n"/>
       <c r="X6" s="389" t="inlineStr">
         <is>
           <t>Cil.Freno</t>
@@ -8521,8 +8548,8 @@
       <c r="Z6" s="22" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="468" t="n"/>
-      <c r="C7" s="465" t="n"/>
+      <c r="A7" s="467" t="n"/>
+      <c r="C7" s="464" t="n"/>
       <c r="D7" s="389" t="inlineStr">
         <is>
           <t>Als</t>
@@ -8534,7 +8561,7 @@
         </is>
       </c>
       <c r="F7" s="22" t="n"/>
-      <c r="G7" s="465" t="n"/>
+      <c r="G7" s="464" t="n"/>
       <c r="H7" s="389" t="inlineStr">
         <is>
           <t>Als</t>
@@ -8546,7 +8573,7 @@
         </is>
       </c>
       <c r="J7" s="22" t="n"/>
-      <c r="K7" s="465" t="n"/>
+      <c r="K7" s="464" t="n"/>
       <c r="L7" s="391" t="inlineStr">
         <is>
           <t>Als</t>
@@ -8558,7 +8585,7 @@
         </is>
       </c>
       <c r="N7" s="23" t="n"/>
-      <c r="O7" s="465" t="n"/>
+      <c r="O7" s="464" t="n"/>
       <c r="P7" s="389" t="inlineStr">
         <is>
           <t>Als</t>
@@ -8570,7 +8597,7 @@
         </is>
       </c>
       <c r="R7" s="22" t="n"/>
-      <c r="S7" s="465" t="n"/>
+      <c r="S7" s="464" t="n"/>
       <c r="T7" s="394" t="inlineStr">
         <is>
           <t>Als</t>
@@ -8582,7 +8609,7 @@
         </is>
       </c>
       <c r="V7" s="24" t="n"/>
-      <c r="W7" s="465" t="n"/>
+      <c r="W7" s="464" t="n"/>
       <c r="X7" s="389" t="inlineStr">
         <is>
           <t>Als</t>
@@ -8592,9 +8619,9 @@
       <c r="Z7" s="22" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="468" t="n"/>
-      <c r="B8" s="441" t="n"/>
-      <c r="C8" s="466" t="n"/>
+      <c r="A8" s="467" t="n"/>
+      <c r="B8" s="440" t="n"/>
+      <c r="C8" s="465" t="n"/>
       <c r="D8" s="389" t="inlineStr">
         <is>
           <t>BMS</t>
@@ -8606,7 +8633,7 @@
           <t>Ephimess fase 2</t>
         </is>
       </c>
-      <c r="G8" s="466" t="n"/>
+      <c r="G8" s="465" t="n"/>
       <c r="H8" s="389" t="inlineStr">
         <is>
           <t>BMS</t>
@@ -8618,7 +8645,7 @@
           <t>Ephimess fase 2</t>
         </is>
       </c>
-      <c r="K8" s="466" t="n"/>
+      <c r="K8" s="465" t="n"/>
       <c r="L8" s="391" t="inlineStr">
         <is>
           <t>BMS</t>
@@ -8626,7 +8653,7 @@
       </c>
       <c r="M8" s="396" t="n"/>
       <c r="N8" s="23" t="n"/>
-      <c r="O8" s="466" t="n"/>
+      <c r="O8" s="465" t="n"/>
       <c r="P8" s="389" t="inlineStr">
         <is>
           <t>BMS</t>
@@ -8634,7 +8661,7 @@
       </c>
       <c r="Q8" s="166" t="n"/>
       <c r="R8" s="22" t="n"/>
-      <c r="S8" s="466" t="n"/>
+      <c r="S8" s="465" t="n"/>
       <c r="T8" s="394" t="inlineStr">
         <is>
           <t>BMS</t>
@@ -8642,7 +8669,7 @@
       </c>
       <c r="U8" s="397" t="n"/>
       <c r="V8" s="24" t="n"/>
-      <c r="W8" s="466" t="n"/>
+      <c r="W8" s="465" t="n"/>
       <c r="X8" s="389" t="inlineStr">
         <is>
           <t>BMS</t>
@@ -8651,14 +8678,14 @@
       <c r="Y8" s="165" t="n"/>
       <c r="Z8" s="22" t="n"/>
     </row>
-    <row r="9" ht="30" customHeight="1" s="479">
-      <c r="A9" s="468" t="n"/>
-      <c r="B9" s="507" t="inlineStr">
+    <row r="9" ht="30" customHeight="1" s="478">
+      <c r="A9" s="467" t="n"/>
+      <c r="B9" s="506" t="inlineStr">
         <is>
           <t>Portanti</t>
         </is>
       </c>
-      <c r="C9" s="495" t="inlineStr">
+      <c r="C9" s="494" t="inlineStr">
         <is>
           <t>100360311
 100360312
@@ -8677,7 +8704,7 @@
         </is>
       </c>
       <c r="F9" s="22" t="n"/>
-      <c r="G9" s="495" t="inlineStr">
+      <c r="G9" s="494" t="inlineStr">
         <is>
           <t>100360311
 100360312
@@ -8696,7 +8723,7 @@
         </is>
       </c>
       <c r="J9" s="22" t="n"/>
-      <c r="K9" s="496" t="inlineStr">
+      <c r="K9" s="495" t="inlineStr">
         <is>
           <t>100360311
 100360312
@@ -8716,7 +8743,7 @@
         </is>
       </c>
       <c r="N9" s="23" t="n"/>
-      <c r="O9" s="495" t="inlineStr">
+      <c r="O9" s="494" t="inlineStr">
         <is>
           <t>100360311
 100329690
@@ -8735,7 +8762,7 @@
         </is>
       </c>
       <c r="R9" s="22" t="n"/>
-      <c r="S9" s="522" t="n"/>
+      <c r="S9" s="521" t="n"/>
       <c r="T9" s="394" t="inlineStr">
         <is>
           <t>Sala</t>
@@ -8743,7 +8770,7 @@
       </c>
       <c r="U9" s="397" t="n"/>
       <c r="V9" s="24" t="n"/>
-      <c r="W9" s="519" t="n"/>
+      <c r="W9" s="518" t="n"/>
       <c r="X9" s="389" t="inlineStr">
         <is>
           <t>Sala</t>
@@ -8753,8 +8780,8 @@
       <c r="Z9" s="22" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="468" t="n"/>
-      <c r="C10" s="465" t="n"/>
+      <c r="A10" s="467" t="n"/>
+      <c r="C10" s="464" t="n"/>
       <c r="D10" s="389" t="inlineStr">
         <is>
           <t>Freno</t>
@@ -8762,7 +8789,7 @@
       </c>
       <c r="E10" s="165" t="n"/>
       <c r="F10" s="22" t="n"/>
-      <c r="G10" s="465" t="n"/>
+      <c r="G10" s="464" t="n"/>
       <c r="H10" s="389" t="inlineStr">
         <is>
           <t>Freno</t>
@@ -8770,7 +8797,7 @@
       </c>
       <c r="I10" s="165" t="n"/>
       <c r="J10" s="22" t="n"/>
-      <c r="K10" s="465" t="n"/>
+      <c r="K10" s="464" t="n"/>
       <c r="L10" s="391" t="inlineStr">
         <is>
           <t>Freno</t>
@@ -8778,7 +8805,7 @@
       </c>
       <c r="M10" s="396" t="n"/>
       <c r="N10" s="23" t="n"/>
-      <c r="O10" s="465" t="n"/>
+      <c r="O10" s="464" t="n"/>
       <c r="P10" s="389" t="inlineStr">
         <is>
           <t>Freno</t>
@@ -8786,7 +8813,7 @@
       </c>
       <c r="Q10" s="165" t="n"/>
       <c r="R10" s="22" t="n"/>
-      <c r="S10" s="465" t="n"/>
+      <c r="S10" s="464" t="n"/>
       <c r="T10" s="394" t="inlineStr">
         <is>
           <t>Freno</t>
@@ -8794,7 +8821,7 @@
       </c>
       <c r="U10" s="397" t="n"/>
       <c r="V10" s="24" t="n"/>
-      <c r="W10" s="465" t="n"/>
+      <c r="W10" s="464" t="n"/>
       <c r="X10" s="389" t="inlineStr">
         <is>
           <t>Freno</t>
@@ -8804,8 +8831,8 @@
       <c r="Z10" s="22" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="468" t="n"/>
-      <c r="C11" s="465" t="n"/>
+      <c r="A11" s="467" t="n"/>
+      <c r="C11" s="464" t="n"/>
       <c r="D11" s="389" t="inlineStr">
         <is>
           <t>Als</t>
@@ -8813,7 +8840,7 @@
       </c>
       <c r="E11" s="165" t="n"/>
       <c r="F11" s="22" t="n"/>
-      <c r="G11" s="465" t="n"/>
+      <c r="G11" s="464" t="n"/>
       <c r="H11" s="389" t="inlineStr">
         <is>
           <t>Als</t>
@@ -8821,7 +8848,7 @@
       </c>
       <c r="I11" s="165" t="n"/>
       <c r="J11" s="22" t="n"/>
-      <c r="K11" s="465" t="n"/>
+      <c r="K11" s="464" t="n"/>
       <c r="L11" s="391" t="inlineStr">
         <is>
           <t>Als</t>
@@ -8829,7 +8856,7 @@
       </c>
       <c r="M11" s="396" t="n"/>
       <c r="N11" s="23" t="n"/>
-      <c r="O11" s="465" t="n"/>
+      <c r="O11" s="464" t="n"/>
       <c r="P11" s="389" t="inlineStr">
         <is>
           <t>Als</t>
@@ -8837,7 +8864,7 @@
       </c>
       <c r="Q11" s="165" t="n"/>
       <c r="R11" s="22" t="n"/>
-      <c r="S11" s="465" t="n"/>
+      <c r="S11" s="464" t="n"/>
       <c r="T11" s="394" t="inlineStr">
         <is>
           <t>Als</t>
@@ -8845,7 +8872,7 @@
       </c>
       <c r="U11" s="397" t="n"/>
       <c r="V11" s="24" t="n"/>
-      <c r="W11" s="465" t="n"/>
+      <c r="W11" s="464" t="n"/>
       <c r="X11" s="389" t="inlineStr">
         <is>
           <t>Als</t>
@@ -8854,10 +8881,10 @@
       <c r="Y11" s="165" t="n"/>
       <c r="Z11" s="22" t="n"/>
     </row>
-    <row r="12" ht="15.75" customHeight="1" s="479" thickBot="1">
-      <c r="A12" s="490" t="n"/>
-      <c r="B12" s="508" t="n"/>
-      <c r="C12" s="470" t="n"/>
+    <row r="12" ht="15.75" customHeight="1" s="478" thickBot="1">
+      <c r="A12" s="489" t="n"/>
+      <c r="B12" s="507" t="n"/>
+      <c r="C12" s="469" t="n"/>
       <c r="D12" s="25" t="inlineStr">
         <is>
           <t>BMS</t>
@@ -8865,7 +8892,7 @@
       </c>
       <c r="E12" s="26" t="n"/>
       <c r="F12" s="27" t="n"/>
-      <c r="G12" s="470" t="n"/>
+      <c r="G12" s="469" t="n"/>
       <c r="H12" s="25" t="inlineStr">
         <is>
           <t>BMS</t>
@@ -8873,7 +8900,7 @@
       </c>
       <c r="I12" s="26" t="n"/>
       <c r="J12" s="27" t="n"/>
-      <c r="K12" s="470" t="n"/>
+      <c r="K12" s="469" t="n"/>
       <c r="L12" s="28" t="inlineStr">
         <is>
           <t>BMS</t>
@@ -8881,7 +8908,7 @@
       </c>
       <c r="M12" s="29" t="n"/>
       <c r="N12" s="30" t="n"/>
-      <c r="O12" s="470" t="n"/>
+      <c r="O12" s="469" t="n"/>
       <c r="P12" s="25" t="inlineStr">
         <is>
           <t>BMS</t>
@@ -8889,7 +8916,7 @@
       </c>
       <c r="Q12" s="26" t="n"/>
       <c r="R12" s="27" t="n"/>
-      <c r="S12" s="470" t="n"/>
+      <c r="S12" s="469" t="n"/>
       <c r="T12" s="31" t="inlineStr">
         <is>
           <t>BMS</t>
@@ -8897,7 +8924,7 @@
       </c>
       <c r="U12" s="32" t="n"/>
       <c r="V12" s="33" t="n"/>
-      <c r="W12" s="470" t="n"/>
+      <c r="W12" s="469" t="n"/>
       <c r="X12" s="25" t="inlineStr">
         <is>
           <t>BMS</t>
@@ -8907,17 +8934,17 @@
       <c r="Z12" s="27" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="504" t="inlineStr">
+      <c r="A13" s="503" t="inlineStr">
         <is>
           <t>Pantografi</t>
         </is>
       </c>
-      <c r="B13" s="460" t="inlineStr">
+      <c r="B13" s="459" t="inlineStr">
         <is>
           <t>3 kV</t>
         </is>
       </c>
-      <c r="C13" s="520" t="n">
+      <c r="C13" s="519" t="n">
         <v>100170460</v>
       </c>
       <c r="D13" s="34" t="inlineStr">
@@ -8929,7 +8956,7 @@
         <v>10573076</v>
       </c>
       <c r="F13" s="36" t="n"/>
-      <c r="G13" s="506" t="n">
+      <c r="G13" s="505" t="n">
         <v>10949272</v>
       </c>
       <c r="H13" s="34" t="inlineStr">
@@ -8941,7 +8968,7 @@
         <v>10573076</v>
       </c>
       <c r="J13" s="36" t="n"/>
-      <c r="K13" s="506" t="n">
+      <c r="K13" s="505" t="n">
         <v>10949272</v>
       </c>
       <c r="L13" s="34" t="inlineStr">
@@ -8953,7 +8980,7 @@
         <v>10573076</v>
       </c>
       <c r="N13" s="36" t="n"/>
-      <c r="O13" s="520" t="n">
+      <c r="O13" s="519" t="n">
         <v>100170460</v>
       </c>
       <c r="P13" s="34" t="inlineStr">
@@ -8965,7 +8992,7 @@
         <v>10573076</v>
       </c>
       <c r="R13" s="36" t="n"/>
-      <c r="S13" s="511" t="n"/>
+      <c r="S13" s="510" t="n"/>
       <c r="T13" s="37" t="inlineStr">
         <is>
           <t>Struttura</t>
@@ -8973,7 +9000,7 @@
       </c>
       <c r="U13" s="37" t="n"/>
       <c r="V13" s="38" t="n"/>
-      <c r="W13" s="520" t="n"/>
+      <c r="W13" s="519" t="n"/>
       <c r="X13" s="34" t="inlineStr">
         <is>
           <t>Struttura</t>
@@ -8983,8 +9010,8 @@
       <c r="Z13" s="36" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="468" t="n"/>
-      <c r="C14" s="465" t="n"/>
+      <c r="A14" s="467" t="n"/>
+      <c r="C14" s="464" t="n"/>
       <c r="D14" s="165" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -8994,7 +9021,7 @@
         <v>10561136</v>
       </c>
       <c r="F14" s="22" t="n"/>
-      <c r="G14" s="465" t="n"/>
+      <c r="G14" s="464" t="n"/>
       <c r="H14" s="165" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -9004,7 +9031,7 @@
         <v>10561136</v>
       </c>
       <c r="J14" s="22" t="n"/>
-      <c r="K14" s="465" t="n"/>
+      <c r="K14" s="464" t="n"/>
       <c r="L14" s="165" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -9014,7 +9041,7 @@
         <v>10561136</v>
       </c>
       <c r="N14" s="22" t="n"/>
-      <c r="O14" s="465" t="n"/>
+      <c r="O14" s="464" t="n"/>
       <c r="P14" s="165" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -9024,7 +9051,7 @@
         <v>10561136</v>
       </c>
       <c r="R14" s="22" t="n"/>
-      <c r="S14" s="465" t="n"/>
+      <c r="S14" s="464" t="n"/>
       <c r="T14" s="397" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -9032,7 +9059,7 @@
       </c>
       <c r="U14" s="397" t="n"/>
       <c r="V14" s="24" t="n"/>
-      <c r="W14" s="465" t="n"/>
+      <c r="W14" s="464" t="n"/>
       <c r="X14" s="165" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -9046,8 +9073,8 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="468" t="n"/>
-      <c r="C15" s="465" t="n"/>
+      <c r="A15" s="467" t="n"/>
+      <c r="C15" s="464" t="n"/>
       <c r="D15" s="165" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -9059,7 +9086,7 @@
         </is>
       </c>
       <c r="F15" s="22" t="n"/>
-      <c r="G15" s="465" t="n"/>
+      <c r="G15" s="464" t="n"/>
       <c r="H15" s="165" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -9071,7 +9098,7 @@
         </is>
       </c>
       <c r="J15" s="22" t="n"/>
-      <c r="K15" s="465" t="n"/>
+      <c r="K15" s="464" t="n"/>
       <c r="L15" s="165" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -9083,7 +9110,7 @@
         </is>
       </c>
       <c r="N15" s="22" t="n"/>
-      <c r="O15" s="465" t="n"/>
+      <c r="O15" s="464" t="n"/>
       <c r="P15" s="165" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -9095,7 +9122,7 @@
         </is>
       </c>
       <c r="R15" s="22" t="n"/>
-      <c r="S15" s="465" t="n"/>
+      <c r="S15" s="464" t="n"/>
       <c r="T15" s="397" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -9103,7 +9130,7 @@
       </c>
       <c r="U15" s="397" t="n"/>
       <c r="V15" s="24" t="n"/>
-      <c r="W15" s="465" t="n"/>
+      <c r="W15" s="464" t="n"/>
       <c r="X15" s="165" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -9113,9 +9140,9 @@
       <c r="Z15" s="22" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="468" t="n"/>
-      <c r="B16" s="441" t="n"/>
-      <c r="C16" s="466" t="n"/>
+      <c r="A16" s="467" t="n"/>
+      <c r="B16" s="440" t="n"/>
+      <c r="C16" s="465" t="n"/>
       <c r="D16" s="165" t="inlineStr">
         <is>
           <t>PPU</t>
@@ -9125,7 +9152,7 @@
         <v>102895</v>
       </c>
       <c r="F16" s="22" t="n"/>
-      <c r="G16" s="466" t="n"/>
+      <c r="G16" s="465" t="n"/>
       <c r="H16" s="165" t="inlineStr">
         <is>
           <t>PPU</t>
@@ -9141,7 +9168,7 @@
           <t>Con isolamento ADD</t>
         </is>
       </c>
-      <c r="K16" s="466" t="n"/>
+      <c r="K16" s="465" t="n"/>
       <c r="L16" s="165" t="inlineStr">
         <is>
           <t>PPU</t>
@@ -9157,7 +9184,7 @@
           <t>Con isolamento ADD</t>
         </is>
       </c>
-      <c r="O16" s="466" t="n"/>
+      <c r="O16" s="465" t="n"/>
       <c r="P16" s="165" t="inlineStr">
         <is>
           <t>PPU</t>
@@ -9173,7 +9200,7 @@
           <t>PPU DC Modificata per agg.panto 1.5</t>
         </is>
       </c>
-      <c r="S16" s="466" t="n"/>
+      <c r="S16" s="465" t="n"/>
       <c r="T16" s="397" t="inlineStr">
         <is>
           <t>PCU</t>
@@ -9181,7 +9208,7 @@
       </c>
       <c r="U16" s="397" t="n"/>
       <c r="V16" s="24" t="n"/>
-      <c r="W16" s="466" t="n"/>
+      <c r="W16" s="465" t="n"/>
       <c r="X16" s="165" t="inlineStr">
         <is>
           <t>PPU</t>
@@ -9195,13 +9222,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="468" t="n"/>
-      <c r="B17" s="507" t="inlineStr">
+      <c r="A17" s="467" t="n"/>
+      <c r="B17" s="506" t="inlineStr">
         <is>
           <t>25 kV</t>
         </is>
       </c>
-      <c r="C17" s="471" t="n">
+      <c r="C17" s="470" t="n">
         <v>100170464</v>
       </c>
       <c r="D17" s="389" t="inlineStr">
@@ -9213,7 +9240,7 @@
         <v>10573076</v>
       </c>
       <c r="F17" s="22" t="n"/>
-      <c r="G17" s="491" t="n">
+      <c r="G17" s="490" t="n">
         <v>10949356</v>
       </c>
       <c r="H17" s="165" t="inlineStr">
@@ -9225,7 +9252,7 @@
         <v>10573076</v>
       </c>
       <c r="J17" s="22" t="n"/>
-      <c r="K17" s="491" t="n">
+      <c r="K17" s="490" t="n">
         <v>10949356</v>
       </c>
       <c r="L17" s="165" t="inlineStr">
@@ -9237,7 +9264,7 @@
         <v>10573076</v>
       </c>
       <c r="N17" s="22" t="n"/>
-      <c r="O17" s="471" t="n">
+      <c r="O17" s="470" t="n">
         <v>100170464</v>
       </c>
       <c r="P17" s="165" t="inlineStr">
@@ -9249,7 +9276,7 @@
         <v>10573076</v>
       </c>
       <c r="R17" s="22" t="n"/>
-      <c r="S17" s="503" t="n"/>
+      <c r="S17" s="502" t="n"/>
       <c r="T17" s="397" t="inlineStr">
         <is>
           <t>Struttura</t>
@@ -9257,7 +9284,7 @@
       </c>
       <c r="U17" s="397" t="n"/>
       <c r="V17" s="24" t="n"/>
-      <c r="W17" s="471" t="n"/>
+      <c r="W17" s="470" t="n"/>
       <c r="X17" s="165" t="inlineStr">
         <is>
           <t>Struttura</t>
@@ -9267,8 +9294,8 @@
       <c r="Z17" s="22" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="468" t="n"/>
-      <c r="C18" s="465" t="n"/>
+      <c r="A18" s="467" t="n"/>
+      <c r="C18" s="464" t="n"/>
       <c r="D18" s="389" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -9278,7 +9305,7 @@
         <v>10572700</v>
       </c>
       <c r="F18" s="22" t="n"/>
-      <c r="G18" s="465" t="n"/>
+      <c r="G18" s="464" t="n"/>
       <c r="H18" s="165" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -9288,7 +9315,7 @@
         <v>10572700</v>
       </c>
       <c r="J18" s="22" t="n"/>
-      <c r="K18" s="465" t="n"/>
+      <c r="K18" s="464" t="n"/>
       <c r="L18" s="165" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -9298,7 +9325,7 @@
         <v>10572700</v>
       </c>
       <c r="N18" s="22" t="n"/>
-      <c r="O18" s="465" t="n"/>
+      <c r="O18" s="464" t="n"/>
       <c r="P18" s="165" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -9312,7 +9339,7 @@
           <t>Vedi strisciante</t>
         </is>
       </c>
-      <c r="S18" s="465" t="n"/>
+      <c r="S18" s="464" t="n"/>
       <c r="T18" s="397" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -9320,7 +9347,7 @@
       </c>
       <c r="U18" s="397" t="n"/>
       <c r="V18" s="24" t="n"/>
-      <c r="W18" s="465" t="n"/>
+      <c r="W18" s="464" t="n"/>
       <c r="X18" s="165" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -9330,8 +9357,8 @@
       <c r="Z18" s="22" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="468" t="n"/>
-      <c r="C19" s="465" t="n"/>
+      <c r="A19" s="467" t="n"/>
+      <c r="C19" s="464" t="n"/>
       <c r="D19" s="389" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -9343,7 +9370,7 @@
         </is>
       </c>
       <c r="F19" s="22" t="n"/>
-      <c r="G19" s="465" t="n"/>
+      <c r="G19" s="464" t="n"/>
       <c r="H19" s="165" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -9355,7 +9382,7 @@
         </is>
       </c>
       <c r="J19" s="22" t="n"/>
-      <c r="K19" s="465" t="n"/>
+      <c r="K19" s="464" t="n"/>
       <c r="L19" s="165" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -9367,7 +9394,7 @@
         </is>
       </c>
       <c r="N19" s="22" t="n"/>
-      <c r="O19" s="465" t="n"/>
+      <c r="O19" s="464" t="n"/>
       <c r="P19" s="165" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -9383,7 +9410,7 @@
           <t>Conforme a norma FR SAM E903</t>
         </is>
       </c>
-      <c r="S19" s="465" t="n"/>
+      <c r="S19" s="464" t="n"/>
       <c r="T19" s="397" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -9395,7 +9422,7 @@
         </is>
       </c>
       <c r="V19" s="24" t="n"/>
-      <c r="W19" s="465" t="n"/>
+      <c r="W19" s="464" t="n"/>
       <c r="X19" s="165" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -9409,9 +9436,9 @@
       <c r="Z19" s="22" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="468" t="n"/>
-      <c r="B20" s="508" t="n"/>
-      <c r="C20" s="466" t="n"/>
+      <c r="A20" s="467" t="n"/>
+      <c r="B20" s="507" t="n"/>
+      <c r="C20" s="465" t="n"/>
       <c r="D20" s="165" t="inlineStr">
         <is>
           <t>PPU</t>
@@ -9421,7 +9448,7 @@
         <v>102895</v>
       </c>
       <c r="F20" s="22" t="n"/>
-      <c r="G20" s="466" t="n"/>
+      <c r="G20" s="465" t="n"/>
       <c r="H20" s="165" t="inlineStr">
         <is>
           <t>PPU</t>
@@ -9437,7 +9464,7 @@
           <t>Con isolamento ADD</t>
         </is>
       </c>
-      <c r="K20" s="466" t="n"/>
+      <c r="K20" s="465" t="n"/>
       <c r="L20" s="165" t="inlineStr">
         <is>
           <t>PPU</t>
@@ -9453,7 +9480,7 @@
           <t>Con isolamento ADD</t>
         </is>
       </c>
-      <c r="O20" s="466" t="n"/>
+      <c r="O20" s="465" t="n"/>
       <c r="P20" s="165" t="inlineStr">
         <is>
           <t>PPU</t>
@@ -9463,7 +9490,7 @@
         <v>102895</v>
       </c>
       <c r="R20" s="22" t="n"/>
-      <c r="S20" s="466" t="n"/>
+      <c r="S20" s="465" t="n"/>
       <c r="T20" s="397" t="inlineStr">
         <is>
           <t>PPU</t>
@@ -9471,7 +9498,7 @@
       </c>
       <c r="U20" s="397" t="n"/>
       <c r="V20" s="24" t="n"/>
-      <c r="W20" s="466" t="n"/>
+      <c r="W20" s="465" t="n"/>
       <c r="X20" s="165" t="inlineStr">
         <is>
           <t>PPU</t>
@@ -9485,13 +9512,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="468" t="n"/>
-      <c r="B21" s="507" t="inlineStr">
+      <c r="A21" s="467" t="n"/>
+      <c r="B21" s="506" t="inlineStr">
         <is>
           <t>1,5 kV</t>
         </is>
       </c>
-      <c r="C21" s="471" t="inlineStr">
+      <c r="C21" s="470" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
@@ -9503,7 +9530,7 @@
       </c>
       <c r="E21" s="396" t="n"/>
       <c r="F21" s="23" t="n"/>
-      <c r="G21" s="471" t="inlineStr">
+      <c r="G21" s="470" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
@@ -9515,7 +9542,7 @@
       </c>
       <c r="I21" s="396" t="n"/>
       <c r="J21" s="23" t="n"/>
-      <c r="K21" s="471" t="inlineStr">
+      <c r="K21" s="470" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
@@ -9527,7 +9554,7 @@
       </c>
       <c r="M21" s="396" t="n"/>
       <c r="N21" s="23" t="n"/>
-      <c r="O21" s="491" t="n">
+      <c r="O21" s="490" t="n">
         <v>10851208</v>
       </c>
       <c r="P21" s="165" t="inlineStr">
@@ -9539,7 +9566,7 @@
         <v>10573076</v>
       </c>
       <c r="R21" s="22" t="n"/>
-      <c r="S21" s="503" t="n"/>
+      <c r="S21" s="502" t="n"/>
       <c r="T21" s="397" t="inlineStr">
         <is>
           <t>Struttura</t>
@@ -9547,7 +9574,7 @@
       </c>
       <c r="U21" s="397" t="n"/>
       <c r="V21" s="24" t="n"/>
-      <c r="W21" s="471" t="n"/>
+      <c r="W21" s="470" t="n"/>
       <c r="X21" s="165" t="inlineStr">
         <is>
           <t>Struttura</t>
@@ -9557,8 +9584,8 @@
       <c r="Z21" s="23" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="468" t="n"/>
-      <c r="C22" s="465" t="n"/>
+      <c r="A22" s="467" t="n"/>
+      <c r="C22" s="464" t="n"/>
       <c r="D22" s="389" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -9566,7 +9593,7 @@
       </c>
       <c r="E22" s="396" t="n"/>
       <c r="F22" s="23" t="n"/>
-      <c r="G22" s="465" t="n"/>
+      <c r="G22" s="464" t="n"/>
       <c r="H22" s="165" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -9574,7 +9601,7 @@
       </c>
       <c r="I22" s="396" t="n"/>
       <c r="J22" s="23" t="n"/>
-      <c r="K22" s="465" t="n"/>
+      <c r="K22" s="464" t="n"/>
       <c r="L22" s="165" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -9582,7 +9609,7 @@
       </c>
       <c r="M22" s="396" t="n"/>
       <c r="N22" s="23" t="n"/>
-      <c r="O22" s="465" t="n"/>
+      <c r="O22" s="464" t="n"/>
       <c r="P22" s="165" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -9596,7 +9623,7 @@
           <t>Larghezza 1.950 mm</t>
         </is>
       </c>
-      <c r="S22" s="465" t="n"/>
+      <c r="S22" s="464" t="n"/>
       <c r="T22" s="397" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -9604,7 +9631,7 @@
       </c>
       <c r="U22" s="397" t="n"/>
       <c r="V22" s="24" t="n"/>
-      <c r="W22" s="465" t="n"/>
+      <c r="W22" s="464" t="n"/>
       <c r="X22" s="165" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -9614,8 +9641,8 @@
       <c r="Z22" s="23" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="468" t="n"/>
-      <c r="C23" s="465" t="n"/>
+      <c r="A23" s="467" t="n"/>
+      <c r="C23" s="464" t="n"/>
       <c r="D23" s="389" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -9623,7 +9650,7 @@
       </c>
       <c r="E23" s="396" t="n"/>
       <c r="F23" s="23" t="n"/>
-      <c r="G23" s="465" t="n"/>
+      <c r="G23" s="464" t="n"/>
       <c r="H23" s="165" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -9631,7 +9658,7 @@
       </c>
       <c r="I23" s="396" t="n"/>
       <c r="J23" s="23" t="n"/>
-      <c r="K23" s="465" t="n"/>
+      <c r="K23" s="464" t="n"/>
       <c r="L23" s="165" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -9639,7 +9666,7 @@
       </c>
       <c r="M23" s="396" t="n"/>
       <c r="N23" s="23" t="n"/>
-      <c r="O23" s="465" t="n"/>
+      <c r="O23" s="464" t="n"/>
       <c r="P23" s="165" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -9651,7 +9678,7 @@
         </is>
       </c>
       <c r="R23" s="22" t="n"/>
-      <c r="S23" s="465" t="n"/>
+      <c r="S23" s="464" t="n"/>
       <c r="T23" s="397" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -9659,7 +9686,7 @@
       </c>
       <c r="U23" s="397" t="n"/>
       <c r="V23" s="24" t="n"/>
-      <c r="W23" s="465" t="n"/>
+      <c r="W23" s="464" t="n"/>
       <c r="X23" s="165" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -9669,9 +9696,9 @@
       <c r="Z23" s="23" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="468" t="n"/>
-      <c r="B24" s="508" t="n"/>
-      <c r="C24" s="466" t="n"/>
+      <c r="A24" s="467" t="n"/>
+      <c r="B24" s="507" t="n"/>
+      <c r="C24" s="465" t="n"/>
       <c r="D24" s="389" t="inlineStr">
         <is>
           <t>PCU</t>
@@ -9679,7 +9706,7 @@
       </c>
       <c r="E24" s="396" t="n"/>
       <c r="F24" s="23" t="n"/>
-      <c r="G24" s="466" t="n"/>
+      <c r="G24" s="465" t="n"/>
       <c r="H24" s="165" t="inlineStr">
         <is>
           <t>PCU</t>
@@ -9687,7 +9714,7 @@
       </c>
       <c r="I24" s="396" t="n"/>
       <c r="J24" s="23" t="n"/>
-      <c r="K24" s="466" t="n"/>
+      <c r="K24" s="465" t="n"/>
       <c r="L24" s="165" t="inlineStr">
         <is>
           <t>PCU</t>
@@ -9695,7 +9722,7 @@
       </c>
       <c r="M24" s="396" t="n"/>
       <c r="N24" s="23" t="n"/>
-      <c r="O24" s="466" t="n"/>
+      <c r="O24" s="465" t="n"/>
       <c r="P24" s="165" t="inlineStr">
         <is>
           <t>PPU</t>
@@ -9711,7 +9738,7 @@
           <t>PPU Modificata per agg.panto 1.5</t>
         </is>
       </c>
-      <c r="S24" s="466" t="n"/>
+      <c r="S24" s="465" t="n"/>
       <c r="T24" s="397" t="inlineStr">
         <is>
           <t>PCU</t>
@@ -9719,7 +9746,7 @@
       </c>
       <c r="U24" s="397" t="n"/>
       <c r="V24" s="24" t="n"/>
-      <c r="W24" s="466" t="n"/>
+      <c r="W24" s="465" t="n"/>
       <c r="X24" s="165" t="inlineStr">
         <is>
           <t>PCU</t>
@@ -9729,13 +9756,13 @@
       <c r="Z24" s="23" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="468" t="n"/>
-      <c r="B25" s="507" t="inlineStr">
+      <c r="A25" s="467" t="n"/>
+      <c r="B25" s="506" t="inlineStr">
         <is>
           <t>15 kV</t>
         </is>
       </c>
-      <c r="C25" s="471" t="inlineStr">
+      <c r="C25" s="470" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
@@ -9747,7 +9774,7 @@
       </c>
       <c r="E25" s="396" t="n"/>
       <c r="F25" s="23" t="n"/>
-      <c r="G25" s="471" t="inlineStr">
+      <c r="G25" s="470" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
@@ -9759,7 +9786,7 @@
       </c>
       <c r="I25" s="396" t="n"/>
       <c r="J25" s="23" t="n"/>
-      <c r="K25" s="471" t="inlineStr">
+      <c r="K25" s="470" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
@@ -9771,7 +9798,7 @@
       </c>
       <c r="M25" s="396" t="n"/>
       <c r="N25" s="23" t="n"/>
-      <c r="O25" s="521" t="n"/>
+      <c r="O25" s="520" t="n"/>
       <c r="P25" s="396" t="inlineStr">
         <is>
           <t>Struttura</t>
@@ -9779,7 +9806,7 @@
       </c>
       <c r="Q25" s="396" t="n"/>
       <c r="R25" s="23" t="n"/>
-      <c r="S25" s="518" t="n"/>
+      <c r="S25" s="517" t="n"/>
       <c r="T25" s="397" t="inlineStr">
         <is>
           <t>Struttura</t>
@@ -9787,7 +9814,7 @@
       </c>
       <c r="U25" s="397" t="n"/>
       <c r="V25" s="24" t="n"/>
-      <c r="W25" s="469" t="n"/>
+      <c r="W25" s="468" t="n"/>
       <c r="X25" s="165" t="inlineStr">
         <is>
           <t>Struttura</t>
@@ -9797,8 +9824,8 @@
       <c r="Z25" s="23" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="468" t="n"/>
-      <c r="C26" s="465" t="n"/>
+      <c r="A26" s="467" t="n"/>
+      <c r="C26" s="464" t="n"/>
       <c r="D26" s="389" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -9806,7 +9833,7 @@
       </c>
       <c r="E26" s="396" t="n"/>
       <c r="F26" s="23" t="n"/>
-      <c r="G26" s="465" t="n"/>
+      <c r="G26" s="464" t="n"/>
       <c r="H26" s="165" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -9814,7 +9841,7 @@
       </c>
       <c r="I26" s="396" t="n"/>
       <c r="J26" s="23" t="n"/>
-      <c r="K26" s="465" t="n"/>
+      <c r="K26" s="464" t="n"/>
       <c r="L26" s="165" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -9822,7 +9849,7 @@
       </c>
       <c r="M26" s="396" t="n"/>
       <c r="N26" s="23" t="n"/>
-      <c r="O26" s="465" t="n"/>
+      <c r="O26" s="464" t="n"/>
       <c r="P26" s="396" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -9830,7 +9857,7 @@
       </c>
       <c r="Q26" s="396" t="n"/>
       <c r="R26" s="23" t="n"/>
-      <c r="S26" s="465" t="n"/>
+      <c r="S26" s="464" t="n"/>
       <c r="T26" s="397" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -9838,7 +9865,7 @@
       </c>
       <c r="U26" s="397" t="n"/>
       <c r="V26" s="24" t="n"/>
-      <c r="W26" s="465" t="n"/>
+      <c r="W26" s="464" t="n"/>
       <c r="X26" s="165" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -9848,8 +9875,8 @@
       <c r="Z26" s="23" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="468" t="n"/>
-      <c r="C27" s="465" t="n"/>
+      <c r="A27" s="467" t="n"/>
+      <c r="C27" s="464" t="n"/>
       <c r="D27" s="389" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -9857,7 +9884,7 @@
       </c>
       <c r="E27" s="396" t="n"/>
       <c r="F27" s="23" t="n"/>
-      <c r="G27" s="465" t="n"/>
+      <c r="G27" s="464" t="n"/>
       <c r="H27" s="165" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -9865,7 +9892,7 @@
       </c>
       <c r="I27" s="396" t="n"/>
       <c r="J27" s="23" t="n"/>
-      <c r="K27" s="465" t="n"/>
+      <c r="K27" s="464" t="n"/>
       <c r="L27" s="165" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -9873,7 +9900,7 @@
       </c>
       <c r="M27" s="396" t="n"/>
       <c r="N27" s="23" t="n"/>
-      <c r="O27" s="465" t="n"/>
+      <c r="O27" s="464" t="n"/>
       <c r="P27" s="396" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -9881,7 +9908,7 @@
       </c>
       <c r="Q27" s="396" t="n"/>
       <c r="R27" s="23" t="n"/>
-      <c r="S27" s="465" t="n"/>
+      <c r="S27" s="464" t="n"/>
       <c r="T27" s="397" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -9889,7 +9916,7 @@
       </c>
       <c r="U27" s="397" t="n"/>
       <c r="V27" s="24" t="n"/>
-      <c r="W27" s="465" t="n"/>
+      <c r="W27" s="464" t="n"/>
       <c r="X27" s="165" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -9898,10 +9925,10 @@
       <c r="Y27" s="396" t="n"/>
       <c r="Z27" s="23" t="n"/>
     </row>
-    <row r="28" ht="15.75" customHeight="1" s="479" thickBot="1">
-      <c r="A28" s="505" t="n"/>
-      <c r="B28" s="508" t="n"/>
-      <c r="C28" s="466" t="n"/>
+    <row r="28" ht="15.75" customHeight="1" s="478" thickBot="1">
+      <c r="A28" s="504" t="n"/>
+      <c r="B28" s="507" t="n"/>
+      <c r="C28" s="465" t="n"/>
       <c r="D28" s="25" t="inlineStr">
         <is>
           <t>PCU</t>
@@ -9909,7 +9936,7 @@
       </c>
       <c r="E28" s="29" t="n"/>
       <c r="F28" s="30" t="n"/>
-      <c r="G28" s="466" t="n"/>
+      <c r="G28" s="465" t="n"/>
       <c r="H28" s="26" t="inlineStr">
         <is>
           <t>PCU</t>
@@ -9917,7 +9944,7 @@
       </c>
       <c r="I28" s="29" t="n"/>
       <c r="J28" s="30" t="n"/>
-      <c r="K28" s="466" t="n"/>
+      <c r="K28" s="465" t="n"/>
       <c r="L28" s="26" t="inlineStr">
         <is>
           <t>PCU</t>
@@ -9925,7 +9952,7 @@
       </c>
       <c r="M28" s="29" t="n"/>
       <c r="N28" s="30" t="n"/>
-      <c r="O28" s="470" t="n"/>
+      <c r="O28" s="469" t="n"/>
       <c r="P28" s="29" t="inlineStr">
         <is>
           <t>PPU</t>
@@ -9933,7 +9960,7 @@
       </c>
       <c r="Q28" s="29" t="n"/>
       <c r="R28" s="30" t="n"/>
-      <c r="S28" s="470" t="n"/>
+      <c r="S28" s="469" t="n"/>
       <c r="T28" s="32" t="inlineStr">
         <is>
           <t>PCU</t>
@@ -9941,7 +9968,7 @@
       </c>
       <c r="U28" s="32" t="n"/>
       <c r="V28" s="33" t="n"/>
-      <c r="W28" s="470" t="n"/>
+      <c r="W28" s="469" t="n"/>
       <c r="X28" s="26" t="inlineStr">
         <is>
           <t>PCU</t>
@@ -9950,13 +9977,13 @@
       <c r="Y28" s="29" t="n"/>
       <c r="Z28" s="30" t="n"/>
     </row>
-    <row r="29" ht="101.45" customHeight="1" s="479">
-      <c r="A29" s="489" t="inlineStr">
+    <row r="29" ht="101.45" customHeight="1" s="478">
+      <c r="A29" s="488" t="inlineStr">
         <is>
           <t>TCMS Hardware</t>
         </is>
       </c>
-      <c r="B29" s="489" t="inlineStr">
+      <c r="B29" s="488" t="inlineStr">
         <is>
           <t>LV</t>
         </is>
@@ -9991,12 +10018,12 @@
           <t>CCU-O</t>
         </is>
       </c>
-      <c r="M29" s="515" t="inlineStr">
+      <c r="M29" s="514" t="inlineStr">
         <is>
           <t>Nuova architettura Full Ethernet</t>
         </is>
       </c>
-      <c r="N29" s="499" t="n"/>
+      <c r="N29" s="498" t="n"/>
       <c r="O29" s="44" t="n"/>
       <c r="P29" s="45" t="inlineStr">
         <is>
@@ -10021,7 +10048,7 @@
         </is>
       </c>
       <c r="V29" s="36" t="n"/>
-      <c r="W29" s="448" t="n"/>
+      <c r="W29" s="447" t="n"/>
       <c r="X29" s="45" t="inlineStr">
         <is>
           <t>CCU-O</t>
@@ -10039,8 +10066,8 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="468" t="n"/>
-      <c r="B30" s="468" t="n"/>
+      <c r="A30" s="467" t="n"/>
+      <c r="B30" s="467" t="n"/>
       <c r="C30" s="48" t="n"/>
       <c r="D30" s="409" t="inlineStr">
         <is>
@@ -10071,8 +10098,8 @@
           <t>CCU-S</t>
         </is>
       </c>
-      <c r="M30" s="516" t="n"/>
-      <c r="N30" s="480" t="n"/>
+      <c r="M30" s="515" t="n"/>
+      <c r="N30" s="479" t="n"/>
       <c r="O30" s="48" t="n"/>
       <c r="P30" s="409" t="inlineStr">
         <is>
@@ -10110,9 +10137,9 @@
       </c>
       <c r="Z30" s="22" t="n"/>
     </row>
-    <row r="31" ht="144.6" customHeight="1" s="479">
-      <c r="A31" s="468" t="n"/>
-      <c r="B31" s="490" t="n"/>
+    <row r="31" ht="144.6" customHeight="1" s="478">
+      <c r="A31" s="467" t="n"/>
+      <c r="B31" s="489" t="n"/>
       <c r="C31" s="48" t="n"/>
       <c r="D31" s="410" t="inlineStr">
         <is>
@@ -10151,8 +10178,8 @@
           <t>MIO-S</t>
         </is>
       </c>
-      <c r="M31" s="516" t="n"/>
-      <c r="N31" s="480" t="n"/>
+      <c r="M31" s="515" t="n"/>
+      <c r="N31" s="479" t="n"/>
       <c r="O31" s="48" t="n"/>
       <c r="P31" s="410" t="inlineStr">
         <is>
@@ -10200,9 +10227,9 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="29.1" customHeight="1" s="479">
-      <c r="A32" s="468" t="n"/>
-      <c r="B32" s="486" t="inlineStr">
+    <row r="32" ht="29.1" customHeight="1" s="478">
+      <c r="A32" s="467" t="n"/>
+      <c r="B32" s="485" t="inlineStr">
         <is>
           <t>Teledia</t>
         </is>
@@ -10241,8 +10268,8 @@
           <t>MCG</t>
         </is>
       </c>
-      <c r="M32" s="516" t="n"/>
-      <c r="N32" s="480" t="n"/>
+      <c r="M32" s="515" t="n"/>
+      <c r="N32" s="479" t="n"/>
       <c r="O32" s="48" t="n"/>
       <c r="P32" s="410" t="inlineStr">
         <is>
@@ -10285,8 +10312,8 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="468" t="n"/>
-      <c r="B33" s="507" t="inlineStr">
+      <c r="A33" s="467" t="n"/>
+      <c r="B33" s="506" t="inlineStr">
         <is>
           <t>Monitor</t>
         </is>
@@ -10321,8 +10348,8 @@
           <t>IDU/TOD</t>
         </is>
       </c>
-      <c r="M33" s="516" t="n"/>
-      <c r="N33" s="480" t="n"/>
+      <c r="M33" s="515" t="n"/>
+      <c r="N33" s="479" t="n"/>
       <c r="O33" s="48" t="n"/>
       <c r="P33" s="409" t="inlineStr">
         <is>
@@ -10360,9 +10387,9 @@
       </c>
       <c r="Z33" s="22" t="n"/>
     </row>
-    <row r="34" ht="14.45" customHeight="1" s="479">
-      <c r="A34" s="468" t="n"/>
-      <c r="B34" s="467" t="inlineStr">
+    <row r="34" ht="14.45" customHeight="1" s="478">
+      <c r="A34" s="467" t="n"/>
+      <c r="B34" s="466" t="inlineStr">
         <is>
           <t>Bus</t>
         </is>
@@ -10390,7 +10417,7 @@
           <t>3EST000236-6770</t>
         </is>
       </c>
-      <c r="J34" s="509" t="inlineStr">
+      <c r="J34" s="508" t="inlineStr">
         <is>
           <t>Sell no more supported for new projects due to internal component out of production (legacy only)</t>
         </is>
@@ -10401,8 +10428,8 @@
           <t>T Repeater</t>
         </is>
       </c>
-      <c r="M34" s="516" t="n"/>
-      <c r="N34" s="480" t="n"/>
+      <c r="M34" s="515" t="n"/>
+      <c r="N34" s="479" t="n"/>
       <c r="O34" s="48" t="n"/>
       <c r="P34" s="409" t="inlineStr">
         <is>
@@ -10438,15 +10465,15 @@
           <t>3EST000236-6770</t>
         </is>
       </c>
-      <c r="Z34" s="509" t="inlineStr">
+      <c r="Z34" s="508" t="inlineStr">
         <is>
           <t>Sell no more supported for new projects due to internal component out of production (legacy only)</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="468" t="n"/>
-      <c r="B35" s="468" t="n"/>
+      <c r="A35" s="467" t="n"/>
+      <c r="B35" s="467" t="n"/>
       <c r="C35" s="48" t="n"/>
       <c r="D35" s="409" t="inlineStr">
         <is>
@@ -10470,15 +10497,15 @@
           <t>3EST000236-6769</t>
         </is>
       </c>
-      <c r="J35" s="510" t="n"/>
+      <c r="J35" s="509" t="n"/>
       <c r="K35" s="48" t="n"/>
       <c r="L35" s="409" t="inlineStr">
         <is>
           <t>T Switch</t>
         </is>
       </c>
-      <c r="M35" s="516" t="n"/>
-      <c r="N35" s="480" t="n"/>
+      <c r="M35" s="515" t="n"/>
+      <c r="N35" s="479" t="n"/>
       <c r="O35" s="48" t="n"/>
       <c r="P35" s="409" t="inlineStr">
         <is>
@@ -10514,11 +10541,11 @@
           <t>3EST000236-6769</t>
         </is>
       </c>
-      <c r="Z35" s="510" t="n"/>
-    </row>
-    <row r="36" ht="15.75" customHeight="1" s="479" thickBot="1">
-      <c r="A36" s="490" t="n"/>
-      <c r="B36" s="468" t="n"/>
+      <c r="Z35" s="509" t="n"/>
+    </row>
+    <row r="36" ht="15.75" customHeight="1" s="478" thickBot="1">
+      <c r="A36" s="489" t="n"/>
+      <c r="B36" s="467" t="n"/>
       <c r="C36" s="51" t="n"/>
       <c r="D36" s="414" t="inlineStr">
         <is>
@@ -10542,15 +10569,15 @@
           <t>3EST000234-7837</t>
         </is>
       </c>
-      <c r="J36" s="510" t="n"/>
+      <c r="J36" s="509" t="n"/>
       <c r="K36" s="51" t="n"/>
       <c r="L36" s="414" t="inlineStr">
         <is>
           <t>R Switch</t>
         </is>
       </c>
-      <c r="M36" s="517" t="n"/>
-      <c r="N36" s="483" t="n"/>
+      <c r="M36" s="516" t="n"/>
+      <c r="N36" s="482" t="n"/>
       <c r="O36" s="51" t="n"/>
       <c r="P36" s="414" t="inlineStr">
         <is>
@@ -10586,9 +10613,9 @@
           <t>3EST000234-7837</t>
         </is>
       </c>
-      <c r="Z36" s="510" t="n"/>
-    </row>
-    <row r="37" ht="15.75" customHeight="1" s="479" thickBot="1">
+      <c r="Z36" s="509" t="n"/>
+    </row>
+    <row r="37" ht="15.75" customHeight="1" s="478" thickBot="1">
       <c r="A37" s="39" t="inlineStr">
         <is>
           <t>Energy Meter</t>
@@ -10599,62 +10626,62 @@
           <t>Tipo</t>
         </is>
       </c>
-      <c r="C37" s="474" t="inlineStr">
+      <c r="C37" s="473" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="D37" s="462" t="n"/>
-      <c r="E37" s="462" t="n"/>
-      <c r="F37" s="463" t="n"/>
-      <c r="G37" s="474" t="inlineStr">
+      <c r="D37" s="461" t="n"/>
+      <c r="E37" s="461" t="n"/>
+      <c r="F37" s="462" t="n"/>
+      <c r="G37" s="473" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="H37" s="462" t="n"/>
-      <c r="I37" s="462" t="n"/>
-      <c r="J37" s="463" t="n"/>
-      <c r="K37" s="485" t="inlineStr">
+      <c r="H37" s="461" t="n"/>
+      <c r="I37" s="461" t="n"/>
+      <c r="J37" s="462" t="n"/>
+      <c r="K37" s="484" t="inlineStr">
         <is>
           <t>EMS Microelettrica  integrato con TCMS</t>
         </is>
       </c>
-      <c r="L37" s="462" t="n"/>
-      <c r="M37" s="462" t="n"/>
-      <c r="N37" s="463" t="n"/>
-      <c r="O37" s="485" t="inlineStr">
+      <c r="L37" s="461" t="n"/>
+      <c r="M37" s="461" t="n"/>
+      <c r="N37" s="462" t="n"/>
+      <c r="O37" s="484" t="inlineStr">
         <is>
           <t>EMS Microelettrica non integrato con TCMS</t>
         </is>
       </c>
-      <c r="P37" s="462" t="n"/>
-      <c r="Q37" s="462" t="n"/>
-      <c r="R37" s="463" t="n"/>
-      <c r="S37" s="485" t="inlineStr">
+      <c r="P37" s="461" t="n"/>
+      <c r="Q37" s="461" t="n"/>
+      <c r="R37" s="462" t="n"/>
+      <c r="S37" s="484" t="inlineStr">
         <is>
           <t>EMS Alstom  integrato con TCMS</t>
         </is>
       </c>
-      <c r="T37" s="462" t="n"/>
-      <c r="U37" s="462" t="n"/>
-      <c r="V37" s="463" t="n"/>
-      <c r="W37" s="485" t="inlineStr">
+      <c r="T37" s="461" t="n"/>
+      <c r="U37" s="461" t="n"/>
+      <c r="V37" s="462" t="n"/>
+      <c r="W37" s="484" t="inlineStr">
         <is>
           <t>EMS Alstom  integrato con TCMS</t>
         </is>
       </c>
-      <c r="X37" s="462" t="n"/>
-      <c r="Y37" s="462" t="n"/>
-      <c r="Z37" s="463" t="n"/>
-    </row>
-    <row r="38" ht="87" customHeight="1" s="479">
-      <c r="A38" s="489" t="inlineStr">
+      <c r="X37" s="461" t="n"/>
+      <c r="Y37" s="461" t="n"/>
+      <c r="Z37" s="462" t="n"/>
+    </row>
+    <row r="38" ht="87" customHeight="1" s="478">
+      <c r="A38" s="488" t="inlineStr">
         <is>
           <t>Freno</t>
         </is>
       </c>
-      <c r="B38" s="460" t="inlineStr">
+      <c r="B38" s="459" t="inlineStr">
         <is>
           <t>Centraline</t>
         </is>
@@ -10728,9 +10755,9 @@
       <c r="Y38" s="34" t="n"/>
       <c r="Z38" s="36" t="n"/>
     </row>
-    <row r="39" ht="101.45" customHeight="1" s="479">
-      <c r="A39" s="468" t="n"/>
-      <c r="B39" s="441" t="n"/>
+    <row r="39" ht="101.45" customHeight="1" s="478">
+      <c r="A39" s="467" t="n"/>
+      <c r="B39" s="440" t="n"/>
       <c r="C39" s="48" t="n"/>
       <c r="D39" s="389" t="inlineStr">
         <is>
@@ -10805,8 +10832,8 @@
       <c r="Z39" s="22" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="468" t="n"/>
-      <c r="B40" s="484" t="inlineStr">
+      <c r="A40" s="467" t="n"/>
+      <c r="B40" s="483" t="inlineStr">
         <is>
           <t>Pneumatica</t>
         </is>
@@ -10877,8 +10904,8 @@
       <c r="Z40" s="22" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="468" t="n"/>
-      <c r="B41" s="478" t="n"/>
+      <c r="A41" s="467" t="n"/>
+      <c r="B41" s="477" t="n"/>
       <c r="C41" s="48" t="n"/>
       <c r="D41" s="389" t="inlineStr">
         <is>
@@ -10944,9 +10971,9 @@
       <c r="Y41" s="165" t="n"/>
       <c r="Z41" s="22" t="n"/>
     </row>
-    <row r="42" ht="15.75" customHeight="1" s="479" thickBot="1">
-      <c r="A42" s="490" t="n"/>
-      <c r="B42" s="481" t="n"/>
+    <row r="42" ht="15.75" customHeight="1" s="478" thickBot="1">
+      <c r="A42" s="489" t="n"/>
+      <c r="B42" s="480" t="n"/>
       <c r="C42" s="51" t="n"/>
       <c r="D42" s="417" t="inlineStr">
         <is>
@@ -11045,194 +11072,194 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="489" t="inlineStr">
+      <c r="A43" s="488" t="inlineStr">
         <is>
           <t>PRM</t>
         </is>
       </c>
-      <c r="B43" s="460" t="inlineStr">
+      <c r="B43" s="459" t="inlineStr">
         <is>
           <t>Toilet</t>
         </is>
       </c>
-      <c r="C43" s="497" t="inlineStr">
+      <c r="C43" s="496" t="inlineStr">
         <is>
           <t>Toilet Production HK standard flotta base</t>
         </is>
       </c>
-      <c r="D43" s="498" t="n"/>
-      <c r="E43" s="498" t="n"/>
-      <c r="F43" s="499" t="n"/>
-      <c r="G43" s="497" t="inlineStr">
+      <c r="D43" s="497" t="n"/>
+      <c r="E43" s="497" t="n"/>
+      <c r="F43" s="498" t="n"/>
+      <c r="G43" s="496" t="inlineStr">
         <is>
           <t>Toilet Production HK standard flotta base</t>
         </is>
       </c>
-      <c r="H43" s="498" t="n"/>
-      <c r="I43" s="498" t="n"/>
-      <c r="J43" s="499" t="n"/>
-      <c r="K43" s="497" t="inlineStr">
+      <c r="H43" s="497" t="n"/>
+      <c r="I43" s="497" t="n"/>
+      <c r="J43" s="498" t="n"/>
+      <c r="K43" s="496" t="inlineStr">
         <is>
           <t>Toilet Production HK - conf. NRD Spagna + STI PRM 2019</t>
         </is>
       </c>
-      <c r="L43" s="498" t="n"/>
-      <c r="M43" s="498" t="n"/>
-      <c r="N43" s="499" t="n"/>
-      <c r="O43" s="497" t="inlineStr">
+      <c r="L43" s="497" t="n"/>
+      <c r="M43" s="497" t="n"/>
+      <c r="N43" s="498" t="n"/>
+      <c r="O43" s="496" t="inlineStr">
         <is>
           <t>Toilet Production HK standard flotta base</t>
         </is>
       </c>
-      <c r="P43" s="498" t="n"/>
-      <c r="Q43" s="498" t="n"/>
-      <c r="R43" s="499" t="n"/>
-      <c r="S43" s="497" t="inlineStr">
+      <c r="P43" s="497" t="n"/>
+      <c r="Q43" s="497" t="n"/>
+      <c r="R43" s="498" t="n"/>
+      <c r="S43" s="496" t="inlineStr">
         <is>
           <t>Toilet Production HK standard flotta base</t>
         </is>
       </c>
-      <c r="T43" s="498" t="n"/>
-      <c r="U43" s="498" t="n"/>
-      <c r="V43" s="499" t="n"/>
-      <c r="W43" s="497" t="inlineStr">
+      <c r="T43" s="497" t="n"/>
+      <c r="U43" s="497" t="n"/>
+      <c r="V43" s="498" t="n"/>
+      <c r="W43" s="496" t="inlineStr">
         <is>
           <t>Toilet Production HK - conf. NRD Spagna + STI PRM 2019</t>
         </is>
       </c>
-      <c r="X43" s="498" t="n"/>
-      <c r="Y43" s="498" t="n"/>
-      <c r="Z43" s="499" t="n"/>
+      <c r="X43" s="497" t="n"/>
+      <c r="Y43" s="497" t="n"/>
+      <c r="Z43" s="498" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="468" t="n"/>
-      <c r="B44" s="441" t="n"/>
-      <c r="C44" s="500" t="n"/>
-      <c r="D44" s="441" t="n"/>
-      <c r="E44" s="441" t="n"/>
-      <c r="F44" s="501" t="n"/>
-      <c r="G44" s="500" t="n"/>
-      <c r="H44" s="441" t="n"/>
-      <c r="I44" s="441" t="n"/>
-      <c r="J44" s="501" t="n"/>
-      <c r="K44" s="500" t="n"/>
-      <c r="L44" s="441" t="n"/>
-      <c r="M44" s="441" t="n"/>
-      <c r="N44" s="501" t="n"/>
-      <c r="O44" s="500" t="n"/>
-      <c r="P44" s="441" t="n"/>
-      <c r="Q44" s="441" t="n"/>
-      <c r="R44" s="501" t="n"/>
-      <c r="S44" s="500" t="n"/>
-      <c r="T44" s="441" t="n"/>
-      <c r="U44" s="441" t="n"/>
-      <c r="V44" s="501" t="n"/>
-      <c r="W44" s="500" t="n"/>
-      <c r="X44" s="441" t="n"/>
-      <c r="Y44" s="441" t="n"/>
-      <c r="Z44" s="501" t="n"/>
+      <c r="A44" s="467" t="n"/>
+      <c r="B44" s="440" t="n"/>
+      <c r="C44" s="499" t="n"/>
+      <c r="D44" s="440" t="n"/>
+      <c r="E44" s="440" t="n"/>
+      <c r="F44" s="500" t="n"/>
+      <c r="G44" s="499" t="n"/>
+      <c r="H44" s="440" t="n"/>
+      <c r="I44" s="440" t="n"/>
+      <c r="J44" s="500" t="n"/>
+      <c r="K44" s="499" t="n"/>
+      <c r="L44" s="440" t="n"/>
+      <c r="M44" s="440" t="n"/>
+      <c r="N44" s="500" t="n"/>
+      <c r="O44" s="499" t="n"/>
+      <c r="P44" s="440" t="n"/>
+      <c r="Q44" s="440" t="n"/>
+      <c r="R44" s="500" t="n"/>
+      <c r="S44" s="499" t="n"/>
+      <c r="T44" s="440" t="n"/>
+      <c r="U44" s="440" t="n"/>
+      <c r="V44" s="500" t="n"/>
+      <c r="W44" s="499" t="n"/>
+      <c r="X44" s="440" t="n"/>
+      <c r="Y44" s="440" t="n"/>
+      <c r="Z44" s="500" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="468" t="n"/>
-      <c r="B45" s="484" t="inlineStr">
+      <c r="A45" s="467" t="n"/>
+      <c r="B45" s="483" t="inlineStr">
         <is>
           <t>Lift</t>
         </is>
       </c>
-      <c r="C45" s="475" t="inlineStr">
+      <c r="C45" s="474" t="inlineStr">
         <is>
           <t>Lift HK standard flotta base azionamento idraulico</t>
         </is>
       </c>
-      <c r="D45" s="476" t="n"/>
-      <c r="E45" s="476" t="n"/>
-      <c r="F45" s="477" t="n"/>
-      <c r="G45" s="475" t="inlineStr">
+      <c r="D45" s="475" t="n"/>
+      <c r="E45" s="475" t="n"/>
+      <c r="F45" s="476" t="n"/>
+      <c r="G45" s="474" t="inlineStr">
         <is>
           <t>Lift HK standard flotta base azionamento idraulico</t>
         </is>
       </c>
-      <c r="H45" s="476" t="n"/>
-      <c r="I45" s="476" t="n"/>
-      <c r="J45" s="477" t="n"/>
-      <c r="K45" s="512" t="inlineStr">
+      <c r="H45" s="475" t="n"/>
+      <c r="I45" s="475" t="n"/>
+      <c r="J45" s="476" t="n"/>
+      <c r="K45" s="511" t="inlineStr">
         <is>
           <t>Lift HK STI PRM 2019 (pedana più grande, azionamento elettrico)</t>
         </is>
       </c>
-      <c r="L45" s="476" t="n"/>
-      <c r="M45" s="476" t="n"/>
-      <c r="N45" s="477" t="n"/>
-      <c r="O45" s="475" t="inlineStr">
+      <c r="L45" s="475" t="n"/>
+      <c r="M45" s="475" t="n"/>
+      <c r="N45" s="476" t="n"/>
+      <c r="O45" s="474" t="inlineStr">
         <is>
           <t>Lift HK standard flotta base azionamento idraulico</t>
         </is>
       </c>
-      <c r="P45" s="476" t="n"/>
-      <c r="Q45" s="476" t="n"/>
-      <c r="R45" s="477" t="n"/>
-      <c r="S45" s="475" t="inlineStr">
+      <c r="P45" s="475" t="n"/>
+      <c r="Q45" s="475" t="n"/>
+      <c r="R45" s="476" t="n"/>
+      <c r="S45" s="474" t="inlineStr">
         <is>
           <t>Lift HK standard flotta base azionamento idraulico</t>
         </is>
       </c>
-      <c r="T45" s="476" t="n"/>
-      <c r="U45" s="476" t="n"/>
-      <c r="V45" s="477" t="n"/>
-      <c r="W45" s="512" t="inlineStr">
+      <c r="T45" s="475" t="n"/>
+      <c r="U45" s="475" t="n"/>
+      <c r="V45" s="476" t="n"/>
+      <c r="W45" s="511" t="inlineStr">
         <is>
           <t>Lift HK STI PRM 2019 (pedana più grande) azionamento idraulico</t>
         </is>
       </c>
-      <c r="X45" s="476" t="n"/>
-      <c r="Y45" s="476" t="n"/>
-      <c r="Z45" s="477" t="n"/>
+      <c r="X45" s="475" t="n"/>
+      <c r="Y45" s="475" t="n"/>
+      <c r="Z45" s="476" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="468" t="n"/>
-      <c r="B46" s="478" t="n"/>
-      <c r="C46" s="478" t="n"/>
-      <c r="F46" s="480" t="n"/>
-      <c r="G46" s="478" t="n"/>
-      <c r="J46" s="480" t="n"/>
-      <c r="K46" s="478" t="n"/>
-      <c r="N46" s="480" t="n"/>
-      <c r="O46" s="478" t="n"/>
-      <c r="R46" s="480" t="n"/>
-      <c r="S46" s="478" t="n"/>
-      <c r="V46" s="480" t="n"/>
-      <c r="W46" s="478" t="n"/>
-      <c r="Z46" s="480" t="n"/>
-    </row>
-    <row r="47" ht="15.75" customHeight="1" s="479" thickBot="1">
-      <c r="A47" s="490" t="n"/>
-      <c r="B47" s="481" t="n"/>
-      <c r="C47" s="481" t="n"/>
-      <c r="D47" s="482" t="n"/>
-      <c r="E47" s="482" t="n"/>
-      <c r="F47" s="483" t="n"/>
-      <c r="G47" s="481" t="n"/>
-      <c r="H47" s="482" t="n"/>
-      <c r="I47" s="482" t="n"/>
-      <c r="J47" s="483" t="n"/>
-      <c r="K47" s="481" t="n"/>
-      <c r="L47" s="482" t="n"/>
-      <c r="M47" s="482" t="n"/>
-      <c r="N47" s="483" t="n"/>
-      <c r="O47" s="481" t="n"/>
-      <c r="P47" s="482" t="n"/>
-      <c r="Q47" s="482" t="n"/>
-      <c r="R47" s="483" t="n"/>
-      <c r="S47" s="481" t="n"/>
-      <c r="T47" s="482" t="n"/>
-      <c r="U47" s="482" t="n"/>
-      <c r="V47" s="483" t="n"/>
-      <c r="W47" s="481" t="n"/>
-      <c r="X47" s="482" t="n"/>
-      <c r="Y47" s="482" t="n"/>
-      <c r="Z47" s="483" t="n"/>
-    </row>
-    <row r="48" ht="29.45" customHeight="1" s="479" thickBot="1">
+      <c r="A46" s="467" t="n"/>
+      <c r="B46" s="477" t="n"/>
+      <c r="C46" s="477" t="n"/>
+      <c r="F46" s="479" t="n"/>
+      <c r="G46" s="477" t="n"/>
+      <c r="J46" s="479" t="n"/>
+      <c r="K46" s="477" t="n"/>
+      <c r="N46" s="479" t="n"/>
+      <c r="O46" s="477" t="n"/>
+      <c r="R46" s="479" t="n"/>
+      <c r="S46" s="477" t="n"/>
+      <c r="V46" s="479" t="n"/>
+      <c r="W46" s="477" t="n"/>
+      <c r="Z46" s="479" t="n"/>
+    </row>
+    <row r="47" ht="15.75" customHeight="1" s="478" thickBot="1">
+      <c r="A47" s="489" t="n"/>
+      <c r="B47" s="480" t="n"/>
+      <c r="C47" s="480" t="n"/>
+      <c r="D47" s="481" t="n"/>
+      <c r="E47" s="481" t="n"/>
+      <c r="F47" s="482" t="n"/>
+      <c r="G47" s="480" t="n"/>
+      <c r="H47" s="481" t="n"/>
+      <c r="I47" s="481" t="n"/>
+      <c r="J47" s="482" t="n"/>
+      <c r="K47" s="480" t="n"/>
+      <c r="L47" s="481" t="n"/>
+      <c r="M47" s="481" t="n"/>
+      <c r="N47" s="482" t="n"/>
+      <c r="O47" s="480" t="n"/>
+      <c r="P47" s="481" t="n"/>
+      <c r="Q47" s="481" t="n"/>
+      <c r="R47" s="482" t="n"/>
+      <c r="S47" s="480" t="n"/>
+      <c r="T47" s="481" t="n"/>
+      <c r="U47" s="481" t="n"/>
+      <c r="V47" s="482" t="n"/>
+      <c r="W47" s="480" t="n"/>
+      <c r="X47" s="481" t="n"/>
+      <c r="Y47" s="481" t="n"/>
+      <c r="Z47" s="482" t="n"/>
+    </row>
+    <row r="48" ht="29.45" customHeight="1" s="478" thickBot="1">
       <c r="A48" s="56" t="inlineStr">
         <is>
           <t>Porte Esterne</t>
@@ -11243,58 +11270,58 @@
           <t>Tipo</t>
         </is>
       </c>
-      <c r="C48" s="513" t="inlineStr">
+      <c r="C48" s="512" t="inlineStr">
         <is>
           <t>Porte esterne IFE standard flotta base</t>
         </is>
       </c>
-      <c r="D48" s="462" t="n"/>
-      <c r="E48" s="462" t="n"/>
-      <c r="F48" s="463" t="n"/>
-      <c r="G48" s="513" t="inlineStr">
+      <c r="D48" s="461" t="n"/>
+      <c r="E48" s="461" t="n"/>
+      <c r="F48" s="462" t="n"/>
+      <c r="G48" s="512" t="inlineStr">
         <is>
           <t>Porte esterne IFE standard flotta base</t>
         </is>
       </c>
-      <c r="H48" s="462" t="n"/>
-      <c r="I48" s="462" t="n"/>
-      <c r="J48" s="463" t="n"/>
-      <c r="K48" s="461" t="inlineStr">
+      <c r="H48" s="461" t="n"/>
+      <c r="I48" s="461" t="n"/>
+      <c r="J48" s="462" t="n"/>
+      <c r="K48" s="460" t="inlineStr">
         <is>
           <t>Porte esterne IFE TSI 2019
 Centralina Ethernet</t>
         </is>
       </c>
-      <c r="L48" s="462" t="n"/>
-      <c r="M48" s="462" t="n"/>
-      <c r="N48" s="463" t="n"/>
-      <c r="O48" s="513" t="inlineStr">
+      <c r="L48" s="461" t="n"/>
+      <c r="M48" s="461" t="n"/>
+      <c r="N48" s="462" t="n"/>
+      <c r="O48" s="512" t="inlineStr">
         <is>
           <t>Porte esterne IFE standard flotta base</t>
         </is>
       </c>
-      <c r="P48" s="462" t="n"/>
-      <c r="Q48" s="462" t="n"/>
-      <c r="R48" s="463" t="n"/>
-      <c r="S48" s="513" t="inlineStr">
+      <c r="P48" s="461" t="n"/>
+      <c r="Q48" s="461" t="n"/>
+      <c r="R48" s="462" t="n"/>
+      <c r="S48" s="512" t="inlineStr">
         <is>
           <t>Porte esterne IFE standard flotta base</t>
         </is>
       </c>
-      <c r="T48" s="462" t="n"/>
-      <c r="U48" s="462" t="n"/>
-      <c r="V48" s="463" t="n"/>
-      <c r="W48" s="473" t="inlineStr">
+      <c r="T48" s="461" t="n"/>
+      <c r="U48" s="461" t="n"/>
+      <c r="V48" s="462" t="n"/>
+      <c r="W48" s="472" t="inlineStr">
         <is>
           <t>Porte esterne IFE (TSI 2019)</t>
         </is>
       </c>
-      <c r="X48" s="462" t="n"/>
-      <c r="Y48" s="462" t="n"/>
-      <c r="Z48" s="463" t="n"/>
-    </row>
-    <row r="49" ht="24" customHeight="1" s="479">
-      <c r="A49" s="504" t="inlineStr">
+      <c r="X48" s="461" t="n"/>
+      <c r="Y48" s="461" t="n"/>
+      <c r="Z48" s="462" t="n"/>
+    </row>
+    <row r="49" ht="24" customHeight="1" s="478">
+      <c r="A49" s="503" t="inlineStr">
         <is>
           <t>Antincendio</t>
         </is>
@@ -11305,110 +11332,110 @@
 Elettronica</t>
         </is>
       </c>
-      <c r="C49" s="497" t="inlineStr">
+      <c r="C49" s="496" t="inlineStr">
         <is>
           <t>SCU Saira</t>
         </is>
       </c>
-      <c r="D49" s="447" t="n"/>
-      <c r="E49" s="447" t="n"/>
-      <c r="F49" s="488" t="n"/>
-      <c r="G49" s="487" t="inlineStr">
+      <c r="D49" s="446" t="n"/>
+      <c r="E49" s="446" t="n"/>
+      <c r="F49" s="487" t="n"/>
+      <c r="G49" s="486" t="inlineStr">
         <is>
           <t>FDU-1000 (fornitura ISE)</t>
         </is>
       </c>
-      <c r="H49" s="447" t="n"/>
-      <c r="I49" s="447" t="n"/>
-      <c r="J49" s="488" t="n"/>
-      <c r="K49" s="487" t="inlineStr">
+      <c r="H49" s="446" t="n"/>
+      <c r="I49" s="446" t="n"/>
+      <c r="J49" s="487" t="n"/>
+      <c r="K49" s="486" t="inlineStr">
         <is>
           <t>FDU ISE</t>
         </is>
       </c>
-      <c r="L49" s="447" t="n"/>
-      <c r="M49" s="447" t="n"/>
-      <c r="N49" s="488" t="n"/>
-      <c r="O49" s="497" t="inlineStr">
+      <c r="L49" s="446" t="n"/>
+      <c r="M49" s="446" t="n"/>
+      <c r="N49" s="487" t="n"/>
+      <c r="O49" s="496" t="inlineStr">
         <is>
           <t>SCU Saira</t>
         </is>
       </c>
-      <c r="P49" s="447" t="n"/>
-      <c r="Q49" s="447" t="n"/>
-      <c r="R49" s="488" t="n"/>
-      <c r="S49" s="497" t="inlineStr">
+      <c r="P49" s="446" t="n"/>
+      <c r="Q49" s="446" t="n"/>
+      <c r="R49" s="487" t="n"/>
+      <c r="S49" s="496" t="inlineStr">
         <is>
           <t>SCU Saira</t>
         </is>
       </c>
-      <c r="T49" s="447" t="n"/>
-      <c r="U49" s="447" t="n"/>
-      <c r="V49" s="488" t="n"/>
-      <c r="W49" s="487" t="inlineStr">
+      <c r="T49" s="446" t="n"/>
+      <c r="U49" s="446" t="n"/>
+      <c r="V49" s="487" t="n"/>
+      <c r="W49" s="486" t="inlineStr">
         <is>
           <t>FDU-1000 (fornitura ISE)</t>
         </is>
       </c>
-      <c r="X49" s="447" t="n"/>
-      <c r="Y49" s="447" t="n"/>
-      <c r="Z49" s="488" t="n"/>
-    </row>
-    <row r="50" ht="15.75" customHeight="1" s="479" thickBot="1">
-      <c r="A50" s="505" t="n"/>
+      <c r="X49" s="446" t="n"/>
+      <c r="Y49" s="446" t="n"/>
+      <c r="Z49" s="487" t="n"/>
+    </row>
+    <row r="50" ht="15.75" customHeight="1" s="478" thickBot="1">
+      <c r="A50" s="504" t="n"/>
       <c r="B50" s="43" t="inlineStr">
         <is>
           <t>Estinzione</t>
         </is>
       </c>
-      <c r="C50" s="494" t="inlineStr">
+      <c r="C50" s="493" t="inlineStr">
         <is>
           <t>WaterMist Marioff - 2 gruppi MAU (DM1/8)</t>
         </is>
       </c>
-      <c r="D50" s="482" t="n"/>
-      <c r="E50" s="482" t="n"/>
-      <c r="F50" s="483" t="n"/>
-      <c r="G50" s="514" t="inlineStr">
+      <c r="D50" s="481" t="n"/>
+      <c r="E50" s="481" t="n"/>
+      <c r="F50" s="482" t="n"/>
+      <c r="G50" s="513" t="inlineStr">
         <is>
           <t>WaterMist Marioff - 2 gruppi MAU (DM1/8)</t>
         </is>
       </c>
-      <c r="H50" s="482" t="n"/>
-      <c r="I50" s="482" t="n"/>
-      <c r="J50" s="483" t="n"/>
-      <c r="K50" s="514" t="inlineStr">
+      <c r="H50" s="481" t="n"/>
+      <c r="I50" s="481" t="n"/>
+      <c r="J50" s="482" t="n"/>
+      <c r="K50" s="513" t="inlineStr">
         <is>
           <t>WaterMist Acquasys - 1 gruppo MAU (DM1)</t>
         </is>
       </c>
-      <c r="L50" s="482" t="n"/>
-      <c r="M50" s="482" t="n"/>
-      <c r="N50" s="483" t="n"/>
-      <c r="O50" s="494" t="inlineStr">
+      <c r="L50" s="481" t="n"/>
+      <c r="M50" s="481" t="n"/>
+      <c r="N50" s="482" t="n"/>
+      <c r="O50" s="493" t="inlineStr">
         <is>
           <t>WaterMist Marioff - 2 gruppi MAU (DM1/8)</t>
         </is>
       </c>
-      <c r="P50" s="482" t="n"/>
-      <c r="Q50" s="482" t="n"/>
-      <c r="R50" s="483" t="n"/>
-      <c r="S50" s="494" t="inlineStr">
+      <c r="P50" s="481" t="n"/>
+      <c r="Q50" s="481" t="n"/>
+      <c r="R50" s="482" t="n"/>
+      <c r="S50" s="493" t="inlineStr">
         <is>
           <t>WaterMist Marioff - 2 gruppi MAU (DM1/8)</t>
         </is>
       </c>
-      <c r="T50" s="482" t="n"/>
-      <c r="U50" s="482" t="n"/>
-      <c r="V50" s="483" t="n"/>
-      <c r="W50" s="494" t="inlineStr">
+      <c r="T50" s="481" t="n"/>
+      <c r="U50" s="481" t="n"/>
+      <c r="V50" s="482" t="n"/>
+      <c r="W50" s="493" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="X50" s="482" t="n"/>
-      <c r="Y50" s="482" t="n"/>
-      <c r="Z50" s="483" t="n"/>
+      <c r="X50" s="481" t="n"/>
+      <c r="Y50" s="481" t="n"/>
+      <c r="Z50" s="482" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="100">
@@ -11501,8 +11528,8 @@
     <mergeCell ref="A43:A47"/>
     <mergeCell ref="W49:Z49"/>
     <mergeCell ref="O25:O28"/>
+    <mergeCell ref="K43:N44"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="K43:N44"/>
     <mergeCell ref="S9:S12"/>
     <mergeCell ref="G3:G8"/>
     <mergeCell ref="C17:C20"/>
@@ -11532,11 +11559,11 @@
     <col width="28.42578125" bestFit="1" customWidth="1" style="8" min="4" max="4"/>
     <col width="21.42578125" customWidth="1" style="8" min="5" max="5"/>
     <col width="35.5703125" customWidth="1" style="8" min="6" max="7"/>
-    <col width="8.7109375" customWidth="1" style="8" min="8" max="16"/>
-    <col width="8.7109375" customWidth="1" style="8" min="17" max="16384"/>
+    <col width="8.7109375" customWidth="1" style="8" min="8" max="17"/>
+    <col width="8.7109375" customWidth="1" style="8" min="18" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" s="479">
+    <row r="1" ht="30" customHeight="1" s="478">
       <c r="A1" s="329" t="inlineStr">
         <is>
           <t>FUNC ID</t>
@@ -11547,18 +11574,18 @@
           <t>DESCRIZIONE FUNZIONE</t>
         </is>
       </c>
-      <c r="C1" s="435" t="inlineStr">
+      <c r="C1" s="434" t="inlineStr">
         <is>
           <t>DOC
 CARTELLA</t>
         </is>
       </c>
-      <c r="D1" s="435" t="inlineStr">
+      <c r="D1" s="434" t="inlineStr">
         <is>
           <t>DOC ID</t>
         </is>
       </c>
-      <c r="E1" s="435" t="inlineStr">
+      <c r="E1" s="434" t="inlineStr">
         <is>
           <t>Info DOC</t>
         </is>
@@ -11615,7 +11642,7 @@
       </c>
       <c r="G3" s="340" t="n"/>
     </row>
-    <row r="4" ht="45" customHeight="1" s="479">
+    <row r="4" ht="45" customHeight="1" s="478">
       <c r="A4" s="59" t="inlineStr">
         <is>
           <t>Nel foglio indicato in Cx nella colonna B, cerca la riga corrispondente al DOC ID indicato in Dx</t>
@@ -11644,7 +11671,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" ht="45" customHeight="1" s="479">
+    <row r="5" ht="45" customHeight="1" s="478">
       <c r="A5" s="59" t="inlineStr">
         <is>
           <t>Nel foglio CONFIG riga 1, cerca la colonna corrispondente alla flotta indicata da F1</t>
@@ -11670,7 +11697,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="45" customHeight="1" s="479">
+    <row r="6" ht="45" customHeight="1" s="478">
       <c r="A6" s="59" t="inlineStr">
         <is>
           <t>Restituisci la posizione della cella corrispondente a riga/colonna sopra identificati</t>
@@ -11696,7 +11723,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1" s="479">
+    <row r="7" ht="30" customHeight="1" s="478">
       <c r="A7" s="59" t="inlineStr">
         <is>
           <t>Alla posizione della cella, concatena il nome del foglio recuperato in Cx</t>
@@ -11722,7 +11749,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1" s="479">
+    <row r="8" ht="60" customHeight="1" s="478">
       <c r="A8" s="59" t="inlineStr">
         <is>
           <t>Recupera il contenuto del foglio/cella indicato nell'indirizzo sopra, il quale corrisponde al nome del file archiviato</t>
@@ -11748,7 +11775,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1" s="479">
+    <row r="9" ht="60" customHeight="1" s="478">
       <c r="A9" s="59" t="inlineStr">
         <is>
           <t>Recupera il prefisso del DOC ID posto prima del carattere "_", al quale corrisponde la sottocartella di archiviazione</t>
@@ -11774,7 +11801,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="165" customHeight="1" s="479">
+    <row r="10" ht="165" customHeight="1" s="478">
       <c r="A10" s="59" t="inlineStr">
         <is>
           <t>crea l'indirizzo completo per la costruzione del link, concatenando:
@@ -11812,7 +11839,7 @@
       <c r="D11" s="217" t="n"/>
       <c r="E11" s="218" t="n"/>
     </row>
-    <row r="12" ht="45" customHeight="1" s="479">
+    <row r="12" ht="45" customHeight="1" s="478">
       <c r="A12" s="59" t="inlineStr">
         <is>
           <t>recupero del formato del file dal foglio indicato in Cx, alla riga indicata del DOC ID e colonna 3</t>
@@ -11842,7 +11869,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1" s="479">
+    <row r="13" ht="60" customHeight="1" s="478">
       <c r="A13" s="59" t="inlineStr">
         <is>
           <t>crea l'indirizzo come sopra, inserendo anche la parte di recupero di estensione del file</t>
@@ -11856,7 +11883,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1" s="479">
+    <row r="14" ht="30" customHeight="1" s="478">
       <c r="A14" s="219" t="inlineStr">
         <is>
           <t>prova link con DOC Type &lt;&gt; pdf</t>
@@ -11888,7 +11915,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1" s="479">
+    <row r="17" ht="30" customHeight="1" s="478">
       <c r="A17" s="219" t="inlineStr">
         <is>
           <t>prova link con DOC Type &lt;&gt; pdf</t>
@@ -11937,7 +11964,7 @@
       <c r="F19" s="350" t="n"/>
       <c r="G19" s="350" t="n"/>
     </row>
-    <row r="20" ht="30" customHeight="1" s="479">
+    <row r="20" ht="30" customHeight="1" s="478">
       <c r="A20" s="62" t="inlineStr">
         <is>
           <t>parte iniziale - posizione cella foglio/flotta</t>
@@ -12137,12 +12164,12 @@
   <dimension ref="B2:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="41.85546875" customWidth="1" style="479" min="2" max="2"/>
-    <col width="6.140625" bestFit="1" customWidth="1" style="479" min="7" max="7"/>
+    <col width="41.85546875" customWidth="1" style="478" min="2" max="2"/>
+    <col width="6.140625" bestFit="1" customWidth="1" style="478" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" s="479" thickBot="1"/>
-    <row r="2" ht="15.75" customHeight="1" s="479" thickBot="1">
+    <row r="1" ht="15.75" customHeight="1" s="478" thickBot="1"/>
+    <row r="2" ht="15.75" customHeight="1" s="478" thickBot="1">
       <c r="C2" s="1" t="inlineStr">
         <is>
           <t>VZI-50</t>
@@ -12173,13 +12200,13 @@
           <t>VZ-ES</t>
         </is>
       </c>
-      <c r="I2" s="463" t="inlineStr">
+      <c r="I2" s="462" t="inlineStr">
         <is>
           <t>VZ-DAI</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" s="479" thickBot="1">
+    <row r="3" ht="15.75" customHeight="1" s="478" thickBot="1">
       <c r="B3" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">IPA (Indicazione Porte Aperte) </t>
@@ -12213,7 +12240,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="30.75" customHeight="1" s="479" thickBot="1">
+    <row r="4" ht="30.75" customHeight="1" s="478" thickBot="1">
       <c r="B4" s="3" t="inlineStr">
         <is>
           <t>BY-PASS ALLARME APPLICAZIONE PARKING
@@ -12248,7 +12275,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="15.75" customHeight="1" s="479" thickBot="1">
+    <row r="5" ht="15.75" customHeight="1" s="478" thickBot="1">
       <c r="B5" s="1" t="inlineStr">
         <is>
           <t>RIDONDANZA LOOP DNRA-BMS</t>
@@ -12282,7 +12309,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="15.75" customHeight="1" s="479" thickBot="1">
+    <row r="6" ht="15.75" customHeight="1" s="478" thickBot="1">
       <c r="B6" s="1" t="inlineStr">
         <is>
           <t>INTERRUTTORI 220V SPOSTATI INTERNO CASSA</t>
@@ -12316,7 +12343,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="15.75" customHeight="1" s="479" thickBot="1">
+    <row r="7" ht="15.75" customHeight="1" s="478" thickBot="1">
       <c r="B7" s="1" t="inlineStr">
         <is>
           <t>COMPRESSORE ARIA (?)</t>
@@ -12330,7 +12357,7 @@
       <c r="H7" s="233" t="n"/>
       <c r="I7" s="233" t="n"/>
     </row>
-    <row r="8" ht="15.75" customHeight="1" s="479" thickBot="1">
+    <row r="8" ht="15.75" customHeight="1" s="478" thickBot="1">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>BY-PASS ADD PER MARCIA SOCCORSO</t>
@@ -12364,7 +12391,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1" s="479" thickBot="1">
+    <row r="9" ht="15.75" customHeight="1" s="478" thickBot="1">
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t>ARREDI TOILET BAR BISTROT</t>
@@ -12378,7 +12405,7 @@
       <c r="H9" s="233" t="n"/>
       <c r="I9" s="233" t="n"/>
     </row>
-    <row r="10" ht="45.75" customHeight="1" s="479" thickBot="1">
+    <row r="10" ht="45.75" customHeight="1" s="478" thickBot="1">
       <c r="B10" s="3" t="inlineStr">
         <is>
           <t>COMANDO DISACCOPPIAMENTO AUTOMATICO 
@@ -12413,7 +12440,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="15.75" customHeight="1" s="479" thickBot="1">
+    <row r="11" ht="15.75" customHeight="1" s="478" thickBot="1">
       <c r="B11" s="1" t="inlineStr">
         <is>
           <t>PANTOGRAFI</t>
@@ -12427,7 +12454,7 @@
       <c r="H11" s="233" t="n"/>
       <c r="I11" s="233" t="n"/>
     </row>
-    <row r="12" ht="15.75" customHeight="1" s="479" thickBot="1">
+    <row r="12" ht="15.75" customHeight="1" s="478" thickBot="1">
       <c r="B12" s="1" t="inlineStr">
         <is>
           <t>PIANO DI MANUTENZIONE</t>
@@ -12441,7 +12468,7 @@
       <c r="H12" s="165" t="n"/>
       <c r="I12" s="165" t="n"/>
     </row>
-    <row r="13" ht="15.75" customHeight="1" s="479" thickBot="1">
+    <row r="13" ht="15.75" customHeight="1" s="478" thickBot="1">
       <c r="B13" s="1" t="inlineStr">
         <is>
           <t>BL SSB</t>
@@ -12455,8 +12482,8 @@
       <c r="H13" s="165" t="n"/>
       <c r="I13" s="165" t="n"/>
     </row>
-    <row r="14" ht="15.75" customHeight="1" s="479" thickBot="1">
-      <c r="B14" s="505" t="inlineStr">
+    <row r="14" ht="15.75" customHeight="1" s="478" thickBot="1">
+      <c r="B14" s="504" t="inlineStr">
         <is>
           <t>BL DIS</t>
         </is>
@@ -12469,7 +12496,7 @@
       <c r="H14" s="165" t="n"/>
       <c r="I14" s="165" t="n"/>
     </row>
-    <row r="15" ht="15.75" customHeight="1" s="479" thickBot="1">
+    <row r="15" ht="15.75" customHeight="1" s="478" thickBot="1">
       <c r="B15" s="1" t="inlineStr">
         <is>
           <t>ETCS HD (HW)</t>
@@ -12483,7 +12510,7 @@
       <c r="H15" s="165" t="n"/>
       <c r="I15" s="165" t="n"/>
     </row>
-    <row r="16" ht="15.75" customHeight="1" s="479" thickBot="1">
+    <row r="16" ht="15.75" customHeight="1" s="478" thickBot="1">
       <c r="B16" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">ANTINCENDIO </t>
@@ -12497,7 +12524,7 @@
       <c r="H16" s="165" t="n"/>
       <c r="I16" s="165" t="n"/>
     </row>
-    <row r="17" ht="15.75" customHeight="1" s="479" thickBot="1">
+    <row r="17" ht="15.75" customHeight="1" s="478" thickBot="1">
       <c r="B17" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">LAYOUT INTERNO </t>
@@ -12538,8 +12565,8 @@
     <col width="8.7109375" customWidth="1" style="9" min="3" max="3"/>
     <col width="120.7109375" customWidth="1" style="59" min="4" max="4"/>
     <col width="60.140625" customWidth="1" style="59" min="5" max="5"/>
-    <col width="8.7109375" customWidth="1" style="8" min="6" max="14"/>
-    <col width="8.7109375" customWidth="1" style="8" min="15" max="16384"/>
+    <col width="8.7109375" customWidth="1" style="8" min="6" max="15"/>
+    <col width="8.7109375" customWidth="1" style="8" min="16" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="23.45" customFormat="1" customHeight="1" s="109">
@@ -12569,7 +12596,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1" s="479">
+    <row r="2" ht="30" customHeight="1" s="478">
       <c r="A2" s="158" t="n">
         <v>46190</v>
       </c>
@@ -12644,7 +12671,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="45" customHeight="1" s="479">
+    <row r="5" ht="45" customHeight="1" s="478">
       <c r="A5" s="158" t="n">
         <v>46190</v>
       </c>
@@ -12694,7 +12721,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="45" customHeight="1" s="479">
+    <row r="7" ht="45" customHeight="1" s="478">
       <c r="A7" s="158" t="n">
         <v>46189</v>
       </c>
@@ -12796,7 +12823,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1" s="479">
+    <row r="11" ht="60" customHeight="1" s="478">
       <c r="A11" s="158" t="n">
         <v>46196</v>
       </c>
@@ -12822,7 +12849,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="105" customHeight="1" s="479">
+    <row r="12" ht="105" customHeight="1" s="478">
       <c r="A12" s="158" t="n">
         <v>46196</v>
       </c>
@@ -12847,7 +12874,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1" s="479">
+    <row r="13" ht="30" customHeight="1" s="478">
       <c r="A13" s="158" t="n">
         <v>46197</v>
       </c>
@@ -12891,11 +12918,11 @@
     <col width="6.5703125" bestFit="1" customWidth="1" style="8" min="3" max="3"/>
     <col width="139.42578125" bestFit="1" customWidth="1" style="60" min="4" max="4"/>
     <col width="8.7109375" customWidth="1" style="9" min="5" max="5"/>
-    <col width="8.7109375" customWidth="1" style="8" min="6" max="14"/>
-    <col width="8.7109375" customWidth="1" style="8" min="15" max="16384"/>
+    <col width="8.7109375" customWidth="1" style="8" min="6" max="15"/>
+    <col width="8.7109375" customWidth="1" style="8" min="16" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21.6" customHeight="1" s="479">
+    <row r="1" ht="21.6" customHeight="1" s="478">
       <c r="A1" s="100" t="inlineStr">
         <is>
           <t>DESCRIZIONE</t>
@@ -12922,7 +12949,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="21.6" customHeight="1" s="479">
+    <row r="2" ht="21.6" customHeight="1" s="478">
       <c r="A2" s="9" t="inlineStr">
         <is>
           <t>Root Sharepoint</t>
@@ -12946,7 +12973,7 @@
         <v/>
       </c>
     </row>
-    <row r="3" ht="21.6" customHeight="1" s="479">
+    <row r="3" ht="21.6" customHeight="1" s="478">
       <c r="A3" s="9" t="inlineStr">
         <is>
           <t>Cartella Documenti Ingegneria</t>
@@ -12969,7 +12996,7 @@
         <v/>
       </c>
     </row>
-    <row r="4" ht="21.6" customHeight="1" s="479">
+    <row r="4" ht="21.6" customHeight="1" s="478">
       <c r="A4" s="9" t="inlineStr">
         <is>
           <t>Cartella Archiviazione doc ETR1000</t>
@@ -12992,7 +13019,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" ht="21.6" customHeight="1" s="479">
+    <row r="5" ht="21.6" customHeight="1" s="478">
       <c r="A5" s="9" t="inlineStr">
         <is>
           <t>Documenti di configurazione</t>
@@ -13015,7 +13042,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" ht="21.6" customHeight="1" s="479">
+    <row r="6" ht="21.6" customHeight="1" s="478">
       <c r="A6" s="9" t="inlineStr">
         <is>
           <t>Raccolta documentazione Funzioni</t>
@@ -13038,17 +13065,17 @@
         <v/>
       </c>
     </row>
-    <row r="7" ht="21.95" customHeight="1" s="479"/>
-    <row r="8" ht="21.95" customHeight="1" s="479"/>
-    <row r="9" ht="21.95" customHeight="1" s="479"/>
-    <row r="10" ht="21.95" customHeight="1" s="479">
+    <row r="7" ht="21.95" customHeight="1" s="478"/>
+    <row r="8" ht="21.95" customHeight="1" s="478"/>
+    <row r="9" ht="21.95" customHeight="1" s="478"/>
+    <row r="10" ht="21.95" customHeight="1" s="478">
       <c r="A10" s="8" t="inlineStr">
         <is>
           <t>VINCOLI</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="21.95" customHeight="1" s="479">
+    <row r="11" ht="21.95" customHeight="1" s="478">
       <c r="A11" s="8" t="inlineStr">
         <is>
           <t>Id Flotta</t>
@@ -13060,7 +13087,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="21.95" customHeight="1" s="479">
+    <row r="12" ht="21.95" customHeight="1" s="478">
       <c r="A12" s="8" t="inlineStr">
         <is>
           <t>DOC ID</t>
@@ -13103,10 +13130,10 @@
   <dimension ref="A1:BW9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19.42578125" bestFit="1" customWidth="1" style="479" min="1" max="1"/>
-    <col width="17.5703125" customWidth="1" style="479" min="2" max="3"/>
-    <col width="15.42578125" customWidth="1" style="479" min="4" max="4"/>
-    <col width="15.140625" customWidth="1" style="479" min="5" max="5"/>
+    <col width="19.42578125" bestFit="1" customWidth="1" style="478" min="1" max="1"/>
+    <col width="17.5703125" customWidth="1" style="478" min="2" max="3"/>
+    <col width="15.42578125" customWidth="1" style="478" min="4" max="4"/>
+    <col width="15.140625" customWidth="1" style="478" min="5" max="5"/>
     <col width="11" customWidth="1" style="7" min="6" max="6"/>
     <col width="3.85546875" bestFit="1" customWidth="1" style="7" min="7" max="52"/>
     <col width="2.85546875" bestFit="1" customWidth="1" style="7" min="53" max="69"/>
@@ -14198,7 +14225,7 @@
       </c>
       <c r="D9" s="152" t="n"/>
       <c r="E9" s="153" t="n"/>
-      <c r="F9" s="475">
+      <c r="F9" s="474">
         <f>COUNTIF(G9:BW9,"&lt;&gt;")</f>
         <v/>
       </c>
@@ -14316,144 +14343,144 @@
     <col width="6.5703125" customWidth="1" style="10" min="21" max="21"/>
     <col width="6.5703125" bestFit="1" customWidth="1" style="10" min="22" max="22"/>
     <col width="6.5703125" customWidth="1" style="10" min="23" max="23"/>
-    <col width="8.7109375" customWidth="1" style="59" min="24" max="32"/>
-    <col width="8.7109375" customWidth="1" style="59" min="33" max="16384"/>
+    <col width="8.7109375" customWidth="1" style="59" min="24" max="33"/>
+    <col width="8.7109375" customWidth="1" style="59" min="34" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" s="61">
-      <c r="A1" s="435" t="inlineStr">
+      <c r="A1" s="434" t="inlineStr">
         <is>
           <t>DOC DESCRIPTION</t>
         </is>
       </c>
-      <c r="B1" s="435" t="inlineStr">
+      <c r="B1" s="434" t="inlineStr">
         <is>
           <t>DOC ID</t>
         </is>
       </c>
-      <c r="C1" s="435" t="inlineStr">
+      <c r="C1" s="434" t="inlineStr">
         <is>
           <t>DOC EXT</t>
         </is>
       </c>
-      <c r="D1" s="432" t="inlineStr">
+      <c r="D1" s="431" t="inlineStr">
         <is>
           <t>VZI_Base</t>
         </is>
       </c>
-      <c r="E1" s="430" t="n"/>
-      <c r="F1" s="431" t="n"/>
-      <c r="G1" s="433" t="inlineStr">
+      <c r="E1" s="429" t="n"/>
+      <c r="F1" s="430" t="n"/>
+      <c r="G1" s="432" t="inlineStr">
         <is>
           <t>VZI_New14</t>
         </is>
       </c>
-      <c r="H1" s="434" t="n"/>
-      <c r="I1" s="434" t="n"/>
-      <c r="J1" s="432" t="inlineStr">
+      <c r="H1" s="433" t="n"/>
+      <c r="I1" s="433" t="n"/>
+      <c r="J1" s="431" t="inlineStr">
         <is>
           <t>VZ_FR</t>
         </is>
       </c>
-      <c r="K1" s="430" t="n"/>
-      <c r="L1" s="431" t="n"/>
-      <c r="M1" s="440" t="inlineStr">
+      <c r="K1" s="429" t="n"/>
+      <c r="L1" s="430" t="n"/>
+      <c r="M1" s="439" t="inlineStr">
         <is>
           <t>VZ_ES</t>
         </is>
       </c>
-      <c r="N1" s="441" t="n"/>
-      <c r="O1" s="441" t="n"/>
-      <c r="P1" s="432" t="inlineStr">
+      <c r="N1" s="440" t="n"/>
+      <c r="O1" s="440" t="n"/>
+      <c r="P1" s="431" t="inlineStr">
         <is>
           <t>VZI-6_R1</t>
         </is>
       </c>
-      <c r="Q1" s="431" t="n"/>
-      <c r="R1" s="432" t="inlineStr">
+      <c r="Q1" s="430" t="n"/>
+      <c r="R1" s="431" t="inlineStr">
         <is>
           <t>VZI-4_R1</t>
         </is>
       </c>
-      <c r="S1" s="431" t="n"/>
-      <c r="T1" s="432" t="inlineStr">
+      <c r="S1" s="430" t="n"/>
+      <c r="T1" s="431" t="inlineStr">
         <is>
           <t>VZ_DAI</t>
         </is>
       </c>
-      <c r="U1" s="431" t="n"/>
-      <c r="V1" s="432" t="inlineStr">
+      <c r="U1" s="430" t="n"/>
+      <c r="V1" s="431" t="inlineStr">
         <is>
           <t>VZ_Esxx</t>
         </is>
       </c>
-      <c r="W1" s="431" t="n"/>
+      <c r="W1" s="430" t="n"/>
     </row>
     <row r="2" ht="41.1" customFormat="1" customHeight="1" s="61">
-      <c r="A2" s="436" t="n"/>
-      <c r="B2" s="436" t="n"/>
-      <c r="C2" s="436" t="n"/>
-      <c r="D2" s="429" t="inlineStr">
+      <c r="A2" s="435" t="n"/>
+      <c r="B2" s="435" t="n"/>
+      <c r="C2" s="435" t="n"/>
+      <c r="D2" s="428" t="inlineStr">
         <is>
           <t>Conf Sheet  BD130033980 - BL 6.0</t>
         </is>
       </c>
-      <c r="E2" s="430" t="n"/>
-      <c r="F2" s="431" t="n"/>
-      <c r="G2" s="438" t="inlineStr">
+      <c r="E2" s="429" t="n"/>
+      <c r="F2" s="430" t="n"/>
+      <c r="G2" s="437" t="inlineStr">
         <is>
           <t>Conf Sheet BD140050695 - BL 4.4</t>
         </is>
       </c>
-      <c r="H2" s="434" t="n"/>
-      <c r="I2" s="434" t="n"/>
-      <c r="J2" s="429" t="inlineStr">
+      <c r="H2" s="433" t="n"/>
+      <c r="I2" s="433" t="n"/>
+      <c r="J2" s="428" t="inlineStr">
         <is>
           <t>Conf Sheet 3ECP414415-0001 - BL 4.0</t>
         </is>
       </c>
-      <c r="K2" s="430" t="n"/>
-      <c r="L2" s="431" t="n"/>
-      <c r="M2" s="442" t="inlineStr">
+      <c r="K2" s="429" t="n"/>
+      <c r="L2" s="430" t="n"/>
+      <c r="M2" s="441" t="inlineStr">
         <is>
           <t>Conf Sheet BD140047828 - BL 2.9</t>
         </is>
       </c>
-      <c r="N2" s="441" t="n"/>
-      <c r="O2" s="441" t="n"/>
-      <c r="P2" s="429" t="inlineStr">
+      <c r="N2" s="440" t="n"/>
+      <c r="O2" s="440" t="n"/>
+      <c r="P2" s="428" t="inlineStr">
         <is>
           <t>VZI-6_IT [R1]
 BL 4.0</t>
         </is>
       </c>
-      <c r="Q2" s="431" t="n"/>
-      <c r="R2" s="439" t="inlineStr">
+      <c r="Q2" s="430" t="n"/>
+      <c r="R2" s="438" t="inlineStr">
         <is>
           <t>VZI-4_IT [R1]
 BL 1.0</t>
         </is>
       </c>
-      <c r="S2" s="431" t="n"/>
-      <c r="T2" s="429" t="inlineStr">
+      <c r="S2" s="430" t="n"/>
+      <c r="T2" s="428" t="inlineStr">
         <is>
           <t>VZ-DAI
 BL xxx</t>
         </is>
       </c>
-      <c r="U2" s="431" t="n"/>
-      <c r="V2" s="429" t="inlineStr">
+      <c r="U2" s="430" t="n"/>
+      <c r="V2" s="428" t="inlineStr">
         <is>
           <t>VZ_ES Full HRI
 BL xxx</t>
         </is>
       </c>
-      <c r="W2" s="431" t="n"/>
+      <c r="W2" s="430" t="n"/>
     </row>
     <row r="3" ht="30" customFormat="1" customHeight="1" s="61">
-      <c r="A3" s="437" t="n"/>
-      <c r="B3" s="437" t="n"/>
-      <c r="C3" s="437" t="n"/>
+      <c r="A3" s="436" t="n"/>
+      <c r="B3" s="436" t="n"/>
+      <c r="C3" s="436" t="n"/>
       <c r="D3" s="183" t="inlineStr">
         <is>
           <t>File/Codice</t>
@@ -14499,7 +14526,7 @@
           <t>Codice Config</t>
         </is>
       </c>
-      <c r="M3" s="438" t="inlineStr">
+      <c r="M3" s="437" t="inlineStr">
         <is>
           <t>File/Codice</t>
         </is>
@@ -14584,7 +14611,7 @@
       <c r="V4" s="320" t="n"/>
       <c r="W4" s="321" t="n"/>
     </row>
-    <row r="5" outlineLevel="1" s="479">
+    <row r="5" outlineLevel="1" s="478">
       <c r="A5" s="322" t="inlineStr">
         <is>
           <t>SW Config. Matrix</t>
@@ -14698,7 +14725,7 @@
       <c r="V6" s="223" t="n"/>
       <c r="W6" s="69" t="n"/>
     </row>
-    <row r="7" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="7" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A7" s="322" t="inlineStr">
         <is>
           <t>Drive Control</t>
@@ -14781,7 +14808,7 @@
       <c r="U7" s="64" t="n"/>
       <c r="W7" s="64" t="n"/>
     </row>
-    <row r="8" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="8" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A8" s="322" t="inlineStr">
         <is>
           <t>Conventional Train Control</t>
@@ -14864,7 +14891,7 @@
       <c r="U8" s="64" t="n"/>
       <c r="W8" s="64" t="n"/>
     </row>
-    <row r="9" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="9" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A9" s="322" t="inlineStr">
         <is>
           <t>Train Protection - ATP</t>
@@ -14947,7 +14974,7 @@
       <c r="U9" s="64" t="n"/>
       <c r="W9" s="64" t="n"/>
     </row>
-    <row r="10" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="10" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A10" s="322" t="inlineStr">
         <is>
           <t>TCMS Architecture</t>
@@ -15030,7 +15057,7 @@
       <c r="U10" s="64" t="n"/>
       <c r="W10" s="64" t="n"/>
     </row>
-    <row r="11" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="11" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A11" s="322" t="inlineStr">
         <is>
           <t>Propulsion and Auxiliary</t>
@@ -15104,7 +15131,7 @@
       <c r="U11" s="64" t="n"/>
       <c r="W11" s="64" t="n"/>
     </row>
-    <row r="12" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="12" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A12" s="322" t="inlineStr">
         <is>
           <t>Line Voltage</t>
@@ -15187,7 +15214,7 @@
       <c r="U12" s="64" t="n"/>
       <c r="W12" s="64" t="n"/>
     </row>
-    <row r="13" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="13" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A13" s="322" t="inlineStr">
         <is>
           <t>Auxiliary Electrical Supply</t>
@@ -15270,7 +15297,7 @@
       <c r="U13" s="64" t="n"/>
       <c r="W13" s="64" t="n"/>
     </row>
-    <row r="14" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="14" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A14" s="322" t="inlineStr">
         <is>
           <t>Battery</t>
@@ -15353,7 +15380,7 @@
       <c r="U14" s="64" t="n"/>
       <c r="W14" s="64" t="n"/>
     </row>
-    <row r="15" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="15" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A15" s="322" t="inlineStr">
         <is>
           <t>Air Supply</t>
@@ -15436,7 +15463,7 @@
       <c r="U15" s="64" t="n"/>
       <c r="W15" s="64" t="n"/>
     </row>
-    <row r="16" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="16" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A16" s="322" t="inlineStr">
         <is>
           <t>Brake Control</t>
@@ -15519,7 +15546,7 @@
       <c r="U16" s="64" t="n"/>
       <c r="W16" s="64" t="n"/>
     </row>
-    <row r="17" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="17" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A17" s="322" t="inlineStr">
         <is>
           <t>Bogie</t>
@@ -15602,7 +15629,7 @@
       <c r="U17" s="64" t="n"/>
       <c r="W17" s="64" t="n"/>
     </row>
-    <row r="18" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="18" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A18" s="322" t="inlineStr">
         <is>
           <t>Wash Wiper</t>
@@ -15685,7 +15712,7 @@
       <c r="U18" s="64" t="n"/>
       <c r="W18" s="64" t="n"/>
     </row>
-    <row r="19" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="19" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A19" s="322" t="inlineStr">
         <is>
           <t>Windscreen heater</t>
@@ -15768,7 +15795,7 @@
       <c r="U19" s="64" t="n"/>
       <c r="W19" s="64" t="n"/>
     </row>
-    <row r="20" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="20" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A20" s="322" t="inlineStr">
         <is>
           <t>Automatic Coupler</t>
@@ -15851,7 +15878,7 @@
       <c r="U20" s="64" t="n"/>
       <c r="W20" s="64" t="n"/>
     </row>
-    <row r="21" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="21" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A21" s="322" t="inlineStr">
         <is>
           <t>Horn</t>
@@ -15934,7 +15961,7 @@
       <c r="U21" s="64" t="n"/>
       <c r="W21" s="64" t="n"/>
     </row>
-    <row r="22" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="22" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A22" s="322" t="inlineStr">
         <is>
           <t>Exterior and Interior Doors</t>
@@ -16017,7 +16044,7 @@
       <c r="U22" s="64" t="n"/>
       <c r="W22" s="64" t="n"/>
     </row>
-    <row r="23" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="23" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A23" s="322" t="inlineStr">
         <is>
           <t>Cab HVAC</t>
@@ -16100,7 +16127,7 @@
       <c r="U23" s="64" t="n"/>
       <c r="W23" s="64" t="n"/>
     </row>
-    <row r="24" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="24" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A24" s="322" t="inlineStr">
         <is>
           <t>Saloon HVAC</t>
@@ -16183,7 +16210,7 @@
       <c r="U24" s="64" t="n"/>
       <c r="W24" s="64" t="n"/>
     </row>
-    <row r="25" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="25" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A25" s="322" t="inlineStr">
         <is>
           <t>Fire Protection and Extinguishing</t>
@@ -16266,7 +16293,7 @@
       <c r="U25" s="64" t="n"/>
       <c r="W25" s="64" t="n"/>
     </row>
-    <row r="26" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="26" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A26" s="322" t="inlineStr">
         <is>
           <t>Toilet</t>
@@ -16349,7 +16376,7 @@
       <c r="U26" s="64" t="n"/>
       <c r="W26" s="64" t="n"/>
     </row>
-    <row r="27" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="27" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A27" s="322" t="inlineStr">
         <is>
           <t>Catering</t>
@@ -16432,7 +16459,7 @@
       <c r="U27" s="64" t="n"/>
       <c r="W27" s="64" t="n"/>
     </row>
-    <row r="28" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="28" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A28" s="322" t="inlineStr">
         <is>
           <t>PIS CCTV</t>
@@ -16515,7 +16542,7 @@
       <c r="U28" s="64" t="n"/>
       <c r="W28" s="64" t="n"/>
     </row>
-    <row r="29" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="29" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A29" s="322" t="inlineStr">
         <is>
           <t>Exterior Lighting</t>
@@ -16598,7 +16625,7 @@
       <c r="U29" s="64" t="n"/>
       <c r="W29" s="64" t="n"/>
     </row>
-    <row r="30" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="30" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A30" s="322" t="inlineStr">
         <is>
           <t>Interior Lighting</t>
@@ -16681,7 +16708,7 @@
       <c r="U30" s="64" t="n"/>
       <c r="W30" s="64" t="n"/>
     </row>
-    <row r="31" outlineLevel="1" s="479">
+    <row r="31" outlineLevel="1" s="478">
       <c r="A31" s="322" t="inlineStr">
         <is>
           <t>Train Control Design System</t>
@@ -16735,7 +16762,7 @@
       <c r="U31" s="64" t="n"/>
       <c r="W31" s="64" t="n"/>
     </row>
-    <row r="32" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="32" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A32" s="322" t="inlineStr">
         <is>
           <t>Schematic diagram for French ATP MU</t>
@@ -16780,7 +16807,7 @@
       <c r="U32" s="64" t="n"/>
       <c r="W32" s="64" t="n"/>
     </row>
-    <row r="33" outlineLevel="1" s="479">
+    <row r="33" outlineLevel="1" s="478">
       <c r="A33" s="324" t="inlineStr">
         <is>
           <t>Energy Meter System</t>
@@ -16821,7 +16848,7 @@
       <c r="U33" s="64" t="n"/>
       <c r="W33" s="64" t="n"/>
     </row>
-    <row r="34" ht="30" customHeight="1" s="479">
+    <row r="34" ht="30" customHeight="1" s="478">
       <c r="A34" s="323" t="inlineStr">
         <is>
           <t>Functional Requirement Specification (FRS)</t>
@@ -16850,7 +16877,7 @@
       <c r="V34" s="223" t="n"/>
       <c r="W34" s="69" t="n"/>
     </row>
-    <row r="35" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="35" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A35" s="322" t="inlineStr">
         <is>
           <t>Functional Vehicle Requirement Specification</t>
@@ -16919,7 +16946,7 @@
       <c r="U35" s="64" t="n"/>
       <c r="W35" s="64" t="n"/>
     </row>
-    <row r="36" outlineLevel="1" ht="60" customHeight="1" s="479">
+    <row r="36" outlineLevel="1" ht="60" customHeight="1" s="478">
       <c r="A36" s="322" t="inlineStr">
         <is>
           <t>Drive Control</t>
@@ -17012,7 +17039,7 @@
       <c r="U36" s="64" t="n"/>
       <c r="W36" s="64" t="n"/>
     </row>
-    <row r="37" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="37" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A37" s="322" t="inlineStr">
         <is>
           <t>Conventional Train Control</t>
@@ -17111,7 +17138,7 @@
       <c r="U37" s="64" t="n"/>
       <c r="W37" s="64" t="n"/>
     </row>
-    <row r="38" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="38" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A38" s="322" t="inlineStr">
         <is>
           <t>Train Protection - ATP</t>
@@ -17212,7 +17239,7 @@
       <c r="U38" s="64" t="n"/>
       <c r="W38" s="64" t="n"/>
     </row>
-    <row r="39" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="39" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A39" s="322" t="inlineStr">
         <is>
           <t>Diagnostics</t>
@@ -17311,7 +17338,7 @@
       <c r="U39" s="64" t="n"/>
       <c r="W39" s="64" t="n"/>
     </row>
-    <row r="40" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="40" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A40" s="322" t="inlineStr">
         <is>
           <t>Visualisation - MMI</t>
@@ -17410,7 +17437,7 @@
       <c r="U40" s="64" t="n"/>
       <c r="W40" s="64" t="n"/>
     </row>
-    <row r="41" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="41" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A41" s="322" t="inlineStr">
         <is>
           <t>TCMS - Operational</t>
@@ -17509,7 +17536,7 @@
       <c r="U41" s="64" t="n"/>
       <c r="W41" s="64" t="n"/>
     </row>
-    <row r="42" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="42" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A42" s="322" t="inlineStr">
         <is>
           <t>Train to Wayside Communication (Teledia)</t>
@@ -17608,7 +17635,7 @@
       <c r="U42" s="64" t="n"/>
       <c r="W42" s="64" t="n"/>
     </row>
-    <row r="43" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="43" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A43" s="322" t="inlineStr">
         <is>
           <t>Line Voltage</t>
@@ -17703,7 +17730,7 @@
       <c r="U43" s="64" t="n"/>
       <c r="W43" s="64" t="n"/>
     </row>
-    <row r="44" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="44" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A44" s="322" t="inlineStr">
         <is>
           <t>Aux Electrical Supply</t>
@@ -17798,7 +17825,7 @@
       <c r="U44" s="64" t="n"/>
       <c r="W44" s="64" t="n"/>
     </row>
-    <row r="45" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="45" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A45" s="322" t="inlineStr">
         <is>
           <t>Battery</t>
@@ -17897,7 +17924,7 @@
       <c r="U45" s="64" t="n"/>
       <c r="W45" s="64" t="n"/>
     </row>
-    <row r="46" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="46" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A46" s="322" t="inlineStr">
         <is>
           <t>Air Supply</t>
@@ -17996,7 +18023,7 @@
       <c r="U46" s="64" t="n"/>
       <c r="W46" s="64" t="n"/>
     </row>
-    <row r="47" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="47" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A47" s="322" t="inlineStr">
         <is>
           <t>Brake Control</t>
@@ -18091,7 +18118,7 @@
       <c r="U47" s="64" t="n"/>
       <c r="W47" s="64" t="n"/>
     </row>
-    <row r="48" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="48" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A48" s="322" t="inlineStr">
         <is>
           <t>Bogies</t>
@@ -18190,7 +18217,7 @@
       <c r="U48" s="64" t="n"/>
       <c r="W48" s="64" t="n"/>
     </row>
-    <row r="49" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="49" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A49" s="322" t="inlineStr">
         <is>
           <t>Wash Wiper</t>
@@ -18289,7 +18316,7 @@
       <c r="U49" s="64" t="n"/>
       <c r="W49" s="64" t="n"/>
     </row>
-    <row r="50" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="50" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A50" s="322" t="inlineStr">
         <is>
           <t>Windscreen</t>
@@ -18388,7 +18415,7 @@
       <c r="U50" s="64" t="n"/>
       <c r="W50" s="64" t="n"/>
     </row>
-    <row r="51" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="51" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A51" s="322" t="inlineStr">
         <is>
           <t>Coupler</t>
@@ -18487,7 +18514,7 @@
       <c r="U51" s="64" t="n"/>
       <c r="W51" s="64" t="n"/>
     </row>
-    <row r="52" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="52" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A52" s="322" t="inlineStr">
         <is>
           <t>Horn</t>
@@ -18586,7 +18613,7 @@
       <c r="U52" s="64" t="n"/>
       <c r="W52" s="64" t="n"/>
     </row>
-    <row r="53" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="53" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A53" s="322" t="inlineStr">
         <is>
           <t>Wheelchair Lifts</t>
@@ -18685,7 +18712,7 @@
       <c r="U53" s="64" t="n"/>
       <c r="W53" s="64" t="n"/>
     </row>
-    <row r="54" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="54" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A54" s="322" t="inlineStr">
         <is>
           <t>Exterior Door and Step Systems</t>
@@ -18784,7 +18811,7 @@
       <c r="U54" s="64" t="n"/>
       <c r="W54" s="64" t="n"/>
     </row>
-    <row r="55" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="55" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A55" s="322" t="inlineStr">
         <is>
           <t>Interior Doors</t>
@@ -18883,7 +18910,7 @@
       <c r="U55" s="64" t="n"/>
       <c r="W55" s="64" t="n"/>
     </row>
-    <row r="56" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="56" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A56" s="322" t="inlineStr">
         <is>
           <t>Cab HVAC</t>
@@ -18982,7 +19009,7 @@
       <c r="U56" s="64" t="n"/>
       <c r="W56" s="64" t="n"/>
     </row>
-    <row r="57" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="57" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A57" s="322" t="inlineStr">
         <is>
           <t>Saloon HVAC</t>
@@ -19081,7 +19108,7 @@
       <c r="U57" s="64" t="n"/>
       <c r="W57" s="64" t="n"/>
     </row>
-    <row r="58" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="58" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A58" s="322" t="inlineStr">
         <is>
           <t>Fire Protection and Extinction</t>
@@ -19180,7 +19207,7 @@
       <c r="U58" s="64" t="n"/>
       <c r="W58" s="64" t="n"/>
     </row>
-    <row r="59" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="59" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A59" s="322" t="inlineStr">
         <is>
           <t>Toilet</t>
@@ -19279,7 +19306,7 @@
       <c r="U59" s="64" t="n"/>
       <c r="W59" s="64" t="n"/>
     </row>
-    <row r="60" outlineLevel="1" s="479">
+    <row r="60" outlineLevel="1" s="478">
       <c r="A60" s="322" t="inlineStr">
         <is>
           <t>Catering - Bistrot</t>
@@ -19378,7 +19405,7 @@
       <c r="U60" s="64" t="n"/>
       <c r="W60" s="64" t="n"/>
     </row>
-    <row r="61" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="61" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A61" s="322" t="inlineStr">
         <is>
           <t>PIES</t>
@@ -19477,7 +19504,7 @@
       <c r="U61" s="64" t="n"/>
       <c r="W61" s="64" t="n"/>
     </row>
-    <row r="62" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="62" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A62" s="322" t="inlineStr">
         <is>
           <t>PIS 2.0</t>
@@ -19563,7 +19590,7 @@
       <c r="U62" s="64" t="n"/>
       <c r="W62" s="64" t="n"/>
     </row>
-    <row r="63" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="63" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A63" s="322" t="inlineStr">
         <is>
           <t>CCTV</t>
@@ -19658,7 +19685,7 @@
       <c r="U63" s="64" t="n"/>
       <c r="W63" s="64" t="n"/>
     </row>
-    <row r="64" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="64" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A64" s="322" t="inlineStr">
         <is>
           <t>Exterior Lighting</t>
@@ -19753,7 +19780,7 @@
       <c r="U64" s="64" t="n"/>
       <c r="W64" s="64" t="n"/>
     </row>
-    <row r="65" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="65" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A65" s="322" t="inlineStr">
         <is>
           <t>Interior Lighting</t>
@@ -19848,7 +19875,7 @@
       <c r="U65" s="64" t="n"/>
       <c r="W65" s="64" t="n"/>
     </row>
-    <row r="66" outlineLevel="1" s="479">
+    <row r="66" outlineLevel="1" s="478">
       <c r="A66" s="322" t="inlineStr">
         <is>
           <t>Train Protection - ATP (France)</t>
@@ -19889,7 +19916,7 @@
       <c r="U66" s="64" t="n"/>
       <c r="W66" s="64" t="n"/>
     </row>
-    <row r="67" outlineLevel="1" s="479">
+    <row r="67" outlineLevel="1" s="478">
       <c r="A67" s="324" t="inlineStr">
         <is>
           <t>Energy Meter System</t>
@@ -19972,7 +19999,7 @@
       <c r="V68" s="223" t="n"/>
       <c r="W68" s="69" t="n"/>
     </row>
-    <row r="69" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="69" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A69" s="322" t="inlineStr">
         <is>
           <t>Functional schematics DM1</t>
@@ -20055,7 +20082,7 @@
       <c r="U69" s="64" t="n"/>
       <c r="W69" s="64" t="n"/>
     </row>
-    <row r="70" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="70" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A70" s="322" t="inlineStr">
         <is>
           <t>Functional schematics TT2</t>
@@ -20138,7 +20165,7 @@
       <c r="U70" s="64" t="n"/>
       <c r="W70" s="64" t="n"/>
     </row>
-    <row r="71" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="71" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A71" s="322" t="inlineStr">
         <is>
           <t>Functional schematics M3</t>
@@ -20221,7 +20248,7 @@
       <c r="U71" s="64" t="n"/>
       <c r="W71" s="64" t="n"/>
     </row>
-    <row r="72" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="72" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A72" s="322" t="inlineStr">
         <is>
           <t>Functional schematics T4</t>
@@ -20304,7 +20331,7 @@
       <c r="U72" s="64" t="n"/>
       <c r="W72" s="64" t="n"/>
     </row>
-    <row r="73" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="73" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A73" s="322" t="inlineStr">
         <is>
           <t>Functional schematics T5</t>
@@ -20387,7 +20414,7 @@
       <c r="U73" s="64" t="n"/>
       <c r="W73" s="64" t="n"/>
     </row>
-    <row r="74" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="74" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A74" s="322" t="inlineStr">
         <is>
           <t>Functional schematics M6</t>
@@ -20470,7 +20497,7 @@
       <c r="U74" s="64" t="n"/>
       <c r="W74" s="64" t="n"/>
     </row>
-    <row r="75" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="75" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A75" s="322" t="inlineStr">
         <is>
           <t>Functional schematics TT7</t>
@@ -20553,7 +20580,7 @@
       <c r="U75" s="64" t="n"/>
       <c r="W75" s="64" t="n"/>
     </row>
-    <row r="76" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="76" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A76" s="322" t="inlineStr">
         <is>
           <t>Functional schematics DM8</t>
@@ -20636,7 +20663,7 @@
       <c r="U76" s="64" t="n"/>
       <c r="W76" s="64" t="n"/>
     </row>
-    <row r="77" ht="30" customHeight="1" s="479">
+    <row r="77" ht="30" customHeight="1" s="478">
       <c r="A77" s="323" t="inlineStr">
         <is>
           <t>Wiring table</t>
@@ -20681,7 +20708,7 @@
       <c r="V77" s="223" t="n"/>
       <c r="W77" s="69" t="n"/>
     </row>
-    <row r="78" outlineLevel="1" s="479">
+    <row r="78" outlineLevel="1" s="478">
       <c r="A78" s="322" t="inlineStr">
         <is>
           <t>Wiring table DM1</t>
@@ -20746,7 +20773,7 @@
       <c r="U78" s="64" t="n"/>
       <c r="W78" s="64" t="n"/>
     </row>
-    <row r="79" outlineLevel="1" s="479">
+    <row r="79" outlineLevel="1" s="478">
       <c r="A79" s="322" t="inlineStr">
         <is>
           <t>Wiring table TT2</t>
@@ -20811,7 +20838,7 @@
       <c r="U79" s="64" t="n"/>
       <c r="W79" s="64" t="n"/>
     </row>
-    <row r="80" outlineLevel="1" s="479">
+    <row r="80" outlineLevel="1" s="478">
       <c r="A80" s="322" t="inlineStr">
         <is>
           <t>Wiring table M3</t>
@@ -20876,7 +20903,7 @@
       <c r="U80" s="64" t="n"/>
       <c r="W80" s="64" t="n"/>
     </row>
-    <row r="81" outlineLevel="1" s="479">
+    <row r="81" outlineLevel="1" s="478">
       <c r="A81" s="322" t="inlineStr">
         <is>
           <t>Wiring table T4</t>
@@ -20941,7 +20968,7 @@
       <c r="U81" s="64" t="n"/>
       <c r="W81" s="64" t="n"/>
     </row>
-    <row r="82" outlineLevel="1" s="479">
+    <row r="82" outlineLevel="1" s="478">
       <c r="A82" s="322" t="inlineStr">
         <is>
           <t>Wiring table T5</t>
@@ -21006,7 +21033,7 @@
       <c r="U82" s="64" t="n"/>
       <c r="W82" s="64" t="n"/>
     </row>
-    <row r="83" outlineLevel="1" s="479">
+    <row r="83" outlineLevel="1" s="478">
       <c r="A83" s="322" t="inlineStr">
         <is>
           <t>Wiring table M6</t>
@@ -21071,7 +21098,7 @@
       <c r="U83" s="64" t="n"/>
       <c r="W83" s="64" t="n"/>
     </row>
-    <row r="84" outlineLevel="1" s="479">
+    <row r="84" outlineLevel="1" s="478">
       <c r="A84" s="322" t="inlineStr">
         <is>
           <t>Wiring table TT7</t>
@@ -21136,7 +21163,7 @@
       <c r="U84" s="64" t="n"/>
       <c r="W84" s="64" t="n"/>
     </row>
-    <row r="85" outlineLevel="1" s="479">
+    <row r="85" outlineLevel="1" s="478">
       <c r="A85" s="322" t="inlineStr">
         <is>
           <t>Wiring table DM8</t>
@@ -21230,7 +21257,7 @@
       <c r="V86" s="223" t="n"/>
       <c r="W86" s="69" t="n"/>
     </row>
-    <row r="87" outlineLevel="1" s="479">
+    <row r="87" outlineLevel="1" s="478">
       <c r="A87" s="322" t="inlineStr">
         <is>
           <t>Electric Part List DM1</t>
@@ -21295,7 +21322,7 @@
       <c r="U87" s="64" t="n"/>
       <c r="W87" s="64" t="n"/>
     </row>
-    <row r="88" outlineLevel="1" s="479">
+    <row r="88" outlineLevel="1" s="478">
       <c r="A88" s="322" t="inlineStr">
         <is>
           <t>Electric Part List TT2</t>
@@ -21360,7 +21387,7 @@
       <c r="U88" s="64" t="n"/>
       <c r="W88" s="64" t="n"/>
     </row>
-    <row r="89" outlineLevel="1" s="479">
+    <row r="89" outlineLevel="1" s="478">
       <c r="A89" s="322" t="inlineStr">
         <is>
           <t>Electric Part List M3</t>
@@ -21425,7 +21452,7 @@
       <c r="U89" s="64" t="n"/>
       <c r="W89" s="64" t="n"/>
     </row>
-    <row r="90" outlineLevel="1" s="479">
+    <row r="90" outlineLevel="1" s="478">
       <c r="A90" s="322" t="inlineStr">
         <is>
           <t>Electric Part List T4</t>
@@ -21490,7 +21517,7 @@
       <c r="U90" s="64" t="n"/>
       <c r="W90" s="64" t="n"/>
     </row>
-    <row r="91" outlineLevel="1" s="479">
+    <row r="91" outlineLevel="1" s="478">
       <c r="A91" s="322" t="inlineStr">
         <is>
           <t>Electric Part List T5</t>
@@ -21555,7 +21582,7 @@
       <c r="U91" s="64" t="n"/>
       <c r="W91" s="64" t="n"/>
     </row>
-    <row r="92" outlineLevel="1" s="479">
+    <row r="92" outlineLevel="1" s="478">
       <c r="A92" s="322" t="inlineStr">
         <is>
           <t>Electric Part List M6</t>
@@ -21620,7 +21647,7 @@
       <c r="U92" s="64" t="n"/>
       <c r="W92" s="64" t="n"/>
     </row>
-    <row r="93" outlineLevel="1" s="479">
+    <row r="93" outlineLevel="1" s="478">
       <c r="A93" s="322" t="inlineStr">
         <is>
           <t>Electric Part List TT7</t>
@@ -21685,7 +21712,7 @@
       <c r="U93" s="64" t="n"/>
       <c r="W93" s="64" t="n"/>
     </row>
-    <row r="94" outlineLevel="1" s="479">
+    <row r="94" outlineLevel="1" s="478">
       <c r="A94" s="322" t="inlineStr">
         <is>
           <t>Electric Part List DM8</t>
@@ -21783,7 +21810,7 @@
       <c r="V95" s="223" t="n"/>
       <c r="W95" s="69" t="n"/>
     </row>
-    <row r="96" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="96" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A96" s="322" t="inlineStr">
         <is>
           <t>ICD Sistema TCMS</t>
@@ -21843,7 +21870,7 @@
       <c r="U96" s="64" t="n"/>
       <c r="W96" s="64" t="n"/>
     </row>
-    <row r="97" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="97" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A97" s="322" t="inlineStr">
         <is>
           <t>ICD Sistema TCMS - Annex</t>
@@ -21894,7 +21921,7 @@
       <c r="U97" s="64" t="n"/>
       <c r="W97" s="64" t="n"/>
     </row>
-    <row r="98" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="98" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A98" s="322" t="inlineStr">
         <is>
           <t>ICD GTW IPTCOM-TRDP</t>
@@ -21949,7 +21976,7 @@
       <c r="U98" s="64" t="n"/>
       <c r="W98" s="64" t="n"/>
     </row>
-    <row r="99" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="99" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A99" s="322" t="inlineStr">
         <is>
           <t>ICD GTW IPTCOM-TRDP - Annex</t>
@@ -22000,7 +22027,7 @@
       <c r="U99" s="64" t="n"/>
       <c r="W99" s="64" t="n"/>
     </row>
-    <row r="100" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="100" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A100" s="322" t="inlineStr">
         <is>
           <t>ICD Sistema Propulsion TCU</t>
@@ -22060,7 +22087,7 @@
       <c r="U100" s="64" t="n"/>
       <c r="W100" s="64" t="n"/>
     </row>
-    <row r="101" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="101" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A101" s="322" t="inlineStr">
         <is>
           <t>ICD Sistema Propulsion TCU - Annex</t>
@@ -22111,7 +22138,7 @@
       <c r="U101" s="64" t="n"/>
       <c r="W101" s="64" t="n"/>
     </row>
-    <row r="102" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="102" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A102" s="322" t="inlineStr">
         <is>
           <t>ICD Pantografo</t>
@@ -22171,7 +22198,7 @@
       <c r="U102" s="64" t="n"/>
       <c r="W102" s="64" t="n"/>
     </row>
-    <row r="103" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="103" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A103" s="322" t="inlineStr">
         <is>
           <t>ICD Pantografo - Annex</t>
@@ -22222,7 +22249,7 @@
       <c r="U103" s="64" t="n"/>
       <c r="W103" s="64" t="n"/>
     </row>
-    <row r="104" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="104" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A104" s="322" t="inlineStr">
         <is>
           <t>ICD Sistema BCU</t>
@@ -22282,7 +22309,7 @@
       <c r="U104" s="64" t="n"/>
       <c r="W104" s="64" t="n"/>
     </row>
-    <row r="105" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="105" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A105" s="322" t="inlineStr">
         <is>
           <t>ICD Sistema BCU - Annex</t>
@@ -22337,7 +22364,7 @@
       <c r="U105" s="64" t="n"/>
       <c r="W105" s="64" t="n"/>
     </row>
-    <row r="106" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="106" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A106" s="322" t="inlineStr">
         <is>
           <t>ICD Sistema Segnalamento</t>
@@ -22392,7 +22419,7 @@
       <c r="U106" s="64" t="n"/>
       <c r="W106" s="64" t="n"/>
     </row>
-    <row r="107" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="107" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A107" s="322" t="inlineStr">
         <is>
           <t>ICD Sistema Segnalamento - Annex</t>
@@ -22443,7 +22470,7 @@
       <c r="U107" s="64" t="n"/>
       <c r="W107" s="64" t="n"/>
     </row>
-    <row r="108" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="108" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A108" s="322" t="inlineStr">
         <is>
           <t>ICD Sistema PIS</t>
@@ -22503,7 +22530,7 @@
       <c r="U108" s="64" t="n"/>
       <c r="W108" s="64" t="n"/>
     </row>
-    <row r="109" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="109" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A109" s="322" t="inlineStr">
         <is>
           <t>ICD Sistema PIS - Annex</t>
@@ -22554,7 +22581,7 @@
       <c r="U109" s="64" t="n"/>
       <c r="W109" s="64" t="n"/>
     </row>
-    <row r="110" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="110" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A110" s="322" t="inlineStr">
         <is>
           <t>ICD Sistema Toilette</t>
@@ -22614,7 +22641,7 @@
       <c r="U110" s="64" t="n"/>
       <c r="W110" s="64" t="n"/>
     </row>
-    <row r="111" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="111" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A111" s="322" t="inlineStr">
         <is>
           <t>ICD Sistema Toilette - Annex</t>
@@ -22665,7 +22692,7 @@
       <c r="U111" s="64" t="n"/>
       <c r="W111" s="64" t="n"/>
     </row>
-    <row r="112" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="112" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A112" s="322" t="inlineStr">
         <is>
           <t>ICD Sistema Anticendio</t>
@@ -22725,7 +22752,7 @@
       <c r="U112" s="64" t="n"/>
       <c r="W112" s="64" t="n"/>
     </row>
-    <row r="113" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="113" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A113" s="322" t="inlineStr">
         <is>
           <t>ICD Sistema Anticendio - Annex</t>
@@ -22776,7 +22803,7 @@
       <c r="U113" s="64" t="n"/>
       <c r="W113" s="64" t="n"/>
     </row>
-    <row r="114" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="114" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A114" s="322" t="inlineStr">
         <is>
           <t>ICD Sistema Porte</t>
@@ -22836,7 +22863,7 @@
       <c r="U114" s="64" t="n"/>
       <c r="W114" s="64" t="n"/>
     </row>
-    <row r="115" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="115" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A115" s="322" t="inlineStr">
         <is>
           <t>ICD Sistema Porte - Annex</t>
@@ -22887,7 +22914,7 @@
       <c r="U115" s="64" t="n"/>
       <c r="W115" s="64" t="n"/>
     </row>
-    <row r="116" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="116" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A116" s="322" t="inlineStr">
         <is>
           <t>ICD Sistema HVSP</t>
@@ -22942,7 +22969,7 @@
       <c r="U116" s="64" t="n"/>
       <c r="W116" s="64" t="n"/>
     </row>
-    <row r="117" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="117" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A117" s="322" t="inlineStr">
         <is>
           <t>ICD Sistema HVSP  - Annex</t>
@@ -22993,7 +23020,7 @@
       <c r="U117" s="64" t="n"/>
       <c r="W117" s="64" t="n"/>
     </row>
-    <row r="118" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="118" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A118" s="322" t="inlineStr">
         <is>
           <t>ICD Sistema Carica Batterie</t>
@@ -23053,7 +23080,7 @@
       <c r="U118" s="64" t="n"/>
       <c r="W118" s="64" t="n"/>
     </row>
-    <row r="119" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="119" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A119" s="322" t="inlineStr">
         <is>
           <t>ICD Sistema Carica Batterie - Annex</t>
@@ -23104,7 +23131,7 @@
       <c r="U119" s="64" t="n"/>
       <c r="W119" s="64" t="n"/>
     </row>
-    <row r="120" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="120" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A120" s="322" t="inlineStr">
         <is>
           <t>ICD HVAC</t>
@@ -23164,7 +23191,7 @@
       <c r="U120" s="64" t="n"/>
       <c r="W120" s="64" t="n"/>
     </row>
-    <row r="121" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="121" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A121" s="322" t="inlineStr">
         <is>
           <t>ICD HVAC - Annex</t>
@@ -23215,7 +23242,7 @@
       <c r="U121" s="64" t="n"/>
       <c r="W121" s="64" t="n"/>
     </row>
-    <row r="122" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="122" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A122" s="322" t="inlineStr">
         <is>
           <t>ICD Energy Measurement System</t>
@@ -23270,7 +23297,7 @@
       <c r="U122" s="64" t="n"/>
       <c r="W122" s="64" t="n"/>
     </row>
-    <row r="123" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="123" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A123" s="322" t="inlineStr">
         <is>
           <t>ICD Energy Measurement System - Annex</t>
@@ -23350,7 +23377,7 @@
       <c r="V124" s="223" t="n"/>
       <c r="W124" s="69" t="n"/>
     </row>
-    <row r="125" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="125" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A125" s="322" t="inlineStr">
         <is>
           <t>Train Performances</t>
@@ -23396,7 +23423,7 @@
       <c r="U125" s="64" t="n"/>
       <c r="W125" s="64" t="n"/>
     </row>
-    <row r="126" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="126" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A126" s="322" t="inlineStr">
         <is>
           <t>Train System Architecture</t>
@@ -23442,7 +23469,7 @@
       <c r="U126" s="64" t="n"/>
       <c r="W126" s="64" t="n"/>
     </row>
-    <row r="127" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="127" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A127" s="322" t="inlineStr">
         <is>
           <t>Train Running Simulations</t>
@@ -23488,7 +23515,7 @@
       <c r="U127" s="64" t="n"/>
       <c r="W127" s="64" t="n"/>
     </row>
-    <row r="128" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="128" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A128" s="322" t="inlineStr">
         <is>
           <t>SyFD Propulsion System</t>
@@ -23534,7 +23561,7 @@
       <c r="U128" s="64" t="n"/>
       <c r="W128" s="64" t="n"/>
     </row>
-    <row r="129" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="129" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A129" s="322" t="inlineStr">
         <is>
           <t>SyFD Train Control and Management System</t>
@@ -23580,7 +23607,7 @@
       <c r="U129" s="64" t="n"/>
       <c r="W129" s="64" t="n"/>
     </row>
-    <row r="130" outlineLevel="1" ht="30" customHeight="1" s="479">
+    <row r="130" outlineLevel="1" ht="30" customHeight="1" s="478">
       <c r="A130" s="327" t="inlineStr">
         <is>
           <t>SyFD Ethernet Train Communication Network</t>
@@ -23689,79 +23716,79 @@
     <col width="6.5703125" customWidth="1" style="10" min="17" max="17"/>
     <col width="6.5703125" bestFit="1" customWidth="1" style="10" min="18" max="18"/>
     <col width="6.5703125" customWidth="1" style="10" min="19" max="19"/>
-    <col width="8.7109375" customWidth="1" style="59" min="20" max="28"/>
-    <col width="8.7109375" customWidth="1" style="59" min="29" max="16384"/>
+    <col width="8.7109375" customWidth="1" style="59" min="20" max="29"/>
+    <col width="8.7109375" customWidth="1" style="59" min="30" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="26.45" customFormat="1" customHeight="1" s="61">
-      <c r="A1" s="435" t="inlineStr">
+      <c r="A1" s="434" t="inlineStr">
         <is>
           <t>DOC DESCRIPTION</t>
         </is>
       </c>
-      <c r="B1" s="444" t="inlineStr">
+      <c r="B1" s="443" t="inlineStr">
         <is>
           <t>DOC ID</t>
         </is>
       </c>
-      <c r="C1" s="435" t="inlineStr">
+      <c r="C1" s="434" t="inlineStr">
         <is>
           <t>DOC EXT</t>
         </is>
       </c>
-      <c r="D1" s="443" t="inlineStr">
+      <c r="D1" s="442" t="inlineStr">
         <is>
           <t>VZI_Base</t>
         </is>
       </c>
-      <c r="E1" s="434" t="n"/>
-      <c r="F1" s="432" t="inlineStr">
+      <c r="E1" s="433" t="n"/>
+      <c r="F1" s="431" t="inlineStr">
         <is>
           <t>VZI_New14</t>
         </is>
       </c>
-      <c r="G1" s="431" t="n"/>
-      <c r="H1" s="443" t="inlineStr">
+      <c r="G1" s="430" t="n"/>
+      <c r="H1" s="442" t="inlineStr">
         <is>
           <t>VZ_FR</t>
         </is>
       </c>
-      <c r="I1" s="434" t="n"/>
-      <c r="J1" s="432" t="inlineStr">
+      <c r="I1" s="433" t="n"/>
+      <c r="J1" s="431" t="inlineStr">
         <is>
           <t>VZ_ES</t>
         </is>
       </c>
-      <c r="K1" s="431" t="n"/>
-      <c r="L1" s="443" t="inlineStr">
+      <c r="K1" s="430" t="n"/>
+      <c r="L1" s="442" t="inlineStr">
         <is>
           <t>VZI-6_R1</t>
         </is>
       </c>
-      <c r="M1" s="434" t="n"/>
-      <c r="N1" s="432" t="inlineStr">
+      <c r="M1" s="433" t="n"/>
+      <c r="N1" s="431" t="inlineStr">
         <is>
           <t>VZI-4_R1</t>
         </is>
       </c>
-      <c r="O1" s="431" t="n"/>
-      <c r="P1" s="443" t="inlineStr">
+      <c r="O1" s="430" t="n"/>
+      <c r="P1" s="442" t="inlineStr">
         <is>
           <t>VZ_DAI</t>
         </is>
       </c>
-      <c r="Q1" s="434" t="n"/>
-      <c r="R1" s="432" t="inlineStr">
+      <c r="Q1" s="433" t="n"/>
+      <c r="R1" s="431" t="inlineStr">
         <is>
           <t>VZ_Esxx</t>
         </is>
       </c>
-      <c r="S1" s="431" t="n"/>
+      <c r="S1" s="430" t="n"/>
     </row>
     <row r="2" ht="26.45" customFormat="1" customHeight="1" s="61">
-      <c r="A2" s="437" t="n"/>
-      <c r="B2" s="445" t="n"/>
-      <c r="C2" s="437" t="n"/>
+      <c r="A2" s="436" t="n"/>
+      <c r="B2" s="444" t="n"/>
+      <c r="C2" s="436" t="n"/>
       <c r="D2" s="183" t="inlineStr">
         <is>
           <t>File/Codice</t>
@@ -23772,7 +23799,7 @@
           <t>Rev</t>
         </is>
       </c>
-      <c r="F2" s="438" t="inlineStr">
+      <c r="F2" s="437" t="inlineStr">
         <is>
           <t>File/Codice</t>
         </is>
@@ -23792,7 +23819,7 @@
           <t>Rev</t>
         </is>
       </c>
-      <c r="J2" s="438" t="inlineStr">
+      <c r="J2" s="437" t="inlineStr">
         <is>
           <t>File/Codice</t>
         </is>
@@ -23802,12 +23829,12 @@
           <t>Rev</t>
         </is>
       </c>
-      <c r="L2" s="442" t="inlineStr">
+      <c r="L2" s="441" t="inlineStr">
         <is>
           <t>Codice</t>
         </is>
       </c>
-      <c r="M2" s="442" t="inlineStr">
+      <c r="M2" s="441" t="inlineStr">
         <is>
           <t>Rev</t>
         </is>
@@ -23832,7 +23859,7 @@
           <t>Rev</t>
         </is>
       </c>
-      <c r="R2" s="438" t="inlineStr">
+      <c r="R2" s="437" t="inlineStr">
         <is>
           <t>Codice</t>
         </is>
@@ -23868,7 +23895,7 @@
       <c r="R3" s="187" t="n"/>
       <c r="S3" s="188" t="n"/>
     </row>
-    <row r="4" ht="30" customHeight="1" s="479">
+    <row r="4" ht="30" customHeight="1" s="478">
       <c r="A4" s="62" t="inlineStr">
         <is>
           <t>Architettura di Controllo Treno ed Interfacce di Comando</t>
@@ -24342,7 +24369,7 @@
       <c r="R17" s="63" t="n"/>
       <c r="S17" s="64" t="n"/>
     </row>
-    <row r="18" ht="30" customHeight="1" s="479">
+    <row r="18" ht="30" customHeight="1" s="478">
       <c r="A18" s="62" t="inlineStr">
         <is>
           <t>Auxiliary converter module, CM-C S 15/10 WA V02</t>
@@ -24377,7 +24404,7 @@
       <c r="R18" s="63" t="n"/>
       <c r="S18" s="64" t="n"/>
     </row>
-    <row r="19" ht="30" customHeight="1" s="479">
+    <row r="19" ht="30" customHeight="1" s="478">
       <c r="A19" s="62" t="inlineStr">
         <is>
           <t>Chopper converter module, CM-C L 30/07 WC V01</t>
@@ -24412,7 +24439,7 @@
       <c r="R19" s="63" t="n"/>
       <c r="S19" s="64" t="n"/>
     </row>
-    <row r="20" ht="30" customHeight="1" s="479">
+    <row r="20" ht="30" customHeight="1" s="478">
       <c r="A20" s="62" t="inlineStr">
         <is>
           <t>Line converter module, CM-C M 15/15 WL V06</t>
@@ -24447,7 +24474,7 @@
       <c r="R20" s="63" t="n"/>
       <c r="S20" s="64" t="n"/>
     </row>
-    <row r="21" ht="30" customHeight="1" s="479">
+    <row r="21" ht="30" customHeight="1" s="478">
       <c r="A21" s="62" t="inlineStr">
         <is>
           <t>Motor converter module, CM-C S 15/10 WM V02</t>
@@ -24623,7 +24650,7 @@
       <c r="R26" s="63" t="n"/>
       <c r="S26" s="64" t="n"/>
     </row>
-    <row r="27" ht="30" customHeight="1" s="479">
+    <row r="27" ht="30" customHeight="1" s="478">
       <c r="A27" s="62" t="inlineStr">
         <is>
           <t>EPVE63 Test Intervento protezioni azionamento</t>
@@ -24661,7 +24688,7 @@
       <c r="S27" s="64" t="n"/>
       <c r="T27" s="212" t="n"/>
     </row>
-    <row r="28" ht="30" customHeight="1" s="479">
+    <row r="28" ht="30" customHeight="1" s="478">
       <c r="A28" s="62" t="inlineStr">
         <is>
           <t>EPVE63 Report Intervento protezioni
@@ -24814,7 +24841,7 @@
       <c r="S31" s="64" t="n"/>
       <c r="T31" s="212" t="n"/>
     </row>
-    <row r="32" ht="30" customHeight="1" s="479">
+    <row r="32" ht="30" customHeight="1" s="478">
       <c r="A32" s="62" t="inlineStr">
         <is>
           <t>Test Intervento protezioni azionamento</t>
@@ -25051,93 +25078,93 @@
     <col width="26.42578125" bestFit="1" customWidth="1" style="9" min="27" max="27"/>
     <col width="4.42578125" bestFit="1" customWidth="1" style="9" min="28" max="28"/>
     <col width="8.85546875" bestFit="1" customWidth="1" style="290" min="29" max="29"/>
-    <col width="8.7109375" customWidth="1" style="8" min="30" max="32"/>
-    <col width="8.7109375" customWidth="1" style="8" min="33" max="16384"/>
+    <col width="8.7109375" customWidth="1" style="8" min="30" max="33"/>
+    <col width="8.7109375" customWidth="1" style="8" min="34" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="29.45" customHeight="1" s="479">
-      <c r="A1" s="435" t="inlineStr">
+    <row r="1" ht="29.45" customHeight="1" s="478">
+      <c r="A1" s="434" t="inlineStr">
         <is>
           <t>DOC DESCRIPTION</t>
         </is>
       </c>
-      <c r="B1" s="444" t="inlineStr">
+      <c r="B1" s="443" t="inlineStr">
         <is>
           <t>DOC ID</t>
         </is>
       </c>
-      <c r="C1" s="444" t="inlineStr">
+      <c r="C1" s="443" t="inlineStr">
         <is>
           <t>DOC EXT</t>
         </is>
       </c>
-      <c r="D1" s="450" t="inlineStr">
+      <c r="D1" s="449" t="inlineStr">
         <is>
           <t>TIPO</t>
         </is>
       </c>
-      <c r="E1" s="450" t="inlineStr">
+      <c r="E1" s="449" t="inlineStr">
         <is>
           <t>VOLUME
 SUBVOLUME
 _TOMO</t>
         </is>
       </c>
-      <c r="F1" s="446" t="inlineStr">
+      <c r="F1" s="445" t="inlineStr">
         <is>
           <t>VZI_Base</t>
         </is>
       </c>
-      <c r="G1" s="447" t="n"/>
-      <c r="H1" s="447" t="n"/>
-      <c r="I1" s="448" t="n"/>
-      <c r="J1" s="446" t="inlineStr">
+      <c r="G1" s="446" t="n"/>
+      <c r="H1" s="446" t="n"/>
+      <c r="I1" s="447" t="n"/>
+      <c r="J1" s="445" t="inlineStr">
         <is>
           <t>VZI_New14</t>
         </is>
       </c>
-      <c r="K1" s="447" t="n"/>
-      <c r="L1" s="447" t="n"/>
-      <c r="M1" s="448" t="n"/>
-      <c r="N1" s="449" t="inlineStr">
+      <c r="K1" s="446" t="n"/>
+      <c r="L1" s="446" t="n"/>
+      <c r="M1" s="447" t="n"/>
+      <c r="N1" s="448" t="inlineStr">
         <is>
           <t>VZ_FR</t>
         </is>
       </c>
-      <c r="O1" s="447" t="n"/>
-      <c r="P1" s="447" t="n"/>
-      <c r="Q1" s="448" t="n"/>
-      <c r="R1" s="449" t="inlineStr">
+      <c r="O1" s="446" t="n"/>
+      <c r="P1" s="446" t="n"/>
+      <c r="Q1" s="447" t="n"/>
+      <c r="R1" s="448" t="inlineStr">
         <is>
           <t>VZ-ES</t>
         </is>
       </c>
-      <c r="S1" s="447" t="n"/>
-      <c r="T1" s="447" t="n"/>
-      <c r="U1" s="448" t="n"/>
-      <c r="V1" s="452" t="inlineStr">
+      <c r="S1" s="446" t="n"/>
+      <c r="T1" s="446" t="n"/>
+      <c r="U1" s="447" t="n"/>
+      <c r="V1" s="451" t="inlineStr">
         <is>
           <t>VZI-6_R1</t>
         </is>
       </c>
-      <c r="W1" s="447" t="n"/>
-      <c r="X1" s="447" t="n"/>
-      <c r="Y1" s="448" t="n"/>
-      <c r="Z1" s="452" t="inlineStr">
+      <c r="W1" s="446" t="n"/>
+      <c r="X1" s="446" t="n"/>
+      <c r="Y1" s="447" t="n"/>
+      <c r="Z1" s="451" t="inlineStr">
         <is>
           <t>VZI-4_R1</t>
         </is>
       </c>
-      <c r="AA1" s="447" t="n"/>
-      <c r="AB1" s="447" t="n"/>
-      <c r="AC1" s="448" t="n"/>
-    </row>
-    <row r="2" ht="29.45" customHeight="1" s="479" thickBot="1">
-      <c r="A2" s="437" t="n"/>
-      <c r="B2" s="445" t="n"/>
-      <c r="C2" s="445" t="n"/>
-      <c r="D2" s="451" t="n"/>
-      <c r="E2" s="451" t="n"/>
+      <c r="AA1" s="446" t="n"/>
+      <c r="AB1" s="446" t="n"/>
+      <c r="AC1" s="447" t="n"/>
+    </row>
+    <row r="2" ht="29.45" customHeight="1" s="478" thickBot="1">
+      <c r="A2" s="436" t="n"/>
+      <c r="B2" s="444" t="n"/>
+      <c r="C2" s="444" t="n"/>
+      <c r="D2" s="450" t="n"/>
+      <c r="E2" s="450" t="n"/>
       <c r="F2" s="172" t="inlineStr">
         <is>
           <t>NOME FILE</t>
@@ -33558,79 +33585,79 @@
     <col width="6.5703125" customWidth="1" style="10" min="17" max="17"/>
     <col width="6.5703125" bestFit="1" customWidth="1" style="10" min="18" max="18"/>
     <col width="6.5703125" customWidth="1" style="10" min="19" max="19"/>
-    <col width="8.7109375" customWidth="1" style="59" min="20" max="28"/>
-    <col width="8.7109375" customWidth="1" style="59" min="29" max="16384"/>
+    <col width="8.7109375" customWidth="1" style="59" min="20" max="29"/>
+    <col width="8.7109375" customWidth="1" style="59" min="30" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="21.6" customFormat="1" customHeight="1" s="61">
-      <c r="A1" s="435" t="inlineStr">
+      <c r="A1" s="434" t="inlineStr">
         <is>
           <t>DOC DESCRIPTION</t>
         </is>
       </c>
-      <c r="B1" s="444" t="inlineStr">
+      <c r="B1" s="443" t="inlineStr">
         <is>
           <t>DOC ID</t>
         </is>
       </c>
-      <c r="C1" s="444" t="inlineStr">
+      <c r="C1" s="443" t="inlineStr">
         <is>
           <t>DOC EXT</t>
         </is>
       </c>
-      <c r="D1" s="443" t="inlineStr">
+      <c r="D1" s="442" t="inlineStr">
         <is>
           <t>VZI_Base</t>
         </is>
       </c>
-      <c r="E1" s="434" t="n"/>
-      <c r="F1" s="432" t="inlineStr">
+      <c r="E1" s="433" t="n"/>
+      <c r="F1" s="431" t="inlineStr">
         <is>
           <t>VZI_New14</t>
         </is>
       </c>
-      <c r="G1" s="431" t="n"/>
-      <c r="H1" s="443" t="inlineStr">
+      <c r="G1" s="430" t="n"/>
+      <c r="H1" s="442" t="inlineStr">
         <is>
           <t>VZ_FR</t>
         </is>
       </c>
-      <c r="I1" s="434" t="n"/>
-      <c r="J1" s="432" t="inlineStr">
+      <c r="I1" s="433" t="n"/>
+      <c r="J1" s="431" t="inlineStr">
         <is>
           <t>VZ_ES</t>
         </is>
       </c>
-      <c r="K1" s="431" t="n"/>
-      <c r="L1" s="443" t="inlineStr">
+      <c r="K1" s="430" t="n"/>
+      <c r="L1" s="442" t="inlineStr">
         <is>
           <t>VZI-6_R1</t>
         </is>
       </c>
-      <c r="M1" s="434" t="n"/>
-      <c r="N1" s="432" t="inlineStr">
+      <c r="M1" s="433" t="n"/>
+      <c r="N1" s="431" t="inlineStr">
         <is>
           <t>VZI-4_R1</t>
         </is>
       </c>
-      <c r="O1" s="431" t="n"/>
-      <c r="P1" s="443" t="inlineStr">
+      <c r="O1" s="430" t="n"/>
+      <c r="P1" s="442" t="inlineStr">
         <is>
           <t>VZ_DAI</t>
         </is>
       </c>
-      <c r="Q1" s="434" t="n"/>
-      <c r="R1" s="432" t="inlineStr">
+      <c r="Q1" s="433" t="n"/>
+      <c r="R1" s="431" t="inlineStr">
         <is>
           <t>VZ_Esxx</t>
         </is>
       </c>
-      <c r="S1" s="431" t="n"/>
+      <c r="S1" s="430" t="n"/>
     </row>
     <row r="2" ht="21.6" customFormat="1" customHeight="1" s="61">
-      <c r="A2" s="437" t="n"/>
-      <c r="B2" s="445" t="n"/>
-      <c r="C2" s="445" t="n"/>
+      <c r="A2" s="436" t="n"/>
+      <c r="B2" s="444" t="n"/>
+      <c r="C2" s="444" t="n"/>
       <c r="D2" s="183" t="inlineStr">
         <is>
           <t>File/Codice</t>
@@ -33641,7 +33668,7 @@
           <t>Rev</t>
         </is>
       </c>
-      <c r="F2" s="438" t="inlineStr">
+      <c r="F2" s="437" t="inlineStr">
         <is>
           <t>File/Codice</t>
         </is>
@@ -33661,7 +33688,7 @@
           <t>Rev</t>
         </is>
       </c>
-      <c r="J2" s="438" t="inlineStr">
+      <c r="J2" s="437" t="inlineStr">
         <is>
           <t>File/Codice</t>
         </is>
@@ -33671,12 +33698,12 @@
           <t>Rev</t>
         </is>
       </c>
-      <c r="L2" s="442" t="inlineStr">
+      <c r="L2" s="441" t="inlineStr">
         <is>
           <t>Codice</t>
         </is>
       </c>
-      <c r="M2" s="442" t="inlineStr">
+      <c r="M2" s="441" t="inlineStr">
         <is>
           <t>Rev</t>
         </is>
@@ -33701,7 +33728,7 @@
           <t>Rev</t>
         </is>
       </c>
-      <c r="R2" s="438" t="inlineStr">
+      <c r="R2" s="437" t="inlineStr">
         <is>
           <t>Codice</t>
         </is>
@@ -33737,7 +33764,7 @@
       <c r="R3" s="187" t="n"/>
       <c r="S3" s="188" t="n"/>
     </row>
-    <row r="4" ht="30" customHeight="1" s="479">
+    <row r="4" ht="30" customHeight="1" s="478">
       <c r="A4" s="322" t="inlineStr">
         <is>
           <t>Sviluppo regole (Algoritmi Diagnostici)</t>
@@ -33901,7 +33928,7 @@
       <c r="R6" s="63" t="n"/>
       <c r="S6" s="64" t="n"/>
     </row>
-    <row r="7" ht="30" customHeight="1" s="479">
+    <row r="7" ht="30" customHeight="1" s="478">
       <c r="A7" s="322" t="inlineStr">
         <is>
           <t>PropulsionDiagnosticDataset</t>
@@ -34167,8 +34194,8 @@
     <col width="14.85546875" customWidth="1" style="10" min="11" max="12"/>
     <col width="8.7109375" customWidth="1" style="59" min="13" max="13"/>
     <col width="33.140625" customWidth="1" style="59" min="14" max="14"/>
-    <col width="8.7109375" customWidth="1" style="59" min="15" max="23"/>
-    <col width="8.7109375" customWidth="1" style="59" min="24" max="16384"/>
+    <col width="8.7109375" customWidth="1" style="59" min="15" max="24"/>
+    <col width="8.7109375" customWidth="1" style="59" min="25" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customFormat="1" customHeight="1" s="61">
@@ -34182,18 +34209,18 @@
           <t>DESCRIZIONE FUNZIONE</t>
         </is>
       </c>
-      <c r="C1" s="435" t="inlineStr">
+      <c r="C1" s="434" t="inlineStr">
         <is>
           <t>DOC
 CARTELLA</t>
         </is>
       </c>
-      <c r="D1" s="435" t="inlineStr">
+      <c r="D1" s="434" t="inlineStr">
         <is>
           <t>DOC ID</t>
         </is>
       </c>
-      <c r="E1" s="435" t="inlineStr">
+      <c r="E1" s="434" t="inlineStr">
         <is>
           <t>Info DOC</t>
         </is>
@@ -34208,22 +34235,22 @@
           <t>VZI_New14</t>
         </is>
       </c>
-      <c r="H1" s="440" t="inlineStr">
+      <c r="H1" s="439" t="inlineStr">
         <is>
           <t>VZ_FR</t>
         </is>
       </c>
-      <c r="I1" s="440" t="inlineStr">
+      <c r="I1" s="439" t="inlineStr">
         <is>
           <t>VZ_ES</t>
         </is>
       </c>
-      <c r="J1" s="440" t="inlineStr">
+      <c r="J1" s="439" t="inlineStr">
         <is>
           <t>VZI-6_R1</t>
         </is>
       </c>
-      <c r="K1" s="440" t="inlineStr">
+      <c r="K1" s="439" t="inlineStr">
         <is>
           <t>VZI-4_R1</t>
         </is>
@@ -34264,7 +34291,7 @@
       <c r="K2" s="334" t="n"/>
       <c r="L2" s="335" t="n"/>
     </row>
-    <row r="3" outlineLevel="1" collapsed="1" s="479">
+    <row r="3" outlineLevel="1" collapsed="1" s="478">
       <c r="A3" s="336" t="n"/>
       <c r="B3" s="337" t="n"/>
       <c r="C3" s="338" t="inlineStr">
@@ -34296,7 +34323,7 @@
       <c r="K3" s="341" t="n"/>
       <c r="L3" s="338" t="n"/>
     </row>
-    <row r="4" hidden="1" outlineLevel="2" s="479">
+    <row r="4" hidden="1" outlineLevel="2" s="478">
       <c r="A4" s="105" t="n"/>
       <c r="B4" s="106">
         <f t="array" ref="B4">INDIRECT("'" &amp; $C9 &amp; "'!B5")</f>
@@ -34321,7 +34348,7 @@
       <c r="K4" s="343" t="n"/>
       <c r="L4" s="217" t="n"/>
     </row>
-    <row r="5" outlineLevel="1" collapsed="1" s="479">
+    <row r="5" outlineLevel="1" collapsed="1" s="478">
       <c r="A5" s="105" t="n"/>
       <c r="B5" s="106" t="n"/>
       <c r="C5" s="338" t="inlineStr">
@@ -34353,7 +34380,7 @@
       <c r="K5" s="338" t="n"/>
       <c r="L5" s="338" t="n"/>
     </row>
-    <row r="6" hidden="1" outlineLevel="2" s="479">
+    <row r="6" hidden="1" outlineLevel="2" s="478">
       <c r="A6" s="105" t="n"/>
       <c r="B6" s="106" t="n"/>
       <c r="C6" s="342" t="n"/>
@@ -34375,7 +34402,7 @@
       <c r="K6" s="217" t="n"/>
       <c r="L6" s="217" t="n"/>
     </row>
-    <row r="7" outlineLevel="1" collapsed="1" s="479">
+    <row r="7" outlineLevel="1" collapsed="1" s="478">
       <c r="A7" s="105" t="n"/>
       <c r="B7" s="106" t="n"/>
       <c r="C7" s="338" t="inlineStr">
@@ -34407,7 +34434,7 @@
       <c r="K7" s="338" t="n"/>
       <c r="L7" s="338" t="n"/>
     </row>
-    <row r="8" hidden="1" outlineLevel="2" s="479">
+    <row r="8" hidden="1" outlineLevel="2" s="478">
       <c r="A8" s="105" t="n"/>
       <c r="B8" s="106" t="n"/>
       <c r="C8" s="106" t="n"/>
@@ -34429,7 +34456,7 @@
       <c r="K8" s="217" t="n"/>
       <c r="L8" s="217" t="n"/>
     </row>
-    <row r="9" outlineLevel="1" collapsed="1" s="479">
+    <row r="9" outlineLevel="1" collapsed="1" s="478">
       <c r="A9" s="67" t="n"/>
       <c r="B9" s="86" t="n"/>
       <c r="C9" s="338" t="inlineStr">
@@ -34461,7 +34488,7 @@
       <c r="K9" s="338" t="n"/>
       <c r="L9" s="338" t="n"/>
     </row>
-    <row r="10" hidden="1" outlineLevel="2" s="479">
+    <row r="10" hidden="1" outlineLevel="2" s="478">
       <c r="A10" s="67" t="n"/>
       <c r="B10" s="86" t="n"/>
       <c r="D10" s="345" t="n"/>
@@ -34482,7 +34509,7 @@
       <c r="K10" s="217" t="n"/>
       <c r="L10" s="217" t="n"/>
     </row>
-    <row r="11" hidden="1" outlineLevel="2" s="479">
+    <row r="11" hidden="1" outlineLevel="2" s="478">
       <c r="A11" s="67" t="n"/>
       <c r="B11" s="86" t="n"/>
       <c r="D11" s="346" t="n"/>
@@ -34499,7 +34526,7 @@
       <c r="K11" s="217" t="n"/>
       <c r="L11" s="217" t="n"/>
     </row>
-    <row r="12" outlineLevel="1" collapsed="1" s="479">
+    <row r="12" outlineLevel="1" collapsed="1" s="478">
       <c r="A12" s="67" t="n"/>
       <c r="B12" s="86" t="n"/>
       <c r="C12" s="338" t="inlineStr">
@@ -34528,7 +34555,7 @@
       <c r="K12" s="338" t="n"/>
       <c r="L12" s="338" t="n"/>
     </row>
-    <row r="13" hidden="1" outlineLevel="2" s="479">
+    <row r="13" hidden="1" outlineLevel="2" s="478">
       <c r="A13" s="67" t="n"/>
       <c r="B13" s="86" t="n"/>
       <c r="D13" s="345" t="n"/>
@@ -34547,7 +34574,7 @@
       <c r="K13" s="217" t="n"/>
       <c r="L13" s="217" t="n"/>
     </row>
-    <row r="14" outlineLevel="1" collapsed="1" s="479">
+    <row r="14" outlineLevel="1" collapsed="1" s="478">
       <c r="A14" s="67" t="n"/>
       <c r="B14" s="176" t="inlineStr">
         <is>
@@ -34580,7 +34607,7 @@
       <c r="K14" s="338" t="n"/>
       <c r="L14" s="338" t="n"/>
     </row>
-    <row r="15" hidden="1" outlineLevel="2" s="479">
+    <row r="15" hidden="1" outlineLevel="2" s="478">
       <c r="A15" s="67" t="n"/>
       <c r="B15" s="86" t="n"/>
       <c r="D15" s="345" t="n"/>
@@ -34599,7 +34626,7 @@
       <c r="K15" s="217" t="n"/>
       <c r="L15" s="217" t="n"/>
     </row>
-    <row r="16" ht="30" customHeight="1" s="479">
+    <row r="16" ht="30" customHeight="1" s="478">
       <c r="A16" s="347" t="inlineStr">
         <is>
           <t>LV_Country_code_selection</t>
@@ -34625,7 +34652,7 @@
       <c r="K16" s="350" t="n"/>
       <c r="L16" s="351" t="n"/>
     </row>
-    <row r="17" outlineLevel="1" s="479">
+    <row r="17" outlineLevel="1" s="478">
       <c r="A17" s="336" t="n"/>
       <c r="B17" s="337" t="n"/>
       <c r="C17" s="338" t="inlineStr">
@@ -34663,7 +34690,7 @@
       <c r="K17" s="341" t="n"/>
       <c r="L17" s="338" t="n"/>
     </row>
-    <row r="18" outlineLevel="2" s="479">
+    <row r="18" outlineLevel="2" s="478">
       <c r="A18" s="105" t="n"/>
       <c r="B18" s="106" t="n"/>
       <c r="C18" s="106" t="n"/>
@@ -34689,7 +34716,7 @@
       <c r="K18" s="343" t="n"/>
       <c r="L18" s="217" t="n"/>
     </row>
-    <row r="19" outlineLevel="2" s="479">
+    <row r="19" outlineLevel="2" s="478">
       <c r="A19" s="105" t="n"/>
       <c r="B19" s="106" t="n"/>
       <c r="C19" s="106" t="n"/>
@@ -34699,59 +34726,55 @@
           <t>Funzioni AI</t>
         </is>
       </c>
-      <c r="F19" s="523" t="inlineStr">
-        <is>
-          <t>La funzione 'LV_Country_code_selection' seleziona il paese di operazione in base all'IDU e invia la selezione ai PCU. La funzione è valida per tutte le configurazioni, ma presenta alcune differenze significative.
+      <c r="F19" s="522" t="inlineStr">
+        <is>
+          <t>La funzione 'LV_Country_code_selection' seleziona il paese di operazione in base all'IDU e invia il codice selezionato a tutte le PCU del treno. In caso di guasto, il sistema comunica il codice più recente noto all'PCU. La funzione è valida per tutte le configurazioni, ma presenta alcune differenze significative.
 Differenze tra configurazioni:
   • VZI_Base ha soglia 750 kPa, VZ_FR ha soglia 800 kPa
-  • VZI_Base e VZ_FR inviano la selezione ai PCU, mentre VZ_ES non lo fa
-  • VZI-6_R1 non ha feedback per i paesi non disponibili
-  • VZI-6_R1 ha un timeout di 35s per la selezione del paese
-  • VZI-6_R1 ha una validazione del paese selezionato solo se è l'Italia
-Questa configurazione (VZI_Base): Nota specifica su questa config: la selezione del paese è valida solo se la pressione è superiore a 750 kPa
+  • VZI_Base e VZ_FR hanno la stessa logica di funzionamento, ma VZI_Base non implementa il timeout di 35s presente nelle altre config
+  • VZI_ES non invia il codice selezionato alle PCU
+  • VZI-6_R1 ha solo 6 paesi disponibili per la selezione, mentre le altre config hanno 8
+Questa configurazione (VZI_Base): Nota specifica: la funzione è identica alle altre config, ma non implementa il timeout di 35s
 Score equivalenza: 85/100
 Pag. iniziale: parte di pag.7 — Pag. finale: parte di pag.8.</t>
         </is>
       </c>
       <c r="G19" s="231" t="n"/>
-      <c r="H19" s="523" t="inlineStr">
-        <is>
-          <t>La funzione 'LV_Country_code_selection' seleziona il paese di operazione in base all'IDU e invia la selezione ai PCU. La funzione è valida per tutte le configurazioni, ma presenta alcune differenze significative.
+      <c r="H19" s="522" t="inlineStr">
+        <is>
+          <t>La funzione 'LV_Country_code_selection' seleziona il paese di operazione in base all'IDU e invia il codice selezionato a tutte le PCU del treno. In caso di guasto, il sistema comunica il codice più recente noto all'PCU. La funzione è valida per tutte le configurazioni, ma presenta alcune differenze significative.
 Differenze tra configurazioni:
   • VZI_Base ha soglia 750 kPa, VZ_FR ha soglia 800 kPa
-  • VZI_Base e VZ_FR inviano la selezione ai PCU, mentre VZ_ES non lo fa
-  • VZI-6_R1 non ha feedback per i paesi non disponibili
-  • VZI-6_R1 ha un timeout di 35s per la selezione del paese
-  • VZI-6_R1 ha una validazione del paese selezionato solo se è l'Italia
-Questa configurazione (VZ_FR): Nota specifica su questa config: la selezione del paese è valida solo se la pressione è superiore a 800 kPa
+  • VZI_Base e VZ_FR hanno la stessa logica di funzionamento, ma VZI_Base non implementa il timeout di 35s presente nelle altre config
+  • VZI_ES non invia il codice selezionato alle PCU
+  • VZI-6_R1 ha solo 6 paesi disponibili per la selezione, mentre le altre config hanno 8
+Questa configurazione (VZ_FR): Nota specifica: la funzione è identica alle altre config
 Score equivalenza: 85/100
 Pag. iniziale: parte di pag.7 — Pag. finale: parte di pag.8.</t>
         </is>
       </c>
-      <c r="I19" s="523" t="inlineStr">
-        <is>
-          <t>La funzione 'LV_Country_code_selection' seleziona il paese di operazione in base all'IDU e invia la selezione ai PCU. La funzione è valida per tutte le configurazioni, ma presenta alcune differenze significative.
+      <c r="I19" s="522" t="inlineStr">
+        <is>
+          <t>La funzione 'LV_Country_code_selection' seleziona il paese di operazione in base all'IDU e invia il codice selezionato a tutte le PCU del treno. In caso di guasto, il sistema comunica il codice più recente noto all'PCU. La funzione è valida per tutte le configurazioni, ma presenta alcune differenze significative.
 Differenze tra configurazioni:
   • VZI_Base ha soglia 750 kPa, VZ_FR ha soglia 800 kPa
-  • VZI_Base e VZ_FR inviano la selezione ai PCU, mentre VZ_ES non lo fa
-  • VZI-6_R1 non ha feedback per i paesi non disponibili
-  • VZI-6_R1 ha un timeout di 35s per la selezione del paese
-  • VZI-6_R1 ha una validazione del paese selezionato solo se è l'Italia
-Questa configurazione (VZ_ES): Nota specifica su questa config: la selezione del paese non è valida e non viene inviata ai PCU
+  • VZI_Base e VZ_FR hanno la stessa logica di funzionamento, ma VZI_Base non implementa il timeout di 35s presente nelle altre config
+  • VZI_ES non invia il codice selezionato alle PCU
+  • VZI-6_R1 ha solo 6 paesi disponibili per la selezione, mentre le altre config hanno 8
+Questa configurazione (VZ_ES): Nota specifica: la funzione non invia il codice selezionato alle PCU
 Score equivalenza: 85/100
 Pag. iniziale: parte di pag.7 — Pag. finale: parte di pag.8.</t>
         </is>
       </c>
-      <c r="J19" s="523" t="inlineStr">
-        <is>
-          <t>La funzione 'LV_Country_code_selection' seleziona il paese di operazione in base all'IDU e invia la selezione ai PCU. La funzione è valida per tutte le configurazioni, ma presenta alcune differenze significative.
+      <c r="J19" s="522" t="inlineStr">
+        <is>
+          <t>La funzione 'LV_Country_code_selection' seleziona il paese di operazione in base all'IDU e invia il codice selezionato a tutte le PCU del treno. In caso di guasto, il sistema comunica il codice più recente noto all'PCU. La funzione è valida per tutte le configurazioni, ma presenta alcune differenze significative.
 Differenze tra configurazioni:
   • VZI_Base ha soglia 750 kPa, VZ_FR ha soglia 800 kPa
-  • VZI_Base e VZ_FR inviano la selezione ai PCU, mentre VZ_ES non lo fa
-  • VZI-6_R1 non ha feedback per i paesi non disponibili
-  • VZI-6_R1 ha un timeout di 35s per la selezione del paese
-  • VZI-6_R1 ha una validazione del paese selezionato solo se è l'Italia
-Questa configurazione (VZI-6_R1): Nota specifica su questa config: la selezione del paese è valida solo se è l'Italia e il timeout di selezione è di 35s
+  • VZI_Base e VZ_FR hanno la stessa logica di funzionamento, ma VZI_Base non implementa il timeout di 35s presente nelle altre config
+  • VZI_ES non invia il codice selezionato alle PCU
+  • VZI-6_R1 ha solo 6 paesi disponibili per la selezione, mentre le altre config hanno 8
+Questa configurazione (VZI-6_R1): Nota specifica: la funzione ha solo 6 paesi disponibili per la selezione
 Score equivalenza: 85/100
 Pag. iniziale: parte di pag.12 — Pag. finale: parte di pag.13.</t>
         </is>
@@ -34759,7 +34782,7 @@
       <c r="K19" s="230" t="n"/>
       <c r="L19" s="232" t="n"/>
     </row>
-    <row r="20" ht="30" customHeight="1" s="479">
+    <row r="20" ht="30" customHeight="1" s="478">
       <c r="A20" s="347" t="inlineStr">
         <is>
           <t>LV_Pantograph_Lifting</t>
@@ -34785,7 +34808,7 @@
       <c r="K20" s="350" t="n"/>
       <c r="L20" s="351" t="n"/>
     </row>
-    <row r="21" outlineLevel="1" collapsed="1" s="479">
+    <row r="21" outlineLevel="1" collapsed="1" s="478">
       <c r="A21" s="336" t="n"/>
       <c r="B21" s="337" t="n"/>
       <c r="C21" s="338" t="inlineStr">
@@ -34823,7 +34846,7 @@
       <c r="K21" s="341" t="n"/>
       <c r="L21" s="338" t="n"/>
     </row>
-    <row r="22" hidden="1" outlineLevel="2" s="479">
+    <row r="22" hidden="1" outlineLevel="2" s="478">
       <c r="A22" s="105" t="n"/>
       <c r="B22" s="106" t="n"/>
       <c r="C22" s="106" t="n"/>
@@ -34849,7 +34872,7 @@
       <c r="K22" s="343" t="n"/>
       <c r="L22" s="217" t="n"/>
     </row>
-    <row r="23" hidden="1" outlineLevel="2" ht="360" customHeight="1" s="479">
+    <row r="23" hidden="1" outlineLevel="2" ht="360" customHeight="1" s="478">
       <c r="A23" s="105" t="n"/>
       <c r="B23" s="106" t="n"/>
       <c r="C23" s="106" t="n"/>
@@ -34887,7 +34910,7 @@
       <c r="K23" s="230" t="n"/>
       <c r="L23" s="232" t="n"/>
     </row>
-    <row r="24" ht="30" customHeight="1" s="479">
+    <row r="24" ht="30" customHeight="1" s="478">
       <c r="A24" s="347" t="inlineStr">
         <is>
           <t>LV_Pantograph_Lowering</t>
@@ -34913,7 +34936,7 @@
       <c r="K24" s="350" t="n"/>
       <c r="L24" s="351" t="n"/>
     </row>
-    <row r="25" outlineLevel="1" collapsed="1" s="479">
+    <row r="25" outlineLevel="1" collapsed="1" s="478">
       <c r="A25" s="336" t="n"/>
       <c r="B25" s="337" t="n"/>
       <c r="C25" s="338" t="inlineStr">
@@ -34951,7 +34974,7 @@
       <c r="K25" s="341" t="n"/>
       <c r="L25" s="338" t="n"/>
     </row>
-    <row r="26" hidden="1" outlineLevel="2" s="479">
+    <row r="26" hidden="1" outlineLevel="2" s="478">
       <c r="A26" s="105" t="n"/>
       <c r="B26" s="106" t="n"/>
       <c r="C26" s="106" t="n"/>
@@ -34977,7 +35000,7 @@
       <c r="K26" s="343" t="n"/>
       <c r="L26" s="217" t="n"/>
     </row>
-    <row r="27" hidden="1" outlineLevel="2" ht="409.5" customHeight="1" s="479">
+    <row r="27" hidden="1" outlineLevel="2" ht="409.5" customHeight="1" s="478">
       <c r="A27" s="105" t="n"/>
       <c r="B27" s="106" t="n"/>
       <c r="C27" s="106" t="n"/>
@@ -35080,7 +35103,7 @@
     </row>
     <row r="30" hidden="1" outlineLevel="2" customFormat="1" s="8">
       <c r="B30" s="59" t="n"/>
-      <c r="C30" s="445" t="n"/>
+      <c r="C30" s="444" t="n"/>
       <c r="D30" s="233" t="n"/>
       <c r="E30" s="270" t="inlineStr">
         <is>
@@ -35105,7 +35128,7 @@
     </row>
     <row r="31" hidden="1" outlineLevel="2" ht="405" customFormat="1" customHeight="1" s="8">
       <c r="B31" s="59" t="n"/>
-      <c r="C31" s="445" t="n"/>
+      <c r="C31" s="444" t="n"/>
       <c r="D31" s="233" t="n"/>
       <c r="E31" s="234" t="inlineStr">
         <is>
@@ -35205,7 +35228,7 @@
     </row>
     <row r="34" hidden="1" outlineLevel="2" customFormat="1" s="8">
       <c r="B34" s="59" t="n"/>
-      <c r="C34" s="445" t="n"/>
+      <c r="C34" s="444" t="n"/>
       <c r="D34" s="233" t="n"/>
       <c r="E34" s="270" t="inlineStr">
         <is>
@@ -35230,7 +35253,7 @@
     </row>
     <row r="35" hidden="1" outlineLevel="2" ht="375" customFormat="1" customHeight="1" s="8">
       <c r="B35" s="59" t="n"/>
-      <c r="C35" s="445" t="n"/>
+      <c r="C35" s="444" t="n"/>
       <c r="D35" s="233" t="n"/>
       <c r="E35" s="234" t="inlineStr">
         <is>
@@ -35330,7 +35353,7 @@
     </row>
     <row r="38" hidden="1" outlineLevel="2" customFormat="1" s="8">
       <c r="B38" s="59" t="n"/>
-      <c r="C38" s="445" t="n"/>
+      <c r="C38" s="444" t="n"/>
       <c r="D38" s="233" t="n"/>
       <c r="E38" s="270" t="inlineStr">
         <is>
@@ -35355,7 +35378,7 @@
     </row>
     <row r="39" hidden="1" outlineLevel="2" ht="375" customFormat="1" customHeight="1" s="8">
       <c r="B39" s="59" t="n"/>
-      <c r="C39" s="445" t="n"/>
+      <c r="C39" s="444" t="n"/>
       <c r="D39" s="233" t="n"/>
       <c r="E39" s="234" t="inlineStr">
         <is>
@@ -35455,7 +35478,7 @@
     </row>
     <row r="42" hidden="1" outlineLevel="2" customFormat="1" s="8">
       <c r="B42" s="59" t="n"/>
-      <c r="C42" s="445" t="n"/>
+      <c r="C42" s="444" t="n"/>
       <c r="D42" s="233" t="n"/>
       <c r="E42" s="270" t="inlineStr">
         <is>
@@ -35480,7 +35503,7 @@
     </row>
     <row r="43" hidden="1" outlineLevel="2" ht="360" customFormat="1" customHeight="1" s="8">
       <c r="B43" s="59" t="n"/>
-      <c r="C43" s="445" t="n"/>
+      <c r="C43" s="444" t="n"/>
       <c r="D43" s="233" t="n"/>
       <c r="E43" s="234" t="inlineStr">
         <is>
@@ -35580,7 +35603,7 @@
     </row>
     <row r="46" hidden="1" outlineLevel="2" customFormat="1" s="8">
       <c r="B46" s="59" t="n"/>
-      <c r="C46" s="445" t="n"/>
+      <c r="C46" s="444" t="n"/>
       <c r="D46" s="233" t="n"/>
       <c r="E46" s="270" t="inlineStr">
         <is>
@@ -35605,7 +35628,7 @@
     </row>
     <row r="47" hidden="1" outlineLevel="2" ht="409.5" customFormat="1" customHeight="1" s="8">
       <c r="B47" s="59" t="n"/>
-      <c r="C47" s="445" t="n"/>
+      <c r="C47" s="444" t="n"/>
       <c r="D47" s="233" t="n"/>
       <c r="E47" s="234" t="inlineStr">
         <is>
@@ -35708,7 +35731,7 @@
     </row>
     <row r="50" hidden="1" outlineLevel="2" customFormat="1" s="8">
       <c r="B50" s="59" t="n"/>
-      <c r="C50" s="445" t="n"/>
+      <c r="C50" s="444" t="n"/>
       <c r="D50" s="233" t="n"/>
       <c r="E50" s="270" t="inlineStr">
         <is>
@@ -35733,7 +35756,7 @@
     </row>
     <row r="51" hidden="1" outlineLevel="2" ht="409.5" customFormat="1" customHeight="1" s="8">
       <c r="B51" s="59" t="n"/>
-      <c r="C51" s="445" t="n"/>
+      <c r="C51" s="444" t="n"/>
       <c r="D51" s="233" t="n"/>
       <c r="E51" s="234" t="inlineStr">
         <is>
@@ -35852,7 +35875,7 @@
     </row>
     <row r="54" hidden="1" outlineLevel="2" customFormat="1" s="8">
       <c r="B54" s="59" t="n"/>
-      <c r="C54" s="445" t="n"/>
+      <c r="C54" s="444" t="n"/>
       <c r="D54" s="233" t="n"/>
       <c r="E54" s="270" t="inlineStr">
         <is>
@@ -35877,7 +35900,7 @@
     </row>
     <row r="55" hidden="1" outlineLevel="2" ht="409.5" customFormat="1" customHeight="1" s="8">
       <c r="B55" s="59" t="n"/>
-      <c r="C55" s="445" t="n"/>
+      <c r="C55" s="444" t="n"/>
       <c r="D55" s="233" t="n"/>
       <c r="E55" s="234" t="inlineStr">
         <is>
@@ -35983,7 +36006,7 @@
     </row>
     <row r="58" hidden="1" outlineLevel="2" customFormat="1" s="8">
       <c r="B58" s="59" t="n"/>
-      <c r="C58" s="445" t="n"/>
+      <c r="C58" s="444" t="n"/>
       <c r="D58" s="233" t="n"/>
       <c r="E58" s="270" t="inlineStr">
         <is>
@@ -36008,7 +36031,7 @@
     </row>
     <row r="59" hidden="1" outlineLevel="2" ht="360" customFormat="1" customHeight="1" s="8">
       <c r="B59" s="59" t="n"/>
-      <c r="C59" s="445" t="n"/>
+      <c r="C59" s="444" t="n"/>
       <c r="D59" s="233" t="n"/>
       <c r="E59" s="234" t="inlineStr">
         <is>
@@ -36110,7 +36133,7 @@
     </row>
     <row r="62" hidden="1" outlineLevel="2" customFormat="1" s="8">
       <c r="B62" s="59" t="n"/>
-      <c r="C62" s="445" t="n"/>
+      <c r="C62" s="444" t="n"/>
       <c r="D62" s="233" t="n"/>
       <c r="E62" s="270" t="inlineStr">
         <is>
@@ -36135,7 +36158,7 @@
     </row>
     <row r="63" hidden="1" outlineLevel="2" ht="409.5" customFormat="1" customHeight="1" s="8">
       <c r="B63" s="59" t="n"/>
-      <c r="C63" s="445" t="n"/>
+      <c r="C63" s="444" t="n"/>
       <c r="D63" s="233" t="n"/>
       <c r="E63" s="234" t="inlineStr">
         <is>
@@ -36235,7 +36258,7 @@
     </row>
     <row r="66" hidden="1" outlineLevel="2" customFormat="1" s="8">
       <c r="B66" s="59" t="n"/>
-      <c r="C66" s="445" t="n"/>
+      <c r="C66" s="444" t="n"/>
       <c r="D66" s="233" t="n"/>
       <c r="E66" s="270" t="inlineStr">
         <is>
@@ -36260,7 +36283,7 @@
     </row>
     <row r="67" hidden="1" outlineLevel="2" ht="315" customFormat="1" customHeight="1" s="8">
       <c r="B67" s="59" t="n"/>
-      <c r="C67" s="445" t="n"/>
+      <c r="C67" s="444" t="n"/>
       <c r="D67" s="233" t="n"/>
       <c r="E67" s="234" t="inlineStr">
         <is>
@@ -36360,7 +36383,7 @@
     </row>
     <row r="70" hidden="1" outlineLevel="2" customFormat="1" s="8">
       <c r="B70" s="59" t="n"/>
-      <c r="C70" s="445" t="n"/>
+      <c r="C70" s="444" t="n"/>
       <c r="D70" s="233" t="n"/>
       <c r="E70" s="270" t="inlineStr">
         <is>
@@ -36385,7 +36408,7 @@
     </row>
     <row r="71" hidden="1" outlineLevel="2" ht="409.5" customFormat="1" customHeight="1" s="8">
       <c r="B71" s="59" t="n"/>
-      <c r="C71" s="445" t="n"/>
+      <c r="C71" s="444" t="n"/>
       <c r="D71" s="233" t="n"/>
       <c r="E71" s="234" t="inlineStr">
         <is>
@@ -36494,7 +36517,7 @@
     </row>
     <row r="74" hidden="1" outlineLevel="2" customFormat="1" s="8">
       <c r="B74" s="59" t="n"/>
-      <c r="C74" s="445" t="n"/>
+      <c r="C74" s="444" t="n"/>
       <c r="D74" s="233" t="n"/>
       <c r="E74" s="270" t="inlineStr">
         <is>
@@ -36519,7 +36542,7 @@
     </row>
     <row r="75" hidden="1" outlineLevel="2" ht="409.5" customFormat="1" customHeight="1" s="8">
       <c r="B75" s="59" t="n"/>
-      <c r="C75" s="445" t="n"/>
+      <c r="C75" s="444" t="n"/>
       <c r="D75" s="233" t="n"/>
       <c r="E75" s="234" t="inlineStr">
         <is>
@@ -36640,7 +36663,7 @@
     </row>
     <row r="78" hidden="1" outlineLevel="2" customFormat="1" s="8">
       <c r="B78" s="59" t="n"/>
-      <c r="C78" s="445" t="n"/>
+      <c r="C78" s="444" t="n"/>
       <c r="D78" s="233" t="n"/>
       <c r="E78" s="270" t="inlineStr">
         <is>
@@ -36665,7 +36688,7 @@
     </row>
     <row r="79" hidden="1" outlineLevel="2" ht="375" customFormat="1" customHeight="1" s="8">
       <c r="B79" s="59" t="n"/>
-      <c r="C79" s="445" t="n"/>
+      <c r="C79" s="444" t="n"/>
       <c r="D79" s="233" t="n"/>
       <c r="E79" s="234" t="inlineStr">
         <is>
@@ -36756,7 +36779,7 @@
     </row>
     <row r="82" hidden="1" outlineLevel="2" customFormat="1" s="8">
       <c r="B82" s="59" t="n"/>
-      <c r="C82" s="445" t="n"/>
+      <c r="C82" s="444" t="n"/>
       <c r="D82" s="233" t="n"/>
       <c r="E82" s="270" t="inlineStr">
         <is>
@@ -36775,7 +36798,7 @@
     </row>
     <row r="83" hidden="1" outlineLevel="2" ht="360" customFormat="1" customHeight="1" s="8">
       <c r="B83" s="59" t="n"/>
-      <c r="C83" s="445" t="n"/>
+      <c r="C83" s="444" t="n"/>
       <c r="D83" s="233" t="n"/>
       <c r="E83" s="234" t="inlineStr">
         <is>
@@ -36850,7 +36873,7 @@
     </row>
     <row r="86" hidden="1" outlineLevel="2" customFormat="1" s="8">
       <c r="B86" s="59" t="n"/>
-      <c r="C86" s="445" t="n"/>
+      <c r="C86" s="444" t="n"/>
       <c r="D86" s="233" t="n"/>
       <c r="E86" s="270" t="inlineStr">
         <is>
@@ -36869,7 +36892,7 @@
     </row>
     <row r="87" hidden="1" outlineLevel="2" ht="195" customFormat="1" customHeight="1" s="8">
       <c r="B87" s="59" t="n"/>
-      <c r="C87" s="445" t="n"/>
+      <c r="C87" s="444" t="n"/>
       <c r="D87" s="233" t="n"/>
       <c r="E87" s="234" t="inlineStr">
         <is>
@@ -36950,7 +36973,7 @@
     </row>
     <row r="90" hidden="1" outlineLevel="2" customFormat="1" s="8">
       <c r="B90" s="59" t="n"/>
-      <c r="C90" s="445" t="n"/>
+      <c r="C90" s="444" t="n"/>
       <c r="D90" s="233" t="n"/>
       <c r="E90" s="270" t="inlineStr">
         <is>
@@ -36973,7 +36996,7 @@
     </row>
     <row r="91" hidden="1" outlineLevel="2" ht="390" customFormat="1" customHeight="1" s="8">
       <c r="B91" s="59" t="n"/>
-      <c r="C91" s="445" t="n"/>
+      <c r="C91" s="444" t="n"/>
       <c r="D91" s="233" t="n"/>
       <c r="E91" s="234" t="inlineStr">
         <is>
@@ -37068,7 +37091,7 @@
     </row>
     <row r="94" hidden="1" outlineLevel="2" customFormat="1" s="8">
       <c r="B94" s="59" t="n"/>
-      <c r="C94" s="445" t="n"/>
+      <c r="C94" s="444" t="n"/>
       <c r="D94" s="233" t="n"/>
       <c r="E94" s="270" t="inlineStr">
         <is>
@@ -37093,7 +37116,7 @@
     </row>
     <row r="95" hidden="1" outlineLevel="2" ht="409.5" customFormat="1" customHeight="1" s="8">
       <c r="B95" s="59" t="n"/>
-      <c r="C95" s="445" t="n"/>
+      <c r="C95" s="444" t="n"/>
       <c r="D95" s="233" t="n"/>
       <c r="E95" s="234" t="inlineStr">
         <is>
@@ -37196,7 +37219,7 @@
     </row>
     <row r="98" hidden="1" outlineLevel="2" customFormat="1" s="8">
       <c r="B98" s="59" t="n"/>
-      <c r="C98" s="445" t="n"/>
+      <c r="C98" s="444" t="n"/>
       <c r="D98" s="233" t="n"/>
       <c r="E98" s="270" t="inlineStr">
         <is>
@@ -37221,7 +37244,7 @@
     </row>
     <row r="99" hidden="1" outlineLevel="2" ht="409.5" customFormat="1" customHeight="1" s="8">
       <c r="B99" s="59" t="n"/>
-      <c r="C99" s="445" t="n"/>
+      <c r="C99" s="444" t="n"/>
       <c r="D99" s="233" t="n"/>
       <c r="E99" s="234" t="inlineStr">
         <is>
@@ -37323,7 +37346,7 @@
     </row>
     <row r="102" hidden="1" outlineLevel="2" customFormat="1" s="8">
       <c r="B102" s="59" t="n"/>
-      <c r="C102" s="445" t="n"/>
+      <c r="C102" s="444" t="n"/>
       <c r="D102" s="233" t="n"/>
       <c r="E102" s="270" t="inlineStr">
         <is>
@@ -37348,7 +37371,7 @@
     </row>
     <row r="103" hidden="1" outlineLevel="2" ht="409.5" customFormat="1" customHeight="1" s="8">
       <c r="B103" s="59" t="n"/>
-      <c r="C103" s="445" t="n"/>
+      <c r="C103" s="444" t="n"/>
       <c r="D103" s="233" t="n"/>
       <c r="E103" s="234" t="inlineStr">
         <is>
@@ -37468,7 +37491,7 @@
     </row>
     <row r="106" hidden="1" outlineLevel="2" customFormat="1" s="8">
       <c r="B106" s="59" t="n"/>
-      <c r="C106" s="445" t="n"/>
+      <c r="C106" s="444" t="n"/>
       <c r="D106" s="233" t="n"/>
       <c r="E106" s="270" t="inlineStr">
         <is>
@@ -37493,7 +37516,7 @@
     </row>
     <row r="107" hidden="1" outlineLevel="2" ht="409.5" customFormat="1" customHeight="1" s="8">
       <c r="B107" s="59" t="n"/>
-      <c r="C107" s="445" t="n"/>
+      <c r="C107" s="444" t="n"/>
       <c r="D107" s="233" t="n"/>
       <c r="E107" s="234" t="inlineStr">
         <is>
@@ -37612,7 +37635,7 @@
     </row>
     <row r="110" hidden="1" outlineLevel="2" customFormat="1" s="8">
       <c r="B110" s="59" t="n"/>
-      <c r="C110" s="516" t="n"/>
+      <c r="C110" s="515" t="n"/>
       <c r="D110" s="365" t="n"/>
       <c r="E110" s="366" t="inlineStr">
         <is>
@@ -37637,7 +37660,7 @@
     </row>
     <row r="111" hidden="1" outlineLevel="2" ht="360" customFormat="1" customHeight="1" s="8">
       <c r="B111" s="59" t="n"/>
-      <c r="C111" s="445" t="n"/>
+      <c r="C111" s="444" t="n"/>
       <c r="D111" s="233" t="n"/>
       <c r="E111" s="234" t="inlineStr">
         <is>
@@ -37733,7 +37756,7 @@
     </row>
     <row r="114" hidden="1" outlineLevel="2" customFormat="1" s="8">
       <c r="B114" s="59" t="n"/>
-      <c r="C114" s="516" t="n"/>
+      <c r="C114" s="515" t="n"/>
       <c r="D114" s="365" t="n"/>
       <c r="E114" s="366" t="inlineStr">
         <is>
@@ -37758,7 +37781,7 @@
     </row>
     <row r="115" hidden="1" outlineLevel="2" ht="409.5" customFormat="1" customHeight="1" s="8">
       <c r="B115" s="59" t="n"/>
-      <c r="C115" s="445" t="n"/>
+      <c r="C115" s="444" t="n"/>
       <c r="D115" s="233" t="n"/>
       <c r="E115" s="234" t="inlineStr">
         <is>
@@ -37854,7 +37877,7 @@
     </row>
     <row r="118" hidden="1" outlineLevel="2" customFormat="1" s="8">
       <c r="B118" s="59" t="n"/>
-      <c r="C118" s="516" t="n"/>
+      <c r="C118" s="515" t="n"/>
       <c r="D118" s="365" t="n"/>
       <c r="E118" s="366" t="inlineStr">
         <is>
@@ -37879,7 +37902,7 @@
     </row>
     <row r="119" hidden="1" outlineLevel="2" ht="345" customFormat="1" customHeight="1" s="8">
       <c r="B119" s="59" t="n"/>
-      <c r="C119" s="445" t="n"/>
+      <c r="C119" s="444" t="n"/>
       <c r="D119" s="233" t="n"/>
       <c r="E119" s="234" t="inlineStr">
         <is>
@@ -37975,7 +37998,7 @@
     </row>
     <row r="122" hidden="1" outlineLevel="2" customFormat="1" s="8">
       <c r="B122" s="59" t="n"/>
-      <c r="C122" s="516" t="n"/>
+      <c r="C122" s="515" t="n"/>
       <c r="D122" s="365" t="n"/>
       <c r="E122" s="366" t="inlineStr">
         <is>
@@ -38000,7 +38023,7 @@
     </row>
     <row r="123" hidden="1" outlineLevel="2" ht="375" customFormat="1" customHeight="1" s="8">
       <c r="B123" s="59" t="n"/>
-      <c r="C123" s="445" t="n"/>
+      <c r="C123" s="444" t="n"/>
       <c r="D123" s="233" t="n"/>
       <c r="E123" s="234" t="inlineStr">
         <is>
@@ -38097,7 +38120,7 @@
     </row>
     <row r="126" hidden="1" outlineLevel="2" customFormat="1" s="8">
       <c r="B126" s="59" t="n"/>
-      <c r="C126" s="516" t="n"/>
+      <c r="C126" s="515" t="n"/>
       <c r="D126" s="365" t="n"/>
       <c r="E126" s="366" t="inlineStr">
         <is>
@@ -38122,7 +38145,7 @@
     </row>
     <row r="127" hidden="1" outlineLevel="2" ht="315" customFormat="1" customHeight="1" s="8">
       <c r="B127" s="59" t="n"/>
-      <c r="C127" s="445" t="n"/>
+      <c r="C127" s="444" t="n"/>
       <c r="D127" s="233" t="n"/>
       <c r="E127" s="234" t="inlineStr">
         <is>
@@ -38218,7 +38241,7 @@
     </row>
     <row r="130" hidden="1" outlineLevel="2" customFormat="1" s="8">
       <c r="B130" s="59" t="n"/>
-      <c r="C130" s="516" t="n"/>
+      <c r="C130" s="515" t="n"/>
       <c r="D130" s="365" t="n"/>
       <c r="E130" s="366" t="inlineStr">
         <is>
@@ -38243,7 +38266,7 @@
     </row>
     <row r="131" hidden="1" outlineLevel="2" ht="409.5" customFormat="1" customHeight="1" s="8">
       <c r="B131" s="59" t="n"/>
-      <c r="C131" s="445" t="n"/>
+      <c r="C131" s="444" t="n"/>
       <c r="D131" s="233" t="n"/>
       <c r="E131" s="234" t="inlineStr">
         <is>
@@ -38360,7 +38383,7 @@
     </row>
     <row r="134" hidden="1" outlineLevel="2" customFormat="1" s="8">
       <c r="B134" s="59" t="n"/>
-      <c r="C134" s="516" t="n"/>
+      <c r="C134" s="515" t="n"/>
       <c r="D134" s="365" t="n"/>
       <c r="E134" s="366" t="inlineStr">
         <is>
@@ -38385,7 +38408,7 @@
     </row>
     <row r="135" hidden="1" outlineLevel="2" ht="360" customFormat="1" customHeight="1" s="8">
       <c r="B135" s="59" t="n"/>
-      <c r="C135" s="445" t="n"/>
+      <c r="C135" s="444" t="n"/>
       <c r="D135" s="233" t="n"/>
       <c r="E135" s="234" t="inlineStr">
         <is>
@@ -38481,7 +38504,7 @@
     </row>
     <row r="138" hidden="1" outlineLevel="2" customFormat="1" s="8">
       <c r="B138" s="59" t="n"/>
-      <c r="C138" s="445" t="n"/>
+      <c r="C138" s="444" t="n"/>
       <c r="D138" s="233" t="n"/>
       <c r="E138" s="270" t="inlineStr">
         <is>
@@ -38508,7 +38531,7 @@
     </row>
     <row r="139" hidden="1" outlineLevel="2" ht="409.5" customFormat="1" customHeight="1" s="8">
       <c r="B139" s="59" t="n"/>
-      <c r="C139" s="445" t="n"/>
+      <c r="C139" s="444" t="n"/>
       <c r="D139" s="233" t="n"/>
       <c r="E139" s="234" t="inlineStr">
         <is>
@@ -38588,7 +38611,7 @@
       <c r="K140" s="163" t="n"/>
       <c r="L140" s="164" t="n"/>
     </row>
-    <row r="141" outlineLevel="1" collapsed="1" s="479">
+    <row r="141" outlineLevel="1" collapsed="1" s="478">
       <c r="B141" s="169" t="n"/>
       <c r="C141" s="338" t="inlineStr">
         <is>
@@ -38619,7 +38642,7 @@
       <c r="K141" s="359" t="n"/>
       <c r="L141" s="359" t="n"/>
     </row>
-    <row r="142" hidden="1" outlineLevel="2" s="479">
+    <row r="142" hidden="1" outlineLevel="2" s="478">
       <c r="B142" s="169" t="n"/>
       <c r="D142" s="166" t="n"/>
       <c r="E142" s="165" t="inlineStr">
@@ -38647,7 +38670,7 @@
     </row>
     <row r="143" hidden="1" outlineLevel="2" ht="390" customFormat="1" customHeight="1" s="8">
       <c r="B143" s="59" t="n"/>
-      <c r="C143" s="445" t="n"/>
+      <c r="C143" s="444" t="n"/>
       <c r="D143" s="233" t="n"/>
       <c r="E143" s="234" t="inlineStr">
         <is>
@@ -38694,7 +38717,7 @@
       <c r="K144" s="163" t="n"/>
       <c r="L144" s="164" t="n"/>
     </row>
-    <row r="145" outlineLevel="1" collapsed="1" s="479">
+    <row r="145" outlineLevel="1" collapsed="1" s="478">
       <c r="B145" s="169" t="n"/>
       <c r="C145" s="338" t="inlineStr">
         <is>
@@ -38725,7 +38748,7 @@
       <c r="K145" s="359" t="n"/>
       <c r="L145" s="359" t="n"/>
     </row>
-    <row r="146" hidden="1" outlineLevel="2" s="479">
+    <row r="146" hidden="1" outlineLevel="2" s="478">
       <c r="B146" s="169" t="n"/>
       <c r="D146" s="166" t="n"/>
       <c r="E146" s="165" t="inlineStr">
@@ -38747,7 +38770,7 @@
     </row>
     <row r="147" hidden="1" outlineLevel="2" ht="345" customFormat="1" customHeight="1" s="8">
       <c r="B147" s="59" t="n"/>
-      <c r="C147" s="445" t="n"/>
+      <c r="C147" s="444" t="n"/>
       <c r="D147" s="233" t="n"/>
       <c r="E147" s="234" t="inlineStr">
         <is>
@@ -38794,7 +38817,7 @@
       <c r="K148" s="163" t="n"/>
       <c r="L148" s="164" t="n"/>
     </row>
-    <row r="149" outlineLevel="1" collapsed="1" s="479">
+    <row r="149" outlineLevel="1" collapsed="1" s="478">
       <c r="B149" s="169" t="n"/>
       <c r="C149" s="338" t="inlineStr">
         <is>
@@ -38825,7 +38848,7 @@
       <c r="K149" s="359" t="n"/>
       <c r="L149" s="359" t="n"/>
     </row>
-    <row r="150" hidden="1" outlineLevel="2" s="479">
+    <row r="150" hidden="1" outlineLevel="2" s="478">
       <c r="B150" s="169" t="n"/>
       <c r="D150" s="166" t="n"/>
       <c r="E150" s="165" t="inlineStr">
@@ -38847,7 +38870,7 @@
     </row>
     <row r="151" hidden="1" outlineLevel="2" ht="390" customFormat="1" customHeight="1" s="8">
       <c r="B151" s="59" t="n"/>
-      <c r="C151" s="445" t="n"/>
+      <c r="C151" s="444" t="n"/>
       <c r="D151" s="233" t="n"/>
       <c r="E151" s="234" t="inlineStr">
         <is>
@@ -38894,7 +38917,7 @@
       <c r="K152" s="163" t="n"/>
       <c r="L152" s="164" t="n"/>
     </row>
-    <row r="153" outlineLevel="1" collapsed="1" s="479">
+    <row r="153" outlineLevel="1" collapsed="1" s="478">
       <c r="B153" s="169" t="n"/>
       <c r="C153" s="338" t="inlineStr">
         <is>
@@ -38925,7 +38948,7 @@
       <c r="K153" s="359" t="n"/>
       <c r="L153" s="359" t="n"/>
     </row>
-    <row r="154" hidden="1" outlineLevel="2" s="479">
+    <row r="154" hidden="1" outlineLevel="2" s="478">
       <c r="B154" s="169" t="n"/>
       <c r="D154" s="166" t="n"/>
       <c r="E154" s="165" t="inlineStr">
@@ -38947,7 +38970,7 @@
     </row>
     <row r="155" hidden="1" outlineLevel="2" ht="345" customFormat="1" customHeight="1" s="8">
       <c r="B155" s="59" t="n"/>
-      <c r="C155" s="445" t="n"/>
+      <c r="C155" s="444" t="n"/>
       <c r="D155" s="233" t="n"/>
       <c r="E155" s="234" t="inlineStr">
         <is>
@@ -38994,7 +39017,7 @@
       <c r="K156" s="163" t="n"/>
       <c r="L156" s="164" t="n"/>
     </row>
-    <row r="157" outlineLevel="1" collapsed="1" s="479">
+    <row r="157" outlineLevel="1" collapsed="1" s="478">
       <c r="B157" s="169" t="n"/>
       <c r="C157" s="338" t="inlineStr">
         <is>
@@ -39025,7 +39048,7 @@
       <c r="K157" s="359" t="n"/>
       <c r="L157" s="359" t="n"/>
     </row>
-    <row r="158" hidden="1" outlineLevel="2" s="479">
+    <row r="158" hidden="1" outlineLevel="2" s="478">
       <c r="B158" s="169" t="n"/>
       <c r="D158" s="166" t="n"/>
       <c r="E158" s="165" t="inlineStr">
@@ -39047,7 +39070,7 @@
     </row>
     <row r="159" hidden="1" outlineLevel="2" ht="375" customFormat="1" customHeight="1" s="8">
       <c r="B159" s="59" t="n"/>
-      <c r="C159" s="445" t="n"/>
+      <c r="C159" s="444" t="n"/>
       <c r="D159" s="233" t="n"/>
       <c r="E159" s="234" t="inlineStr">
         <is>
@@ -39094,7 +39117,7 @@
       <c r="K160" s="163" t="n"/>
       <c r="L160" s="164" t="n"/>
     </row>
-    <row r="161" outlineLevel="1" collapsed="1" s="479">
+    <row r="161" outlineLevel="1" collapsed="1" s="478">
       <c r="B161" s="169" t="n"/>
       <c r="C161" s="338" t="inlineStr">
         <is>
@@ -39125,7 +39148,7 @@
       <c r="K161" s="359" t="n"/>
       <c r="L161" s="359" t="n"/>
     </row>
-    <row r="162" hidden="1" outlineLevel="2" s="479">
+    <row r="162" hidden="1" outlineLevel="2" s="478">
       <c r="B162" s="169" t="n"/>
       <c r="D162" s="166" t="n"/>
       <c r="E162" s="165" t="inlineStr">
@@ -39153,7 +39176,7 @@
     </row>
     <row r="163" hidden="1" outlineLevel="2" ht="390" customFormat="1" customHeight="1" s="8">
       <c r="B163" s="59" t="n"/>
-      <c r="C163" s="445" t="n"/>
+      <c r="C163" s="444" t="n"/>
       <c r="D163" s="233" t="n"/>
       <c r="E163" s="234" t="inlineStr">
         <is>
@@ -39200,7 +39223,7 @@
       <c r="K164" s="163" t="n"/>
       <c r="L164" s="164" t="n"/>
     </row>
-    <row r="165" outlineLevel="1" collapsed="1" s="479">
+    <row r="165" outlineLevel="1" collapsed="1" s="478">
       <c r="B165" s="169" t="n"/>
       <c r="C165" s="338" t="inlineStr">
         <is>
@@ -39234,7 +39257,7 @@
       <c r="K165" s="359" t="n"/>
       <c r="L165" s="359" t="n"/>
     </row>
-    <row r="166" hidden="1" outlineLevel="2" s="479">
+    <row r="166" hidden="1" outlineLevel="2" s="478">
       <c r="B166" s="169" t="n"/>
       <c r="D166" s="168" t="n"/>
       <c r="E166" s="167" t="inlineStr">
@@ -39262,7 +39285,7 @@
     </row>
     <row r="167" hidden="1" outlineLevel="2" ht="409.5" customFormat="1" customHeight="1" s="8">
       <c r="B167" s="59" t="n"/>
-      <c r="C167" s="445" t="n"/>
+      <c r="C167" s="444" t="n"/>
       <c r="D167" s="233" t="n"/>
       <c r="E167" s="234" t="inlineStr">
         <is>
@@ -39314,7 +39337,7 @@
       <c r="K168" s="163" t="n"/>
       <c r="L168" s="164" t="n"/>
     </row>
-    <row r="169" outlineLevel="1" collapsed="1" s="479">
+    <row r="169" outlineLevel="1" collapsed="1" s="478">
       <c r="B169" s="169" t="n"/>
       <c r="C169" s="338" t="inlineStr">
         <is>
@@ -39348,7 +39371,7 @@
       <c r="K169" s="359" t="n"/>
       <c r="L169" s="359" t="n"/>
     </row>
-    <row r="170" hidden="1" outlineLevel="2" s="479">
+    <row r="170" hidden="1" outlineLevel="2" s="478">
       <c r="B170" s="169" t="n"/>
       <c r="D170" s="168" t="n"/>
       <c r="E170" s="167" t="inlineStr">
@@ -39376,7 +39399,7 @@
     </row>
     <row r="171" hidden="1" outlineLevel="2" ht="375" customFormat="1" customHeight="1" s="8">
       <c r="B171" s="59" t="n"/>
-      <c r="C171" s="445" t="n"/>
+      <c r="C171" s="444" t="n"/>
       <c r="D171" s="233" t="n"/>
       <c r="E171" s="234" t="inlineStr">
         <is>
@@ -39428,7 +39451,7 @@
       <c r="K172" s="163" t="n"/>
       <c r="L172" s="164" t="n"/>
     </row>
-    <row r="173" outlineLevel="1" collapsed="1" s="479">
+    <row r="173" outlineLevel="1" collapsed="1" s="478">
       <c r="B173" s="169" t="n"/>
       <c r="C173" s="338" t="inlineStr">
         <is>
@@ -39462,7 +39485,7 @@
       <c r="K173" s="359" t="n"/>
       <c r="L173" s="359" t="n"/>
     </row>
-    <row r="174" hidden="1" outlineLevel="2" s="479">
+    <row r="174" hidden="1" outlineLevel="2" s="478">
       <c r="B174" s="169" t="n"/>
       <c r="D174" s="168" t="n"/>
       <c r="E174" s="167" t="inlineStr">
@@ -39490,7 +39513,7 @@
     </row>
     <row r="175" hidden="1" outlineLevel="2" ht="409.5" customFormat="1" customHeight="1" s="8">
       <c r="B175" s="59" t="n"/>
-      <c r="C175" s="445" t="n"/>
+      <c r="C175" s="444" t="n"/>
       <c r="D175" s="233" t="n"/>
       <c r="E175" s="234" t="inlineStr">
         <is>
@@ -39559,7 +39582,7 @@
       <c r="K176" s="163" t="n"/>
       <c r="L176" s="164" t="n"/>
     </row>
-    <row r="177" outlineLevel="1" collapsed="1" s="479">
+    <row r="177" outlineLevel="1" collapsed="1" s="478">
       <c r="B177" s="169" t="n"/>
       <c r="C177" s="338" t="inlineStr">
         <is>
@@ -39593,7 +39616,7 @@
       <c r="K177" s="359" t="n"/>
       <c r="L177" s="359" t="n"/>
     </row>
-    <row r="178" hidden="1" outlineLevel="2" s="479">
+    <row r="178" hidden="1" outlineLevel="2" s="478">
       <c r="B178" s="169" t="n"/>
       <c r="D178" s="168" t="n"/>
       <c r="E178" s="167" t="inlineStr">
@@ -39621,7 +39644,7 @@
     </row>
     <row r="179" hidden="1" outlineLevel="2" ht="409.5" customFormat="1" customHeight="1" s="8">
       <c r="B179" s="59" t="n"/>
-      <c r="C179" s="445" t="n"/>
+      <c r="C179" s="444" t="n"/>
       <c r="D179" s="233" t="n"/>
       <c r="E179" s="234" t="inlineStr">
         <is>
@@ -39683,7 +39706,7 @@
       <c r="K180" s="163" t="n"/>
       <c r="L180" s="164" t="n"/>
     </row>
-    <row r="181" outlineLevel="1" collapsed="1" s="479">
+    <row r="181" outlineLevel="1" collapsed="1" s="478">
       <c r="B181" s="169" t="n"/>
       <c r="C181" s="338" t="inlineStr">
         <is>
@@ -39717,7 +39740,7 @@
       <c r="K181" s="359" t="n"/>
       <c r="L181" s="359" t="n"/>
     </row>
-    <row r="182" hidden="1" outlineLevel="2" s="479">
+    <row r="182" hidden="1" outlineLevel="2" s="478">
       <c r="B182" s="169" t="n"/>
       <c r="D182" s="168" t="n"/>
       <c r="E182" s="167" t="inlineStr">
@@ -39745,7 +39768,7 @@
     </row>
     <row r="183" hidden="1" outlineLevel="2" ht="315" customFormat="1" customHeight="1" s="8">
       <c r="B183" s="59" t="n"/>
-      <c r="C183" s="445" t="n"/>
+      <c r="C183" s="444" t="n"/>
       <c r="D183" s="233" t="n"/>
       <c r="E183" s="234" t="inlineStr">
         <is>
@@ -39797,7 +39820,7 @@
       <c r="K184" s="163" t="n"/>
       <c r="L184" s="164" t="n"/>
     </row>
-    <row r="185" outlineLevel="1" collapsed="1" s="479">
+    <row r="185" outlineLevel="1" collapsed="1" s="478">
       <c r="B185" s="169" t="n"/>
       <c r="C185" s="338" t="inlineStr">
         <is>
@@ -39831,7 +39854,7 @@
       <c r="K185" s="359" t="n"/>
       <c r="L185" s="359" t="n"/>
     </row>
-    <row r="186" hidden="1" outlineLevel="2" s="479">
+    <row r="186" hidden="1" outlineLevel="2" s="478">
       <c r="B186" s="169" t="n"/>
       <c r="D186" s="168" t="n"/>
       <c r="E186" s="167" t="inlineStr">
@@ -39859,7 +39882,7 @@
     </row>
     <row r="187" hidden="1" outlineLevel="2" ht="405" customFormat="1" customHeight="1" s="8">
       <c r="B187" s="59" t="n"/>
-      <c r="C187" s="445" t="n"/>
+      <c r="C187" s="444" t="n"/>
       <c r="D187" s="233" t="n"/>
       <c r="E187" s="234" t="inlineStr">
         <is>
@@ -39911,7 +39934,7 @@
       <c r="K188" s="163" t="n"/>
       <c r="L188" s="164" t="n"/>
     </row>
-    <row r="189" outlineLevel="1" collapsed="1" s="479">
+    <row r="189" outlineLevel="1" collapsed="1" s="478">
       <c r="B189" s="169" t="n"/>
       <c r="C189" s="338" t="inlineStr">
         <is>
@@ -39945,7 +39968,7 @@
       <c r="K189" s="359" t="n"/>
       <c r="L189" s="359" t="n"/>
     </row>
-    <row r="190" hidden="1" outlineLevel="2" s="479">
+    <row r="190" hidden="1" outlineLevel="2" s="478">
       <c r="B190" s="169" t="n"/>
       <c r="D190" s="168" t="n"/>
       <c r="E190" s="167" t="inlineStr">
@@ -39973,7 +39996,7 @@
     </row>
     <row r="191" hidden="1" outlineLevel="2" ht="330" customFormat="1" customHeight="1" s="8">
       <c r="B191" s="59" t="n"/>
-      <c r="C191" s="445" t="n"/>
+      <c r="C191" s="444" t="n"/>
       <c r="D191" s="233" t="n"/>
       <c r="E191" s="234" t="inlineStr">
         <is>
@@ -40025,7 +40048,7 @@
       <c r="K192" s="163" t="n"/>
       <c r="L192" s="164" t="n"/>
     </row>
-    <row r="193" outlineLevel="1" collapsed="1" s="479">
+    <row r="193" outlineLevel="1" collapsed="1" s="478">
       <c r="B193" s="169" t="n"/>
       <c r="C193" s="338" t="inlineStr">
         <is>
@@ -40059,7 +40082,7 @@
       <c r="K193" s="359" t="n"/>
       <c r="L193" s="359" t="n"/>
     </row>
-    <row r="194" hidden="1" outlineLevel="2" s="479">
+    <row r="194" hidden="1" outlineLevel="2" s="478">
       <c r="B194" s="169" t="n"/>
       <c r="D194" s="166" t="n"/>
       <c r="E194" s="165" t="inlineStr">
@@ -40087,7 +40110,7 @@
     </row>
     <row r="195" hidden="1" outlineLevel="2" ht="409.5" customFormat="1" customHeight="1" s="8">
       <c r="B195" s="59" t="n"/>
-      <c r="C195" s="445" t="n"/>
+      <c r="C195" s="444" t="n"/>
       <c r="D195" s="233" t="n"/>
       <c r="E195" s="234" t="inlineStr">
         <is>
@@ -40139,7 +40162,7 @@
       <c r="K196" s="163" t="n"/>
       <c r="L196" s="164" t="n"/>
     </row>
-    <row r="197" outlineLevel="1" s="479">
+    <row r="197" outlineLevel="1" s="478">
       <c r="B197" s="169" t="n"/>
       <c r="C197" s="338" t="inlineStr">
         <is>
@@ -40176,7 +40199,7 @@
       <c r="K197" s="359" t="n"/>
       <c r="L197" s="359" t="n"/>
     </row>
-    <row r="198" outlineLevel="2" s="479">
+    <row r="198" outlineLevel="2" s="478">
       <c r="B198" s="169" t="n"/>
       <c r="D198" s="168" t="n"/>
       <c r="E198" s="167" t="inlineStr">
@@ -40202,7 +40225,7 @@
     </row>
     <row r="199" outlineLevel="2" ht="409.5" customFormat="1" customHeight="1" s="8">
       <c r="B199" s="59" t="n"/>
-      <c r="C199" s="445" t="n"/>
+      <c r="C199" s="444" t="n"/>
       <c r="D199" s="233" t="n"/>
       <c r="E199" s="234" t="inlineStr">
         <is>
@@ -40259,7 +40282,7 @@
       <c r="K200" s="163" t="n"/>
       <c r="L200" s="164" t="n"/>
     </row>
-    <row r="201" outlineLevel="1" collapsed="1" s="479">
+    <row r="201" outlineLevel="1" collapsed="1" s="478">
       <c r="B201" s="169" t="n"/>
       <c r="C201" s="338" t="inlineStr">
         <is>
@@ -40296,7 +40319,7 @@
       <c r="K201" s="359" t="n"/>
       <c r="L201" s="359" t="n"/>
     </row>
-    <row r="202" hidden="1" outlineLevel="2" s="479">
+    <row r="202" hidden="1" outlineLevel="2" s="478">
       <c r="B202" s="169" t="n"/>
       <c r="D202" s="168" t="n"/>
       <c r="E202" s="167" t="inlineStr">
@@ -40322,7 +40345,7 @@
     </row>
     <row r="203" hidden="1" outlineLevel="2" ht="390" customFormat="1" customHeight="1" s="8">
       <c r="B203" s="59" t="n"/>
-      <c r="C203" s="445" t="n"/>
+      <c r="C203" s="444" t="n"/>
       <c r="D203" s="233" t="n"/>
       <c r="E203" s="234" t="inlineStr">
         <is>
@@ -40379,7 +40402,7 @@
       <c r="K204" s="163" t="n"/>
       <c r="L204" s="164" t="n"/>
     </row>
-    <row r="205" outlineLevel="1" collapsed="1" s="479">
+    <row r="205" outlineLevel="1" collapsed="1" s="478">
       <c r="B205" s="169" t="n"/>
       <c r="C205" s="338" t="inlineStr">
         <is>
@@ -40416,7 +40439,7 @@
       <c r="K205" s="359" t="n"/>
       <c r="L205" s="359" t="n"/>
     </row>
-    <row r="206" hidden="1" outlineLevel="2" s="479">
+    <row r="206" hidden="1" outlineLevel="2" s="478">
       <c r="B206" s="169" t="n"/>
       <c r="D206" s="168" t="n"/>
       <c r="E206" s="167" t="inlineStr">
@@ -40442,7 +40465,7 @@
     </row>
     <row r="207" hidden="1" outlineLevel="2" ht="405" customFormat="1" customHeight="1" s="8">
       <c r="B207" s="59" t="n"/>
-      <c r="C207" s="445" t="n"/>
+      <c r="C207" s="444" t="n"/>
       <c r="D207" s="233" t="n"/>
       <c r="E207" s="234" t="inlineStr">
         <is>
@@ -40501,7 +40524,7 @@
       <c r="K208" s="163" t="n"/>
       <c r="L208" s="164" t="n"/>
     </row>
-    <row r="209" outlineLevel="1" collapsed="1" s="479">
+    <row r="209" outlineLevel="1" collapsed="1" s="478">
       <c r="B209" s="169" t="n"/>
       <c r="C209" s="338" t="inlineStr">
         <is>
@@ -40538,7 +40561,7 @@
       <c r="K209" s="359" t="n"/>
       <c r="L209" s="359" t="n"/>
     </row>
-    <row r="210" hidden="1" outlineLevel="2" s="479">
+    <row r="210" hidden="1" outlineLevel="2" s="478">
       <c r="B210" s="169" t="n"/>
       <c r="D210" s="168" t="n"/>
       <c r="E210" s="167" t="inlineStr">
@@ -40564,7 +40587,7 @@
     </row>
     <row r="211" hidden="1" outlineLevel="2" ht="375" customFormat="1" customHeight="1" s="8">
       <c r="B211" s="59" t="n"/>
-      <c r="C211" s="445" t="n"/>
+      <c r="C211" s="444" t="n"/>
       <c r="D211" s="233" t="n"/>
       <c r="E211" s="234" t="inlineStr">
         <is>
@@ -40621,7 +40644,7 @@
       <c r="K212" s="163" t="n"/>
       <c r="L212" s="164" t="n"/>
     </row>
-    <row r="213" outlineLevel="1" collapsed="1" s="479">
+    <row r="213" outlineLevel="1" collapsed="1" s="478">
       <c r="B213" s="169" t="n"/>
       <c r="C213" s="338" t="inlineStr">
         <is>
@@ -40658,7 +40681,7 @@
       <c r="K213" s="359" t="n"/>
       <c r="L213" s="359" t="n"/>
     </row>
-    <row r="214" hidden="1" outlineLevel="2" s="479">
+    <row r="214" hidden="1" outlineLevel="2" s="478">
       <c r="B214" s="169" t="n"/>
       <c r="D214" s="168" t="n"/>
       <c r="E214" s="167" t="inlineStr">
@@ -40682,7 +40705,7 @@
       <c r="K214" s="168" t="n"/>
       <c r="L214" s="168" t="n"/>
     </row>
-    <row r="215" hidden="1" outlineLevel="2" ht="409.5" customHeight="1" s="479">
+    <row r="215" hidden="1" outlineLevel="2" ht="409.5" customHeight="1" s="478">
       <c r="B215" s="169" t="n"/>
       <c r="D215" s="168" t="n"/>
       <c r="E215" s="234" t="inlineStr">
@@ -40753,7 +40776,7 @@
       <c r="K216" s="163" t="n"/>
       <c r="L216" s="164" t="n"/>
     </row>
-    <row r="217" outlineLevel="1" collapsed="1" s="479">
+    <row r="217" outlineLevel="1" collapsed="1" s="478">
       <c r="B217" s="169" t="n"/>
       <c r="C217" s="338" t="inlineStr">
         <is>
@@ -40790,7 +40813,7 @@
       <c r="K217" s="359" t="n"/>
       <c r="L217" s="359" t="n"/>
     </row>
-    <row r="218" hidden="1" outlineLevel="2" s="479">
+    <row r="218" hidden="1" outlineLevel="2" s="478">
       <c r="B218" s="169" t="n"/>
       <c r="D218" s="168" t="n"/>
       <c r="E218" s="167" t="inlineStr">
@@ -40814,7 +40837,7 @@
       <c r="K218" s="168" t="n"/>
       <c r="L218" s="168" t="n"/>
     </row>
-    <row r="219" hidden="1" outlineLevel="2" ht="360" customHeight="1" s="479">
+    <row r="219" hidden="1" outlineLevel="2" ht="360" customHeight="1" s="478">
       <c r="B219" s="169" t="n"/>
       <c r="D219" s="168" t="n"/>
       <c r="E219" s="270" t="inlineStr">
@@ -40850,7 +40873,7 @@
       <c r="K219" s="166" t="n"/>
       <c r="L219" s="166" t="n"/>
     </row>
-    <row r="220" hidden="1" outlineLevel="2" ht="240" customHeight="1" s="479">
+    <row r="220" hidden="1" outlineLevel="2" ht="240" customHeight="1" s="478">
       <c r="B220" s="86" t="n"/>
       <c r="D220" s="346" t="n"/>
       <c r="E220" s="218" t="inlineStr">
@@ -40875,7 +40898,7 @@
       <c r="K220" s="217" t="n"/>
       <c r="L220" s="217" t="n"/>
     </row>
-    <row r="221" outlineLevel="1" collapsed="1" s="479">
+    <row r="221" outlineLevel="1" collapsed="1" s="478">
       <c r="B221" s="86" t="n"/>
       <c r="C221" s="338" t="inlineStr">
         <is>
@@ -40906,7 +40929,7 @@
       <c r="K221" s="341" t="n"/>
       <c r="L221" s="338" t="n"/>
     </row>
-    <row r="222" hidden="1" outlineLevel="2" s="479">
+    <row r="222" hidden="1" outlineLevel="2" s="478">
       <c r="B222" s="86" t="n"/>
       <c r="D222" s="345" t="n"/>
       <c r="E222" s="218" t="inlineStr">
@@ -40928,7 +40951,7 @@
       <c r="K222" s="343" t="n"/>
       <c r="L222" s="217" t="n"/>
     </row>
-    <row r="223" hidden="1" outlineLevel="2" ht="75" customHeight="1" s="479">
+    <row r="223" hidden="1" outlineLevel="2" ht="75" customHeight="1" s="478">
       <c r="B223" s="86" t="n"/>
       <c r="D223" s="328" t="n"/>
       <c r="E223" s="218" t="inlineStr">
@@ -40957,7 +40980,7 @@
       <c r="K223" s="372" t="n"/>
       <c r="L223" s="217" t="n"/>
     </row>
-    <row r="224" hidden="1" outlineLevel="2" ht="330" customHeight="1" s="479">
+    <row r="224" hidden="1" outlineLevel="2" ht="330" customHeight="1" s="478">
       <c r="B224" s="86" t="n"/>
       <c r="D224" s="346" t="n"/>
       <c r="E224" s="218" t="inlineStr">
@@ -40984,7 +41007,7 @@
       <c r="K224" s="217" t="n"/>
       <c r="L224" s="217" t="n"/>
     </row>
-    <row r="225" outlineLevel="1" collapsed="1" s="479">
+    <row r="225" outlineLevel="1" collapsed="1" s="478">
       <c r="B225" s="86" t="n"/>
       <c r="C225" s="338" t="inlineStr">
         <is>
@@ -41015,7 +41038,7 @@
       <c r="K225" s="341" t="n"/>
       <c r="L225" s="338" t="n"/>
     </row>
-    <row r="226" hidden="1" outlineLevel="2" s="479">
+    <row r="226" hidden="1" outlineLevel="2" s="478">
       <c r="B226" s="86" t="n"/>
       <c r="D226" s="345" t="n"/>
       <c r="E226" s="218" t="inlineStr">
@@ -41035,7 +41058,7 @@
       <c r="K226" s="343" t="n"/>
       <c r="L226" s="217" t="n"/>
     </row>
-    <row r="227" hidden="1" outlineLevel="2" ht="120" customHeight="1" s="479">
+    <row r="227" hidden="1" outlineLevel="2" ht="120" customHeight="1" s="478">
       <c r="B227" s="86" t="n"/>
       <c r="D227" s="328" t="n"/>
       <c r="E227" s="218" t="inlineStr">
@@ -41066,7 +41089,7 @@
       <c r="K227" s="372" t="n"/>
       <c r="L227" s="217" t="n"/>
     </row>
-    <row r="228" hidden="1" outlineLevel="2" ht="270" customHeight="1" s="479">
+    <row r="228" hidden="1" outlineLevel="2" ht="270" customHeight="1" s="478">
       <c r="B228" s="86" t="n"/>
       <c r="D228" s="346" t="n"/>
       <c r="E228" s="218" t="inlineStr">
@@ -41112,7 +41135,7 @@
       <c r="K229" s="163" t="n"/>
       <c r="L229" s="164" t="n"/>
     </row>
-    <row r="230" outlineLevel="1" collapsed="1" s="479">
+    <row r="230" outlineLevel="1" collapsed="1" s="478">
       <c r="B230" s="169" t="n"/>
       <c r="C230" s="338" t="inlineStr">
         <is>
@@ -41149,7 +41172,7 @@
       <c r="K230" s="359" t="n"/>
       <c r="L230" s="359" t="n"/>
     </row>
-    <row r="231" hidden="1" outlineLevel="2" s="479">
+    <row r="231" hidden="1" outlineLevel="2" s="478">
       <c r="B231" s="169" t="n"/>
       <c r="D231" s="168" t="n"/>
       <c r="E231" s="167" t="inlineStr">
@@ -41173,7 +41196,7 @@
       <c r="K231" s="168" t="n"/>
       <c r="L231" s="168" t="n"/>
     </row>
-    <row r="232" hidden="1" outlineLevel="2" ht="390" customHeight="1" s="479">
+    <row r="232" hidden="1" outlineLevel="2" ht="390" customHeight="1" s="478">
       <c r="B232" s="169" t="n"/>
       <c r="D232" s="168" t="n"/>
       <c r="E232" s="234" t="inlineStr">
@@ -41231,7 +41254,7 @@
       <c r="K233" s="163" t="n"/>
       <c r="L233" s="164" t="n"/>
     </row>
-    <row r="234" outlineLevel="1" collapsed="1" s="479">
+    <row r="234" outlineLevel="1" collapsed="1" s="478">
       <c r="B234" s="169" t="n"/>
       <c r="C234" s="338" t="inlineStr">
         <is>
@@ -41268,7 +41291,7 @@
       <c r="K234" s="359" t="n"/>
       <c r="L234" s="359" t="n"/>
     </row>
-    <row r="235" hidden="1" outlineLevel="2" s="479">
+    <row r="235" hidden="1" outlineLevel="2" s="478">
       <c r="B235" s="169" t="n"/>
       <c r="D235" s="168" t="n"/>
       <c r="E235" s="167" t="inlineStr">
@@ -41292,7 +41315,7 @@
       <c r="K235" s="168" t="n"/>
       <c r="L235" s="168" t="n"/>
     </row>
-    <row r="236" hidden="1" outlineLevel="2" ht="390" customHeight="1" s="479">
+    <row r="236" hidden="1" outlineLevel="2" ht="390" customHeight="1" s="478">
       <c r="B236" s="169" t="n"/>
       <c r="D236" s="168" t="n"/>
       <c r="E236" s="234" t="inlineStr">
@@ -41350,7 +41373,7 @@
       <c r="K237" s="163" t="n"/>
       <c r="L237" s="164" t="n"/>
     </row>
-    <row r="238" outlineLevel="1" collapsed="1" s="479">
+    <row r="238" outlineLevel="1" collapsed="1" s="478">
       <c r="B238" s="169" t="n"/>
       <c r="C238" s="338" t="inlineStr">
         <is>
@@ -41387,7 +41410,7 @@
       <c r="K238" s="359" t="n"/>
       <c r="L238" s="359" t="n"/>
     </row>
-    <row r="239" hidden="1" outlineLevel="2" s="479">
+    <row r="239" hidden="1" outlineLevel="2" s="478">
       <c r="B239" s="169" t="n"/>
       <c r="D239" s="168" t="n"/>
       <c r="E239" s="167" t="inlineStr">
@@ -41411,7 +41434,7 @@
       <c r="K239" s="168" t="n"/>
       <c r="L239" s="168" t="n"/>
     </row>
-    <row r="240" hidden="1" outlineLevel="2" ht="375" customHeight="1" s="479">
+    <row r="240" hidden="1" outlineLevel="2" ht="375" customHeight="1" s="478">
       <c r="B240" s="169" t="n"/>
       <c r="D240" s="168" t="n"/>
       <c r="E240" s="234" t="inlineStr">
@@ -41469,7 +41492,7 @@
       <c r="K241" s="163" t="n"/>
       <c r="L241" s="164" t="n"/>
     </row>
-    <row r="242" outlineLevel="1" collapsed="1" s="479">
+    <row r="242" outlineLevel="1" collapsed="1" s="478">
       <c r="B242" s="169" t="n"/>
       <c r="C242" s="338" t="inlineStr">
         <is>
@@ -41506,7 +41529,7 @@
       <c r="K242" s="359" t="n"/>
       <c r="L242" s="359" t="n"/>
     </row>
-    <row r="243" hidden="1" outlineLevel="2" s="479">
+    <row r="243" hidden="1" outlineLevel="2" s="478">
       <c r="B243" s="169" t="n"/>
       <c r="D243" s="168" t="n"/>
       <c r="E243" s="167" t="inlineStr">
@@ -41530,7 +41553,7 @@
       <c r="K243" s="168" t="n"/>
       <c r="L243" s="168" t="n"/>
     </row>
-    <row r="244" hidden="1" outlineLevel="2" ht="405" customHeight="1" s="479">
+    <row r="244" hidden="1" outlineLevel="2" ht="405" customHeight="1" s="478">
       <c r="B244" s="169" t="n"/>
       <c r="D244" s="168" t="n"/>
       <c r="E244" s="234" t="inlineStr">
@@ -41588,7 +41611,7 @@
       <c r="K245" s="163" t="n"/>
       <c r="L245" s="164" t="n"/>
     </row>
-    <row r="246" outlineLevel="1" collapsed="1" s="479">
+    <row r="246" outlineLevel="1" collapsed="1" s="478">
       <c r="B246" s="169" t="n"/>
       <c r="C246" s="338" t="inlineStr">
         <is>
@@ -41625,7 +41648,7 @@
       <c r="K246" s="359" t="n"/>
       <c r="L246" s="359" t="n"/>
     </row>
-    <row r="247" hidden="1" outlineLevel="2" s="479">
+    <row r="247" hidden="1" outlineLevel="2" s="478">
       <c r="B247" s="169" t="n"/>
       <c r="D247" s="168" t="n"/>
       <c r="E247" s="167" t="inlineStr">
@@ -41649,7 +41672,7 @@
       <c r="K247" s="168" t="n"/>
       <c r="L247" s="168" t="n"/>
     </row>
-    <row r="248" hidden="1" outlineLevel="2" ht="409.5" customHeight="1" s="479">
+    <row r="248" hidden="1" outlineLevel="2" ht="409.5" customHeight="1" s="478">
       <c r="B248" s="169" t="n"/>
       <c r="D248" s="168" t="n"/>
       <c r="E248" s="234" t="inlineStr">
@@ -41721,7 +41744,7 @@
       <c r="K249" s="163" t="n"/>
       <c r="L249" s="164" t="n"/>
     </row>
-    <row r="250" outlineLevel="1" collapsed="1" s="479">
+    <row r="250" outlineLevel="1" collapsed="1" s="478">
       <c r="B250" s="169" t="n"/>
       <c r="C250" s="338" t="inlineStr">
         <is>
@@ -41758,7 +41781,7 @@
       <c r="K250" s="359" t="n"/>
       <c r="L250" s="359" t="n"/>
     </row>
-    <row r="251" hidden="1" outlineLevel="2" s="479">
+    <row r="251" hidden="1" outlineLevel="2" s="478">
       <c r="B251" s="169" t="n"/>
       <c r="D251" s="168" t="n"/>
       <c r="E251" s="167" t="inlineStr">
@@ -41782,7 +41805,7 @@
       <c r="K251" s="168" t="n"/>
       <c r="L251" s="168" t="n"/>
     </row>
-    <row r="252" hidden="1" outlineLevel="2" ht="360" customHeight="1" s="479">
+    <row r="252" hidden="1" outlineLevel="2" ht="360" customHeight="1" s="478">
       <c r="B252" s="169" t="n"/>
       <c r="D252" s="168" t="n"/>
       <c r="E252" s="234" t="inlineStr">
@@ -41840,7 +41863,7 @@
       <c r="K253" s="163" t="n"/>
       <c r="L253" s="164" t="n"/>
     </row>
-    <row r="254" outlineLevel="1" collapsed="1" s="479">
+    <row r="254" outlineLevel="1" collapsed="1" s="478">
       <c r="B254" s="169" t="n"/>
       <c r="C254" s="338" t="inlineStr">
         <is>
@@ -41877,7 +41900,7 @@
       <c r="K254" s="359" t="n"/>
       <c r="L254" s="359" t="n"/>
     </row>
-    <row r="255" hidden="1" outlineLevel="2" s="479">
+    <row r="255" hidden="1" outlineLevel="2" s="478">
       <c r="B255" s="169" t="n"/>
       <c r="D255" s="168" t="n"/>
       <c r="E255" s="167" t="inlineStr">
@@ -41901,7 +41924,7 @@
       <c r="K255" s="168" t="n"/>
       <c r="L255" s="168" t="n"/>
     </row>
-    <row r="256" hidden="1" outlineLevel="2" ht="375" customHeight="1" s="479">
+    <row r="256" hidden="1" outlineLevel="2" ht="375" customHeight="1" s="478">
       <c r="B256" s="169" t="n"/>
       <c r="D256" s="168" t="n"/>
       <c r="E256" s="234" t="inlineStr">
@@ -41959,7 +41982,7 @@
       <c r="K257" s="163" t="n"/>
       <c r="L257" s="164" t="n"/>
     </row>
-    <row r="258" outlineLevel="1" collapsed="1" s="479">
+    <row r="258" outlineLevel="1" collapsed="1" s="478">
       <c r="B258" s="169" t="n"/>
       <c r="C258" s="338" t="inlineStr">
         <is>
@@ -41996,7 +42019,7 @@
       <c r="K258" s="359" t="n"/>
       <c r="L258" s="359" t="n"/>
     </row>
-    <row r="259" hidden="1" outlineLevel="2" s="479">
+    <row r="259" hidden="1" outlineLevel="2" s="478">
       <c r="B259" s="169" t="n"/>
       <c r="D259" s="166" t="n"/>
       <c r="E259" s="165" t="inlineStr">
@@ -42016,7 +42039,7 @@
       <c r="K259" s="166" t="n"/>
       <c r="L259" s="166" t="n"/>
     </row>
-    <row r="260" hidden="1" outlineLevel="2" ht="390" customHeight="1" s="479">
+    <row r="260" hidden="1" outlineLevel="2" ht="390" customHeight="1" s="478">
       <c r="B260" s="169" t="n"/>
       <c r="D260" s="168" t="n"/>
       <c r="E260" s="234" t="inlineStr">
@@ -42074,7 +42097,7 @@
       <c r="K261" s="163" t="n"/>
       <c r="L261" s="164" t="n"/>
     </row>
-    <row r="262" outlineLevel="1" collapsed="1" s="479">
+    <row r="262" outlineLevel="1" collapsed="1" s="478">
       <c r="B262" s="169" t="n"/>
       <c r="C262" s="338" t="inlineStr">
         <is>
@@ -42108,7 +42131,7 @@
       <c r="K262" s="359" t="n"/>
       <c r="L262" s="359" t="n"/>
     </row>
-    <row r="263" hidden="1" outlineLevel="2" s="479">
+    <row r="263" hidden="1" outlineLevel="2" s="478">
       <c r="B263" s="169" t="n"/>
       <c r="D263" s="168" t="n"/>
       <c r="E263" s="167" t="inlineStr">
@@ -42130,7 +42153,7 @@
       <c r="K263" s="168" t="n"/>
       <c r="L263" s="168" t="n"/>
     </row>
-    <row r="264" hidden="1" outlineLevel="2" ht="409.5" customHeight="1" s="479">
+    <row r="264" hidden="1" outlineLevel="2" ht="409.5" customHeight="1" s="478">
       <c r="B264" s="169" t="n"/>
       <c r="D264" s="168" t="n"/>
       <c r="E264" s="234" t="inlineStr">
@@ -42188,7 +42211,7 @@
       <c r="K265" s="163" t="n"/>
       <c r="L265" s="164" t="n"/>
     </row>
-    <row r="266" outlineLevel="1" collapsed="1" s="479">
+    <row r="266" outlineLevel="1" collapsed="1" s="478">
       <c r="B266" s="169" t="n"/>
       <c r="C266" s="338" t="inlineStr">
         <is>
@@ -42222,7 +42245,7 @@
       <c r="K266" s="359" t="n"/>
       <c r="L266" s="359" t="n"/>
     </row>
-    <row r="267" hidden="1" outlineLevel="2" s="479">
+    <row r="267" hidden="1" outlineLevel="2" s="478">
       <c r="B267" s="169" t="n"/>
       <c r="D267" s="168" t="n"/>
       <c r="E267" s="167" t="inlineStr">
@@ -42244,7 +42267,7 @@
       <c r="K267" s="168" t="n"/>
       <c r="L267" s="168" t="n"/>
     </row>
-    <row r="268" hidden="1" outlineLevel="2" ht="409.5" customHeight="1" s="479">
+    <row r="268" hidden="1" outlineLevel="2" ht="409.5" customHeight="1" s="478">
       <c r="B268" s="169" t="n"/>
       <c r="D268" s="168" t="n"/>
       <c r="E268" s="234" t="inlineStr">
@@ -42285,7 +42308,7 @@
       <c r="K268" s="237" t="n"/>
       <c r="L268" s="238" t="n"/>
     </row>
-    <row r="269" hidden="1" outlineLevel="2" ht="409.5" customHeight="1" s="479">
+    <row r="269" hidden="1" outlineLevel="2" ht="409.5" customHeight="1" s="478">
       <c r="A269" s="103" t="n"/>
       <c r="B269" s="175" t="n"/>
       <c r="C269" s="104" t="n"/>
@@ -42324,7 +42347,7 @@
       <c r="K269" s="217" t="n"/>
       <c r="L269" s="217" t="n"/>
     </row>
-    <row r="270" outlineLevel="1" collapsed="1" s="479">
+    <row r="270" outlineLevel="1" collapsed="1" s="478">
       <c r="A270" s="373" t="n"/>
       <c r="B270" s="374" t="n"/>
       <c r="C270" s="338" t="inlineStr">
@@ -42356,7 +42379,7 @@
       <c r="K270" s="341" t="n"/>
       <c r="L270" s="338" t="n"/>
     </row>
-    <row r="271" hidden="1" outlineLevel="2" s="479">
+    <row r="271" hidden="1" outlineLevel="2" s="478">
       <c r="A271" s="103" t="n"/>
       <c r="B271" s="175" t="n"/>
       <c r="C271" s="104" t="n"/>
@@ -42378,7 +42401,7 @@
       <c r="K271" s="343" t="n"/>
       <c r="L271" s="217" t="n"/>
     </row>
-    <row r="272" hidden="1" outlineLevel="2" ht="150" customHeight="1" s="479">
+    <row r="272" hidden="1" outlineLevel="2" ht="150" customHeight="1" s="478">
       <c r="A272" s="103" t="n"/>
       <c r="B272" s="175" t="n"/>
       <c r="C272" s="104" t="n"/>
@@ -42416,7 +42439,7 @@
       <c r="K272" s="343" t="n"/>
       <c r="L272" s="217" t="n"/>
     </row>
-    <row r="273" hidden="1" outlineLevel="2" ht="345" customHeight="1" s="479">
+    <row r="273" hidden="1" outlineLevel="2" ht="345" customHeight="1" s="478">
       <c r="A273" s="103" t="n"/>
       <c r="B273" s="175" t="n"/>
       <c r="C273" s="104" t="n"/>
@@ -42468,7 +42491,7 @@
       <c r="K274" s="163" t="n"/>
       <c r="L274" s="164" t="n"/>
     </row>
-    <row r="275" outlineLevel="1" collapsed="1" s="479">
+    <row r="275" outlineLevel="1" collapsed="1" s="478">
       <c r="B275" s="169" t="n"/>
       <c r="C275" s="338" t="inlineStr">
         <is>
@@ -42502,7 +42525,7 @@
       <c r="K275" s="359" t="n"/>
       <c r="L275" s="359" t="n"/>
     </row>
-    <row r="276" hidden="1" outlineLevel="2" s="479">
+    <row r="276" hidden="1" outlineLevel="2" s="478">
       <c r="B276" s="169" t="n"/>
       <c r="D276" s="168" t="n"/>
       <c r="E276" s="167" t="inlineStr">
@@ -42524,7 +42547,7 @@
       <c r="K276" s="168" t="n"/>
       <c r="L276" s="168" t="n"/>
     </row>
-    <row r="277" hidden="1" outlineLevel="2" ht="405" customHeight="1" s="479">
+    <row r="277" hidden="1" outlineLevel="2" ht="405" customHeight="1" s="478">
       <c r="B277" s="169" t="n"/>
       <c r="D277" s="168" t="n"/>
       <c r="E277" s="234" t="inlineStr">
@@ -42577,7 +42600,7 @@
       <c r="K278" s="163" t="n"/>
       <c r="L278" s="164" t="n"/>
     </row>
-    <row r="279" outlineLevel="1" collapsed="1" s="479">
+    <row r="279" outlineLevel="1" collapsed="1" s="478">
       <c r="B279" s="169" t="n"/>
       <c r="C279" s="338" t="inlineStr">
         <is>
@@ -42611,7 +42634,7 @@
       <c r="K279" s="359" t="n"/>
       <c r="L279" s="359" t="n"/>
     </row>
-    <row r="280" hidden="1" outlineLevel="2" s="479">
+    <row r="280" hidden="1" outlineLevel="2" s="478">
       <c r="B280" s="169" t="n"/>
       <c r="D280" s="168" t="n"/>
       <c r="E280" s="167" t="inlineStr">
@@ -42633,7 +42656,7 @@
       <c r="K280" s="168" t="n"/>
       <c r="L280" s="168" t="n"/>
     </row>
-    <row r="281" hidden="1" outlineLevel="2" ht="390" customHeight="1" s="479">
+    <row r="281" hidden="1" outlineLevel="2" ht="390" customHeight="1" s="478">
       <c r="B281" s="169" t="n"/>
       <c r="D281" s="168" t="n"/>
       <c r="E281" s="234" t="inlineStr">
@@ -42686,7 +42709,7 @@
       <c r="K282" s="163" t="n"/>
       <c r="L282" s="164" t="n"/>
     </row>
-    <row r="283" outlineLevel="1" collapsed="1" s="479">
+    <row r="283" outlineLevel="1" collapsed="1" s="478">
       <c r="B283" s="169" t="n"/>
       <c r="C283" s="338" t="inlineStr">
         <is>
@@ -42720,7 +42743,7 @@
       <c r="K283" s="359" t="n"/>
       <c r="L283" s="359" t="n"/>
     </row>
-    <row r="284" hidden="1" outlineLevel="2" s="479">
+    <row r="284" hidden="1" outlineLevel="2" s="478">
       <c r="B284" s="169" t="n"/>
       <c r="D284" s="166" t="n"/>
       <c r="E284" s="165" t="inlineStr">
@@ -42744,7 +42767,7 @@
       <c r="K284" s="166" t="n"/>
       <c r="L284" s="166" t="n"/>
     </row>
-    <row r="285" hidden="1" outlineLevel="2" ht="375" customHeight="1" s="479">
+    <row r="285" hidden="1" outlineLevel="2" ht="375" customHeight="1" s="478">
       <c r="B285" s="169" t="n"/>
       <c r="D285" s="168" t="n"/>
       <c r="E285" s="234" t="inlineStr">

--- a/DB Flotte ETR1000 Ver_1.8_PROVA.xlsx
+++ b/DB Flotte ETR1000 Ver_1.8_PROVA.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="Questa_cartella_di_lavoro"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="600" firstSheet="5" activeTab="8" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="600" firstSheet="5" activeTab="9" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issue" sheetId="1" state="visible" r:id="rId1"/>
@@ -22,7 +22,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Modifiche progettuali" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Requisiti'!$A$1:$K$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Requisiti'!$A$1:$K$53</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'PBS (TBD)'!$A$2:$J$86</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -34,7 +34,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-410]mmm\-yy;@"/>
   </numFmts>
-  <fonts count="36">
+  <fonts count="37">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -279,6 +279,9 @@
     </font>
     <font>
       <color rgb="00BF8F00"/>
+    </font>
+    <font>
+      <color rgb="001F4E79"/>
     </font>
     <font>
       <color rgb="0000AA00"/>
@@ -1480,7 +1483,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="524">
+  <cellXfs count="525">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2853,10 +2856,13 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3820,8 +3826,8 @@
   <cols>
     <col width="10.85546875" customWidth="1" style="8" min="1" max="2"/>
     <col width="59" customWidth="1" style="8" min="3" max="3"/>
-    <col width="8.7109375" customWidth="1" style="8" min="4" max="13"/>
-    <col width="8.7109375" customWidth="1" style="8" min="14" max="16384"/>
+    <col width="8.7109375" customWidth="1" style="8" min="4" max="14"/>
+    <col width="8.7109375" customWidth="1" style="8" min="15" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" s="107">
@@ -3940,7 +3946,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K75"/>
+  <dimension ref="A1:K82"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="22.140625" bestFit="1" customWidth="1" style="62" min="1" max="1"/>
@@ -3951,8 +3957,8 @@
     <col width="14.85546875" customWidth="1" style="10" min="10" max="11"/>
     <col width="8.7109375" customWidth="1" style="59" min="12" max="12"/>
     <col width="33.140625" customWidth="1" style="59" min="13" max="13"/>
-    <col width="8.7109375" customWidth="1" style="59" min="14" max="17"/>
-    <col width="8.7109375" customWidth="1" style="59" min="18" max="16384"/>
+    <col width="8.7109375" customWidth="1" style="59" min="14" max="18"/>
+    <col width="8.7109375" customWidth="1" style="59" min="19" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" s="61">
@@ -4061,6 +4067,47 @@
         </is>
       </c>
       <c r="D4" s="421" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00BF8F00"/>
+            </rPr>
+            <t>VZI-6_R1</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+            </rPr>
+            <t xml:space="preserve">, </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="001F4E79"/>
+            </rPr>
+            <t>VZI_Base</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+            </rPr>
+            <t xml:space="preserve">, </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="0000703C"/>
+            </rPr>
+            <t>VZ_FR</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customFormat="1" customHeight="1" s="8">
+      <c r="C5" s="523" t="inlineStr">
+        <is>
+          <t>2F_04.01.Zefiro-Europe.CONCEPT.775</t>
+        </is>
+      </c>
+      <c r="D5" s="421" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4107,13 +4154,13 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customFormat="1" customHeight="1" s="8">
-      <c r="C5" s="523" t="inlineStr">
-        <is>
-          <t>2F_04.01.Zefiro-</t>
-        </is>
-      </c>
-      <c r="D5" s="421" t="inlineStr">
+    <row r="6" ht="30" customFormat="1" customHeight="1" s="8">
+      <c r="C6" s="523" t="inlineStr">
+        <is>
+          <t>2F_04.01.Zefiro-Europe.CONCEPT.965</t>
+        </is>
+      </c>
+      <c r="D6" s="421" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4160,13 +4207,13 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="30" customFormat="1" customHeight="1" s="8">
-      <c r="C6" s="523" t="inlineStr">
-        <is>
-          <t>4S_09.03.05.-.TCMS</t>
-        </is>
-      </c>
-      <c r="D6" s="421" t="inlineStr">
+    <row r="7" ht="30" customFormat="1" customHeight="1" s="8">
+      <c r="C7" s="523" t="inlineStr">
+        <is>
+          <t>2F_04.01.Zefiro-Europe.CONCEPT.1013</t>
+        </is>
+      </c>
+      <c r="D7" s="421" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4213,216 +4260,211 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customFormat="1" customHeight="1" s="8">
-      <c r="C7" s="523" t="inlineStr">
-        <is>
-          <t>4S_04.-.Power</t>
-        </is>
-      </c>
-      <c r="D7" s="523" t="inlineStr">
+    <row r="8" ht="30" customFormat="1" customHeight="1" s="8">
+      <c r="C8" s="523" t="inlineStr">
+        <is>
+          <t>2F_04.01.Zefiro-Europe.CONCEPT.HR01</t>
+        </is>
+      </c>
+      <c r="D8" s="523" t="inlineStr">
         <is>
           <t>VZI-6_R1</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="45" customFormat="1" customHeight="1" s="8">
-      <c r="A8" s="347" t="inlineStr">
+    <row r="9" ht="30" customFormat="1" customHeight="1" s="8">
+      <c r="C9" s="523" t="inlineStr">
+        <is>
+          <t>2F_04.01.Zefiro-Europe.CONCEPT.HR310</t>
+        </is>
+      </c>
+      <c r="D9" s="523" t="inlineStr">
+        <is>
+          <t>VZI-6_R1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customFormat="1" customHeight="1" s="8">
+      <c r="C10" s="523" t="inlineStr">
+        <is>
+          <t>2F_04.01.Zefiro-Europe.CONCEPT.797</t>
+        </is>
+      </c>
+      <c r="D10" s="421" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00BF8F00"/>
+            </rPr>
+            <t>VZI-6_R1</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+            </rPr>
+            <t xml:space="preserve">, </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="001F4E79"/>
+            </rPr>
+            <t>VZI_Base</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+            </rPr>
+            <t xml:space="preserve">, </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="007030A0"/>
+            </rPr>
+            <t>VZ_ES</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+            </rPr>
+            <t xml:space="preserve">, </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="0000703C"/>
+            </rPr>
+            <t>VZ_FR</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customFormat="1" customHeight="1" s="8">
+      <c r="C11" s="523" t="inlineStr">
+        <is>
+          <t>2F_04.01.Zefiro-Europe.CONCEPT.HR02</t>
+        </is>
+      </c>
+      <c r="D11" s="523" t="inlineStr">
+        <is>
+          <t>VZI-6_R1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customFormat="1" customHeight="1" s="8">
+      <c r="C12" s="523" t="inlineStr">
+        <is>
+          <t>2F_04.01.Zefiro-Europe.CONCEPT.HR03</t>
+        </is>
+      </c>
+      <c r="D12" s="523" t="inlineStr">
+        <is>
+          <t>VZI-6_R1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customFormat="1" customHeight="1" s="8">
+      <c r="C13" s="524" t="inlineStr">
+        <is>
+          <t>2F_04.01.Zefiro-Europe.TRS.619</t>
+        </is>
+      </c>
+      <c r="D13" s="421" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="001F4E79"/>
+            </rPr>
+            <t>VZI_Base</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+            </rPr>
+            <t xml:space="preserve">, </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="007030A0"/>
+            </rPr>
+            <t>VZ_ES</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+            </rPr>
+            <t xml:space="preserve">, </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="0000703C"/>
+            </rPr>
+            <t>VZ_FR</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customFormat="1" customHeight="1" s="8">
+      <c r="C14" s="524" t="inlineStr">
+        <is>
+          <t>2F_04.01.Zefiro-Europe.CONCEPT.735</t>
+        </is>
+      </c>
+      <c r="D14" s="524" t="inlineStr">
+        <is>
+          <t>VZI_Base</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customFormat="1" customHeight="1" s="8">
+      <c r="A15" s="347" t="inlineStr">
         <is>
           <t>LV_Pantograph_Lifting</t>
         </is>
       </c>
-      <c r="B8" s="347" t="inlineStr">
+      <c r="B15" s="347" t="inlineStr">
         <is>
           <t>Comando di alzamento pantografo 1 o 2 sulla base di tensione di linea (switch) e paese (IDU) selezionati</t>
         </is>
       </c>
-      <c r="C8" s="303" t="n"/>
-      <c r="D8" s="303" t="n"/>
-      <c r="E8" s="350" t="n"/>
-      <c r="F8" s="350" t="n"/>
-      <c r="G8" s="350" t="n"/>
-      <c r="H8" s="350" t="n"/>
-      <c r="I8" s="350" t="n"/>
-      <c r="J8" s="350" t="n"/>
-      <c r="K8" s="351" t="n"/>
-    </row>
-    <row r="9" ht="30" customFormat="1" customHeight="1" s="8">
-      <c r="A9" s="347" t="inlineStr">
+      <c r="C15" s="303" t="n"/>
+      <c r="D15" s="303" t="n"/>
+      <c r="E15" s="350" t="n"/>
+      <c r="F15" s="350" t="n"/>
+      <c r="G15" s="350" t="n"/>
+      <c r="H15" s="350" t="n"/>
+      <c r="I15" s="350" t="n"/>
+      <c r="J15" s="350" t="n"/>
+      <c r="K15" s="351" t="n"/>
+    </row>
+    <row r="16" ht="30" customFormat="1" customHeight="1" s="8">
+      <c r="A16" s="347" t="inlineStr">
         <is>
           <t>LV_Pantograph_Lowering</t>
         </is>
       </c>
-      <c r="B9" s="347" t="inlineStr">
+      <c r="B16" s="347" t="inlineStr">
         <is>
           <t>Comando di abbassamento pantografo manuale/automatico</t>
         </is>
       </c>
-      <c r="C9" s="303" t="n"/>
-      <c r="D9" s="303" t="n"/>
-      <c r="E9" s="350" t="n"/>
-      <c r="F9" s="350" t="n"/>
-      <c r="G9" s="350" t="n"/>
-      <c r="H9" s="350" t="n"/>
-      <c r="I9" s="350" t="n"/>
-      <c r="J9" s="350" t="n"/>
-      <c r="K9" s="351" t="n"/>
-    </row>
-    <row r="10" ht="30" customFormat="1" customHeight="1" s="8">
-      <c r="A10" s="353" t="inlineStr">
-        <is>
-          <t>LV_Automatic_Dropping_Device_(ADD)</t>
-        </is>
-      </c>
-      <c r="B10" s="354" t="inlineStr">
-        <is>
-          <t>Dispositivo di abbassamento automatico del pantografo in caso di guasto</t>
-        </is>
-      </c>
-      <c r="C10" s="302" t="n"/>
-      <c r="D10" s="302" t="n"/>
-      <c r="E10" s="357" t="n"/>
-      <c r="F10" s="357" t="n"/>
-      <c r="G10" s="357" t="n"/>
-      <c r="H10" s="357" t="n"/>
-      <c r="I10" s="357" t="n"/>
-      <c r="J10" s="357" t="n"/>
-      <c r="K10" s="358" t="n"/>
-    </row>
-    <row r="11" ht="30" customFormat="1" customHeight="1" s="8">
-      <c r="A11" s="353" t="inlineStr">
-        <is>
-          <t>LV_Pantograph_Interlock</t>
-        </is>
-      </c>
-      <c r="B11" s="360" t="inlineStr">
-        <is>
-          <t>Interblocco automatico dei pantografi in caso di guasto rilevato. Il Pdc può bloccare anche manualmente un pantografo per impedirne la selezione</t>
-        </is>
-      </c>
-      <c r="C11" s="302" t="n"/>
-      <c r="D11" s="302" t="n"/>
-      <c r="E11" s="357" t="n"/>
-      <c r="F11" s="357" t="n"/>
-      <c r="G11" s="357" t="n"/>
-      <c r="H11" s="357" t="n"/>
-      <c r="I11" s="357" t="n"/>
-      <c r="J11" s="357" t="n"/>
-      <c r="K11" s="358" t="n"/>
-    </row>
-    <row r="12" ht="30" customFormat="1" customHeight="1" s="8">
-      <c r="A12" s="353" t="inlineStr">
-        <is>
-          <t>LV_Pantograph_Selection</t>
-        </is>
-      </c>
-      <c r="B12" s="360" t="inlineStr">
-        <is>
-          <t>Selezione del pantografo in base al paese (tipologia/dimensioni pantografo) e al sistema di alimentazione (AC/DC) selezionato</t>
-        </is>
-      </c>
-      <c r="C12" s="302" t="n"/>
-      <c r="D12" s="302" t="n"/>
-      <c r="E12" s="357" t="n"/>
-      <c r="F12" s="357" t="n"/>
-      <c r="G12" s="357" t="n"/>
-      <c r="H12" s="357" t="n"/>
-      <c r="I12" s="357" t="n"/>
-      <c r="J12" s="357" t="n"/>
-      <c r="K12" s="358" t="n"/>
-    </row>
-    <row r="13" ht="30" customFormat="1" customHeight="1" s="8">
-      <c r="A13" s="353" t="inlineStr">
-        <is>
-          <t>LV_Pantograph_Control_of_Static_Contact_Force</t>
-        </is>
-      </c>
-      <c r="B13" s="360" t="inlineStr">
-        <is>
-          <t>Controllo della forza statica/pressione del pantografo alzato in funzione del sistema di tensione, della velocità, della direzione di marcia e della posizione del pantografo stesso</t>
-        </is>
-      </c>
-      <c r="C13" s="302" t="n"/>
-      <c r="D13" s="302" t="n"/>
-      <c r="E13" s="357" t="n"/>
-      <c r="F13" s="357" t="n"/>
-      <c r="G13" s="357" t="n"/>
-      <c r="H13" s="357" t="n"/>
-      <c r="I13" s="357" t="n"/>
-      <c r="J13" s="357" t="n"/>
-      <c r="K13" s="358" t="n"/>
-    </row>
-    <row r="14" ht="30" customFormat="1" customHeight="1" s="8">
-      <c r="A14" s="353" t="inlineStr">
-        <is>
-          <t>LV_Line_Voltage_Supervision</t>
-        </is>
-      </c>
-      <c r="B14" s="360" t="inlineStr">
-        <is>
-          <t>Controllo della tensione di linea tramite sensori di tensione letti dal sistema di propulsione</t>
-        </is>
-      </c>
-      <c r="C14" s="302" t="n"/>
-      <c r="D14" s="302" t="n"/>
-      <c r="E14" s="357" t="n"/>
-      <c r="F14" s="357" t="n"/>
-      <c r="G14" s="357" t="n"/>
-      <c r="H14" s="357" t="n"/>
-      <c r="I14" s="357" t="n"/>
-      <c r="J14" s="357" t="n"/>
-      <c r="K14" s="358" t="n"/>
-    </row>
-    <row r="15" ht="30" customFormat="1" customHeight="1" s="8">
-      <c r="A15" s="353" t="inlineStr">
-        <is>
-          <t>LV_Line_Current_Supervision</t>
-        </is>
-      </c>
-      <c r="B15" s="360" t="inlineStr">
-        <is>
-          <t>Controllo della corrente di linea</t>
-        </is>
-      </c>
-      <c r="C15" s="302" t="n"/>
-      <c r="D15" s="302" t="n"/>
-      <c r="E15" s="357" t="n"/>
-      <c r="F15" s="357" t="n"/>
-      <c r="G15" s="357" t="n"/>
-      <c r="H15" s="357" t="n"/>
-      <c r="I15" s="357" t="n"/>
-      <c r="J15" s="357" t="n"/>
-      <c r="K15" s="358" t="n"/>
-    </row>
-    <row r="16" ht="30" customFormat="1" customHeight="1" s="8">
-      <c r="A16" s="353" t="inlineStr">
-        <is>
-          <t>LV_Line_Interference_Monitor</t>
-        </is>
-      </c>
-      <c r="B16" s="360" t="inlineStr">
-        <is>
-          <t>Controllo correnti/interferenze indesiderate di linea</t>
-        </is>
-      </c>
-      <c r="C16" s="302" t="n"/>
-      <c r="D16" s="302" t="n"/>
-      <c r="E16" s="357" t="n"/>
-      <c r="F16" s="357" t="n"/>
-      <c r="G16" s="357" t="n"/>
-      <c r="H16" s="357" t="n"/>
-      <c r="I16" s="357" t="n"/>
-      <c r="J16" s="357" t="n"/>
-      <c r="K16" s="358" t="n"/>
+      <c r="C16" s="303" t="n"/>
+      <c r="D16" s="303" t="n"/>
+      <c r="E16" s="350" t="n"/>
+      <c r="F16" s="350" t="n"/>
+      <c r="G16" s="350" t="n"/>
+      <c r="H16" s="350" t="n"/>
+      <c r="I16" s="350" t="n"/>
+      <c r="J16" s="350" t="n"/>
+      <c r="K16" s="351" t="n"/>
     </row>
     <row r="17" ht="30" customFormat="1" customHeight="1" s="8">
       <c r="A17" s="353" t="inlineStr">
         <is>
-          <t>LV_LIM_50Hz_protection_bypass</t>
-        </is>
-      </c>
-      <c r="B17" s="360" t="inlineStr">
-        <is>
-          <t>Bypass della protezione LIM 50 Hz</t>
+          <t>LV_Automatic_Dropping_Device_(ADD)</t>
+        </is>
+      </c>
+      <c r="B17" s="354" t="inlineStr">
+        <is>
+          <t>Dispositivo di abbassamento automatico del pantografo in caso di guasto</t>
         </is>
       </c>
       <c r="C17" s="302" t="n"/>
@@ -4438,18 +4480,16 @@
     <row r="18" ht="30" customFormat="1" customHeight="1" s="8">
       <c r="A18" s="353" t="inlineStr">
         <is>
-          <t>LV_Neutral_Section_Passing</t>
+          <t>LV_Pantograph_Interlock</t>
         </is>
       </c>
       <c r="B18" s="360" t="inlineStr">
         <is>
-          <t>Gestione del passaggio in sezione neutra:
-- automatica da ATP in caso di tratto neutro al cambio fase
-- inizializzata da ATP con selezione manuale deò PdC della tensione di linea, in caso di tratto neutro al cambio tensione</t>
-        </is>
-      </c>
-      <c r="C18" s="304" t="n"/>
-      <c r="D18" s="304" t="n"/>
+          <t>Interblocco automatico dei pantografi in caso di guasto rilevato. Il Pdc può bloccare anche manualmente un pantografo per impedirne la selezione</t>
+        </is>
+      </c>
+      <c r="C18" s="302" t="n"/>
+      <c r="D18" s="302" t="n"/>
       <c r="E18" s="357" t="n"/>
       <c r="F18" s="357" t="n"/>
       <c r="G18" s="357" t="n"/>
@@ -4461,16 +4501,16 @@
     <row r="19" ht="30" customFormat="1" customHeight="1" s="8">
       <c r="A19" s="353" t="inlineStr">
         <is>
-          <t>LV_System_Selection</t>
+          <t>LV_Pantograph_Selection</t>
         </is>
       </c>
       <c r="B19" s="360" t="inlineStr">
         <is>
-          <t>Selezione tramite commutatore a 4 posizioni della tensione di linea (25 kV AC, 15 kV AC, 3 kV DC o 1,5 kV DC)</t>
-        </is>
-      </c>
-      <c r="C19" s="304" t="n"/>
-      <c r="D19" s="304" t="n"/>
+          <t>Selezione del pantografo in base al paese (tipologia/dimensioni pantografo) e al sistema di alimentazione (AC/DC) selezionato</t>
+        </is>
+      </c>
+      <c r="C19" s="302" t="n"/>
+      <c r="D19" s="302" t="n"/>
       <c r="E19" s="357" t="n"/>
       <c r="F19" s="357" t="n"/>
       <c r="G19" s="357" t="n"/>
@@ -4482,16 +4522,16 @@
     <row r="20" ht="30" customFormat="1" customHeight="1" s="8">
       <c r="A20" s="353" t="inlineStr">
         <is>
-          <t>LV_Line_Circuit_Breaker_Closing</t>
+          <t>LV_Pantograph_Control_of_Static_Contact_Force</t>
         </is>
       </c>
       <c r="B20" s="360" t="inlineStr">
         <is>
-          <t>Chiusura dell’interruttore di linea (LCB) per collegare la tensione di linea al treno</t>
-        </is>
-      </c>
-      <c r="C20" s="304" t="n"/>
-      <c r="D20" s="304" t="n"/>
+          <t>Controllo della forza statica/pressione del pantografo alzato in funzione del sistema di tensione, della velocità, della direzione di marcia e della posizione del pantografo stesso</t>
+        </is>
+      </c>
+      <c r="C20" s="302" t="n"/>
+      <c r="D20" s="302" t="n"/>
       <c r="E20" s="357" t="n"/>
       <c r="F20" s="357" t="n"/>
       <c r="G20" s="357" t="n"/>
@@ -4500,19 +4540,19 @@
       <c r="J20" s="357" t="n"/>
       <c r="K20" s="358" t="n"/>
     </row>
-    <row r="21" ht="30" customFormat="1" customHeight="1" s="8">
+    <row r="21" ht="30" customHeight="1" s="478">
       <c r="A21" s="353" t="inlineStr">
         <is>
-          <t>LV_Line_Circuit_Breaker_Opening</t>
+          <t>LV_Line_Voltage_Supervision</t>
         </is>
       </c>
       <c r="B21" s="360" t="inlineStr">
         <is>
-          <t>Apertura LCB su comando o per intervento protezione</t>
-        </is>
-      </c>
-      <c r="C21" s="304" t="n"/>
-      <c r="D21" s="304" t="n"/>
+          <t>Controllo della tensione di linea tramite sensori di tensione letti dal sistema di propulsione</t>
+        </is>
+      </c>
+      <c r="C21" s="302" t="n"/>
+      <c r="D21" s="302" t="n"/>
       <c r="E21" s="357" t="n"/>
       <c r="F21" s="357" t="n"/>
       <c r="G21" s="357" t="n"/>
@@ -4521,19 +4561,19 @@
       <c r="J21" s="357" t="n"/>
       <c r="K21" s="358" t="n"/>
     </row>
-    <row r="22" ht="30" customFormat="1" customHeight="1" s="8">
+    <row r="22">
       <c r="A22" s="353" t="inlineStr">
         <is>
-          <t>LV_Isolate_High_Voltage</t>
+          <t>LV_Line_Current_Supervision</t>
         </is>
       </c>
       <c r="B22" s="360" t="inlineStr">
         <is>
-          <t>Isolamento di sezioni HV guaste per mantenere disponibile parte della trazione</t>
-        </is>
-      </c>
-      <c r="C22" s="304" t="n"/>
-      <c r="D22" s="304" t="n"/>
+          <t>Controllo della corrente di linea</t>
+        </is>
+      </c>
+      <c r="C22" s="302" t="n"/>
+      <c r="D22" s="302" t="n"/>
       <c r="E22" s="357" t="n"/>
       <c r="F22" s="357" t="n"/>
       <c r="G22" s="357" t="n"/>
@@ -4542,19 +4582,19 @@
       <c r="J22" s="357" t="n"/>
       <c r="K22" s="358" t="n"/>
     </row>
-    <row r="23" ht="30" customFormat="1" customHeight="1" s="8">
+    <row r="23" ht="30" customHeight="1" s="478">
       <c r="A23" s="353" t="inlineStr">
         <is>
-          <t>LV_Main_Transformer_cooling_control</t>
+          <t>LV_Line_Interference_Monitor</t>
         </is>
       </c>
       <c r="B23" s="360" t="inlineStr">
         <is>
-          <t>Controllo da parte della PCU della velocità delle ventole del circuito di raffreddamento ad olio</t>
-        </is>
-      </c>
-      <c r="C23" s="304" t="n"/>
-      <c r="D23" s="304" t="n"/>
+          <t>Controllo correnti/interferenze indesiderate di linea</t>
+        </is>
+      </c>
+      <c r="C23" s="302" t="n"/>
+      <c r="D23" s="302" t="n"/>
       <c r="E23" s="357" t="n"/>
       <c r="F23" s="357" t="n"/>
       <c r="G23" s="357" t="n"/>
@@ -4563,19 +4603,19 @@
       <c r="J23" s="357" t="n"/>
       <c r="K23" s="358" t="n"/>
     </row>
-    <row r="24" ht="30" customFormat="1" customHeight="1" s="8">
+    <row r="24" ht="30" customHeight="1" s="478">
       <c r="A24" s="353" t="inlineStr">
         <is>
-          <t>LV_Main_Transformer_Supervision</t>
+          <t>LV_LIM_50Hz_protection_bypass</t>
         </is>
       </c>
       <c r="B24" s="360" t="inlineStr">
         <is>
-          <t>Controllo da parte della PCU della temperatura del trasformatore e degli induttori linea</t>
-        </is>
-      </c>
-      <c r="C24" s="304" t="n"/>
-      <c r="D24" s="304" t="n"/>
+          <t>Bypass della protezione LIM 50 Hz</t>
+        </is>
+      </c>
+      <c r="C24" s="302" t="n"/>
+      <c r="D24" s="302" t="n"/>
       <c r="E24" s="357" t="n"/>
       <c r="F24" s="357" t="n"/>
       <c r="G24" s="357" t="n"/>
@@ -4587,12 +4627,14 @@
     <row r="25">
       <c r="A25" s="353" t="inlineStr">
         <is>
-          <t>LV_Energy_Meter</t>
+          <t>LV_Neutral_Section_Passing</t>
         </is>
       </c>
       <c r="B25" s="360" t="inlineStr">
         <is>
-          <t>Sistema di lettura dell'evergia assorbita dal treno e invio a terra dei dati</t>
+          <t>Gestione del passaggio in sezione neutra:
+- automatica da ATP in caso di tratto neutro al cambio fase
+- inizializzata da ATP con selezione manuale deò PdC della tensione di linea, in caso di tratto neutro al cambio tensione</t>
         </is>
       </c>
       <c r="C25" s="304" t="n"/>
@@ -4608,12 +4650,12 @@
     <row r="26">
       <c r="A26" s="353" t="inlineStr">
         <is>
-          <t>LV_Key_interlocking</t>
-        </is>
-      </c>
-      <c r="B26" s="364" t="inlineStr">
-        <is>
-          <t>Interblocco tramite giro chiavi del sistema alta tensione</t>
+          <t>LV_System_Selection</t>
+        </is>
+      </c>
+      <c r="B26" s="360" t="inlineStr">
+        <is>
+          <t>Selezione tramite commutatore a 4 posizioni della tensione di linea (25 kV AC, 15 kV AC, 3 kV DC o 1,5 kV DC)</t>
         </is>
       </c>
       <c r="C26" s="304" t="n"/>
@@ -4629,12 +4671,12 @@
     <row r="27">
       <c r="A27" s="353" t="inlineStr">
         <is>
-          <t>LV_Function_Earthing_of_High_Voltage_Supply</t>
-        </is>
-      </c>
-      <c r="B27" s="364" t="inlineStr">
-        <is>
-          <t>Messa a terra dell'alta tensione per consentire la manutenzione in sicurezza</t>
+          <t>LV_Line_Circuit_Breaker_Closing</t>
+        </is>
+      </c>
+      <c r="B27" s="360" t="inlineStr">
+        <is>
+          <t>Chiusura dell’interruttore di linea (LCB) per collegare la tensione di linea al treno</t>
         </is>
       </c>
       <c r="C27" s="304" t="n"/>
@@ -4650,12 +4692,12 @@
     <row r="28">
       <c r="A28" s="353" t="inlineStr">
         <is>
-          <t>LV_Function_Earthing_of_Converter_boxes</t>
-        </is>
-      </c>
-      <c r="B28" s="364" t="inlineStr">
-        <is>
-          <t>Messa a terra dei box convertitori per consentire l’accesso e la manutenzione in sicurezza</t>
+          <t>LV_Line_Circuit_Breaker_Opening</t>
+        </is>
+      </c>
+      <c r="B28" s="360" t="inlineStr">
+        <is>
+          <t>Apertura LCB su comando o per intervento protezione</t>
         </is>
       </c>
       <c r="C28" s="304" t="n"/>
@@ -4671,12 +4713,12 @@
     <row r="29">
       <c r="A29" s="353" t="inlineStr">
         <is>
-          <t>LV_HVAC_pre-conditioning_on_DC_line</t>
-        </is>
-      </c>
-      <c r="B29" s="364" t="inlineStr">
-        <is>
-          <t>Funzione per alimentare gli HVAC senza superare i limiti di corrente</t>
+          <t>LV_Isolate_High_Voltage</t>
+        </is>
+      </c>
+      <c r="B29" s="360" t="inlineStr">
+        <is>
+          <t>Isolamento di sezioni HV guaste per mantenere disponibile parte della trazione</t>
         </is>
       </c>
       <c r="C29" s="304" t="n"/>
@@ -4692,10 +4734,14 @@
     <row r="30">
       <c r="A30" s="353" t="inlineStr">
         <is>
-          <t>AUX_Function_General</t>
-        </is>
-      </c>
-      <c r="B30" s="360" t="n"/>
+          <t>LV_Main_Transformer_cooling_control</t>
+        </is>
+      </c>
+      <c r="B30" s="360" t="inlineStr">
+        <is>
+          <t>Controllo da parte della PCU della velocità delle ventole del circuito di raffreddamento ad olio</t>
+        </is>
+      </c>
       <c r="C30" s="304" t="n"/>
       <c r="D30" s="304" t="n"/>
       <c r="E30" s="357" t="n"/>
@@ -4709,10 +4755,14 @@
     <row r="31">
       <c r="A31" s="353" t="inlineStr">
         <is>
-          <t>AUX_Activation_and_Synchronisation_of_ACM</t>
-        </is>
-      </c>
-      <c r="B31" s="360" t="n"/>
+          <t>LV_Main_Transformer_Supervision</t>
+        </is>
+      </c>
+      <c r="B31" s="360" t="inlineStr">
+        <is>
+          <t>Controllo da parte della PCU della temperatura del trasformatore e degli induttori linea</t>
+        </is>
+      </c>
       <c r="C31" s="304" t="n"/>
       <c r="D31" s="304" t="n"/>
       <c r="E31" s="357" t="n"/>
@@ -4726,10 +4776,14 @@
     <row r="32">
       <c r="A32" s="353" t="inlineStr">
         <is>
-          <t>AUX_ACM_reset</t>
-        </is>
-      </c>
-      <c r="B32" s="360" t="n"/>
+          <t>LV_Energy_Meter</t>
+        </is>
+      </c>
+      <c r="B32" s="360" t="inlineStr">
+        <is>
+          <t>Sistema di lettura dell'evergia assorbita dal treno e invio a terra dei dati</t>
+        </is>
+      </c>
       <c r="C32" s="304" t="n"/>
       <c r="D32" s="304" t="n"/>
       <c r="E32" s="357" t="n"/>
@@ -4743,10 +4797,14 @@
     <row r="33">
       <c r="A33" s="353" t="inlineStr">
         <is>
-          <t>AUX_AC_on_Board_Supply_System</t>
-        </is>
-      </c>
-      <c r="B33" s="360" t="n"/>
+          <t>LV_Key_interlocking</t>
+        </is>
+      </c>
+      <c r="B33" s="364" t="inlineStr">
+        <is>
+          <t>Interblocco tramite giro chiavi del sistema alta tensione</t>
+        </is>
+      </c>
       <c r="C33" s="304" t="n"/>
       <c r="D33" s="304" t="n"/>
       <c r="E33" s="357" t="n"/>
@@ -4760,10 +4818,14 @@
     <row r="34">
       <c r="A34" s="353" t="inlineStr">
         <is>
-          <t>AUX_External_Power_Supply</t>
-        </is>
-      </c>
-      <c r="B34" s="360" t="n"/>
+          <t>LV_Function_Earthing_of_High_Voltage_Supply</t>
+        </is>
+      </c>
+      <c r="B34" s="364" t="inlineStr">
+        <is>
+          <t>Messa a terra dell'alta tensione per consentire la manutenzione in sicurezza</t>
+        </is>
+      </c>
       <c r="C34" s="304" t="n"/>
       <c r="D34" s="304" t="n"/>
       <c r="E34" s="357" t="n"/>
@@ -4777,10 +4839,14 @@
     <row r="35">
       <c r="A35" s="353" t="inlineStr">
         <is>
-          <t>AUX_Earthing_switch</t>
-        </is>
-      </c>
-      <c r="B35" s="360" t="n"/>
+          <t>LV_Function_Earthing_of_Converter_boxes</t>
+        </is>
+      </c>
+      <c r="B35" s="364" t="inlineStr">
+        <is>
+          <t>Messa a terra dei box convertitori per consentire l’accesso e la manutenzione in sicurezza</t>
+        </is>
+      </c>
       <c r="C35" s="304" t="n"/>
       <c r="D35" s="304" t="n"/>
       <c r="E35" s="357" t="n"/>
@@ -4794,10 +4860,14 @@
     <row r="36">
       <c r="A36" s="353" t="inlineStr">
         <is>
-          <t>AUX_230V,_50Hz_Sockets</t>
-        </is>
-      </c>
-      <c r="B36" s="360" t="n"/>
+          <t>LV_HVAC_pre-conditioning_on_DC_line</t>
+        </is>
+      </c>
+      <c r="B36" s="364" t="inlineStr">
+        <is>
+          <t>Funzione per alimentare gli HVAC senza superare i limiti di corrente</t>
+        </is>
+      </c>
       <c r="C36" s="304" t="n"/>
       <c r="D36" s="304" t="n"/>
       <c r="E36" s="357" t="n"/>
@@ -4811,7 +4881,7 @@
     <row r="37">
       <c r="A37" s="353" t="inlineStr">
         <is>
-          <t>AUX_Mini_Circuit_Breaker_Supervision</t>
+          <t>AUX_Function_General</t>
         </is>
       </c>
       <c r="B37" s="360" t="n"/>
@@ -4826,128 +4896,128 @@
       <c r="K37" s="358" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="181" t="inlineStr">
-        <is>
-          <t>BAT_Failure_cases_battery_system</t>
-        </is>
-      </c>
-      <c r="B38" s="367" t="n"/>
+      <c r="A38" s="353" t="inlineStr">
+        <is>
+          <t>AUX_Activation_and_Synchronisation_of_ACM</t>
+        </is>
+      </c>
+      <c r="B38" s="360" t="n"/>
       <c r="C38" s="304" t="n"/>
       <c r="D38" s="304" t="n"/>
-      <c r="E38" s="163" t="n"/>
-      <c r="F38" s="163" t="n"/>
-      <c r="G38" s="163" t="n"/>
-      <c r="H38" s="163" t="n"/>
-      <c r="I38" s="163" t="n"/>
-      <c r="J38" s="163" t="n"/>
-      <c r="K38" s="164" t="n"/>
+      <c r="E38" s="357" t="n"/>
+      <c r="F38" s="357" t="n"/>
+      <c r="G38" s="357" t="n"/>
+      <c r="H38" s="357" t="n"/>
+      <c r="I38" s="357" t="n"/>
+      <c r="J38" s="357" t="n"/>
+      <c r="K38" s="358" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="181" t="inlineStr">
-        <is>
-          <t>BAT_Function_Battery_Isolation</t>
-        </is>
-      </c>
-      <c r="B39" s="367" t="n"/>
+      <c r="A39" s="353" t="inlineStr">
+        <is>
+          <t>AUX_ACM_reset</t>
+        </is>
+      </c>
+      <c r="B39" s="360" t="n"/>
       <c r="C39" s="304" t="n"/>
       <c r="D39" s="304" t="n"/>
-      <c r="E39" s="163" t="n"/>
-      <c r="F39" s="163" t="n"/>
-      <c r="G39" s="163" t="n"/>
-      <c r="H39" s="163" t="n"/>
-      <c r="I39" s="163" t="n"/>
-      <c r="J39" s="163" t="n"/>
-      <c r="K39" s="164" t="n"/>
+      <c r="E39" s="357" t="n"/>
+      <c r="F39" s="357" t="n"/>
+      <c r="G39" s="357" t="n"/>
+      <c r="H39" s="357" t="n"/>
+      <c r="I39" s="357" t="n"/>
+      <c r="J39" s="357" t="n"/>
+      <c r="K39" s="358" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="181" t="inlineStr">
-        <is>
-          <t>BAT_Battery_Contactors</t>
-        </is>
-      </c>
-      <c r="B40" s="367" t="n"/>
+      <c r="A40" s="353" t="inlineStr">
+        <is>
+          <t>AUX_AC_on_Board_Supply_System</t>
+        </is>
+      </c>
+      <c r="B40" s="360" t="n"/>
       <c r="C40" s="304" t="n"/>
       <c r="D40" s="304" t="n"/>
-      <c r="E40" s="163" t="n"/>
-      <c r="F40" s="163" t="n"/>
-      <c r="G40" s="163" t="n"/>
-      <c r="H40" s="163" t="n"/>
-      <c r="I40" s="163" t="n"/>
-      <c r="J40" s="163" t="n"/>
-      <c r="K40" s="164" t="n"/>
+      <c r="E40" s="357" t="n"/>
+      <c r="F40" s="357" t="n"/>
+      <c r="G40" s="357" t="n"/>
+      <c r="H40" s="357" t="n"/>
+      <c r="I40" s="357" t="n"/>
+      <c r="J40" s="357" t="n"/>
+      <c r="K40" s="358" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="181" t="inlineStr">
-        <is>
-          <t>BAT_Load_Shed_Contactors</t>
-        </is>
-      </c>
-      <c r="B41" s="367" t="n"/>
+      <c r="A41" s="353" t="inlineStr">
+        <is>
+          <t>AUX_External_Power_Supply</t>
+        </is>
+      </c>
+      <c r="B41" s="360" t="n"/>
       <c r="C41" s="304" t="n"/>
       <c r="D41" s="304" t="n"/>
-      <c r="E41" s="163" t="n"/>
-      <c r="F41" s="163" t="n"/>
-      <c r="G41" s="163" t="n"/>
-      <c r="H41" s="163" t="n"/>
-      <c r="I41" s="163" t="n"/>
-      <c r="J41" s="163" t="n"/>
-      <c r="K41" s="164" t="n"/>
+      <c r="E41" s="357" t="n"/>
+      <c r="F41" s="357" t="n"/>
+      <c r="G41" s="357" t="n"/>
+      <c r="H41" s="357" t="n"/>
+      <c r="I41" s="357" t="n"/>
+      <c r="J41" s="357" t="n"/>
+      <c r="K41" s="358" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="181" t="inlineStr">
-        <is>
-          <t>BAT_DC_Busline_Distribution</t>
-        </is>
-      </c>
-      <c r="B42" s="367" t="n"/>
+      <c r="A42" s="353" t="inlineStr">
+        <is>
+          <t>AUX_Earthing_switch</t>
+        </is>
+      </c>
+      <c r="B42" s="360" t="n"/>
       <c r="C42" s="304" t="n"/>
       <c r="D42" s="304" t="n"/>
-      <c r="E42" s="163" t="n"/>
-      <c r="F42" s="163" t="n"/>
-      <c r="G42" s="163" t="n"/>
-      <c r="H42" s="163" t="n"/>
-      <c r="I42" s="163" t="n"/>
-      <c r="J42" s="163" t="n"/>
-      <c r="K42" s="164" t="n"/>
+      <c r="E42" s="357" t="n"/>
+      <c r="F42" s="357" t="n"/>
+      <c r="G42" s="357" t="n"/>
+      <c r="H42" s="357" t="n"/>
+      <c r="I42" s="357" t="n"/>
+      <c r="J42" s="357" t="n"/>
+      <c r="K42" s="358" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="181" t="inlineStr">
-        <is>
-          <t>BAT_Battery_Charging</t>
-        </is>
-      </c>
-      <c r="B43" s="367" t="n"/>
+      <c r="A43" s="353" t="inlineStr">
+        <is>
+          <t>AUX_230V,_50Hz_Sockets</t>
+        </is>
+      </c>
+      <c r="B43" s="360" t="n"/>
       <c r="C43" s="304" t="n"/>
       <c r="D43" s="304" t="n"/>
-      <c r="E43" s="163" t="n"/>
-      <c r="F43" s="163" t="n"/>
-      <c r="G43" s="163" t="n"/>
-      <c r="H43" s="163" t="n"/>
-      <c r="I43" s="163" t="n"/>
-      <c r="J43" s="163" t="n"/>
-      <c r="K43" s="164" t="n"/>
+      <c r="E43" s="357" t="n"/>
+      <c r="F43" s="357" t="n"/>
+      <c r="G43" s="357" t="n"/>
+      <c r="H43" s="357" t="n"/>
+      <c r="I43" s="357" t="n"/>
+      <c r="J43" s="357" t="n"/>
+      <c r="K43" s="358" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="181" t="inlineStr">
-        <is>
-          <t>AIR_Control_of_Main_Compressor</t>
-        </is>
-      </c>
-      <c r="B44" s="367" t="n"/>
+      <c r="A44" s="353" t="inlineStr">
+        <is>
+          <t>AUX_Mini_Circuit_Breaker_Supervision</t>
+        </is>
+      </c>
+      <c r="B44" s="360" t="n"/>
       <c r="C44" s="304" t="n"/>
       <c r="D44" s="304" t="n"/>
-      <c r="E44" s="163" t="n"/>
-      <c r="F44" s="163" t="n"/>
-      <c r="G44" s="163" t="n"/>
-      <c r="H44" s="163" t="n"/>
-      <c r="I44" s="163" t="n"/>
-      <c r="J44" s="163" t="n"/>
-      <c r="K44" s="164" t="n"/>
+      <c r="E44" s="357" t="n"/>
+      <c r="F44" s="357" t="n"/>
+      <c r="G44" s="357" t="n"/>
+      <c r="H44" s="357" t="n"/>
+      <c r="I44" s="357" t="n"/>
+      <c r="J44" s="357" t="n"/>
+      <c r="K44" s="358" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="181" t="inlineStr">
         <is>
-          <t>AIR_Monitoring_of_Main_Compressor</t>
+          <t>BAT_Failure_cases_battery_system</t>
         </is>
       </c>
       <c r="B45" s="367" t="n"/>
@@ -4964,7 +5034,7 @@
     <row r="46">
       <c r="A46" s="181" t="inlineStr">
         <is>
-          <t>AIR_Forcing_of_Main_compressor</t>
+          <t>BAT_Function_Battery_Isolation</t>
         </is>
       </c>
       <c r="B46" s="367" t="n"/>
@@ -4981,7 +5051,7 @@
     <row r="47">
       <c r="A47" s="181" t="inlineStr">
         <is>
-          <t>AIR_Air_Dryer</t>
+          <t>BAT_Battery_Contactors</t>
         </is>
       </c>
       <c r="B47" s="367" t="n"/>
@@ -4998,7 +5068,7 @@
     <row r="48">
       <c r="A48" s="181" t="inlineStr">
         <is>
-          <t>AIR_External_Air_Supply</t>
+          <t>BAT_Load_Shed_Contactors</t>
         </is>
       </c>
       <c r="B48" s="367" t="n"/>
@@ -5015,7 +5085,7 @@
     <row r="49">
       <c r="A49" s="181" t="inlineStr">
         <is>
-          <t>AIR_Control_of_Auxiliary_Compressor</t>
+          <t>BAT_DC_Busline_Distribution</t>
         </is>
       </c>
       <c r="B49" s="367" t="n"/>
@@ -5032,7 +5102,7 @@
     <row r="50">
       <c r="A50" s="181" t="inlineStr">
         <is>
-          <t>AIR_Suspension_Supervision</t>
+          <t>BAT_Battery_Charging</t>
         </is>
       </c>
       <c r="B50" s="367" t="n"/>
@@ -5049,7 +5119,7 @@
     <row r="51">
       <c r="A51" s="181" t="inlineStr">
         <is>
-          <t>AIR_Provision_for_Tilt_system</t>
+          <t>AIR_Control_of_Main_Compressor</t>
         </is>
       </c>
       <c r="B51" s="367" t="n"/>
@@ -5066,7 +5136,7 @@
     <row r="52">
       <c r="A52" s="181" t="inlineStr">
         <is>
-          <t>BRK_Service_Brake_Direct_Electro-Pneumatic_Brake</t>
+          <t>AIR_Monitoring_of_Main_Compressor</t>
         </is>
       </c>
       <c r="B52" s="367" t="n"/>
@@ -5083,7 +5153,7 @@
     <row r="53">
       <c r="A53" s="181" t="inlineStr">
         <is>
-          <t>BRK_Service_Brake_Indirect_Brake</t>
+          <t>AIR_Forcing_of_Main_compressor</t>
         </is>
       </c>
       <c r="B53" s="367" t="n"/>
@@ -5100,7 +5170,7 @@
     <row r="54">
       <c r="A54" s="181" t="inlineStr">
         <is>
-          <t>BRK_Holding_Brake</t>
+          <t>AIR_Air_Dryer</t>
         </is>
       </c>
       <c r="B54" s="367" t="n"/>
@@ -5117,7 +5187,7 @@
     <row r="55">
       <c r="A55" s="181" t="inlineStr">
         <is>
-          <t>BRK_Urgency_Brake_(Optional)</t>
+          <t>AIR_External_Air_Supply</t>
         </is>
       </c>
       <c r="B55" s="367" t="n"/>
@@ -5134,7 +5204,7 @@
     <row r="56">
       <c r="A56" s="181" t="inlineStr">
         <is>
-          <t>BRK_Emergency_Brake</t>
+          <t>AIR_Control_of_Auxiliary_Compressor</t>
         </is>
       </c>
       <c r="B56" s="367" t="n"/>
@@ -5151,7 +5221,7 @@
     <row r="57">
       <c r="A57" s="181" t="inlineStr">
         <is>
-          <t>BRK_Parking_Brake</t>
+          <t>AIR_Suspension_Supervision</t>
         </is>
       </c>
       <c r="B57" s="367" t="n"/>
@@ -5168,7 +5238,7 @@
     <row r="58">
       <c r="A58" s="181" t="inlineStr">
         <is>
-          <t>BRK_Wheel_Slide_Protection</t>
+          <t>AIR_Provision_for_Tilt_system</t>
         </is>
       </c>
       <c r="B58" s="367" t="n"/>
@@ -5185,7 +5255,7 @@
     <row r="59">
       <c r="A59" s="181" t="inlineStr">
         <is>
-          <t>BRK_Detection_of_Non-Rotating_Axle_(DNRA)</t>
+          <t>BRK_Service_Brake_Direct_Electro-Pneumatic_Brake</t>
         </is>
       </c>
       <c r="B59" s="367" t="n"/>
@@ -5202,7 +5272,7 @@
     <row r="60">
       <c r="A60" s="181" t="inlineStr">
         <is>
-          <t>BRK_Passenger_Emergency_Brake</t>
+          <t>BRK_Service_Brake_Indirect_Brake</t>
         </is>
       </c>
       <c r="B60" s="367" t="n"/>
@@ -5219,7 +5289,7 @@
     <row r="61">
       <c r="A61" s="181" t="inlineStr">
         <is>
-          <t>BRK_Sanding</t>
+          <t>BRK_Holding_Brake</t>
         </is>
       </c>
       <c r="B61" s="367" t="n"/>
@@ -5236,7 +5306,7 @@
     <row r="62">
       <c r="A62" s="181" t="inlineStr">
         <is>
-          <t>BRK_Brake_Test</t>
+          <t>BRK_Urgency_Brake_(Optional)</t>
         </is>
       </c>
       <c r="B62" s="367" t="n"/>
@@ -5253,7 +5323,7 @@
     <row r="63">
       <c r="A63" s="181" t="inlineStr">
         <is>
-          <t>BRK_Towing</t>
+          <t>BRK_Emergency_Brake</t>
         </is>
       </c>
       <c r="B63" s="367" t="n"/>
@@ -5270,7 +5340,7 @@
     <row r="64">
       <c r="A64" s="181" t="inlineStr">
         <is>
-          <t>BRK_Fire_Safety_&amp;_Running_Capability</t>
+          <t>BRK_Parking_Brake</t>
         </is>
       </c>
       <c r="B64" s="367" t="n"/>
@@ -5287,7 +5357,7 @@
     <row r="65">
       <c r="A65" s="181" t="inlineStr">
         <is>
-          <t>BRK_Magnetic_Track_Brake_Optional</t>
+          <t>BRK_Wheel_Slide_Protection</t>
         </is>
       </c>
       <c r="B65" s="367" t="n"/>
@@ -5304,7 +5374,7 @@
     <row r="66">
       <c r="A66" s="181" t="inlineStr">
         <is>
-          <t>BOG_Flange_Lubrication</t>
+          <t>BRK_Detection_of_Non-Rotating_Axle_(DNRA)</t>
         </is>
       </c>
       <c r="B66" s="367" t="n"/>
@@ -5321,7 +5391,7 @@
     <row r="67">
       <c r="A67" s="181" t="inlineStr">
         <is>
-          <t>BOG_Hotbox_Detection</t>
+          <t>BRK_Passenger_Emergency_Brake</t>
         </is>
       </c>
       <c r="B67" s="367" t="n"/>
@@ -5338,7 +5408,7 @@
     <row r="68">
       <c r="A68" s="181" t="inlineStr">
         <is>
-          <t>BOG_Instability_Monitoring</t>
+          <t>BRK_Sanding</t>
         </is>
       </c>
       <c r="B68" s="367" t="n"/>
@@ -5355,7 +5425,7 @@
     <row r="69">
       <c r="A69" s="181" t="inlineStr">
         <is>
-          <t>BOG_Active_Lateral_Suspension_(ALS)</t>
+          <t>BRK_Brake_Test</t>
         </is>
       </c>
       <c r="B69" s="367" t="n"/>
@@ -5372,7 +5442,7 @@
     <row r="70">
       <c r="A70" s="181" t="inlineStr">
         <is>
-          <t>BOG_Diagnostics_&amp;_CBM</t>
+          <t>BRK_Towing</t>
         </is>
       </c>
       <c r="B70" s="367" t="n"/>
@@ -5387,46 +5457,165 @@
       <c r="K70" s="164" t="n"/>
     </row>
     <row r="71">
-      <c r="B71" s="169" t="n"/>
-      <c r="E71" s="242" t="n"/>
-      <c r="F71" s="242" t="n"/>
-      <c r="G71" s="237" t="n"/>
-      <c r="H71" s="237" t="n"/>
-      <c r="I71" s="242" t="n"/>
-      <c r="J71" s="237" t="n"/>
-      <c r="K71" s="238" t="n"/>
+      <c r="A71" s="181" t="inlineStr">
+        <is>
+          <t>BRK_Fire_Safety_&amp;_Running_Capability</t>
+        </is>
+      </c>
+      <c r="B71" s="367" t="n"/>
+      <c r="C71" s="304" t="n"/>
+      <c r="D71" s="304" t="n"/>
+      <c r="E71" s="163" t="n"/>
+      <c r="F71" s="163" t="n"/>
+      <c r="G71" s="163" t="n"/>
+      <c r="H71" s="163" t="n"/>
+      <c r="I71" s="163" t="n"/>
+      <c r="J71" s="163" t="n"/>
+      <c r="K71" s="164" t="n"/>
     </row>
     <row r="72">
-      <c r="C72" s="420" t="n"/>
-      <c r="D72" s="421" t="n"/>
-      <c r="E72" s="422" t="n"/>
-      <c r="G72" s="423" t="n"/>
-      <c r="H72" s="424" t="n"/>
-      <c r="I72" s="425" t="n"/>
+      <c r="A72" s="181" t="inlineStr">
+        <is>
+          <t>BRK_Magnetic_Track_Brake_Optional</t>
+        </is>
+      </c>
+      <c r="B72" s="367" t="n"/>
+      <c r="C72" s="304" t="n"/>
+      <c r="D72" s="304" t="n"/>
+      <c r="E72" s="163" t="n"/>
+      <c r="F72" s="163" t="n"/>
+      <c r="G72" s="163" t="n"/>
+      <c r="H72" s="163" t="n"/>
+      <c r="I72" s="163" t="n"/>
+      <c r="J72" s="163" t="n"/>
+      <c r="K72" s="164" t="n"/>
     </row>
     <row r="73">
-      <c r="C73" s="420" t="n"/>
-      <c r="D73" s="421" t="n"/>
-      <c r="E73" s="422" t="n"/>
-      <c r="G73" s="423" t="n"/>
-      <c r="H73" s="424" t="n"/>
-      <c r="I73" s="425" t="n"/>
+      <c r="A73" s="181" t="inlineStr">
+        <is>
+          <t>BOG_Flange_Lubrication</t>
+        </is>
+      </c>
+      <c r="B73" s="367" t="n"/>
+      <c r="C73" s="304" t="n"/>
+      <c r="D73" s="304" t="n"/>
+      <c r="E73" s="163" t="n"/>
+      <c r="F73" s="163" t="n"/>
+      <c r="G73" s="163" t="n"/>
+      <c r="H73" s="163" t="n"/>
+      <c r="I73" s="163" t="n"/>
+      <c r="J73" s="163" t="n"/>
+      <c r="K73" s="164" t="n"/>
     </row>
     <row r="74">
-      <c r="C74" s="420" t="n"/>
-      <c r="D74" s="421" t="n"/>
-      <c r="E74" s="422" t="n"/>
-      <c r="G74" s="423" t="n"/>
-      <c r="H74" s="424" t="n"/>
-      <c r="I74" s="425" t="n"/>
+      <c r="A74" s="181" t="inlineStr">
+        <is>
+          <t>BOG_Hotbox_Detection</t>
+        </is>
+      </c>
+      <c r="B74" s="367" t="n"/>
+      <c r="C74" s="304" t="n"/>
+      <c r="D74" s="304" t="n"/>
+      <c r="E74" s="163" t="n"/>
+      <c r="F74" s="163" t="n"/>
+      <c r="G74" s="163" t="n"/>
+      <c r="H74" s="163" t="n"/>
+      <c r="I74" s="163" t="n"/>
+      <c r="J74" s="163" t="n"/>
+      <c r="K74" s="164" t="n"/>
     </row>
     <row r="75">
-      <c r="C75" s="426" t="n"/>
-      <c r="D75" s="421" t="n"/>
-      <c r="I75" s="425" t="n"/>
+      <c r="A75" s="181" t="inlineStr">
+        <is>
+          <t>BOG_Instability_Monitoring</t>
+        </is>
+      </c>
+      <c r="B75" s="367" t="n"/>
+      <c r="C75" s="304" t="n"/>
+      <c r="D75" s="304" t="n"/>
+      <c r="E75" s="163" t="n"/>
+      <c r="F75" s="163" t="n"/>
+      <c r="G75" s="163" t="n"/>
+      <c r="H75" s="163" t="n"/>
+      <c r="I75" s="163" t="n"/>
+      <c r="J75" s="163" t="n"/>
+      <c r="K75" s="164" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="181" t="inlineStr">
+        <is>
+          <t>BOG_Active_Lateral_Suspension_(ALS)</t>
+        </is>
+      </c>
+      <c r="B76" s="367" t="n"/>
+      <c r="C76" s="304" t="n"/>
+      <c r="D76" s="304" t="n"/>
+      <c r="E76" s="163" t="n"/>
+      <c r="F76" s="163" t="n"/>
+      <c r="G76" s="163" t="n"/>
+      <c r="H76" s="163" t="n"/>
+      <c r="I76" s="163" t="n"/>
+      <c r="J76" s="163" t="n"/>
+      <c r="K76" s="164" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="181" t="inlineStr">
+        <is>
+          <t>BOG_Diagnostics_&amp;_CBM</t>
+        </is>
+      </c>
+      <c r="B77" s="367" t="n"/>
+      <c r="C77" s="304" t="n"/>
+      <c r="D77" s="304" t="n"/>
+      <c r="E77" s="163" t="n"/>
+      <c r="F77" s="163" t="n"/>
+      <c r="G77" s="163" t="n"/>
+      <c r="H77" s="163" t="n"/>
+      <c r="I77" s="163" t="n"/>
+      <c r="J77" s="163" t="n"/>
+      <c r="K77" s="164" t="n"/>
+    </row>
+    <row r="78">
+      <c r="B78" s="169" t="n"/>
+      <c r="E78" s="242" t="n"/>
+      <c r="F78" s="242" t="n"/>
+      <c r="G78" s="237" t="n"/>
+      <c r="H78" s="237" t="n"/>
+      <c r="I78" s="242" t="n"/>
+      <c r="J78" s="237" t="n"/>
+      <c r="K78" s="238" t="n"/>
+    </row>
+    <row r="79">
+      <c r="C79" s="420" t="n"/>
+      <c r="D79" s="421" t="n"/>
+      <c r="E79" s="422" t="n"/>
+      <c r="G79" s="423" t="n"/>
+      <c r="H79" s="424" t="n"/>
+      <c r="I79" s="425" t="n"/>
+    </row>
+    <row r="80">
+      <c r="C80" s="420" t="n"/>
+      <c r="D80" s="421" t="n"/>
+      <c r="E80" s="422" t="n"/>
+      <c r="G80" s="423" t="n"/>
+      <c r="H80" s="424" t="n"/>
+      <c r="I80" s="425" t="n"/>
+    </row>
+    <row r="81">
+      <c r="C81" s="420" t="n"/>
+      <c r="D81" s="421" t="n"/>
+      <c r="E81" s="422" t="n"/>
+      <c r="G81" s="423" t="n"/>
+      <c r="H81" s="424" t="n"/>
+      <c r="I81" s="425" t="n"/>
+    </row>
+    <row r="82">
+      <c r="C82" s="426" t="n"/>
+      <c r="D82" s="421" t="n"/>
+      <c r="I82" s="425" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K57"/>
+  <autoFilter ref="A1:K53"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5446,8 +5635,8 @@
     <col width="24.28515625" customWidth="1" style="10" min="3" max="3"/>
     <col width="18.7109375" bestFit="1" customWidth="1" style="10" min="4" max="4"/>
     <col width="16.5703125" customWidth="1" style="10" min="5" max="10"/>
-    <col width="8.7109375" customWidth="1" style="59" min="11" max="20"/>
-    <col width="8.7109375" customWidth="1" style="59" min="21" max="16384"/>
+    <col width="8.7109375" customWidth="1" style="59" min="11" max="21"/>
+    <col width="8.7109375" customWidth="1" style="59" min="22" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="31.5" customFormat="1" customHeight="1" s="61">
@@ -11528,8 +11717,8 @@
     <mergeCell ref="A43:A47"/>
     <mergeCell ref="W49:Z49"/>
     <mergeCell ref="O25:O28"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="K43:N44"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="S9:S12"/>
     <mergeCell ref="G3:G8"/>
     <mergeCell ref="C17:C20"/>
@@ -11559,8 +11748,8 @@
     <col width="28.42578125" bestFit="1" customWidth="1" style="8" min="4" max="4"/>
     <col width="21.42578125" customWidth="1" style="8" min="5" max="5"/>
     <col width="35.5703125" customWidth="1" style="8" min="6" max="7"/>
-    <col width="8.7109375" customWidth="1" style="8" min="8" max="17"/>
-    <col width="8.7109375" customWidth="1" style="8" min="18" max="16384"/>
+    <col width="8.7109375" customWidth="1" style="8" min="8" max="18"/>
+    <col width="8.7109375" customWidth="1" style="8" min="19" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" s="478">
@@ -12565,8 +12754,8 @@
     <col width="8.7109375" customWidth="1" style="9" min="3" max="3"/>
     <col width="120.7109375" customWidth="1" style="59" min="4" max="4"/>
     <col width="60.140625" customWidth="1" style="59" min="5" max="5"/>
-    <col width="8.7109375" customWidth="1" style="8" min="6" max="15"/>
-    <col width="8.7109375" customWidth="1" style="8" min="16" max="16384"/>
+    <col width="8.7109375" customWidth="1" style="8" min="6" max="16"/>
+    <col width="8.7109375" customWidth="1" style="8" min="17" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="23.45" customFormat="1" customHeight="1" s="109">
@@ -12918,8 +13107,8 @@
     <col width="6.5703125" bestFit="1" customWidth="1" style="8" min="3" max="3"/>
     <col width="139.42578125" bestFit="1" customWidth="1" style="60" min="4" max="4"/>
     <col width="8.7109375" customWidth="1" style="9" min="5" max="5"/>
-    <col width="8.7109375" customWidth="1" style="8" min="6" max="15"/>
-    <col width="8.7109375" customWidth="1" style="8" min="16" max="16384"/>
+    <col width="8.7109375" customWidth="1" style="8" min="6" max="16"/>
+    <col width="8.7109375" customWidth="1" style="8" min="17" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="21.6" customHeight="1" s="478">
@@ -14343,8 +14532,8 @@
     <col width="6.5703125" customWidth="1" style="10" min="21" max="21"/>
     <col width="6.5703125" bestFit="1" customWidth="1" style="10" min="22" max="22"/>
     <col width="6.5703125" customWidth="1" style="10" min="23" max="23"/>
-    <col width="8.7109375" customWidth="1" style="59" min="24" max="33"/>
-    <col width="8.7109375" customWidth="1" style="59" min="34" max="16384"/>
+    <col width="8.7109375" customWidth="1" style="59" min="24" max="34"/>
+    <col width="8.7109375" customWidth="1" style="59" min="35" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" s="61">
@@ -23716,8 +23905,8 @@
     <col width="6.5703125" customWidth="1" style="10" min="17" max="17"/>
     <col width="6.5703125" bestFit="1" customWidth="1" style="10" min="18" max="18"/>
     <col width="6.5703125" customWidth="1" style="10" min="19" max="19"/>
-    <col width="8.7109375" customWidth="1" style="59" min="20" max="29"/>
-    <col width="8.7109375" customWidth="1" style="59" min="30" max="16384"/>
+    <col width="8.7109375" customWidth="1" style="59" min="20" max="30"/>
+    <col width="8.7109375" customWidth="1" style="59" min="31" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="26.45" customFormat="1" customHeight="1" s="61">
@@ -25078,8 +25267,8 @@
     <col width="26.42578125" bestFit="1" customWidth="1" style="9" min="27" max="27"/>
     <col width="4.42578125" bestFit="1" customWidth="1" style="9" min="28" max="28"/>
     <col width="8.85546875" bestFit="1" customWidth="1" style="290" min="29" max="29"/>
-    <col width="8.7109375" customWidth="1" style="8" min="30" max="33"/>
-    <col width="8.7109375" customWidth="1" style="8" min="34" max="16384"/>
+    <col width="8.7109375" customWidth="1" style="8" min="30" max="34"/>
+    <col width="8.7109375" customWidth="1" style="8" min="35" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="29.45" customHeight="1" s="478">
@@ -33585,8 +33774,8 @@
     <col width="6.5703125" customWidth="1" style="10" min="17" max="17"/>
     <col width="6.5703125" bestFit="1" customWidth="1" style="10" min="18" max="18"/>
     <col width="6.5703125" customWidth="1" style="10" min="19" max="19"/>
-    <col width="8.7109375" customWidth="1" style="59" min="20" max="29"/>
-    <col width="8.7109375" customWidth="1" style="59" min="30" max="16384"/>
+    <col width="8.7109375" customWidth="1" style="59" min="20" max="30"/>
+    <col width="8.7109375" customWidth="1" style="59" min="31" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="21.6" customFormat="1" customHeight="1" s="61">
@@ -34194,8 +34383,8 @@
     <col width="14.85546875" customWidth="1" style="10" min="11" max="12"/>
     <col width="8.7109375" customWidth="1" style="59" min="13" max="13"/>
     <col width="33.140625" customWidth="1" style="59" min="14" max="14"/>
-    <col width="8.7109375" customWidth="1" style="59" min="15" max="24"/>
-    <col width="8.7109375" customWidth="1" style="59" min="25" max="16384"/>
+    <col width="8.7109375" customWidth="1" style="59" min="15" max="25"/>
+    <col width="8.7109375" customWidth="1" style="59" min="26" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customFormat="1" customHeight="1" s="61">

--- a/DB Flotte ETR1000 Ver_1.8_PROVA.xlsx
+++ b/DB Flotte ETR1000 Ver_1.8_PROVA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\__SCRIPTS\AskTrainMind\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BD369D2-51C2-4FB0-A1F5-CC731A06A687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{001C1F38-B7D0-469D-99FA-24F051CB4EB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="6" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="3" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Issue" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'PBS (TBD)'!$A$2:$J$86</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">Requisiti!$A$1:$K$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">Requisiti!$A$1:$K$5</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1499,7 +1499,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4568" uniqueCount="1738">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4488" uniqueCount="1693">
   <si>
     <t>FUNC ID</t>
   </si>
@@ -6144,281 +6144,6 @@
     <t>CONFIGURAZIONE APPARTENENZA</t>
   </si>
   <si>
-    <t>2F_04.01.Zefiro-Europe.TRS.772</t>
-  </si>
-  <si>
-    <t>VZI-6_R1, VZI_Base, VZ_ES, VZ_FR</t>
-  </si>
-  <si>
-    <t>2F_04.01.Zefiro-Europe.CONCEPT.775</t>
-  </si>
-  <si>
-    <t>2F_04.01.Zefiro-Europe.CONCEPT.965</t>
-  </si>
-  <si>
-    <t>2F_04.01.Zefiro-Europe.CONCEPT.1013</t>
-  </si>
-  <si>
-    <t>2F_04.01.Zefiro-Europe.CONCEPT.HR01</t>
-  </si>
-  <si>
-    <t>2F_04.01.Zefiro-Europe.CONCEPT.HR310</t>
-  </si>
-  <si>
-    <t>2F_04.01.Zefiro-Europe.CONCEPT.797</t>
-  </si>
-  <si>
-    <t>2F_04.01.Zefiro-Europe.CONCEPT.HR02</t>
-  </si>
-  <si>
-    <t>2F_04.01.Zefiro-Europe.CONCEPT.HR03</t>
-  </si>
-  <si>
-    <t>2F_04.01.Zefiro-Europe.TRS.619</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFBF8F00"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>VZI-6_R1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>VZI_Base</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>VZ_ES</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00703C"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>VZ_FR</t>
-    </r>
-  </si>
-  <si>
-    <t>2F_04.01.Zefiro-Europe.CONCEPT.735</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFBF8F00"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>VZI-6_R1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>VZI_Base</t>
-    </r>
-  </si>
-  <si>
-    <t>2F_04.01.Zefiro-Europe.CONCEPT.1099</t>
-  </si>
-  <si>
-    <t>2F_04.01.Zefiro-Europe.CONCEPT.1096</t>
-  </si>
-  <si>
-    <t>2F_04.01.Zefiro-Europe.CONCEPT.1113</t>
-  </si>
-  <si>
-    <t>2F_04.01.Zefiro-Europe.CONCEPT.1114</t>
-  </si>
-  <si>
-    <t>2F_04.01.Zefiro-Europe.CONCEPT.1168</t>
-  </si>
-  <si>
-    <t>2F_04.01.Zefiro-Europe.CONCEPT.1174</t>
-  </si>
-  <si>
-    <t>2F_04.01.Zefiro-Europe.TRS.266</t>
-  </si>
-  <si>
-    <t>2F_04.01.Zefiro-Europe.TRS.769</t>
-  </si>
-  <si>
-    <t>2F_04.01.Zefiro-Europe.TRS.770</t>
-  </si>
-  <si>
-    <t>2F_04.01.Zefiro-Europe.CONCEPT.984</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFBF8F00"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>VZI-6_R1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>VZI_Base</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00703C"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>VZ_FR</t>
-    </r>
-  </si>
-  <si>
-    <t>2F_04.01.Zefiro-Europe.CONCEPT.983</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFBF8F00"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>VZI-6_R1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00703C"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>VZ_FR</t>
-    </r>
-  </si>
-  <si>
-    <t>2F_04.01.Zefiro-Europe.CONCEPT.968</t>
-  </si>
-  <si>
-    <t>2F_04.01.Zefiro-Europe.CONCEPT.969</t>
-  </si>
-  <si>
-    <t>2F_04.01.Zefiro-Europe.CONCEPT.561</t>
-  </si>
-  <si>
-    <t>2F_04.01.Zefiro-Europe.CONCEPT.1219</t>
-  </si>
-  <si>
-    <t>2F_04.01.Zefiro-Europe.CONCEPT.1220</t>
-  </si>
-  <si>
-    <t>2F_04.01.Zefiro-Europe.CONCEPT.1225</t>
-  </si>
-  <si>
-    <t>2F_04.01.Zefiro-Europe.CONCEPT.370</t>
-  </si>
-  <si>
-    <t>2F_04.01.Zefiro-Europe.CONCEPT.565</t>
-  </si>
-  <si>
-    <t>2F_04.01.Zefiro-Europe.CONCEPT.1073</t>
-  </si>
-  <si>
-    <t>2F_04.01.Zefiro-Europe.CONCEPT.77</t>
-  </si>
-  <si>
-    <t>2F_04.01.Zefiro-Europe.CONCEPT.289</t>
-  </si>
-  <si>
-    <t>2F_04.01.Zefiro-Europe.CONCEPT.562</t>
-  </si>
-  <si>
-    <t>2F_04.01.Zefiro-Europe.CONCEPT.1098</t>
-  </si>
-  <si>
-    <t>2F_04.01.Zefiro-Europe.CONCEPT.994</t>
-  </si>
-  <si>
-    <t>2F_04.01.Zefiro-Europe.CONCEPT.1008</t>
-  </si>
-  <si>
-    <t>2F_04.01.Zefiro-Europe.CONCEPT.1153</t>
-  </si>
-  <si>
-    <t>2F_04.01.Zefiro-Europe.CONCEPT.1165</t>
-  </si>
-  <si>
-    <t>2F_04.01.Zefiro-Europe.CONCEPT.1172</t>
-  </si>
-  <si>
     <t>Impianto</t>
   </si>
   <si>
@@ -7405,7 +7130,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-410]mmm\-yy;@"/>
   </numFmts>
-  <fonts count="43" x14ac:knownFonts="1">
+  <fonts count="35" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7644,52 +7369,12 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFBF8F00"/>
+      <color rgb="FF00AA00"/>
       <name val="Calibri"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF00AA00"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF1F4E79"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF7030A0"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF00703C"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFBF8F00"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF00AA00"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF00703C"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -8858,7 +8543,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="528">
+  <cellXfs count="523">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -10024,26 +9709,11 @@
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -10633,7 +10303,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:K111"/>
+  <dimension ref="A1:K71"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.140625" style="62" bestFit="1" customWidth="1"/>
@@ -10718,1355 +10388,1035 @@
       <c r="K3" s="351"/>
     </row>
     <row r="4" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C4" s="428" t="s">
-        <v>1381</v>
-      </c>
-      <c r="D4" s="421" t="s">
-        <v>1382</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C5" s="428" t="s">
-        <v>1383</v>
-      </c>
-      <c r="D5" s="421" t="s">
-        <v>1382</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C6" s="428" t="s">
-        <v>1384</v>
-      </c>
-      <c r="D6" s="421" t="s">
-        <v>1382</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C7" s="428" t="s">
-        <v>1385</v>
-      </c>
-      <c r="D7" s="421" t="s">
-        <v>1382</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C8" s="428" t="s">
-        <v>1386</v>
-      </c>
-      <c r="D8" s="429" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C9" s="428" t="s">
-        <v>1387</v>
-      </c>
-      <c r="D9" s="429" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C10" s="428" t="s">
-        <v>1388</v>
-      </c>
-      <c r="D10" s="421" t="s">
-        <v>1382</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C11" s="428" t="s">
-        <v>1389</v>
-      </c>
-      <c r="D11" s="429" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C12" s="428" t="s">
-        <v>1390</v>
-      </c>
-      <c r="D12" s="429" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="347" t="s">
+      <c r="A4" s="347" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="347" t="s">
+      <c r="B4" s="347" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="303"/>
-      <c r="D13" s="303"/>
-      <c r="E13" s="350"/>
-      <c r="F13" s="350"/>
-      <c r="G13" s="350"/>
-      <c r="H13" s="350"/>
-      <c r="I13" s="350"/>
-      <c r="J13" s="350"/>
-      <c r="K13" s="351"/>
-    </row>
-    <row r="14" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C14" s="431" t="s">
-        <v>1391</v>
-      </c>
-      <c r="D14" s="421" t="s">
-        <v>1392</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C15" s="431" t="s">
-        <v>1393</v>
-      </c>
-      <c r="D15" s="421" t="s">
-        <v>1394</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C16" s="431" t="s">
-        <v>1395</v>
-      </c>
-      <c r="D16" s="432" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C17" s="431" t="s">
-        <v>1396</v>
-      </c>
-      <c r="D17" s="432" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C18" s="431" t="s">
-        <v>1397</v>
-      </c>
-      <c r="D18" s="432" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C19" s="431" t="s">
-        <v>1398</v>
-      </c>
-      <c r="D19" s="432" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C20" s="431" t="s">
-        <v>1399</v>
-      </c>
-      <c r="D20" s="432" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C21" s="431" t="s">
-        <v>1400</v>
-      </c>
-      <c r="D21" s="432" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A22" s="347" t="s">
+      <c r="C4" s="303"/>
+      <c r="D4" s="303"/>
+      <c r="E4" s="350"/>
+      <c r="F4" s="350"/>
+      <c r="G4" s="350"/>
+      <c r="H4" s="350"/>
+      <c r="I4" s="350"/>
+      <c r="J4" s="350"/>
+      <c r="K4" s="351"/>
+    </row>
+    <row r="5" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="347" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="347" t="s">
+      <c r="B5" s="347" t="s">
         <v>38</v>
       </c>
-      <c r="C22" s="303"/>
-      <c r="D22" s="303"/>
-      <c r="E22" s="350"/>
-      <c r="F22" s="350"/>
-      <c r="G22" s="350"/>
-      <c r="H22" s="350"/>
-      <c r="I22" s="350"/>
-      <c r="J22" s="350"/>
-      <c r="K22" s="351"/>
-    </row>
-    <row r="23" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C23" s="428" t="s">
-        <v>1401</v>
-      </c>
-      <c r="D23" s="421" t="s">
-        <v>1392</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C24" s="431" t="s">
-        <v>1402</v>
-      </c>
-      <c r="D24" s="421" t="s">
-        <v>1392</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C25" s="431" t="s">
-        <v>1403</v>
-      </c>
-      <c r="D25" s="421" t="s">
-        <v>1392</v>
-      </c>
+      <c r="C5" s="303"/>
+      <c r="D5" s="303"/>
+      <c r="E5" s="350"/>
+      <c r="F5" s="350"/>
+      <c r="G5" s="350"/>
+      <c r="H5" s="350"/>
+      <c r="I5" s="350"/>
+      <c r="J5" s="350"/>
+      <c r="K5" s="351"/>
+    </row>
+    <row r="6" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="353" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="354" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="302"/>
+      <c r="D6" s="302"/>
+      <c r="E6" s="357"/>
+      <c r="F6" s="357"/>
+      <c r="G6" s="357"/>
+      <c r="H6" s="357"/>
+      <c r="I6" s="357"/>
+      <c r="J6" s="357"/>
+      <c r="K6" s="358"/>
+    </row>
+    <row r="7" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A7" s="353" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" s="360" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" s="302"/>
+      <c r="D7" s="302"/>
+      <c r="E7" s="357"/>
+      <c r="F7" s="357"/>
+      <c r="G7" s="357"/>
+      <c r="H7" s="357"/>
+      <c r="I7" s="357"/>
+      <c r="J7" s="357"/>
+      <c r="K7" s="358"/>
+    </row>
+    <row r="8" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="353" t="s">
+        <v>51</v>
+      </c>
+      <c r="B8" s="360" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" s="302"/>
+      <c r="D8" s="302"/>
+      <c r="E8" s="357"/>
+      <c r="F8" s="357"/>
+      <c r="G8" s="357"/>
+      <c r="H8" s="357"/>
+      <c r="I8" s="357"/>
+      <c r="J8" s="357"/>
+      <c r="K8" s="358"/>
+    </row>
+    <row r="9" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A9" s="353" t="s">
+        <v>57</v>
+      </c>
+      <c r="B9" s="360" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9" s="302"/>
+      <c r="D9" s="302"/>
+      <c r="E9" s="357"/>
+      <c r="F9" s="357"/>
+      <c r="G9" s="357"/>
+      <c r="H9" s="357"/>
+      <c r="I9" s="357"/>
+      <c r="J9" s="357"/>
+      <c r="K9" s="358"/>
+    </row>
+    <row r="10" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="353" t="s">
+        <v>63</v>
+      </c>
+      <c r="B10" s="360" t="s">
+        <v>64</v>
+      </c>
+      <c r="C10" s="302"/>
+      <c r="D10" s="302"/>
+      <c r="E10" s="357"/>
+      <c r="F10" s="357"/>
+      <c r="G10" s="357"/>
+      <c r="H10" s="357"/>
+      <c r="I10" s="357"/>
+      <c r="J10" s="357"/>
+      <c r="K10" s="358"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="353" t="s">
+        <v>69</v>
+      </c>
+      <c r="B11" s="360" t="s">
+        <v>70</v>
+      </c>
+      <c r="C11" s="302"/>
+      <c r="D11" s="302"/>
+      <c r="E11" s="357"/>
+      <c r="F11" s="357"/>
+      <c r="G11" s="357"/>
+      <c r="H11" s="357"/>
+      <c r="I11" s="357"/>
+      <c r="J11" s="357"/>
+      <c r="K11" s="358"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="353" t="s">
+        <v>75</v>
+      </c>
+      <c r="B12" s="360" t="s">
+        <v>76</v>
+      </c>
+      <c r="C12" s="302"/>
+      <c r="D12" s="302"/>
+      <c r="E12" s="357"/>
+      <c r="F12" s="357"/>
+      <c r="G12" s="357"/>
+      <c r="H12" s="357"/>
+      <c r="I12" s="357"/>
+      <c r="J12" s="357"/>
+      <c r="K12" s="358"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="353" t="s">
+        <v>81</v>
+      </c>
+      <c r="B13" s="360" t="s">
+        <v>82</v>
+      </c>
+      <c r="C13" s="302"/>
+      <c r="D13" s="302"/>
+      <c r="E13" s="357"/>
+      <c r="F13" s="357"/>
+      <c r="G13" s="357"/>
+      <c r="H13" s="357"/>
+      <c r="I13" s="357"/>
+      <c r="J13" s="357"/>
+      <c r="K13" s="358"/>
+    </row>
+    <row r="14" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="A14" s="353" t="s">
+        <v>87</v>
+      </c>
+      <c r="B14" s="360" t="s">
+        <v>88</v>
+      </c>
+      <c r="C14" s="304"/>
+      <c r="D14" s="304"/>
+      <c r="E14" s="357"/>
+      <c r="F14" s="357"/>
+      <c r="G14" s="357"/>
+      <c r="H14" s="357"/>
+      <c r="I14" s="357"/>
+      <c r="J14" s="357"/>
+      <c r="K14" s="358"/>
+    </row>
+    <row r="15" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A15" s="353" t="s">
+        <v>93</v>
+      </c>
+      <c r="B15" s="360" t="s">
+        <v>94</v>
+      </c>
+      <c r="C15" s="304"/>
+      <c r="D15" s="304"/>
+      <c r="E15" s="357"/>
+      <c r="F15" s="357"/>
+      <c r="G15" s="357"/>
+      <c r="H15" s="357"/>
+      <c r="I15" s="357"/>
+      <c r="J15" s="357"/>
+      <c r="K15" s="358"/>
+    </row>
+    <row r="16" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="353" t="s">
+        <v>99</v>
+      </c>
+      <c r="B16" s="360" t="s">
+        <v>100</v>
+      </c>
+      <c r="C16" s="304"/>
+      <c r="D16" s="304"/>
+      <c r="E16" s="357"/>
+      <c r="F16" s="357"/>
+      <c r="G16" s="357"/>
+      <c r="H16" s="357"/>
+      <c r="I16" s="357"/>
+      <c r="J16" s="357"/>
+      <c r="K16" s="358"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="353" t="s">
+        <v>105</v>
+      </c>
+      <c r="B17" s="360" t="s">
+        <v>106</v>
+      </c>
+      <c r="C17" s="304"/>
+      <c r="D17" s="304"/>
+      <c r="E17" s="357"/>
+      <c r="F17" s="357"/>
+      <c r="G17" s="357"/>
+      <c r="H17" s="357"/>
+      <c r="I17" s="357"/>
+      <c r="J17" s="357"/>
+      <c r="K17" s="358"/>
+    </row>
+    <row r="18" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="353" t="s">
+        <v>111</v>
+      </c>
+      <c r="B18" s="360" t="s">
+        <v>112</v>
+      </c>
+      <c r="C18" s="304"/>
+      <c r="D18" s="304"/>
+      <c r="E18" s="357"/>
+      <c r="F18" s="357"/>
+      <c r="G18" s="357"/>
+      <c r="H18" s="357"/>
+      <c r="I18" s="357"/>
+      <c r="J18" s="357"/>
+      <c r="K18" s="358"/>
+    </row>
+    <row r="19" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A19" s="353" t="s">
+        <v>117</v>
+      </c>
+      <c r="B19" s="360" t="s">
+        <v>118</v>
+      </c>
+      <c r="C19" s="304"/>
+      <c r="D19" s="304"/>
+      <c r="E19" s="357"/>
+      <c r="F19" s="357"/>
+      <c r="G19" s="357"/>
+      <c r="H19" s="357"/>
+      <c r="I19" s="357"/>
+      <c r="J19" s="357"/>
+      <c r="K19" s="358"/>
+    </row>
+    <row r="20" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A20" s="353" t="s">
+        <v>120</v>
+      </c>
+      <c r="B20" s="360" t="s">
+        <v>121</v>
+      </c>
+      <c r="C20" s="304"/>
+      <c r="D20" s="304"/>
+      <c r="E20" s="357"/>
+      <c r="F20" s="357"/>
+      <c r="G20" s="357"/>
+      <c r="H20" s="357"/>
+      <c r="I20" s="357"/>
+      <c r="J20" s="357"/>
+      <c r="K20" s="358"/>
+    </row>
+    <row r="21" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A21" s="353" t="s">
+        <v>123</v>
+      </c>
+      <c r="B21" s="360" t="s">
+        <v>124</v>
+      </c>
+      <c r="C21" s="304"/>
+      <c r="D21" s="304"/>
+      <c r="E21" s="357"/>
+      <c r="F21" s="357"/>
+      <c r="G21" s="357"/>
+      <c r="H21" s="357"/>
+      <c r="I21" s="357"/>
+      <c r="J21" s="357"/>
+      <c r="K21" s="358"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="353" t="s">
+        <v>128</v>
+      </c>
+      <c r="B22" s="364" t="s">
+        <v>129</v>
+      </c>
+      <c r="C22" s="304"/>
+      <c r="D22" s="304"/>
+      <c r="E22" s="357"/>
+      <c r="F22" s="357"/>
+      <c r="G22" s="357"/>
+      <c r="H22" s="357"/>
+      <c r="I22" s="357"/>
+      <c r="J22" s="357"/>
+      <c r="K22" s="358"/>
+    </row>
+    <row r="23" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" s="353" t="s">
+        <v>134</v>
+      </c>
+      <c r="B23" s="364" t="s">
+        <v>135</v>
+      </c>
+      <c r="C23" s="304"/>
+      <c r="D23" s="304"/>
+      <c r="E23" s="357"/>
+      <c r="F23" s="357"/>
+      <c r="G23" s="357"/>
+      <c r="H23" s="357"/>
+      <c r="I23" s="357"/>
+      <c r="J23" s="357"/>
+      <c r="K23" s="358"/>
+    </row>
+    <row r="24" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A24" s="353" t="s">
+        <v>140</v>
+      </c>
+      <c r="B24" s="364" t="s">
+        <v>141</v>
+      </c>
+      <c r="C24" s="304"/>
+      <c r="D24" s="304"/>
+      <c r="E24" s="357"/>
+      <c r="F24" s="357"/>
+      <c r="G24" s="357"/>
+      <c r="H24" s="357"/>
+      <c r="I24" s="357"/>
+      <c r="J24" s="357"/>
+      <c r="K24" s="358"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="353" t="s">
+        <v>146</v>
+      </c>
+      <c r="B25" s="364" t="s">
+        <v>147</v>
+      </c>
+      <c r="C25" s="304"/>
+      <c r="D25" s="304"/>
+      <c r="E25" s="357"/>
+      <c r="F25" s="357"/>
+      <c r="G25" s="357"/>
+      <c r="H25" s="357"/>
+      <c r="I25" s="357"/>
+      <c r="J25" s="357"/>
+      <c r="K25" s="358"/>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C26" s="431" t="s">
-        <v>1404</v>
-      </c>
-      <c r="D26" s="421" t="s">
-        <v>1405</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C27" s="431" t="s">
-        <v>1406</v>
-      </c>
-      <c r="D27" s="421" t="s">
-        <v>1407</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C28" s="431" t="s">
-        <v>1408</v>
-      </c>
-      <c r="D28" s="421" t="s">
-        <v>1407</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C29" s="431" t="s">
-        <v>1409</v>
-      </c>
-      <c r="D29" s="421" t="s">
-        <v>1407</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C30" s="431" t="s">
-        <v>1410</v>
-      </c>
-      <c r="D30" s="421" t="s">
-        <v>1407</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="C31" s="431" t="s">
-        <v>1411</v>
-      </c>
-      <c r="D31" s="421" t="s">
-        <v>1407</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C32" s="431" t="s">
-        <v>1412</v>
-      </c>
-      <c r="D32" s="421" t="s">
-        <v>1407</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C33" s="431" t="s">
-        <v>1413</v>
-      </c>
-      <c r="D33" s="421" t="s">
-        <v>1407</v>
-      </c>
+      <c r="A26" s="353" t="s">
+        <v>152</v>
+      </c>
+      <c r="B26" s="360"/>
+      <c r="C26" s="304"/>
+      <c r="D26" s="304"/>
+      <c r="E26" s="357"/>
+      <c r="F26" s="357"/>
+      <c r="G26" s="357"/>
+      <c r="H26" s="357"/>
+      <c r="I26" s="357"/>
+      <c r="J26" s="357"/>
+      <c r="K26" s="358"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="353" t="s">
+        <v>158</v>
+      </c>
+      <c r="B27" s="360"/>
+      <c r="C27" s="304"/>
+      <c r="D27" s="304"/>
+      <c r="E27" s="357"/>
+      <c r="F27" s="357"/>
+      <c r="G27" s="357"/>
+      <c r="H27" s="357"/>
+      <c r="I27" s="357"/>
+      <c r="J27" s="357"/>
+      <c r="K27" s="358"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="353" t="s">
+        <v>163</v>
+      </c>
+      <c r="B28" s="360"/>
+      <c r="C28" s="304"/>
+      <c r="D28" s="304"/>
+      <c r="E28" s="357"/>
+      <c r="F28" s="357"/>
+      <c r="G28" s="357"/>
+      <c r="H28" s="357"/>
+      <c r="I28" s="357"/>
+      <c r="J28" s="357"/>
+      <c r="K28" s="358"/>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="353" t="s">
+        <v>168</v>
+      </c>
+      <c r="B29" s="360"/>
+      <c r="C29" s="304"/>
+      <c r="D29" s="304"/>
+      <c r="E29" s="357"/>
+      <c r="F29" s="357"/>
+      <c r="G29" s="357"/>
+      <c r="H29" s="357"/>
+      <c r="I29" s="357"/>
+      <c r="J29" s="357"/>
+      <c r="K29" s="358"/>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" s="353" t="s">
+        <v>173</v>
+      </c>
+      <c r="B30" s="360"/>
+      <c r="C30" s="304"/>
+      <c r="D30" s="304"/>
+      <c r="E30" s="357"/>
+      <c r="F30" s="357"/>
+      <c r="G30" s="357"/>
+      <c r="H30" s="357"/>
+      <c r="I30" s="357"/>
+      <c r="J30" s="357"/>
+      <c r="K30" s="358"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" s="353" t="s">
+        <v>178</v>
+      </c>
+      <c r="B31" s="360"/>
+      <c r="C31" s="304"/>
+      <c r="D31" s="304"/>
+      <c r="E31" s="357"/>
+      <c r="F31" s="357"/>
+      <c r="G31" s="357"/>
+      <c r="H31" s="357"/>
+      <c r="I31" s="357"/>
+      <c r="J31" s="357"/>
+      <c r="K31" s="358"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" s="353" t="s">
+        <v>183</v>
+      </c>
+      <c r="B32" s="360"/>
+      <c r="C32" s="304"/>
+      <c r="D32" s="304"/>
+      <c r="E32" s="357"/>
+      <c r="F32" s="357"/>
+      <c r="G32" s="357"/>
+      <c r="H32" s="357"/>
+      <c r="I32" s="357"/>
+      <c r="J32" s="357"/>
+      <c r="K32" s="358"/>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" s="353" t="s">
+        <v>188</v>
+      </c>
+      <c r="B33" s="360"/>
+      <c r="C33" s="304"/>
+      <c r="D33" s="304"/>
+      <c r="E33" s="357"/>
+      <c r="F33" s="357"/>
+      <c r="G33" s="357"/>
+      <c r="H33" s="357"/>
+      <c r="I33" s="357"/>
+      <c r="J33" s="357"/>
+      <c r="K33" s="358"/>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C34" s="431" t="s">
-        <v>1414</v>
-      </c>
-      <c r="D34" s="433" t="s">
-        <v>7</v>
-      </c>
+      <c r="A34" s="181" t="s">
+        <v>193</v>
+      </c>
+      <c r="B34" s="367"/>
+      <c r="C34" s="304"/>
+      <c r="D34" s="304"/>
+      <c r="E34" s="163"/>
+      <c r="F34" s="163"/>
+      <c r="G34" s="163"/>
+      <c r="H34" s="163"/>
+      <c r="I34" s="163"/>
+      <c r="J34" s="163"/>
+      <c r="K34" s="164"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C35" s="431" t="s">
-        <v>1415</v>
-      </c>
-      <c r="D35" s="433" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="C36" s="431" t="s">
-        <v>1416</v>
-      </c>
-      <c r="D36" s="433" t="s">
-        <v>7</v>
-      </c>
+      <c r="A35" s="181" t="s">
+        <v>197</v>
+      </c>
+      <c r="B35" s="367"/>
+      <c r="C35" s="304"/>
+      <c r="D35" s="304"/>
+      <c r="E35" s="163"/>
+      <c r="F35" s="163"/>
+      <c r="G35" s="163"/>
+      <c r="H35" s="163"/>
+      <c r="I35" s="163"/>
+      <c r="J35" s="163"/>
+      <c r="K35" s="164"/>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A36" s="181" t="s">
+        <v>200</v>
+      </c>
+      <c r="B36" s="367"/>
+      <c r="C36" s="304"/>
+      <c r="D36" s="304"/>
+      <c r="E36" s="163"/>
+      <c r="F36" s="163"/>
+      <c r="G36" s="163"/>
+      <c r="H36" s="163"/>
+      <c r="I36" s="163"/>
+      <c r="J36" s="163"/>
+      <c r="K36" s="164"/>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C37" s="431" t="s">
-        <v>1417</v>
-      </c>
-      <c r="D37" s="433" t="s">
-        <v>7</v>
-      </c>
+      <c r="A37" s="181" t="s">
+        <v>203</v>
+      </c>
+      <c r="B37" s="367"/>
+      <c r="C37" s="304"/>
+      <c r="D37" s="304"/>
+      <c r="E37" s="163"/>
+      <c r="F37" s="163"/>
+      <c r="G37" s="163"/>
+      <c r="H37" s="163"/>
+      <c r="I37" s="163"/>
+      <c r="J37" s="163"/>
+      <c r="K37" s="164"/>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C38" s="431" t="s">
-        <v>1418</v>
-      </c>
-      <c r="D38" s="433" t="s">
-        <v>7</v>
-      </c>
+      <c r="A38" s="181" t="s">
+        <v>206</v>
+      </c>
+      <c r="B38" s="367"/>
+      <c r="C38" s="304"/>
+      <c r="D38" s="304"/>
+      <c r="E38" s="163"/>
+      <c r="F38" s="163"/>
+      <c r="G38" s="163"/>
+      <c r="H38" s="163"/>
+      <c r="I38" s="163"/>
+      <c r="J38" s="163"/>
+      <c r="K38" s="164"/>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C39" s="431" t="s">
-        <v>1419</v>
-      </c>
-      <c r="D39" s="433" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="C40" s="431" t="s">
-        <v>1420</v>
-      </c>
-      <c r="D40" s="433" t="s">
-        <v>7</v>
-      </c>
+      <c r="A39" s="181" t="s">
+        <v>209</v>
+      </c>
+      <c r="B39" s="367"/>
+      <c r="C39" s="304"/>
+      <c r="D39" s="304"/>
+      <c r="E39" s="163"/>
+      <c r="F39" s="163"/>
+      <c r="G39" s="163"/>
+      <c r="H39" s="163"/>
+      <c r="I39" s="163"/>
+      <c r="J39" s="163"/>
+      <c r="K39" s="164"/>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A40" s="181" t="s">
+        <v>212</v>
+      </c>
+      <c r="B40" s="367"/>
+      <c r="C40" s="304"/>
+      <c r="D40" s="304"/>
+      <c r="E40" s="163"/>
+      <c r="F40" s="163"/>
+      <c r="G40" s="163"/>
+      <c r="H40" s="163"/>
+      <c r="I40" s="163"/>
+      <c r="J40" s="163"/>
+      <c r="K40" s="164"/>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C41" s="431" t="s">
-        <v>1421</v>
-      </c>
-      <c r="D41" s="433" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="C42" s="431" t="s">
-        <v>1422</v>
-      </c>
-      <c r="D42" s="433" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="C43" s="431" t="s">
-        <v>1423</v>
-      </c>
-      <c r="D43" s="433" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="C44" s="431" t="s">
-        <v>1424</v>
-      </c>
-      <c r="D44" s="433" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="C45" s="431" t="s">
-        <v>1425</v>
-      </c>
-      <c r="D45" s="433" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A46" s="353" t="s">
-        <v>39</v>
-      </c>
-      <c r="B46" s="354" t="s">
-        <v>40</v>
-      </c>
-      <c r="C46" s="302"/>
-      <c r="D46" s="302"/>
-      <c r="E46" s="357"/>
-      <c r="F46" s="357"/>
-      <c r="G46" s="357"/>
-      <c r="H46" s="357"/>
-      <c r="I46" s="357"/>
-      <c r="J46" s="357"/>
-      <c r="K46" s="358"/>
-    </row>
-    <row r="47" spans="1:11" ht="45" x14ac:dyDescent="0.25">
-      <c r="A47" s="353" t="s">
-        <v>45</v>
-      </c>
-      <c r="B47" s="360" t="s">
-        <v>46</v>
-      </c>
-      <c r="C47" s="302"/>
-      <c r="D47" s="302"/>
-      <c r="E47" s="357"/>
-      <c r="F47" s="357"/>
-      <c r="G47" s="357"/>
-      <c r="H47" s="357"/>
-      <c r="I47" s="357"/>
-      <c r="J47" s="357"/>
-      <c r="K47" s="358"/>
-    </row>
-    <row r="48" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A48" s="353" t="s">
-        <v>51</v>
-      </c>
-      <c r="B48" s="360" t="s">
-        <v>52</v>
-      </c>
-      <c r="C48" s="302"/>
-      <c r="D48" s="302"/>
-      <c r="E48" s="357"/>
-      <c r="F48" s="357"/>
-      <c r="G48" s="357"/>
-      <c r="H48" s="357"/>
-      <c r="I48" s="357"/>
-      <c r="J48" s="357"/>
-      <c r="K48" s="358"/>
-    </row>
-    <row r="49" spans="1:11" ht="45" x14ac:dyDescent="0.25">
-      <c r="A49" s="353" t="s">
-        <v>57</v>
-      </c>
-      <c r="B49" s="360" t="s">
-        <v>58</v>
-      </c>
-      <c r="C49" s="302"/>
-      <c r="D49" s="302"/>
-      <c r="E49" s="357"/>
-      <c r="F49" s="357"/>
-      <c r="G49" s="357"/>
-      <c r="H49" s="357"/>
-      <c r="I49" s="357"/>
-      <c r="J49" s="357"/>
-      <c r="K49" s="358"/>
-    </row>
-    <row r="50" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A50" s="353" t="s">
-        <v>63</v>
-      </c>
-      <c r="B50" s="360" t="s">
-        <v>64</v>
-      </c>
-      <c r="C50" s="302"/>
-      <c r="D50" s="302"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
-      <c r="G50" s="357"/>
-      <c r="H50" s="357"/>
-      <c r="I50" s="357"/>
-      <c r="J50" s="357"/>
-      <c r="K50" s="358"/>
+      <c r="A41" s="181" t="s">
+        <v>217</v>
+      </c>
+      <c r="B41" s="367"/>
+      <c r="C41" s="304"/>
+      <c r="D41" s="304"/>
+      <c r="E41" s="163"/>
+      <c r="F41" s="163"/>
+      <c r="G41" s="163"/>
+      <c r="H41" s="163"/>
+      <c r="I41" s="163"/>
+      <c r="J41" s="163"/>
+      <c r="K41" s="164"/>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A42" s="181" t="s">
+        <v>221</v>
+      </c>
+      <c r="B42" s="367"/>
+      <c r="C42" s="304"/>
+      <c r="D42" s="304"/>
+      <c r="E42" s="163"/>
+      <c r="F42" s="163"/>
+      <c r="G42" s="163"/>
+      <c r="H42" s="163"/>
+      <c r="I42" s="163"/>
+      <c r="J42" s="163"/>
+      <c r="K42" s="164"/>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A43" s="181" t="s">
+        <v>225</v>
+      </c>
+      <c r="B43" s="367"/>
+      <c r="C43" s="304"/>
+      <c r="D43" s="304"/>
+      <c r="E43" s="163"/>
+      <c r="F43" s="163"/>
+      <c r="G43" s="163"/>
+      <c r="H43" s="163"/>
+      <c r="I43" s="163"/>
+      <c r="J43" s="163"/>
+      <c r="K43" s="164"/>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A44" s="181" t="s">
+        <v>229</v>
+      </c>
+      <c r="B44" s="367"/>
+      <c r="C44" s="304"/>
+      <c r="D44" s="304"/>
+      <c r="E44" s="163"/>
+      <c r="F44" s="163"/>
+      <c r="G44" s="163"/>
+      <c r="H44" s="163"/>
+      <c r="I44" s="163"/>
+      <c r="J44" s="163"/>
+      <c r="K44" s="164"/>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A45" s="181" t="s">
+        <v>233</v>
+      </c>
+      <c r="B45" s="367"/>
+      <c r="C45" s="304"/>
+      <c r="D45" s="304"/>
+      <c r="E45" s="163"/>
+      <c r="F45" s="163"/>
+      <c r="G45" s="163"/>
+      <c r="H45" s="163"/>
+      <c r="I45" s="163"/>
+      <c r="J45" s="163"/>
+      <c r="K45" s="164"/>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A46" s="181" t="s">
+        <v>237</v>
+      </c>
+      <c r="B46" s="367"/>
+      <c r="C46" s="304"/>
+      <c r="D46" s="304"/>
+      <c r="E46" s="163"/>
+      <c r="F46" s="163"/>
+      <c r="G46" s="163"/>
+      <c r="H46" s="163"/>
+      <c r="I46" s="163"/>
+      <c r="J46" s="163"/>
+      <c r="K46" s="164"/>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A47" s="181" t="s">
+        <v>241</v>
+      </c>
+      <c r="B47" s="367"/>
+      <c r="C47" s="304"/>
+      <c r="D47" s="304"/>
+      <c r="E47" s="163"/>
+      <c r="F47" s="163"/>
+      <c r="G47" s="163"/>
+      <c r="H47" s="163"/>
+      <c r="I47" s="163"/>
+      <c r="J47" s="163"/>
+      <c r="K47" s="164"/>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A48" s="181" t="s">
+        <v>245</v>
+      </c>
+      <c r="B48" s="367"/>
+      <c r="C48" s="304"/>
+      <c r="D48" s="304"/>
+      <c r="E48" s="163"/>
+      <c r="F48" s="163"/>
+      <c r="G48" s="163"/>
+      <c r="H48" s="163"/>
+      <c r="I48" s="163"/>
+      <c r="J48" s="163"/>
+      <c r="K48" s="164"/>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A49" s="181" t="s">
+        <v>251</v>
+      </c>
+      <c r="B49" s="367"/>
+      <c r="C49" s="304"/>
+      <c r="D49" s="304"/>
+      <c r="E49" s="163"/>
+      <c r="F49" s="163"/>
+      <c r="G49" s="163"/>
+      <c r="H49" s="163"/>
+      <c r="I49" s="163"/>
+      <c r="J49" s="163"/>
+      <c r="K49" s="164"/>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A50" s="181" t="s">
+        <v>256</v>
+      </c>
+      <c r="B50" s="367"/>
+      <c r="C50" s="304"/>
+      <c r="D50" s="304"/>
+      <c r="E50" s="163"/>
+      <c r="F50" s="163"/>
+      <c r="G50" s="163"/>
+      <c r="H50" s="163"/>
+      <c r="I50" s="163"/>
+      <c r="J50" s="163"/>
+      <c r="K50" s="164"/>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A51" s="353" t="s">
-        <v>69</v>
-      </c>
-      <c r="B51" s="360" t="s">
-        <v>70</v>
-      </c>
-      <c r="C51" s="302"/>
-      <c r="D51" s="302"/>
-      <c r="E51" s="357"/>
-      <c r="F51" s="357"/>
-      <c r="G51" s="357"/>
-      <c r="H51" s="357"/>
-      <c r="I51" s="357"/>
-      <c r="J51" s="357"/>
-      <c r="K51" s="358"/>
+      <c r="A51" s="181" t="s">
+        <v>261</v>
+      </c>
+      <c r="B51" s="367"/>
+      <c r="C51" s="304"/>
+      <c r="D51" s="304"/>
+      <c r="E51" s="163"/>
+      <c r="F51" s="163"/>
+      <c r="G51" s="163"/>
+      <c r="H51" s="163"/>
+      <c r="I51" s="163"/>
+      <c r="J51" s="163"/>
+      <c r="K51" s="164"/>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A52" s="353" t="s">
-        <v>75</v>
-      </c>
-      <c r="B52" s="360" t="s">
-        <v>76</v>
-      </c>
-      <c r="C52" s="302"/>
-      <c r="D52" s="302"/>
-      <c r="E52" s="357"/>
-      <c r="F52" s="357"/>
-      <c r="G52" s="357"/>
-      <c r="H52" s="357"/>
-      <c r="I52" s="357"/>
-      <c r="J52" s="357"/>
-      <c r="K52" s="358"/>
+      <c r="A52" s="181" t="s">
+        <v>266</v>
+      </c>
+      <c r="B52" s="367"/>
+      <c r="C52" s="304"/>
+      <c r="D52" s="304"/>
+      <c r="E52" s="163"/>
+      <c r="F52" s="163"/>
+      <c r="G52" s="163"/>
+      <c r="H52" s="163"/>
+      <c r="I52" s="163"/>
+      <c r="J52" s="163"/>
+      <c r="K52" s="164"/>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A53" s="353" t="s">
-        <v>81</v>
-      </c>
-      <c r="B53" s="360" t="s">
-        <v>82</v>
-      </c>
-      <c r="C53" s="302"/>
-      <c r="D53" s="302"/>
-      <c r="E53" s="357"/>
-      <c r="F53" s="357"/>
-      <c r="G53" s="357"/>
-      <c r="H53" s="357"/>
-      <c r="I53" s="357"/>
-      <c r="J53" s="357"/>
-      <c r="K53" s="358"/>
-    </row>
-    <row r="54" spans="1:11" ht="60" x14ac:dyDescent="0.25">
-      <c r="A54" s="353" t="s">
-        <v>87</v>
-      </c>
-      <c r="B54" s="360" t="s">
-        <v>88</v>
-      </c>
+      <c r="A53" s="181" t="s">
+        <v>271</v>
+      </c>
+      <c r="B53" s="367"/>
+      <c r="C53" s="304"/>
+      <c r="D53" s="304"/>
+      <c r="E53" s="163"/>
+      <c r="F53" s="163"/>
+      <c r="G53" s="163"/>
+      <c r="H53" s="163"/>
+      <c r="I53" s="163"/>
+      <c r="J53" s="163"/>
+      <c r="K53" s="164"/>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A54" s="181" t="s">
+        <v>289</v>
+      </c>
+      <c r="B54" s="367"/>
       <c r="C54" s="304"/>
       <c r="D54" s="304"/>
-      <c r="E54" s="357"/>
-      <c r="F54" s="357"/>
-      <c r="G54" s="357"/>
-      <c r="H54" s="357"/>
-      <c r="I54" s="357"/>
-      <c r="J54" s="357"/>
-      <c r="K54" s="358"/>
-    </row>
-    <row r="55" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A55" s="353" t="s">
-        <v>93</v>
-      </c>
-      <c r="B55" s="360" t="s">
-        <v>94</v>
-      </c>
+      <c r="E54" s="163"/>
+      <c r="F54" s="163"/>
+      <c r="G54" s="163"/>
+      <c r="H54" s="163"/>
+      <c r="I54" s="163"/>
+      <c r="J54" s="163"/>
+      <c r="K54" s="164"/>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A55" s="181" t="s">
+        <v>294</v>
+      </c>
+      <c r="B55" s="367"/>
       <c r="C55" s="304"/>
       <c r="D55" s="304"/>
-      <c r="E55" s="357"/>
-      <c r="F55" s="357"/>
-      <c r="G55" s="357"/>
-      <c r="H55" s="357"/>
-      <c r="I55" s="357"/>
-      <c r="J55" s="357"/>
-      <c r="K55" s="358"/>
-    </row>
-    <row r="56" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A56" s="353" t="s">
-        <v>99</v>
-      </c>
-      <c r="B56" s="360" t="s">
-        <v>100</v>
-      </c>
+      <c r="E55" s="163"/>
+      <c r="F55" s="163"/>
+      <c r="G55" s="163"/>
+      <c r="H55" s="163"/>
+      <c r="I55" s="163"/>
+      <c r="J55" s="163"/>
+      <c r="K55" s="164"/>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A56" s="181" t="s">
+        <v>299</v>
+      </c>
+      <c r="B56" s="367"/>
       <c r="C56" s="304"/>
       <c r="D56" s="304"/>
-      <c r="E56" s="357"/>
-      <c r="F56" s="357"/>
-      <c r="G56" s="357"/>
-      <c r="H56" s="357"/>
-      <c r="I56" s="357"/>
-      <c r="J56" s="357"/>
-      <c r="K56" s="358"/>
+      <c r="E56" s="163"/>
+      <c r="F56" s="163"/>
+      <c r="G56" s="163"/>
+      <c r="H56" s="163"/>
+      <c r="I56" s="163"/>
+      <c r="J56" s="163"/>
+      <c r="K56" s="164"/>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A57" s="353" t="s">
-        <v>105</v>
-      </c>
-      <c r="B57" s="360" t="s">
-        <v>106</v>
-      </c>
+      <c r="A57" s="181" t="s">
+        <v>304</v>
+      </c>
+      <c r="B57" s="367"/>
       <c r="C57" s="304"/>
       <c r="D57" s="304"/>
-      <c r="E57" s="357"/>
-      <c r="F57" s="357"/>
-      <c r="G57" s="357"/>
-      <c r="H57" s="357"/>
-      <c r="I57" s="357"/>
-      <c r="J57" s="357"/>
-      <c r="K57" s="358"/>
-    </row>
-    <row r="58" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A58" s="353" t="s">
-        <v>111</v>
-      </c>
-      <c r="B58" s="360" t="s">
-        <v>112</v>
-      </c>
+      <c r="E57" s="163"/>
+      <c r="F57" s="163"/>
+      <c r="G57" s="163"/>
+      <c r="H57" s="163"/>
+      <c r="I57" s="163"/>
+      <c r="J57" s="163"/>
+      <c r="K57" s="164"/>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A58" s="181" t="s">
+        <v>309</v>
+      </c>
+      <c r="B58" s="367"/>
       <c r="C58" s="304"/>
       <c r="D58" s="304"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
-      <c r="G58" s="357"/>
-      <c r="H58" s="357"/>
-      <c r="I58" s="357"/>
-      <c r="J58" s="357"/>
-      <c r="K58" s="358"/>
-    </row>
-    <row r="59" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A59" s="353" t="s">
-        <v>117</v>
-      </c>
-      <c r="B59" s="360" t="s">
-        <v>118</v>
-      </c>
+      <c r="E58" s="163"/>
+      <c r="F58" s="163"/>
+      <c r="G58" s="163"/>
+      <c r="H58" s="163"/>
+      <c r="I58" s="163"/>
+      <c r="J58" s="163"/>
+      <c r="K58" s="164"/>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A59" s="181" t="s">
+        <v>314</v>
+      </c>
+      <c r="B59" s="367"/>
       <c r="C59" s="304"/>
       <c r="D59" s="304"/>
-      <c r="E59" s="357"/>
-      <c r="F59" s="357"/>
-      <c r="G59" s="357"/>
-      <c r="H59" s="357"/>
-      <c r="I59" s="357"/>
-      <c r="J59" s="357"/>
-      <c r="K59" s="358"/>
-    </row>
-    <row r="60" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A60" s="353" t="s">
-        <v>120</v>
-      </c>
-      <c r="B60" s="360" t="s">
-        <v>121</v>
-      </c>
+      <c r="E59" s="163"/>
+      <c r="F59" s="163"/>
+      <c r="G59" s="163"/>
+      <c r="H59" s="163"/>
+      <c r="I59" s="163"/>
+      <c r="J59" s="163"/>
+      <c r="K59" s="164"/>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A60" s="181" t="s">
+        <v>319</v>
+      </c>
+      <c r="B60" s="367"/>
       <c r="C60" s="304"/>
       <c r="D60" s="304"/>
-      <c r="E60" s="357"/>
-      <c r="F60" s="357"/>
-      <c r="G60" s="357"/>
-      <c r="H60" s="357"/>
-      <c r="I60" s="357"/>
-      <c r="J60" s="357"/>
-      <c r="K60" s="358"/>
-    </row>
-    <row r="61" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A61" s="353" t="s">
-        <v>123</v>
-      </c>
-      <c r="B61" s="360" t="s">
-        <v>124</v>
-      </c>
+      <c r="E60" s="163"/>
+      <c r="F60" s="163"/>
+      <c r="G60" s="163"/>
+      <c r="H60" s="163"/>
+      <c r="I60" s="163"/>
+      <c r="J60" s="163"/>
+      <c r="K60" s="164"/>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A61" s="181" t="s">
+        <v>324</v>
+      </c>
+      <c r="B61" s="367"/>
       <c r="C61" s="304"/>
       <c r="D61" s="304"/>
-      <c r="E61" s="357"/>
-      <c r="F61" s="357"/>
-      <c r="G61" s="357"/>
-      <c r="H61" s="357"/>
-      <c r="I61" s="357"/>
-      <c r="J61" s="357"/>
-      <c r="K61" s="358"/>
+      <c r="E61" s="163"/>
+      <c r="F61" s="163"/>
+      <c r="G61" s="163"/>
+      <c r="H61" s="163"/>
+      <c r="I61" s="163"/>
+      <c r="J61" s="163"/>
+      <c r="K61" s="164"/>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A62" s="353" t="s">
-        <v>128</v>
-      </c>
-      <c r="B62" s="364" t="s">
-        <v>129</v>
-      </c>
+      <c r="A62" s="181" t="s">
+        <v>329</v>
+      </c>
+      <c r="B62" s="367"/>
       <c r="C62" s="304"/>
       <c r="D62" s="304"/>
-      <c r="E62" s="357"/>
-      <c r="F62" s="357"/>
-      <c r="G62" s="357"/>
-      <c r="H62" s="357"/>
-      <c r="I62" s="357"/>
-      <c r="J62" s="357"/>
-      <c r="K62" s="358"/>
-    </row>
-    <row r="63" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A63" s="353" t="s">
-        <v>134</v>
-      </c>
-      <c r="B63" s="364" t="s">
-        <v>135</v>
-      </c>
+      <c r="E62" s="163"/>
+      <c r="F62" s="163"/>
+      <c r="G62" s="163"/>
+      <c r="H62" s="163"/>
+      <c r="I62" s="163"/>
+      <c r="J62" s="163"/>
+      <c r="K62" s="164"/>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A63" s="181" t="s">
+        <v>334</v>
+      </c>
+      <c r="B63" s="367"/>
       <c r="C63" s="304"/>
       <c r="D63" s="304"/>
-      <c r="E63" s="357"/>
-      <c r="F63" s="357"/>
-      <c r="G63" s="357"/>
-      <c r="H63" s="357"/>
-      <c r="I63" s="357"/>
-      <c r="J63" s="357"/>
-      <c r="K63" s="358"/>
-    </row>
-    <row r="64" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A64" s="353" t="s">
-        <v>140</v>
-      </c>
-      <c r="B64" s="364" t="s">
-        <v>141</v>
-      </c>
+      <c r="E63" s="163"/>
+      <c r="F63" s="163"/>
+      <c r="G63" s="163"/>
+      <c r="H63" s="163"/>
+      <c r="I63" s="163"/>
+      <c r="J63" s="163"/>
+      <c r="K63" s="164"/>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A64" s="181" t="s">
+        <v>348</v>
+      </c>
+      <c r="B64" s="367"/>
       <c r="C64" s="304"/>
       <c r="D64" s="304"/>
-      <c r="E64" s="357"/>
-      <c r="F64" s="357"/>
-      <c r="G64" s="357"/>
-      <c r="H64" s="357"/>
-      <c r="I64" s="357"/>
-      <c r="J64" s="357"/>
-      <c r="K64" s="358"/>
+      <c r="E64" s="163"/>
+      <c r="F64" s="163"/>
+      <c r="G64" s="163"/>
+      <c r="H64" s="163"/>
+      <c r="I64" s="163"/>
+      <c r="J64" s="163"/>
+      <c r="K64" s="164"/>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A65" s="353" t="s">
-        <v>146</v>
-      </c>
-      <c r="B65" s="364" t="s">
-        <v>147</v>
-      </c>
+      <c r="A65" s="181" t="s">
+        <v>352</v>
+      </c>
+      <c r="B65" s="367"/>
       <c r="C65" s="304"/>
       <c r="D65" s="304"/>
-      <c r="E65" s="357"/>
-      <c r="F65" s="357"/>
-      <c r="G65" s="357"/>
-      <c r="H65" s="357"/>
-      <c r="I65" s="357"/>
-      <c r="J65" s="357"/>
-      <c r="K65" s="358"/>
+      <c r="E65" s="163"/>
+      <c r="F65" s="163"/>
+      <c r="G65" s="163"/>
+      <c r="H65" s="163"/>
+      <c r="I65" s="163"/>
+      <c r="J65" s="163"/>
+      <c r="K65" s="164"/>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A66" s="353" t="s">
-        <v>152</v>
-      </c>
-      <c r="B66" s="360"/>
+      <c r="A66" s="181" t="s">
+        <v>356</v>
+      </c>
+      <c r="B66" s="367"/>
       <c r="C66" s="304"/>
       <c r="D66" s="304"/>
-      <c r="E66" s="357"/>
-      <c r="F66" s="357"/>
-      <c r="G66" s="357"/>
-      <c r="H66" s="357"/>
-      <c r="I66" s="357"/>
-      <c r="J66" s="357"/>
-      <c r="K66" s="358"/>
+      <c r="E66" s="163"/>
+      <c r="F66" s="163"/>
+      <c r="G66" s="163"/>
+      <c r="H66" s="163"/>
+      <c r="I66" s="163"/>
+      <c r="J66" s="163"/>
+      <c r="K66" s="164"/>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A67" s="353" t="s">
-        <v>158</v>
-      </c>
-      <c r="B67" s="360"/>
-      <c r="C67" s="304"/>
-      <c r="D67" s="304"/>
-      <c r="E67" s="357"/>
-      <c r="F67" s="357"/>
-      <c r="G67" s="357"/>
-      <c r="H67" s="357"/>
-      <c r="I67" s="357"/>
-      <c r="J67" s="357"/>
-      <c r="K67" s="358"/>
+      <c r="B67" s="169"/>
+      <c r="E67" s="242"/>
+      <c r="F67" s="242"/>
+      <c r="G67" s="237"/>
+      <c r="H67" s="237"/>
+      <c r="I67" s="242"/>
+      <c r="J67" s="237"/>
+      <c r="K67" s="238"/>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A68" s="353" t="s">
-        <v>163</v>
-      </c>
-      <c r="B68" s="360"/>
-      <c r="C68" s="304"/>
-      <c r="D68" s="304"/>
-      <c r="E68" s="357"/>
-      <c r="F68" s="357"/>
-      <c r="G68" s="357"/>
-      <c r="H68" s="357"/>
-      <c r="I68" s="357"/>
-      <c r="J68" s="357"/>
-      <c r="K68" s="358"/>
+      <c r="C68" s="420"/>
+      <c r="D68" s="421"/>
+      <c r="E68" s="422"/>
+      <c r="G68" s="423"/>
+      <c r="H68" s="424"/>
+      <c r="I68" s="425"/>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A69" s="353" t="s">
-        <v>168</v>
-      </c>
-      <c r="B69" s="360"/>
-      <c r="C69" s="304"/>
-      <c r="D69" s="304"/>
-      <c r="E69" s="357"/>
-      <c r="F69" s="357"/>
-      <c r="G69" s="357"/>
-      <c r="H69" s="357"/>
-      <c r="I69" s="357"/>
-      <c r="J69" s="357"/>
-      <c r="K69" s="358"/>
+      <c r="C69" s="420"/>
+      <c r="D69" s="421"/>
+      <c r="E69" s="422"/>
+      <c r="G69" s="423"/>
+      <c r="H69" s="424"/>
+      <c r="I69" s="425"/>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A70" s="353" t="s">
-        <v>173</v>
-      </c>
-      <c r="B70" s="360"/>
-      <c r="C70" s="304"/>
-      <c r="D70" s="304"/>
-      <c r="E70" s="357"/>
-      <c r="F70" s="357"/>
-      <c r="G70" s="357"/>
-      <c r="H70" s="357"/>
-      <c r="I70" s="357"/>
-      <c r="J70" s="357"/>
-      <c r="K70" s="358"/>
+      <c r="C70" s="420"/>
+      <c r="D70" s="421"/>
+      <c r="E70" s="422"/>
+      <c r="G70" s="423"/>
+      <c r="H70" s="424"/>
+      <c r="I70" s="425"/>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A71" s="353" t="s">
-        <v>178</v>
-      </c>
-      <c r="B71" s="360"/>
-      <c r="C71" s="304"/>
-      <c r="D71" s="304"/>
-      <c r="E71" s="357"/>
-      <c r="F71" s="357"/>
-      <c r="G71" s="357"/>
-      <c r="H71" s="357"/>
-      <c r="I71" s="357"/>
-      <c r="J71" s="357"/>
-      <c r="K71" s="358"/>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A72" s="353" t="s">
-        <v>183</v>
-      </c>
-      <c r="B72" s="360"/>
-      <c r="C72" s="304"/>
-      <c r="D72" s="304"/>
-      <c r="E72" s="357"/>
-      <c r="F72" s="357"/>
-      <c r="G72" s="357"/>
-      <c r="H72" s="357"/>
-      <c r="I72" s="357"/>
-      <c r="J72" s="357"/>
-      <c r="K72" s="358"/>
-    </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A73" s="353" t="s">
-        <v>188</v>
-      </c>
-      <c r="B73" s="360"/>
-      <c r="C73" s="304"/>
-      <c r="D73" s="304"/>
-      <c r="E73" s="357"/>
-      <c r="F73" s="357"/>
-      <c r="G73" s="357"/>
-      <c r="H73" s="357"/>
-      <c r="I73" s="357"/>
-      <c r="J73" s="357"/>
-      <c r="K73" s="358"/>
-    </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A74" s="181" t="s">
-        <v>193</v>
-      </c>
-      <c r="B74" s="367"/>
-      <c r="C74" s="304"/>
-      <c r="D74" s="304"/>
-      <c r="E74" s="163"/>
-      <c r="F74" s="163"/>
-      <c r="G74" s="163"/>
-      <c r="H74" s="163"/>
-      <c r="I74" s="163"/>
-      <c r="J74" s="163"/>
-      <c r="K74" s="164"/>
-    </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A75" s="181" t="s">
-        <v>197</v>
-      </c>
-      <c r="B75" s="367"/>
-      <c r="C75" s="304"/>
-      <c r="D75" s="304"/>
-      <c r="E75" s="163"/>
-      <c r="F75" s="163"/>
-      <c r="G75" s="163"/>
-      <c r="H75" s="163"/>
-      <c r="I75" s="163"/>
-      <c r="J75" s="163"/>
-      <c r="K75" s="164"/>
-    </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A76" s="181" t="s">
-        <v>200</v>
-      </c>
-      <c r="B76" s="367"/>
-      <c r="C76" s="304"/>
-      <c r="D76" s="304"/>
-      <c r="E76" s="163"/>
-      <c r="F76" s="163"/>
-      <c r="G76" s="163"/>
-      <c r="H76" s="163"/>
-      <c r="I76" s="163"/>
-      <c r="J76" s="163"/>
-      <c r="K76" s="164"/>
-    </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A77" s="181" t="s">
-        <v>203</v>
-      </c>
-      <c r="B77" s="367"/>
-      <c r="C77" s="304"/>
-      <c r="D77" s="304"/>
-      <c r="E77" s="163"/>
-      <c r="F77" s="163"/>
-      <c r="G77" s="163"/>
-      <c r="H77" s="163"/>
-      <c r="I77" s="163"/>
-      <c r="J77" s="163"/>
-      <c r="K77" s="164"/>
-    </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A78" s="181" t="s">
-        <v>206</v>
-      </c>
-      <c r="B78" s="367"/>
-      <c r="C78" s="304"/>
-      <c r="D78" s="304"/>
-      <c r="E78" s="163"/>
-      <c r="F78" s="163"/>
-      <c r="G78" s="163"/>
-      <c r="H78" s="163"/>
-      <c r="I78" s="163"/>
-      <c r="J78" s="163"/>
-      <c r="K78" s="164"/>
-    </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A79" s="181" t="s">
-        <v>209</v>
-      </c>
-      <c r="B79" s="367"/>
-      <c r="C79" s="304"/>
-      <c r="D79" s="304"/>
-      <c r="E79" s="163"/>
-      <c r="F79" s="163"/>
-      <c r="G79" s="163"/>
-      <c r="H79" s="163"/>
-      <c r="I79" s="163"/>
-      <c r="J79" s="163"/>
-      <c r="K79" s="164"/>
-    </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A80" s="181" t="s">
-        <v>212</v>
-      </c>
-      <c r="B80" s="367"/>
-      <c r="C80" s="304"/>
-      <c r="D80" s="304"/>
-      <c r="E80" s="163"/>
-      <c r="F80" s="163"/>
-      <c r="G80" s="163"/>
-      <c r="H80" s="163"/>
-      <c r="I80" s="163"/>
-      <c r="J80" s="163"/>
-      <c r="K80" s="164"/>
-    </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A81" s="181" t="s">
-        <v>217</v>
-      </c>
-      <c r="B81" s="367"/>
-      <c r="C81" s="304"/>
-      <c r="D81" s="304"/>
-      <c r="E81" s="163"/>
-      <c r="F81" s="163"/>
-      <c r="G81" s="163"/>
-      <c r="H81" s="163"/>
-      <c r="I81" s="163"/>
-      <c r="J81" s="163"/>
-      <c r="K81" s="164"/>
-    </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A82" s="181" t="s">
-        <v>221</v>
-      </c>
-      <c r="B82" s="367"/>
-      <c r="C82" s="304"/>
-      <c r="D82" s="304"/>
-      <c r="E82" s="163"/>
-      <c r="F82" s="163"/>
-      <c r="G82" s="163"/>
-      <c r="H82" s="163"/>
-      <c r="I82" s="163"/>
-      <c r="J82" s="163"/>
-      <c r="K82" s="164"/>
-    </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A83" s="181" t="s">
-        <v>225</v>
-      </c>
-      <c r="B83" s="367"/>
-      <c r="C83" s="304"/>
-      <c r="D83" s="304"/>
-      <c r="E83" s="163"/>
-      <c r="F83" s="163"/>
-      <c r="G83" s="163"/>
-      <c r="H83" s="163"/>
-      <c r="I83" s="163"/>
-      <c r="J83" s="163"/>
-      <c r="K83" s="164"/>
-    </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A84" s="181" t="s">
-        <v>229</v>
-      </c>
-      <c r="B84" s="367"/>
-      <c r="C84" s="304"/>
-      <c r="D84" s="304"/>
-      <c r="E84" s="163"/>
-      <c r="F84" s="163"/>
-      <c r="G84" s="163"/>
-      <c r="H84" s="163"/>
-      <c r="I84" s="163"/>
-      <c r="J84" s="163"/>
-      <c r="K84" s="164"/>
-    </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A85" s="181" t="s">
-        <v>233</v>
-      </c>
-      <c r="B85" s="367"/>
-      <c r="C85" s="304"/>
-      <c r="D85" s="304"/>
-      <c r="E85" s="163"/>
-      <c r="F85" s="163"/>
-      <c r="G85" s="163"/>
-      <c r="H85" s="163"/>
-      <c r="I85" s="163"/>
-      <c r="J85" s="163"/>
-      <c r="K85" s="164"/>
-    </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A86" s="181" t="s">
-        <v>237</v>
-      </c>
-      <c r="B86" s="367"/>
-      <c r="C86" s="304"/>
-      <c r="D86" s="304"/>
-      <c r="E86" s="163"/>
-      <c r="F86" s="163"/>
-      <c r="G86" s="163"/>
-      <c r="H86" s="163"/>
-      <c r="I86" s="163"/>
-      <c r="J86" s="163"/>
-      <c r="K86" s="164"/>
-    </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A87" s="181" t="s">
-        <v>241</v>
-      </c>
-      <c r="B87" s="367"/>
-      <c r="C87" s="304"/>
-      <c r="D87" s="304"/>
-      <c r="E87" s="163"/>
-      <c r="F87" s="163"/>
-      <c r="G87" s="163"/>
-      <c r="H87" s="163"/>
-      <c r="I87" s="163"/>
-      <c r="J87" s="163"/>
-      <c r="K87" s="164"/>
-    </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A88" s="181" t="s">
-        <v>245</v>
-      </c>
-      <c r="B88" s="367"/>
-      <c r="C88" s="304"/>
-      <c r="D88" s="304"/>
-      <c r="E88" s="163"/>
-      <c r="F88" s="163"/>
-      <c r="G88" s="163"/>
-      <c r="H88" s="163"/>
-      <c r="I88" s="163"/>
-      <c r="J88" s="163"/>
-      <c r="K88" s="164"/>
-    </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A89" s="181" t="s">
-        <v>251</v>
-      </c>
-      <c r="B89" s="367"/>
-      <c r="C89" s="304"/>
-      <c r="D89" s="304"/>
-      <c r="E89" s="163"/>
-      <c r="F89" s="163"/>
-      <c r="G89" s="163"/>
-      <c r="H89" s="163"/>
-      <c r="I89" s="163"/>
-      <c r="J89" s="163"/>
-      <c r="K89" s="164"/>
-    </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A90" s="181" t="s">
-        <v>256</v>
-      </c>
-      <c r="B90" s="367"/>
-      <c r="C90" s="304"/>
-      <c r="D90" s="304"/>
-      <c r="E90" s="163"/>
-      <c r="F90" s="163"/>
-      <c r="G90" s="163"/>
-      <c r="H90" s="163"/>
-      <c r="I90" s="163"/>
-      <c r="J90" s="163"/>
-      <c r="K90" s="164"/>
-    </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A91" s="181" t="s">
-        <v>261</v>
-      </c>
-      <c r="B91" s="367"/>
-      <c r="C91" s="304"/>
-      <c r="D91" s="304"/>
-      <c r="E91" s="163"/>
-      <c r="F91" s="163"/>
-      <c r="G91" s="163"/>
-      <c r="H91" s="163"/>
-      <c r="I91" s="163"/>
-      <c r="J91" s="163"/>
-      <c r="K91" s="164"/>
-    </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A92" s="181" t="s">
-        <v>266</v>
-      </c>
-      <c r="B92" s="367"/>
-      <c r="C92" s="304"/>
-      <c r="D92" s="304"/>
-      <c r="E92" s="163"/>
-      <c r="F92" s="163"/>
-      <c r="G92" s="163"/>
-      <c r="H92" s="163"/>
-      <c r="I92" s="163"/>
-      <c r="J92" s="163"/>
-      <c r="K92" s="164"/>
-    </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A93" s="181" t="s">
-        <v>271</v>
-      </c>
-      <c r="B93" s="367"/>
-      <c r="C93" s="304"/>
-      <c r="D93" s="304"/>
-      <c r="E93" s="163"/>
-      <c r="F93" s="163"/>
-      <c r="G93" s="163"/>
-      <c r="H93" s="163"/>
-      <c r="I93" s="163"/>
-      <c r="J93" s="163"/>
-      <c r="K93" s="164"/>
-    </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A94" s="181" t="s">
-        <v>289</v>
-      </c>
-      <c r="B94" s="367"/>
-      <c r="C94" s="304"/>
-      <c r="D94" s="304"/>
-      <c r="E94" s="163"/>
-      <c r="F94" s="163"/>
-      <c r="G94" s="163"/>
-      <c r="H94" s="163"/>
-      <c r="I94" s="163"/>
-      <c r="J94" s="163"/>
-      <c r="K94" s="164"/>
-    </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A95" s="181" t="s">
-        <v>294</v>
-      </c>
-      <c r="B95" s="367"/>
-      <c r="C95" s="304"/>
-      <c r="D95" s="304"/>
-      <c r="E95" s="163"/>
-      <c r="F95" s="163"/>
-      <c r="G95" s="163"/>
-      <c r="H95" s="163"/>
-      <c r="I95" s="163"/>
-      <c r="J95" s="163"/>
-      <c r="K95" s="164"/>
-    </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A96" s="181" t="s">
-        <v>299</v>
-      </c>
-      <c r="B96" s="367"/>
-      <c r="C96" s="304"/>
-      <c r="D96" s="304"/>
-      <c r="E96" s="163"/>
-      <c r="F96" s="163"/>
-      <c r="G96" s="163"/>
-      <c r="H96" s="163"/>
-      <c r="I96" s="163"/>
-      <c r="J96" s="163"/>
-      <c r="K96" s="164"/>
-    </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A97" s="181" t="s">
-        <v>304</v>
-      </c>
-      <c r="B97" s="367"/>
-      <c r="C97" s="304"/>
-      <c r="D97" s="304"/>
-      <c r="E97" s="163"/>
-      <c r="F97" s="163"/>
-      <c r="G97" s="163"/>
-      <c r="H97" s="163"/>
-      <c r="I97" s="163"/>
-      <c r="J97" s="163"/>
-      <c r="K97" s="164"/>
-    </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A98" s="181" t="s">
-        <v>309</v>
-      </c>
-      <c r="B98" s="367"/>
-      <c r="C98" s="304"/>
-      <c r="D98" s="304"/>
-      <c r="E98" s="163"/>
-      <c r="F98" s="163"/>
-      <c r="G98" s="163"/>
-      <c r="H98" s="163"/>
-      <c r="I98" s="163"/>
-      <c r="J98" s="163"/>
-      <c r="K98" s="164"/>
-    </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A99" s="181" t="s">
-        <v>314</v>
-      </c>
-      <c r="B99" s="367"/>
-      <c r="C99" s="304"/>
-      <c r="D99" s="304"/>
-      <c r="E99" s="163"/>
-      <c r="F99" s="163"/>
-      <c r="G99" s="163"/>
-      <c r="H99" s="163"/>
-      <c r="I99" s="163"/>
-      <c r="J99" s="163"/>
-      <c r="K99" s="164"/>
-    </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A100" s="181" t="s">
-        <v>319</v>
-      </c>
-      <c r="B100" s="367"/>
-      <c r="C100" s="304"/>
-      <c r="D100" s="304"/>
-      <c r="E100" s="163"/>
-      <c r="F100" s="163"/>
-      <c r="G100" s="163"/>
-      <c r="H100" s="163"/>
-      <c r="I100" s="163"/>
-      <c r="J100" s="163"/>
-      <c r="K100" s="164"/>
-    </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A101" s="181" t="s">
-        <v>324</v>
-      </c>
-      <c r="B101" s="367"/>
-      <c r="C101" s="304"/>
-      <c r="D101" s="304"/>
-      <c r="E101" s="163"/>
-      <c r="F101" s="163"/>
-      <c r="G101" s="163"/>
-      <c r="H101" s="163"/>
-      <c r="I101" s="163"/>
-      <c r="J101" s="163"/>
-      <c r="K101" s="164"/>
-    </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A102" s="181" t="s">
-        <v>329</v>
-      </c>
-      <c r="B102" s="367"/>
-      <c r="C102" s="304"/>
-      <c r="D102" s="304"/>
-      <c r="E102" s="163"/>
-      <c r="F102" s="163"/>
-      <c r="G102" s="163"/>
-      <c r="H102" s="163"/>
-      <c r="I102" s="163"/>
-      <c r="J102" s="163"/>
-      <c r="K102" s="164"/>
-    </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A103" s="181" t="s">
-        <v>334</v>
-      </c>
-      <c r="B103" s="367"/>
-      <c r="C103" s="304"/>
-      <c r="D103" s="304"/>
-      <c r="E103" s="163"/>
-      <c r="F103" s="163"/>
-      <c r="G103" s="163"/>
-      <c r="H103" s="163"/>
-      <c r="I103" s="163"/>
-      <c r="J103" s="163"/>
-      <c r="K103" s="164"/>
-    </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A104" s="181" t="s">
-        <v>348</v>
-      </c>
-      <c r="B104" s="367"/>
-      <c r="C104" s="304"/>
-      <c r="D104" s="304"/>
-      <c r="E104" s="163"/>
-      <c r="F104" s="163"/>
-      <c r="G104" s="163"/>
-      <c r="H104" s="163"/>
-      <c r="I104" s="163"/>
-      <c r="J104" s="163"/>
-      <c r="K104" s="164"/>
-    </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A105" s="181" t="s">
-        <v>352</v>
-      </c>
-      <c r="B105" s="367"/>
-      <c r="C105" s="304"/>
-      <c r="D105" s="304"/>
-      <c r="E105" s="163"/>
-      <c r="F105" s="163"/>
-      <c r="G105" s="163"/>
-      <c r="H105" s="163"/>
-      <c r="I105" s="163"/>
-      <c r="J105" s="163"/>
-      <c r="K105" s="164"/>
-    </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A106" s="181" t="s">
-        <v>356</v>
-      </c>
-      <c r="B106" s="367"/>
-      <c r="C106" s="304"/>
-      <c r="D106" s="304"/>
-      <c r="E106" s="163"/>
-      <c r="F106" s="163"/>
-      <c r="G106" s="163"/>
-      <c r="H106" s="163"/>
-      <c r="I106" s="163"/>
-      <c r="J106" s="163"/>
-      <c r="K106" s="164"/>
-    </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B107" s="169"/>
-      <c r="E107" s="242"/>
-      <c r="F107" s="242"/>
-      <c r="G107" s="237"/>
-      <c r="H107" s="237"/>
-      <c r="I107" s="242"/>
-      <c r="J107" s="237"/>
-      <c r="K107" s="238"/>
-    </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C108" s="420"/>
-      <c r="D108" s="421"/>
-      <c r="E108" s="422"/>
-      <c r="G108" s="423"/>
-      <c r="H108" s="424"/>
-      <c r="I108" s="425"/>
-    </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C109" s="420"/>
-      <c r="D109" s="421"/>
-      <c r="E109" s="422"/>
-      <c r="G109" s="423"/>
-      <c r="H109" s="424"/>
-      <c r="I109" s="425"/>
-    </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C110" s="420"/>
-      <c r="D110" s="421"/>
-      <c r="E110" s="422"/>
-      <c r="G110" s="423"/>
-      <c r="H110" s="424"/>
-      <c r="I110" s="425"/>
-    </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C111" s="426"/>
-      <c r="D111" s="421"/>
-      <c r="I111" s="425"/>
+      <c r="C71" s="426"/>
+      <c r="D71" s="421"/>
+      <c r="I71" s="425"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K31" xr:uid="{00000000-0009-0000-0000-000009000000}"/>
+  <autoFilter ref="A1:K5" xr:uid="{00000000-0009-0000-0000-000009000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -12090,29 +11440,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="61" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="464" t="s">
-        <v>1426</v>
-      </c>
-      <c r="B1" s="462" t="s">
-        <v>1427</v>
-      </c>
-      <c r="C1" s="461" t="s">
-        <v>1428</v>
-      </c>
-      <c r="D1" s="458" t="s">
-        <v>1429</v>
-      </c>
-      <c r="E1" s="459"/>
-      <c r="F1" s="459"/>
-      <c r="G1" s="459"/>
-      <c r="H1" s="459"/>
-      <c r="I1" s="459"/>
-      <c r="J1" s="460"/>
+      <c r="A1" s="459" t="s">
+        <v>1381</v>
+      </c>
+      <c r="B1" s="457" t="s">
+        <v>1382</v>
+      </c>
+      <c r="C1" s="456" t="s">
+        <v>1383</v>
+      </c>
+      <c r="D1" s="453" t="s">
+        <v>1384</v>
+      </c>
+      <c r="E1" s="454"/>
+      <c r="F1" s="454"/>
+      <c r="G1" s="454"/>
+      <c r="H1" s="454"/>
+      <c r="I1" s="454"/>
+      <c r="J1" s="455"/>
     </row>
     <row r="2" spans="1:10" s="61" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="450"/>
-      <c r="B2" s="463"/>
-      <c r="C2" s="442"/>
+      <c r="A2" s="445"/>
+      <c r="B2" s="458"/>
+      <c r="C2" s="437"/>
       <c r="D2" s="330" t="s">
         <v>5</v>
       </c>
@@ -12137,108 +11487,108 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="110" t="s">
-        <v>1430</v>
+        <v>1385</v>
       </c>
       <c r="B3" s="111"/>
       <c r="C3" s="376"/>
       <c r="D3" s="110" t="s">
-        <v>1431</v>
+        <v>1386</v>
       </c>
       <c r="E3" s="112" t="s">
-        <v>1431</v>
+        <v>1386</v>
       </c>
       <c r="F3" s="112" t="s">
-        <v>1431</v>
+        <v>1386</v>
       </c>
       <c r="G3" s="112" t="s">
-        <v>1431</v>
+        <v>1386</v>
       </c>
       <c r="H3" s="112" t="s">
-        <v>1431</v>
+        <v>1386</v>
       </c>
       <c r="I3" s="112" t="s">
-        <v>1431</v>
+        <v>1386</v>
       </c>
       <c r="J3" s="111" t="s">
-        <v>1431</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="4" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A4" s="113"/>
       <c r="B4" s="69" t="s">
-        <v>1432</v>
+        <v>1387</v>
       </c>
       <c r="C4" s="377"/>
       <c r="D4" s="113" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
       <c r="E4" s="101" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
       <c r="F4" s="101" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
       <c r="G4" s="101" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
       <c r="H4" s="101" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
       <c r="I4" s="101" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
       <c r="J4" s="114" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="5" spans="1:10" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A5" s="63"/>
       <c r="B5" s="64" t="s">
-        <v>1434</v>
+        <v>1389</v>
       </c>
       <c r="C5" s="328">
         <v>10574479</v>
       </c>
       <c r="D5" s="63" t="s">
-        <v>1435</v>
+        <v>1390</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>1435</v>
+        <v>1390</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>1436</v>
+        <v>1391</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>1435</v>
+        <v>1390</v>
       </c>
       <c r="J5" s="64"/>
     </row>
     <row r="6" spans="1:10" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A6" s="63"/>
       <c r="B6" s="64" t="s">
-        <v>1437</v>
+        <v>1392</v>
       </c>
       <c r="C6" s="328">
         <v>10542152</v>
       </c>
       <c r="D6" s="63" t="s">
-        <v>1438</v>
+        <v>1393</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>1438</v>
+        <v>1393</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>1436</v>
+        <v>1391</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>1438</v>
+        <v>1393</v>
       </c>
       <c r="J6" s="64"/>
     </row>
     <row r="7" spans="1:10" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A7" s="63"/>
       <c r="B7" s="64" t="s">
-        <v>1439</v>
+        <v>1394</v>
       </c>
       <c r="C7" s="328"/>
       <c r="D7" s="63"/>
@@ -12247,55 +11597,55 @@
     <row r="8" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A8" s="113"/>
       <c r="B8" s="69" t="s">
-        <v>1440</v>
+        <v>1395</v>
       </c>
       <c r="C8" s="377"/>
       <c r="D8" s="113" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
       <c r="E8" s="101" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
       <c r="F8" s="101" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
       <c r="G8" s="101" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
       <c r="H8" s="101" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
       <c r="I8" s="101" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
       <c r="J8" s="114" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="9" spans="1:10" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A9" s="63"/>
       <c r="B9" s="73" t="s">
-        <v>1441</v>
+        <v>1396</v>
       </c>
       <c r="C9" s="378" t="s">
-        <v>1442</v>
+        <v>1397</v>
       </c>
       <c r="D9" s="63" t="s">
-        <v>1443</v>
+        <v>1398</v>
       </c>
       <c r="J9" s="64"/>
     </row>
     <row r="10" spans="1:10" s="118" customFormat="1" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A10" s="77"/>
       <c r="B10" s="74" t="s">
-        <v>1441</v>
+        <v>1396</v>
       </c>
       <c r="C10" s="379" t="s">
-        <v>1444</v>
+        <v>1399</v>
       </c>
       <c r="D10" s="75"/>
       <c r="E10" s="76" t="s">
-        <v>1443</v>
+        <v>1398</v>
       </c>
       <c r="F10" s="78"/>
       <c r="G10" s="78"/>
@@ -12306,1369 +11656,1369 @@
     <row r="11" spans="1:10" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A11" s="63"/>
       <c r="B11" s="115" t="s">
-        <v>1441</v>
+        <v>1396</v>
       </c>
       <c r="C11" s="380" t="s">
-        <v>1445</v>
+        <v>1400</v>
       </c>
       <c r="D11" s="119"/>
       <c r="E11" s="116"/>
       <c r="F11" s="116"/>
       <c r="G11" s="116"/>
       <c r="H11" s="116" t="s">
-        <v>1443</v>
+        <v>1398</v>
       </c>
       <c r="J11" s="64"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="110" t="s">
-        <v>1446</v>
+        <v>1401</v>
       </c>
       <c r="B12" s="117"/>
       <c r="C12" s="376"/>
       <c r="D12" s="110" t="s">
-        <v>1431</v>
+        <v>1386</v>
       </c>
       <c r="E12" s="112" t="s">
-        <v>1431</v>
+        <v>1386</v>
       </c>
       <c r="F12" s="112" t="s">
-        <v>1431</v>
+        <v>1386</v>
       </c>
       <c r="G12" s="112" t="s">
-        <v>1431</v>
+        <v>1386</v>
       </c>
       <c r="H12" s="112" t="s">
-        <v>1431</v>
+        <v>1386</v>
       </c>
       <c r="I12" s="112" t="s">
-        <v>1431</v>
+        <v>1386</v>
       </c>
       <c r="J12" s="111" t="s">
-        <v>1431</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="13" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A13" s="113"/>
       <c r="B13" s="69" t="s">
-        <v>1440</v>
+        <v>1395</v>
       </c>
       <c r="C13" s="377"/>
       <c r="D13" s="113" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
       <c r="E13" s="101" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
       <c r="F13" s="101" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
       <c r="G13" s="101" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
       <c r="H13" s="101" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
       <c r="I13" s="101" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
       <c r="J13" s="114" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="14" spans="1:10" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A14" s="63"/>
       <c r="B14" s="73" t="s">
-        <v>1447</v>
+        <v>1402</v>
       </c>
       <c r="C14" s="381" t="s">
-        <v>1448</v>
+        <v>1403</v>
       </c>
       <c r="D14" s="63" t="s">
-        <v>1449</v>
+        <v>1404</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>1449</v>
+        <v>1404</v>
       </c>
       <c r="J14" s="64"/>
     </row>
     <row r="15" spans="1:10" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A15" s="63"/>
       <c r="B15" s="73" t="s">
-        <v>1450</v>
+        <v>1405</v>
       </c>
       <c r="C15" s="381" t="s">
-        <v>1451</v>
+        <v>1406</v>
       </c>
       <c r="D15" s="63" t="s">
-        <v>1452</v>
+        <v>1407</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>1452</v>
+        <v>1407</v>
       </c>
       <c r="J15" s="64"/>
     </row>
     <row r="16" spans="1:10" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A16" s="63"/>
       <c r="B16" s="73" t="s">
-        <v>1453</v>
+        <v>1408</v>
       </c>
       <c r="C16" s="381" t="s">
-        <v>1454</v>
+        <v>1409</v>
       </c>
       <c r="D16" s="63" t="s">
-        <v>1449</v>
+        <v>1404</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>1449</v>
+        <v>1404</v>
       </c>
       <c r="J16" s="64"/>
     </row>
     <row r="17" spans="1:10" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A17" s="63"/>
       <c r="B17" s="73" t="s">
-        <v>1455</v>
+        <v>1410</v>
       </c>
       <c r="C17" s="381" t="s">
-        <v>1456</v>
+        <v>1411</v>
       </c>
       <c r="D17" s="63" t="s">
-        <v>1449</v>
+        <v>1404</v>
       </c>
       <c r="J17" s="64"/>
     </row>
     <row r="18" spans="1:10" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A18" s="63"/>
       <c r="B18" s="74" t="s">
-        <v>1457</v>
+        <v>1412</v>
       </c>
       <c r="C18" s="379" t="s">
-        <v>1458</v>
+        <v>1413</v>
       </c>
       <c r="D18" s="63"/>
       <c r="E18" s="76" t="s">
-        <v>1449</v>
+        <v>1404</v>
       </c>
       <c r="J18" s="64"/>
     </row>
     <row r="19" spans="1:10" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A19" s="63"/>
       <c r="B19" s="73" t="s">
-        <v>1459</v>
+        <v>1414</v>
       </c>
       <c r="C19" s="381" t="s">
-        <v>1460</v>
+        <v>1415</v>
       </c>
       <c r="D19" s="63" t="s">
-        <v>1449</v>
+        <v>1404</v>
       </c>
       <c r="J19" s="64"/>
     </row>
     <row r="20" spans="1:10" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A20" s="63"/>
       <c r="B20" s="74" t="s">
-        <v>1461</v>
+        <v>1416</v>
       </c>
       <c r="C20" s="379" t="s">
-        <v>1462</v>
+        <v>1417</v>
       </c>
       <c r="D20" s="63"/>
       <c r="E20" s="76" t="s">
-        <v>1449</v>
+        <v>1404</v>
       </c>
       <c r="J20" s="64"/>
     </row>
     <row r="21" spans="1:10" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A21" s="63"/>
       <c r="B21" s="73" t="s">
-        <v>1463</v>
+        <v>1418</v>
       </c>
       <c r="C21" s="381" t="s">
-        <v>1464</v>
+        <v>1419</v>
       </c>
       <c r="D21" s="63" t="s">
-        <v>1465</v>
+        <v>1420</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>1465</v>
+        <v>1420</v>
       </c>
       <c r="J21" s="64"/>
     </row>
     <row r="22" spans="1:10" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A22" s="63"/>
       <c r="B22" s="64" t="s">
-        <v>1466</v>
+        <v>1421</v>
       </c>
       <c r="C22" s="328" t="s">
-        <v>1467</v>
+        <v>1422</v>
       </c>
       <c r="D22" s="63" t="s">
-        <v>1465</v>
+        <v>1420</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>1465</v>
+        <v>1420</v>
       </c>
       <c r="J22" s="64"/>
     </row>
     <row r="23" spans="1:10" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A23" s="63"/>
       <c r="B23" s="64" t="s">
-        <v>1468</v>
+        <v>1423</v>
       </c>
       <c r="C23" s="328" t="s">
-        <v>1469</v>
+        <v>1424</v>
       </c>
       <c r="D23" s="63" t="s">
-        <v>1470</v>
+        <v>1425</v>
       </c>
       <c r="E23" s="78" t="s">
-        <v>1470</v>
+        <v>1425</v>
       </c>
       <c r="J23" s="64"/>
     </row>
     <row r="24" spans="1:10" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A24" s="63"/>
       <c r="B24" s="64" t="s">
-        <v>1471</v>
+        <v>1426</v>
       </c>
       <c r="C24" s="328" t="s">
-        <v>1472</v>
+        <v>1427</v>
       </c>
       <c r="D24" s="63" t="s">
-        <v>1465</v>
+        <v>1420</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>1465</v>
+        <v>1420</v>
       </c>
       <c r="J24" s="64"/>
     </row>
     <row r="25" spans="1:10" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A25" s="63"/>
       <c r="B25" s="115" t="s">
-        <v>1473</v>
+        <v>1428</v>
       </c>
       <c r="C25" s="380" t="s">
-        <v>1474</v>
+        <v>1429</v>
       </c>
       <c r="D25" s="63"/>
       <c r="H25" s="116" t="s">
-        <v>1449</v>
+        <v>1404</v>
       </c>
       <c r="I25" s="116" t="s">
-        <v>1449</v>
+        <v>1404</v>
       </c>
       <c r="J25" s="64"/>
     </row>
     <row r="26" spans="1:10" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A26" s="63"/>
       <c r="B26" s="115" t="s">
-        <v>1475</v>
+        <v>1430</v>
       </c>
       <c r="C26" s="380" t="s">
-        <v>1476</v>
+        <v>1431</v>
       </c>
       <c r="D26" s="63"/>
       <c r="H26" s="116" t="s">
-        <v>1449</v>
+        <v>1404</v>
       </c>
       <c r="I26" s="116" t="s">
-        <v>1449</v>
+        <v>1404</v>
       </c>
       <c r="J26" s="64"/>
     </row>
     <row r="27" spans="1:10" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A27" s="63"/>
       <c r="B27" s="115" t="s">
-        <v>1477</v>
+        <v>1432</v>
       </c>
       <c r="C27" s="380" t="s">
-        <v>1478</v>
+        <v>1433</v>
       </c>
       <c r="D27" s="63"/>
       <c r="H27" s="116" t="s">
-        <v>1470</v>
+        <v>1425</v>
       </c>
       <c r="I27" s="116" t="s">
-        <v>1470</v>
+        <v>1425</v>
       </c>
       <c r="J27" s="64"/>
     </row>
     <row r="28" spans="1:10" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A28" s="63"/>
       <c r="B28" s="115" t="s">
-        <v>1479</v>
+        <v>1434</v>
       </c>
       <c r="C28" s="380" t="s">
-        <v>1480</v>
+        <v>1435</v>
       </c>
       <c r="D28" s="63"/>
       <c r="H28" s="116" t="s">
-        <v>1470</v>
+        <v>1425</v>
       </c>
       <c r="I28" s="116" t="s">
-        <v>1470</v>
+        <v>1425</v>
       </c>
       <c r="J28" s="64"/>
     </row>
     <row r="29" spans="1:10" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A29" s="63"/>
       <c r="B29" s="115" t="s">
-        <v>1481</v>
+        <v>1436</v>
       </c>
       <c r="C29" s="380" t="s">
-        <v>1482</v>
+        <v>1437</v>
       </c>
       <c r="D29" s="63"/>
       <c r="H29" s="116" t="s">
-        <v>1449</v>
+        <v>1404</v>
       </c>
       <c r="I29" s="116" t="s">
-        <v>1449</v>
+        <v>1404</v>
       </c>
       <c r="J29" s="64"/>
     </row>
     <row r="30" spans="1:10" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A30" s="63"/>
       <c r="B30" s="115" t="s">
-        <v>1483</v>
+        <v>1438</v>
       </c>
       <c r="C30" s="380" t="s">
-        <v>1484</v>
+        <v>1439</v>
       </c>
       <c r="D30" s="63"/>
       <c r="H30" s="116" t="s">
-        <v>1449</v>
+        <v>1404</v>
       </c>
       <c r="I30" s="116" t="s">
-        <v>1449</v>
+        <v>1404</v>
       </c>
       <c r="J30" s="64"/>
     </row>
     <row r="31" spans="1:10" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A31" s="63"/>
       <c r="B31" s="115" t="s">
-        <v>1485</v>
+        <v>1440</v>
       </c>
       <c r="C31" s="380" t="s">
-        <v>1486</v>
+        <v>1441</v>
       </c>
       <c r="D31" s="63"/>
       <c r="H31" s="116" t="s">
-        <v>1449</v>
+        <v>1404</v>
       </c>
       <c r="I31" s="116" t="s">
-        <v>1449</v>
+        <v>1404</v>
       </c>
       <c r="J31" s="64"/>
     </row>
     <row r="32" spans="1:10" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A32" s="63"/>
       <c r="B32" s="115" t="s">
-        <v>1487</v>
+        <v>1442</v>
       </c>
       <c r="C32" s="380" t="s">
-        <v>1488</v>
+        <v>1443</v>
       </c>
       <c r="D32" s="63"/>
       <c r="H32" s="116" t="s">
-        <v>1438</v>
+        <v>1393</v>
       </c>
       <c r="I32" s="116" t="s">
-        <v>1438</v>
+        <v>1393</v>
       </c>
       <c r="J32" s="64"/>
     </row>
     <row r="33" spans="1:10" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A33" s="63"/>
       <c r="B33" s="115" t="s">
-        <v>1489</v>
+        <v>1444</v>
       </c>
       <c r="C33" s="380" t="s">
-        <v>1490</v>
+        <v>1445</v>
       </c>
       <c r="D33" s="63"/>
       <c r="H33" s="116" t="s">
-        <v>1491</v>
+        <v>1446</v>
       </c>
       <c r="I33" s="116" t="s">
-        <v>1491</v>
+        <v>1446</v>
       </c>
       <c r="J33" s="64"/>
     </row>
     <row r="34" spans="1:10" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A34" s="63"/>
       <c r="B34" s="115" t="s">
-        <v>1492</v>
+        <v>1447</v>
       </c>
       <c r="C34" s="380" t="s">
-        <v>1493</v>
+        <v>1448</v>
       </c>
       <c r="D34" s="63"/>
       <c r="H34" s="116" t="s">
-        <v>1435</v>
+        <v>1390</v>
       </c>
       <c r="I34" s="116" t="s">
-        <v>1435</v>
+        <v>1390</v>
       </c>
       <c r="J34" s="64"/>
     </row>
     <row r="35" spans="1:10" ht="30" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A35" s="63"/>
       <c r="B35" s="115" t="s">
-        <v>1494</v>
+        <v>1449</v>
       </c>
       <c r="C35" s="380" t="s">
-        <v>1495</v>
+        <v>1450</v>
       </c>
       <c r="D35" s="63"/>
       <c r="H35" s="116" t="s">
-        <v>1496</v>
+        <v>1451</v>
       </c>
       <c r="I35" s="116" t="s">
-        <v>1496</v>
+        <v>1451</v>
       </c>
       <c r="J35" s="64"/>
     </row>
     <row r="36" spans="1:10" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A36" s="63"/>
       <c r="B36" s="115" t="s">
-        <v>1497</v>
+        <v>1452</v>
       </c>
       <c r="C36" s="380" t="s">
-        <v>1498</v>
+        <v>1453</v>
       </c>
       <c r="D36" s="63"/>
       <c r="H36" s="116" t="s">
-        <v>1435</v>
+        <v>1390</v>
       </c>
       <c r="I36" s="116" t="s">
-        <v>1435</v>
+        <v>1390</v>
       </c>
       <c r="J36" s="64"/>
     </row>
     <row r="37" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A37" s="113"/>
       <c r="B37" s="69" t="s">
-        <v>1499</v>
+        <v>1454</v>
       </c>
       <c r="C37" s="377"/>
       <c r="D37" s="113" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
       <c r="E37" s="101" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
       <c r="F37" s="101" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
       <c r="G37" s="101" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
       <c r="H37" s="101" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
       <c r="I37" s="101" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
       <c r="J37" s="114" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="38" spans="1:10" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A38" s="63"/>
       <c r="B38" s="73" t="s">
-        <v>1500</v>
+        <v>1455</v>
       </c>
       <c r="C38" s="381" t="s">
-        <v>1501</v>
+        <v>1456</v>
       </c>
       <c r="D38" s="63" t="s">
-        <v>1436</v>
+        <v>1391</v>
       </c>
       <c r="J38" s="64"/>
     </row>
     <row r="39" spans="1:10" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A39" s="63"/>
       <c r="B39" s="74" t="s">
-        <v>1502</v>
+        <v>1457</v>
       </c>
       <c r="C39" s="379" t="s">
-        <v>1503</v>
+        <v>1458</v>
       </c>
       <c r="D39" s="75"/>
       <c r="E39" s="76" t="s">
-        <v>1436</v>
+        <v>1391</v>
       </c>
       <c r="J39" s="64"/>
     </row>
     <row r="40" spans="1:10" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A40" s="63"/>
       <c r="B40" s="73" t="s">
-        <v>1504</v>
+        <v>1459</v>
       </c>
       <c r="C40" s="381" t="s">
-        <v>1505</v>
+        <v>1460</v>
       </c>
       <c r="D40" s="77" t="s">
-        <v>1452</v>
+        <v>1407</v>
       </c>
       <c r="E40" s="78" t="s">
-        <v>1452</v>
+        <v>1407</v>
       </c>
       <c r="J40" s="64"/>
     </row>
     <row r="41" spans="1:10" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A41" s="63"/>
       <c r="B41" s="115" t="s">
-        <v>1504</v>
+        <v>1459</v>
       </c>
       <c r="C41" s="380" t="s">
-        <v>1506</v>
+        <v>1461</v>
       </c>
       <c r="D41" s="63"/>
       <c r="H41" s="116" t="s">
-        <v>1452</v>
+        <v>1407</v>
       </c>
       <c r="I41" s="116" t="s">
-        <v>1452</v>
+        <v>1407</v>
       </c>
       <c r="J41" s="64"/>
     </row>
     <row r="42" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A42" s="113"/>
       <c r="B42" s="69" t="s">
-        <v>1507</v>
+        <v>1462</v>
       </c>
       <c r="C42" s="377"/>
       <c r="D42" s="113" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
       <c r="E42" s="101" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
       <c r="F42" s="101" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
       <c r="G42" s="101" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
       <c r="H42" s="101" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
       <c r="I42" s="101" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
       <c r="J42" s="114" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="43" spans="1:10" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A43" s="63"/>
       <c r="B43" s="64" t="s">
-        <v>1508</v>
+        <v>1463</v>
       </c>
       <c r="C43" s="328" t="s">
-        <v>1509</v>
+        <v>1464</v>
       </c>
       <c r="D43" s="63" t="s">
-        <v>1470</v>
+        <v>1425</v>
       </c>
       <c r="J43" s="64"/>
     </row>
     <row r="44" spans="1:10" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A44" s="63"/>
       <c r="B44" s="74" t="s">
-        <v>1510</v>
+        <v>1465</v>
       </c>
       <c r="C44" s="379" t="s">
-        <v>1511</v>
+        <v>1466</v>
       </c>
       <c r="D44" s="75"/>
       <c r="E44" s="76" t="s">
-        <v>1470</v>
+        <v>1425</v>
       </c>
       <c r="J44" s="64"/>
     </row>
     <row r="45" spans="1:10" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A45" s="63"/>
       <c r="B45" s="64" t="s">
-        <v>1512</v>
+        <v>1467</v>
       </c>
       <c r="C45" s="328" t="s">
-        <v>1513</v>
+        <v>1468</v>
       </c>
       <c r="D45" s="63" t="s">
-        <v>1449</v>
+        <v>1404</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>1449</v>
+        <v>1404</v>
       </c>
       <c r="J45" s="64"/>
     </row>
     <row r="46" spans="1:10" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A46" s="63"/>
       <c r="B46" s="73" t="s">
-        <v>1514</v>
+        <v>1469</v>
       </c>
       <c r="C46" s="381" t="s">
-        <v>1515</v>
+        <v>1470</v>
       </c>
       <c r="D46" s="63" t="s">
-        <v>1449</v>
+        <v>1404</v>
       </c>
       <c r="J46" s="64"/>
     </row>
     <row r="47" spans="1:10" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A47" s="63"/>
       <c r="B47" s="74" t="s">
-        <v>1514</v>
+        <v>1469</v>
       </c>
       <c r="C47" s="379" t="s">
-        <v>1516</v>
+        <v>1471</v>
       </c>
       <c r="D47" s="75"/>
       <c r="E47" s="76" t="s">
-        <v>1449</v>
+        <v>1404</v>
       </c>
       <c r="J47" s="64"/>
     </row>
     <row r="48" spans="1:10" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A48" s="63"/>
       <c r="B48" s="73" t="s">
-        <v>1517</v>
+        <v>1472</v>
       </c>
       <c r="C48" s="381" t="s">
-        <v>1518</v>
+        <v>1473</v>
       </c>
       <c r="D48" s="63" t="s">
-        <v>1519</v>
+        <v>1474</v>
       </c>
       <c r="J48" s="64"/>
     </row>
     <row r="49" spans="1:10" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A49" s="63"/>
       <c r="B49" s="72" t="s">
-        <v>1517</v>
+        <v>1472</v>
       </c>
       <c r="C49" s="382" t="s">
-        <v>1520</v>
+        <v>1475</v>
       </c>
       <c r="D49" s="63"/>
       <c r="E49" s="10" t="s">
-        <v>1519</v>
+        <v>1474</v>
       </c>
       <c r="J49" s="64"/>
     </row>
     <row r="50" spans="1:10" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A50" s="63"/>
       <c r="B50" s="73" t="s">
-        <v>1521</v>
+        <v>1476</v>
       </c>
       <c r="C50" s="381" t="s">
-        <v>1522</v>
+        <v>1477</v>
       </c>
       <c r="D50" s="63" t="s">
-        <v>1465</v>
+        <v>1420</v>
       </c>
       <c r="J50" s="64"/>
     </row>
     <row r="51" spans="1:10" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A51" s="63"/>
       <c r="B51" s="74" t="s">
-        <v>1521</v>
+        <v>1476</v>
       </c>
       <c r="C51" s="379" t="s">
-        <v>1523</v>
+        <v>1478</v>
       </c>
       <c r="D51" s="75"/>
       <c r="E51" s="76" t="s">
-        <v>1524</v>
+        <v>1479</v>
       </c>
       <c r="J51" s="64"/>
     </row>
     <row r="52" spans="1:10" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A52" s="63"/>
       <c r="B52" s="74" t="s">
-        <v>1521</v>
+        <v>1476</v>
       </c>
       <c r="C52" s="379" t="s">
-        <v>1525</v>
+        <v>1480</v>
       </c>
       <c r="D52" s="75"/>
       <c r="E52" s="76" t="s">
-        <v>1526</v>
+        <v>1481</v>
       </c>
       <c r="J52" s="64"/>
     </row>
     <row r="53" spans="1:10" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A53" s="63"/>
       <c r="B53" s="64" t="s">
-        <v>1527</v>
+        <v>1482</v>
       </c>
       <c r="C53" s="328" t="s">
-        <v>1528</v>
+        <v>1483</v>
       </c>
       <c r="D53" s="63" t="s">
-        <v>1529</v>
+        <v>1484</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>1529</v>
+        <v>1484</v>
       </c>
       <c r="J53" s="64"/>
     </row>
     <row r="54" spans="1:10" ht="30" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A54" s="63"/>
       <c r="B54" s="115" t="s">
-        <v>1530</v>
+        <v>1485</v>
       </c>
       <c r="C54" s="380" t="s">
-        <v>1531</v>
+        <v>1486</v>
       </c>
       <c r="D54" s="63"/>
       <c r="H54" s="116" t="s">
-        <v>1465</v>
+        <v>1420</v>
       </c>
       <c r="I54" s="116" t="s">
-        <v>1465</v>
+        <v>1420</v>
       </c>
       <c r="J54" s="64"/>
     </row>
     <row r="55" spans="1:10" ht="30" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A55" s="63"/>
       <c r="B55" s="115" t="s">
-        <v>1532</v>
+        <v>1487</v>
       </c>
       <c r="C55" s="380" t="s">
-        <v>1533</v>
+        <v>1488</v>
       </c>
       <c r="D55" s="63"/>
       <c r="H55" s="116" t="s">
-        <v>1449</v>
+        <v>1404</v>
       </c>
       <c r="I55" s="116" t="s">
-        <v>1449</v>
+        <v>1404</v>
       </c>
       <c r="J55" s="64"/>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="110" t="s">
-        <v>1534</v>
+        <v>1489</v>
       </c>
       <c r="B56" s="111"/>
       <c r="C56" s="376"/>
       <c r="D56" s="110" t="s">
-        <v>1431</v>
+        <v>1386</v>
       </c>
       <c r="E56" s="112" t="s">
-        <v>1431</v>
+        <v>1386</v>
       </c>
       <c r="F56" s="112" t="s">
-        <v>1431</v>
+        <v>1386</v>
       </c>
       <c r="G56" s="112" t="s">
-        <v>1431</v>
+        <v>1386</v>
       </c>
       <c r="H56" s="112" t="s">
-        <v>1431</v>
+        <v>1386</v>
       </c>
       <c r="I56" s="112" t="s">
-        <v>1431</v>
+        <v>1386</v>
       </c>
       <c r="J56" s="111" t="s">
-        <v>1431</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="57" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A57" s="68"/>
       <c r="B57" s="69" t="s">
-        <v>1535</v>
+        <v>1490</v>
       </c>
       <c r="C57" s="383"/>
       <c r="D57" s="113" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
       <c r="E57" s="101" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
       <c r="F57" s="101" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
       <c r="G57" s="101" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
       <c r="H57" s="101" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
       <c r="I57" s="101" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
       <c r="J57" s="114" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="58" spans="1:10" ht="30" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A58" s="63"/>
       <c r="B58" s="64" t="s">
-        <v>1536</v>
+        <v>1491</v>
       </c>
       <c r="C58" s="328" t="s">
-        <v>1537</v>
+        <v>1492</v>
       </c>
       <c r="D58" s="63" t="s">
-        <v>1538</v>
+        <v>1493</v>
       </c>
       <c r="E58" s="10" t="s">
-        <v>1538</v>
+        <v>1493</v>
       </c>
       <c r="J58" s="64"/>
     </row>
     <row r="59" spans="1:10" ht="30" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="A59" s="63"/>
       <c r="B59" s="64" t="s">
-        <v>1539</v>
+        <v>1494</v>
       </c>
       <c r="C59" s="328" t="s">
-        <v>1540</v>
+        <v>1495</v>
       </c>
       <c r="D59" s="63" t="s">
-        <v>1538</v>
+        <v>1493</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>1538</v>
+        <v>1493</v>
       </c>
       <c r="J59" s="64"/>
     </row>
     <row r="60" spans="1:10" ht="30" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="A60" s="63"/>
       <c r="B60" s="64" t="s">
-        <v>1541</v>
+        <v>1496</v>
       </c>
       <c r="C60" s="328" t="s">
-        <v>1542</v>
+        <v>1497</v>
       </c>
       <c r="D60" s="63" t="s">
-        <v>1538</v>
+        <v>1493</v>
       </c>
       <c r="E60" s="10" t="s">
-        <v>1538</v>
+        <v>1493</v>
       </c>
       <c r="J60" s="64"/>
     </row>
     <row r="61" spans="1:10" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A61" s="63"/>
       <c r="B61" s="115" t="s">
-        <v>1543</v>
+        <v>1498</v>
       </c>
       <c r="C61" s="380" t="s">
-        <v>1544</v>
+        <v>1499</v>
       </c>
       <c r="D61" s="75"/>
       <c r="E61" s="76"/>
       <c r="F61" s="76"/>
       <c r="G61" s="76"/>
       <c r="H61" s="116" t="s">
-        <v>1436</v>
+        <v>1391</v>
       </c>
       <c r="I61" s="116" t="s">
-        <v>1436</v>
+        <v>1391</v>
       </c>
       <c r="J61" s="64"/>
     </row>
     <row r="62" spans="1:10" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="A62" s="63"/>
       <c r="B62" s="115" t="s">
-        <v>1545</v>
+        <v>1500</v>
       </c>
       <c r="C62" s="380" t="s">
-        <v>1546</v>
+        <v>1501</v>
       </c>
       <c r="D62" s="75"/>
       <c r="E62" s="76"/>
       <c r="F62" s="76"/>
       <c r="G62" s="76"/>
       <c r="H62" s="116" t="s">
-        <v>1436</v>
+        <v>1391</v>
       </c>
       <c r="I62" s="116" t="s">
-        <v>1436</v>
+        <v>1391</v>
       </c>
       <c r="J62" s="64"/>
     </row>
     <row r="63" spans="1:10" outlineLevel="3" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A63" s="63"/>
       <c r="B63" s="115" t="s">
-        <v>1541</v>
+        <v>1496</v>
       </c>
       <c r="C63" s="380" t="s">
-        <v>1547</v>
+        <v>1502</v>
       </c>
       <c r="D63" s="75"/>
       <c r="E63" s="76"/>
       <c r="F63" s="76"/>
       <c r="G63" s="76"/>
       <c r="H63" s="116" t="s">
-        <v>1436</v>
+        <v>1391</v>
       </c>
       <c r="I63" s="116" t="s">
-        <v>1436</v>
+        <v>1391</v>
       </c>
       <c r="J63" s="64"/>
     </row>
     <row r="64" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A64" s="68"/>
       <c r="B64" s="69" t="s">
-        <v>1548</v>
+        <v>1503</v>
       </c>
       <c r="C64" s="383"/>
       <c r="D64" s="113" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
       <c r="E64" s="101" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
       <c r="F64" s="101" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
       <c r="G64" s="101" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
       <c r="H64" s="101" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
       <c r="I64" s="101" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
       <c r="J64" s="114" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="65" spans="1:10" ht="30" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A65" s="63"/>
       <c r="B65" s="64" t="s">
-        <v>1549</v>
+        <v>1504</v>
       </c>
       <c r="C65" s="328" t="s">
-        <v>1550</v>
+        <v>1505</v>
       </c>
       <c r="D65" s="63" t="s">
-        <v>1538</v>
+        <v>1493</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>1538</v>
+        <v>1493</v>
       </c>
       <c r="J65" s="64"/>
     </row>
     <row r="66" spans="1:10" ht="30" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="A66" s="63"/>
       <c r="B66" s="64" t="s">
-        <v>1551</v>
+        <v>1506</v>
       </c>
       <c r="C66" s="328" t="s">
-        <v>1540</v>
+        <v>1495</v>
       </c>
       <c r="D66" s="63" t="s">
-        <v>1538</v>
+        <v>1493</v>
       </c>
       <c r="E66" s="10" t="s">
-        <v>1538</v>
+        <v>1493</v>
       </c>
       <c r="J66" s="64"/>
     </row>
     <row r="67" spans="1:10" ht="30" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="A67" s="63"/>
       <c r="B67" s="64" t="s">
-        <v>1541</v>
+        <v>1496</v>
       </c>
       <c r="C67" s="328" t="s">
-        <v>1552</v>
+        <v>1507</v>
       </c>
       <c r="D67" s="63" t="s">
-        <v>1538</v>
+        <v>1493</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>1538</v>
+        <v>1493</v>
       </c>
       <c r="J67" s="64"/>
     </row>
     <row r="68" spans="1:10" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A68" s="63"/>
       <c r="B68" s="115" t="s">
-        <v>1553</v>
+        <v>1508</v>
       </c>
       <c r="C68" s="380" t="s">
-        <v>1554</v>
+        <v>1509</v>
       </c>
       <c r="D68" s="75"/>
       <c r="E68" s="76"/>
       <c r="F68" s="76"/>
       <c r="G68" s="76"/>
       <c r="H68" s="116" t="s">
-        <v>1436</v>
+        <v>1391</v>
       </c>
       <c r="I68" s="116" t="s">
-        <v>1436</v>
+        <v>1391</v>
       </c>
       <c r="J68" s="64"/>
     </row>
     <row r="69" spans="1:10" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="A69" s="63"/>
       <c r="B69" s="71" t="s">
-        <v>1555</v>
+        <v>1510</v>
       </c>
       <c r="C69" s="384" t="s">
-        <v>1556</v>
+        <v>1511</v>
       </c>
       <c r="D69" s="70"/>
       <c r="E69" s="79"/>
       <c r="F69" s="79"/>
       <c r="G69" s="79"/>
       <c r="H69" s="79" t="s">
-        <v>1436</v>
+        <v>1391</v>
       </c>
       <c r="I69" s="79" t="s">
-        <v>1436</v>
+        <v>1391</v>
       </c>
       <c r="J69" s="64"/>
     </row>
     <row r="70" spans="1:10" outlineLevel="3" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A70" s="63"/>
       <c r="B70" s="115" t="s">
-        <v>1541</v>
+        <v>1496</v>
       </c>
       <c r="C70" s="380" t="s">
-        <v>1557</v>
+        <v>1512</v>
       </c>
       <c r="D70" s="75"/>
       <c r="E70" s="76"/>
       <c r="F70" s="76"/>
       <c r="G70" s="76"/>
       <c r="H70" s="116" t="s">
-        <v>1436</v>
+        <v>1391</v>
       </c>
       <c r="I70" s="116" t="s">
-        <v>1436</v>
+        <v>1391</v>
       </c>
       <c r="J70" s="64"/>
     </row>
     <row r="71" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A71" s="68"/>
       <c r="B71" s="69" t="s">
-        <v>1558</v>
+        <v>1513</v>
       </c>
       <c r="C71" s="383"/>
       <c r="D71" s="113" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
       <c r="E71" s="101" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
       <c r="F71" s="101" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
       <c r="G71" s="101" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
       <c r="H71" s="101" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
       <c r="I71" s="101" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
       <c r="J71" s="114" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="72" spans="1:10" ht="30" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A72" s="63"/>
       <c r="B72" s="64" t="s">
-        <v>1559</v>
+        <v>1514</v>
       </c>
       <c r="C72" s="328" t="s">
-        <v>1560</v>
+        <v>1515</v>
       </c>
       <c r="D72" s="63" t="s">
-        <v>1538</v>
+        <v>1493</v>
       </c>
       <c r="E72" s="10" t="s">
-        <v>1538</v>
+        <v>1493</v>
       </c>
       <c r="J72" s="64"/>
     </row>
     <row r="73" spans="1:10" ht="30" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="A73" s="63"/>
       <c r="B73" s="64" t="s">
-        <v>1561</v>
+        <v>1516</v>
       </c>
       <c r="C73" s="328" t="s">
-        <v>1540</v>
+        <v>1495</v>
       </c>
       <c r="D73" s="63" t="s">
-        <v>1538</v>
+        <v>1493</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>1538</v>
+        <v>1493</v>
       </c>
       <c r="J73" s="64"/>
     </row>
     <row r="74" spans="1:10" ht="30" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="A74" s="63"/>
       <c r="B74" s="64" t="s">
-        <v>1541</v>
+        <v>1496</v>
       </c>
       <c r="C74" s="328" t="s">
-        <v>1542</v>
+        <v>1497</v>
       </c>
       <c r="D74" s="63" t="s">
-        <v>1538</v>
+        <v>1493</v>
       </c>
       <c r="E74" s="10" t="s">
-        <v>1538</v>
+        <v>1493</v>
       </c>
       <c r="J74" s="64"/>
     </row>
     <row r="75" spans="1:10" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A75" s="63"/>
       <c r="B75" s="115" t="s">
-        <v>1562</v>
+        <v>1517</v>
       </c>
       <c r="C75" s="380" t="s">
-        <v>1563</v>
+        <v>1518</v>
       </c>
       <c r="D75" s="75"/>
       <c r="E75" s="76"/>
       <c r="F75" s="76"/>
       <c r="G75" s="76"/>
       <c r="H75" s="116" t="s">
-        <v>1436</v>
+        <v>1391</v>
       </c>
       <c r="I75" s="116" t="s">
-        <v>1436</v>
+        <v>1391</v>
       </c>
       <c r="J75" s="64"/>
     </row>
     <row r="76" spans="1:10" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="A76" s="63"/>
       <c r="B76" s="115" t="s">
-        <v>1545</v>
+        <v>1500</v>
       </c>
       <c r="C76" s="380" t="s">
-        <v>1564</v>
+        <v>1519</v>
       </c>
       <c r="D76" s="75"/>
       <c r="E76" s="76"/>
       <c r="F76" s="76"/>
       <c r="G76" s="76"/>
       <c r="H76" s="116" t="s">
-        <v>1436</v>
+        <v>1391</v>
       </c>
       <c r="I76" s="116" t="s">
-        <v>1436</v>
+        <v>1391</v>
       </c>
       <c r="J76" s="64"/>
     </row>
     <row r="77" spans="1:10" outlineLevel="3" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A77" s="63"/>
       <c r="B77" s="115" t="s">
-        <v>1541</v>
+        <v>1496</v>
       </c>
       <c r="C77" s="380" t="s">
-        <v>1547</v>
+        <v>1502</v>
       </c>
       <c r="D77" s="75"/>
       <c r="E77" s="76"/>
       <c r="F77" s="76"/>
       <c r="G77" s="76"/>
       <c r="H77" s="116" t="s">
-        <v>1436</v>
+        <v>1391</v>
       </c>
       <c r="I77" s="116" t="s">
-        <v>1436</v>
+        <v>1391</v>
       </c>
       <c r="J77" s="64"/>
     </row>
     <row r="78" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A78" s="68"/>
       <c r="B78" s="69" t="s">
-        <v>1565</v>
+        <v>1520</v>
       </c>
       <c r="C78" s="383"/>
       <c r="D78" s="113" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
       <c r="E78" s="101" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
       <c r="F78" s="101" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
       <c r="G78" s="101" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
       <c r="H78" s="101" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
       <c r="I78" s="101" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
       <c r="J78" s="114" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="79" spans="1:10" ht="30" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A79" s="63"/>
       <c r="B79" s="64" t="s">
-        <v>1566</v>
+        <v>1521</v>
       </c>
       <c r="C79" s="328" t="s">
-        <v>1567</v>
+        <v>1522</v>
       </c>
       <c r="D79" s="63" t="s">
-        <v>1538</v>
+        <v>1493</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>1538</v>
+        <v>1493</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>1436</v>
+        <v>1391</v>
       </c>
       <c r="I79" s="10" t="s">
-        <v>1436</v>
+        <v>1391</v>
       </c>
       <c r="J79" s="64"/>
     </row>
     <row r="80" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A80" s="68"/>
       <c r="B80" s="69" t="s">
-        <v>1568</v>
+        <v>1523</v>
       </c>
       <c r="C80" s="383"/>
       <c r="D80" s="113" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
       <c r="E80" s="101" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
       <c r="F80" s="101" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
       <c r="G80" s="101" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
       <c r="H80" s="101" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
       <c r="I80" s="101" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
       <c r="J80" s="114" t="s">
-        <v>1433</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="81" spans="1:10" ht="30" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A81" s="63"/>
       <c r="B81" s="64" t="s">
-        <v>1569</v>
+        <v>1524</v>
       </c>
       <c r="C81" s="328" t="s">
-        <v>1570</v>
+        <v>1525</v>
       </c>
       <c r="D81" s="63" t="s">
-        <v>1538</v>
+        <v>1493</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>1538</v>
+        <v>1493</v>
       </c>
       <c r="J81" s="64"/>
     </row>
     <row r="82" spans="1:10" ht="30" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="A82" s="63"/>
       <c r="B82" s="64" t="s">
-        <v>1551</v>
+        <v>1506</v>
       </c>
       <c r="C82" s="328" t="s">
-        <v>1540</v>
+        <v>1495</v>
       </c>
       <c r="D82" s="63" t="s">
-        <v>1538</v>
+        <v>1493</v>
       </c>
       <c r="E82" s="10" t="s">
-        <v>1538</v>
+        <v>1493</v>
       </c>
       <c r="J82" s="64"/>
     </row>
     <row r="83" spans="1:10" ht="30" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="A83" s="63"/>
       <c r="B83" s="64" t="s">
-        <v>1541</v>
+        <v>1496</v>
       </c>
       <c r="C83" s="384" t="s">
-        <v>1542</v>
+        <v>1497</v>
       </c>
       <c r="D83" s="63" t="s">
-        <v>1538</v>
+        <v>1493</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>1538</v>
+        <v>1493</v>
       </c>
       <c r="J83" s="64"/>
     </row>
     <row r="84" spans="1:10" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A84" s="63"/>
       <c r="B84" s="115" t="s">
-        <v>1569</v>
+        <v>1524</v>
       </c>
       <c r="C84" s="380" t="s">
-        <v>1571</v>
+        <v>1526</v>
       </c>
       <c r="D84" s="75"/>
       <c r="E84" s="76"/>
       <c r="F84" s="76"/>
       <c r="G84" s="76"/>
       <c r="H84" s="116" t="s">
-        <v>1436</v>
+        <v>1391</v>
       </c>
       <c r="I84" s="116" t="s">
-        <v>1436</v>
+        <v>1391</v>
       </c>
       <c r="J84" s="64"/>
     </row>
     <row r="85" spans="1:10" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="A85" s="63"/>
       <c r="B85" s="71" t="s">
-        <v>1551</v>
+        <v>1506</v>
       </c>
       <c r="C85" s="384" t="s">
-        <v>1572</v>
+        <v>1527</v>
       </c>
       <c r="D85" s="70"/>
       <c r="E85" s="79"/>
       <c r="F85" s="79"/>
       <c r="G85" s="79"/>
       <c r="H85" s="79" t="s">
-        <v>1436</v>
+        <v>1391</v>
       </c>
       <c r="I85" s="79" t="s">
-        <v>1436</v>
+        <v>1391</v>
       </c>
       <c r="J85" s="64"/>
     </row>
     <row r="86" spans="1:10" outlineLevel="3" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A86" s="63"/>
       <c r="B86" s="71" t="s">
-        <v>1541</v>
+        <v>1496</v>
       </c>
       <c r="C86" s="384" t="s">
-        <v>1572</v>
+        <v>1527</v>
       </c>
       <c r="D86" s="70"/>
       <c r="E86" s="79"/>
       <c r="F86" s="79"/>
       <c r="G86" s="79"/>
       <c r="H86" s="79" t="s">
-        <v>1436</v>
+        <v>1391</v>
       </c>
       <c r="I86" s="79" t="s">
-        <v>1436</v>
+        <v>1391</v>
       </c>
       <c r="J86" s="64"/>
     </row>
@@ -13703,10 +13053,10 @@
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" s="63"/>
       <c r="B91" s="64" t="s">
-        <v>1573</v>
+        <v>1528</v>
       </c>
       <c r="C91" s="328" t="s">
-        <v>1574</v>
+        <v>1529</v>
       </c>
       <c r="D91" s="63"/>
       <c r="J91" s="64"/>
@@ -13714,10 +13064,10 @@
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" s="63"/>
       <c r="B92" s="64" t="s">
-        <v>1575</v>
+        <v>1530</v>
       </c>
       <c r="C92" s="328" t="s">
-        <v>1576</v>
+        <v>1531</v>
       </c>
       <c r="D92" s="63"/>
       <c r="J92" s="64"/>
@@ -13725,10 +13075,10 @@
     <row r="93" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="63"/>
       <c r="B93" s="64" t="s">
-        <v>1577</v>
+        <v>1532</v>
       </c>
       <c r="C93" s="328" t="s">
-        <v>1578</v>
+        <v>1533</v>
       </c>
       <c r="D93" s="63"/>
       <c r="J93" s="64"/>
@@ -13736,10 +13086,10 @@
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" s="63"/>
       <c r="B94" s="64" t="s">
-        <v>1579</v>
+        <v>1534</v>
       </c>
       <c r="C94" s="328" t="s">
-        <v>1580</v>
+        <v>1535</v>
       </c>
       <c r="D94" s="63"/>
       <c r="J94" s="64"/>
@@ -13747,10 +13097,10 @@
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" s="63"/>
       <c r="B95" s="64" t="s">
-        <v>1581</v>
+        <v>1536</v>
       </c>
       <c r="C95" s="328" t="s">
-        <v>1582</v>
+        <v>1537</v>
       </c>
       <c r="D95" s="63"/>
       <c r="J95" s="64"/>
@@ -13758,10 +13108,10 @@
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" s="63"/>
       <c r="B96" s="64" t="s">
-        <v>1575</v>
+        <v>1530</v>
       </c>
       <c r="C96" s="328" t="s">
-        <v>1576</v>
+        <v>1531</v>
       </c>
       <c r="D96" s="63"/>
       <c r="J96" s="64"/>
@@ -13769,10 +13119,10 @@
     <row r="97" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="63"/>
       <c r="B97" s="64" t="s">
-        <v>1577</v>
+        <v>1532</v>
       </c>
       <c r="C97" s="328" t="s">
-        <v>1583</v>
+        <v>1538</v>
       </c>
       <c r="D97" s="63"/>
       <c r="J97" s="64"/>
@@ -13780,10 +13130,10 @@
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" s="63"/>
       <c r="B98" s="64" t="s">
-        <v>1579</v>
+        <v>1534</v>
       </c>
       <c r="C98" s="328" t="s">
-        <v>1580</v>
+        <v>1535</v>
       </c>
       <c r="D98" s="63"/>
       <c r="J98" s="64"/>
@@ -13853,2428 +13203,2428 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="497" t="s">
-        <v>1584</v>
-      </c>
-      <c r="D1" s="467"/>
-      <c r="E1" s="467"/>
-      <c r="F1" s="498"/>
-      <c r="G1" s="497" t="s">
-        <v>1585</v>
-      </c>
-      <c r="H1" s="467"/>
-      <c r="I1" s="467"/>
-      <c r="J1" s="498"/>
-      <c r="K1" s="497" t="s">
-        <v>1586</v>
-      </c>
-      <c r="L1" s="467"/>
-      <c r="M1" s="467"/>
-      <c r="N1" s="498"/>
-      <c r="O1" s="497" t="s">
-        <v>1587</v>
-      </c>
-      <c r="P1" s="467"/>
-      <c r="Q1" s="467"/>
-      <c r="R1" s="498"/>
-      <c r="S1" s="497" t="s">
-        <v>1588</v>
-      </c>
-      <c r="T1" s="467"/>
-      <c r="U1" s="467"/>
-      <c r="V1" s="498"/>
-      <c r="W1" s="497" t="s">
-        <v>1589</v>
-      </c>
-      <c r="X1" s="467"/>
-      <c r="Y1" s="467"/>
-      <c r="Z1" s="498"/>
+      <c r="C1" s="492" t="s">
+        <v>1539</v>
+      </c>
+      <c r="D1" s="462"/>
+      <c r="E1" s="462"/>
+      <c r="F1" s="493"/>
+      <c r="G1" s="492" t="s">
+        <v>1540</v>
+      </c>
+      <c r="H1" s="462"/>
+      <c r="I1" s="462"/>
+      <c r="J1" s="493"/>
+      <c r="K1" s="492" t="s">
+        <v>1541</v>
+      </c>
+      <c r="L1" s="462"/>
+      <c r="M1" s="462"/>
+      <c r="N1" s="493"/>
+      <c r="O1" s="492" t="s">
+        <v>1542</v>
+      </c>
+      <c r="P1" s="462"/>
+      <c r="Q1" s="462"/>
+      <c r="R1" s="493"/>
+      <c r="S1" s="492" t="s">
+        <v>1543</v>
+      </c>
+      <c r="T1" s="462"/>
+      <c r="U1" s="462"/>
+      <c r="V1" s="493"/>
+      <c r="W1" s="492" t="s">
+        <v>1544</v>
+      </c>
+      <c r="X1" s="462"/>
+      <c r="Y1" s="462"/>
+      <c r="Z1" s="493"/>
     </row>
     <row r="2" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="509" t="s">
-        <v>1590</v>
-      </c>
-      <c r="B2" s="468"/>
+      <c r="A2" s="504" t="s">
+        <v>1545</v>
+      </c>
+      <c r="B2" s="463"/>
       <c r="C2" s="12" t="s">
-        <v>1428</v>
+        <v>1383</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>1591</v>
+        <v>1546</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>1428</v>
+        <v>1383</v>
       </c>
       <c r="F2" s="14" t="s">
         <v>24</v>
       </c>
       <c r="G2" s="15" t="s">
-        <v>1428</v>
+        <v>1383</v>
       </c>
       <c r="H2" s="13" t="s">
-        <v>1591</v>
+        <v>1546</v>
       </c>
       <c r="I2" s="13" t="s">
-        <v>1428</v>
+        <v>1383</v>
       </c>
       <c r="J2" s="14" t="s">
         <v>24</v>
       </c>
       <c r="K2" s="15" t="s">
-        <v>1428</v>
+        <v>1383</v>
       </c>
       <c r="L2" s="13" t="s">
-        <v>1591</v>
+        <v>1546</v>
       </c>
       <c r="M2" s="13" t="s">
-        <v>1428</v>
+        <v>1383</v>
       </c>
       <c r="N2" s="14" t="s">
         <v>24</v>
       </c>
       <c r="O2" s="15" t="s">
-        <v>1428</v>
+        <v>1383</v>
       </c>
       <c r="P2" s="13" t="s">
-        <v>1591</v>
+        <v>1546</v>
       </c>
       <c r="Q2" s="13" t="s">
-        <v>1428</v>
+        <v>1383</v>
       </c>
       <c r="R2" s="14" t="s">
         <v>24</v>
       </c>
       <c r="S2" s="15" t="s">
-        <v>1428</v>
+        <v>1383</v>
       </c>
       <c r="T2" s="13" t="s">
-        <v>1591</v>
+        <v>1546</v>
       </c>
       <c r="U2" s="13" t="s">
-        <v>1428</v>
+        <v>1383</v>
       </c>
       <c r="V2" s="14" t="s">
         <v>24</v>
       </c>
       <c r="W2" s="15" t="s">
-        <v>1428</v>
+        <v>1383</v>
       </c>
       <c r="X2" s="13" t="s">
-        <v>1591</v>
+        <v>1546</v>
       </c>
       <c r="Y2" s="13" t="s">
-        <v>1428</v>
+        <v>1383</v>
       </c>
       <c r="Z2" s="14" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:26" ht="286.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="494" t="s">
-        <v>1592</v>
-      </c>
-      <c r="B3" s="491" t="s">
-        <v>1593</v>
-      </c>
-      <c r="C3" s="469" t="s">
-        <v>1594</v>
+      <c r="A3" s="489" t="s">
+        <v>1547</v>
+      </c>
+      <c r="B3" s="486" t="s">
+        <v>1548</v>
+      </c>
+      <c r="C3" s="464" t="s">
+        <v>1549</v>
       </c>
       <c r="D3" s="385" t="s">
-        <v>1595</v>
+        <v>1550</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>1596</v>
+        <v>1551</v>
       </c>
       <c r="F3" s="17" t="s">
-        <v>1597</v>
-      </c>
-      <c r="G3" s="469" t="s">
-        <v>1594</v>
+        <v>1552</v>
+      </c>
+      <c r="G3" s="464" t="s">
+        <v>1549</v>
       </c>
       <c r="H3" s="385" t="s">
-        <v>1595</v>
+        <v>1550</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>1596</v>
+        <v>1551</v>
       </c>
       <c r="J3" s="17" t="s">
-        <v>1597</v>
-      </c>
-      <c r="K3" s="507" t="s">
-        <v>1598</v>
+        <v>1552</v>
+      </c>
+      <c r="K3" s="502" t="s">
+        <v>1553</v>
       </c>
       <c r="L3" s="386" t="s">
-        <v>1595</v>
+        <v>1550</v>
       </c>
       <c r="M3" s="18" t="s">
-        <v>1596</v>
+        <v>1551</v>
       </c>
       <c r="N3" s="19" t="s">
-        <v>1599</v>
-      </c>
-      <c r="O3" s="469" t="s">
-        <v>1600</v>
+        <v>1554</v>
+      </c>
+      <c r="O3" s="464" t="s">
+        <v>1555</v>
       </c>
       <c r="P3" s="385" t="s">
-        <v>1595</v>
+        <v>1550</v>
       </c>
       <c r="Q3" s="297"/>
       <c r="R3" s="20" t="s">
-        <v>1601</v>
-      </c>
-      <c r="S3" s="477"/>
+        <v>1556</v>
+      </c>
+      <c r="S3" s="472"/>
       <c r="T3" s="387" t="s">
-        <v>1595</v>
+        <v>1550</v>
       </c>
       <c r="U3" s="388"/>
       <c r="V3" s="21" t="s">
-        <v>1602</v>
-      </c>
-      <c r="W3" s="469" t="s">
-        <v>1603</v>
+        <v>1557</v>
+      </c>
+      <c r="W3" s="464" t="s">
+        <v>1558</v>
       </c>
       <c r="X3" s="385" t="s">
-        <v>1595</v>
+        <v>1550</v>
       </c>
       <c r="Y3" s="297"/>
       <c r="Z3" s="17" t="s">
-        <v>1604</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A4" s="473"/>
-      <c r="B4" s="484"/>
-      <c r="C4" s="470"/>
+      <c r="A4" s="468"/>
+      <c r="B4" s="479"/>
+      <c r="C4" s="465"/>
       <c r="D4" s="389" t="s">
-        <v>1605</v>
+        <v>1560</v>
       </c>
       <c r="E4" s="390">
         <v>13900244911</v>
       </c>
       <c r="F4" s="22"/>
-      <c r="G4" s="470"/>
+      <c r="G4" s="465"/>
       <c r="H4" s="389" t="s">
-        <v>1605</v>
+        <v>1560</v>
       </c>
       <c r="I4" s="390">
         <v>13900244911</v>
       </c>
       <c r="J4" s="22"/>
-      <c r="K4" s="470"/>
+      <c r="K4" s="465"/>
       <c r="L4" s="391" t="s">
-        <v>1605</v>
+        <v>1560</v>
       </c>
       <c r="M4" s="392">
         <v>13900244911</v>
       </c>
       <c r="N4" s="23"/>
-      <c r="O4" s="470"/>
+      <c r="O4" s="465"/>
       <c r="P4" s="389" t="s">
-        <v>1605</v>
+        <v>1560</v>
       </c>
       <c r="Q4" s="393">
         <v>13900244911</v>
       </c>
       <c r="R4" s="22"/>
-      <c r="S4" s="470"/>
+      <c r="S4" s="465"/>
       <c r="T4" s="394" t="s">
-        <v>1605</v>
+        <v>1560</v>
       </c>
       <c r="U4" s="395">
         <v>13900244911</v>
       </c>
       <c r="V4" s="24"/>
-      <c r="W4" s="470"/>
+      <c r="W4" s="465"/>
       <c r="X4" s="389" t="s">
-        <v>1605</v>
+        <v>1560</v>
       </c>
       <c r="Y4" s="165"/>
       <c r="Z4" s="22"/>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A5" s="473"/>
-      <c r="B5" s="484"/>
-      <c r="C5" s="470"/>
+      <c r="A5" s="468"/>
+      <c r="B5" s="479"/>
+      <c r="C5" s="465"/>
       <c r="D5" s="389" t="s">
-        <v>1606</v>
+        <v>1561</v>
       </c>
       <c r="E5" s="165" t="s">
-        <v>1607</v>
+        <v>1562</v>
       </c>
       <c r="F5" s="22"/>
-      <c r="G5" s="470"/>
+      <c r="G5" s="465"/>
       <c r="H5" s="389" t="s">
-        <v>1606</v>
+        <v>1561</v>
       </c>
       <c r="I5" s="165" t="s">
-        <v>1607</v>
+        <v>1562</v>
       </c>
       <c r="J5" s="22"/>
-      <c r="K5" s="470"/>
+      <c r="K5" s="465"/>
       <c r="L5" s="391" t="s">
-        <v>1606</v>
+        <v>1561</v>
       </c>
       <c r="M5" s="396" t="s">
-        <v>1607</v>
+        <v>1562</v>
       </c>
       <c r="N5" s="23"/>
-      <c r="O5" s="470"/>
+      <c r="O5" s="465"/>
       <c r="P5" s="389" t="s">
-        <v>1606</v>
+        <v>1561</v>
       </c>
       <c r="Q5" s="166" t="s">
-        <v>1607</v>
+        <v>1562</v>
       </c>
       <c r="R5" s="22"/>
-      <c r="S5" s="470"/>
+      <c r="S5" s="465"/>
       <c r="T5" s="394" t="s">
-        <v>1606</v>
+        <v>1561</v>
       </c>
       <c r="U5" s="397" t="s">
-        <v>1607</v>
+        <v>1562</v>
       </c>
       <c r="V5" s="24"/>
-      <c r="W5" s="470"/>
+      <c r="W5" s="465"/>
       <c r="X5" s="389" t="s">
-        <v>1606</v>
+        <v>1561</v>
       </c>
       <c r="Y5" s="165"/>
       <c r="Z5" s="22"/>
     </row>
     <row r="6" spans="1:26" ht="87" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="473"/>
-      <c r="B6" s="484"/>
-      <c r="C6" s="470"/>
+      <c r="A6" s="468"/>
+      <c r="B6" s="479"/>
+      <c r="C6" s="465"/>
       <c r="D6" s="389" t="s">
-        <v>1608</v>
+        <v>1563</v>
       </c>
       <c r="E6" s="398" t="s">
-        <v>1609</v>
+        <v>1564</v>
       </c>
       <c r="F6" s="22"/>
-      <c r="G6" s="470"/>
+      <c r="G6" s="465"/>
       <c r="H6" s="389" t="s">
-        <v>1608</v>
+        <v>1563</v>
       </c>
       <c r="I6" s="398" t="s">
-        <v>1609</v>
+        <v>1564</v>
       </c>
       <c r="J6" s="22"/>
-      <c r="K6" s="470"/>
+      <c r="K6" s="465"/>
       <c r="L6" s="391" t="s">
-        <v>1608</v>
+        <v>1563</v>
       </c>
       <c r="M6" s="399" t="s">
-        <v>1609</v>
+        <v>1564</v>
       </c>
       <c r="N6" s="23"/>
-      <c r="O6" s="470"/>
+      <c r="O6" s="465"/>
       <c r="P6" s="389" t="s">
-        <v>1608</v>
+        <v>1563</v>
       </c>
       <c r="Q6" s="400" t="s">
-        <v>1609</v>
+        <v>1564</v>
       </c>
       <c r="R6" s="22"/>
-      <c r="S6" s="470"/>
+      <c r="S6" s="465"/>
       <c r="T6" s="394" t="s">
-        <v>1608</v>
+        <v>1563</v>
       </c>
       <c r="U6" s="401" t="s">
-        <v>1609</v>
+        <v>1564</v>
       </c>
       <c r="V6" s="24"/>
-      <c r="W6" s="470"/>
+      <c r="W6" s="465"/>
       <c r="X6" s="389" t="s">
-        <v>1608</v>
+        <v>1563</v>
       </c>
       <c r="Y6" s="398" t="s">
-        <v>1609</v>
+        <v>1564</v>
       </c>
       <c r="Z6" s="22"/>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A7" s="473"/>
-      <c r="B7" s="484"/>
-      <c r="C7" s="470"/>
+      <c r="A7" s="468"/>
+      <c r="B7" s="479"/>
+      <c r="C7" s="465"/>
       <c r="D7" s="389" t="s">
-        <v>1610</v>
+        <v>1565</v>
       </c>
       <c r="E7" s="165" t="s">
-        <v>1611</v>
+        <v>1566</v>
       </c>
       <c r="F7" s="22"/>
-      <c r="G7" s="470"/>
+      <c r="G7" s="465"/>
       <c r="H7" s="389" t="s">
-        <v>1610</v>
+        <v>1565</v>
       </c>
       <c r="I7" s="165" t="s">
-        <v>1611</v>
+        <v>1566</v>
       </c>
       <c r="J7" s="22"/>
-      <c r="K7" s="470"/>
+      <c r="K7" s="465"/>
       <c r="L7" s="391" t="s">
-        <v>1610</v>
+        <v>1565</v>
       </c>
       <c r="M7" s="396" t="s">
-        <v>1611</v>
+        <v>1566</v>
       </c>
       <c r="N7" s="23"/>
-      <c r="O7" s="470"/>
+      <c r="O7" s="465"/>
       <c r="P7" s="389" t="s">
-        <v>1610</v>
+        <v>1565</v>
       </c>
       <c r="Q7" s="166" t="s">
-        <v>1611</v>
+        <v>1566</v>
       </c>
       <c r="R7" s="22"/>
-      <c r="S7" s="470"/>
+      <c r="S7" s="465"/>
       <c r="T7" s="394" t="s">
-        <v>1610</v>
+        <v>1565</v>
       </c>
       <c r="U7" s="397" t="s">
-        <v>1611</v>
+        <v>1566</v>
       </c>
       <c r="V7" s="24"/>
-      <c r="W7" s="470"/>
+      <c r="W7" s="465"/>
       <c r="X7" s="389" t="s">
-        <v>1610</v>
+        <v>1565</v>
       </c>
       <c r="Y7" s="165"/>
       <c r="Z7" s="22"/>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A8" s="473"/>
-      <c r="B8" s="446"/>
-      <c r="C8" s="471"/>
+      <c r="A8" s="468"/>
+      <c r="B8" s="441"/>
+      <c r="C8" s="466"/>
       <c r="D8" s="389" t="s">
-        <v>1612</v>
+        <v>1567</v>
       </c>
       <c r="E8" s="165"/>
       <c r="F8" s="22" t="s">
-        <v>1613</v>
-      </c>
-      <c r="G8" s="471"/>
+        <v>1568</v>
+      </c>
+      <c r="G8" s="466"/>
       <c r="H8" s="389" t="s">
-        <v>1612</v>
+        <v>1567</v>
       </c>
       <c r="I8" s="165"/>
       <c r="J8" s="22" t="s">
-        <v>1613</v>
-      </c>
-      <c r="K8" s="471"/>
+        <v>1568</v>
+      </c>
+      <c r="K8" s="466"/>
       <c r="L8" s="391" t="s">
-        <v>1612</v>
+        <v>1567</v>
       </c>
       <c r="M8" s="396"/>
       <c r="N8" s="23"/>
-      <c r="O8" s="471"/>
+      <c r="O8" s="466"/>
       <c r="P8" s="389" t="s">
-        <v>1612</v>
+        <v>1567</v>
       </c>
       <c r="Q8" s="166"/>
       <c r="R8" s="22"/>
-      <c r="S8" s="471"/>
+      <c r="S8" s="466"/>
       <c r="T8" s="394" t="s">
-        <v>1612</v>
+        <v>1567</v>
       </c>
       <c r="U8" s="397"/>
       <c r="V8" s="24"/>
-      <c r="W8" s="471"/>
+      <c r="W8" s="466"/>
       <c r="X8" s="389" t="s">
-        <v>1612</v>
+        <v>1567</v>
       </c>
       <c r="Y8" s="165"/>
       <c r="Z8" s="22"/>
     </row>
     <row r="9" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="473"/>
-      <c r="B9" s="512" t="s">
-        <v>1614</v>
-      </c>
-      <c r="C9" s="500" t="s">
-        <v>1615</v>
+      <c r="A9" s="468"/>
+      <c r="B9" s="507" t="s">
+        <v>1569</v>
+      </c>
+      <c r="C9" s="495" t="s">
+        <v>1570</v>
       </c>
       <c r="D9" s="389" t="s">
-        <v>1616</v>
+        <v>1571</v>
       </c>
       <c r="E9" s="217" t="s">
-        <v>1617</v>
+        <v>1572</v>
       </c>
       <c r="F9" s="22"/>
-      <c r="G9" s="500" t="s">
-        <v>1615</v>
+      <c r="G9" s="495" t="s">
+        <v>1570</v>
       </c>
       <c r="H9" s="389" t="s">
-        <v>1616</v>
+        <v>1571</v>
       </c>
       <c r="I9" s="217" t="s">
-        <v>1617</v>
+        <v>1572</v>
       </c>
       <c r="J9" s="22"/>
-      <c r="K9" s="501" t="s">
-        <v>1618</v>
+      <c r="K9" s="496" t="s">
+        <v>1573</v>
       </c>
       <c r="L9" s="391" t="s">
-        <v>1616</v>
+        <v>1571</v>
       </c>
       <c r="M9" s="403" t="s">
-        <v>1617</v>
+        <v>1572</v>
       </c>
       <c r="N9" s="23"/>
-      <c r="O9" s="500" t="s">
-        <v>1619</v>
+      <c r="O9" s="495" t="s">
+        <v>1574</v>
       </c>
       <c r="P9" s="389" t="s">
-        <v>1616</v>
+        <v>1571</v>
       </c>
       <c r="Q9" s="217" t="s">
-        <v>1617</v>
+        <v>1572</v>
       </c>
       <c r="R9" s="22"/>
-      <c r="S9" s="527"/>
+      <c r="S9" s="522"/>
       <c r="T9" s="394" t="s">
-        <v>1616</v>
+        <v>1571</v>
       </c>
       <c r="U9" s="397"/>
       <c r="V9" s="24"/>
-      <c r="W9" s="524"/>
+      <c r="W9" s="519"/>
       <c r="X9" s="389" t="s">
-        <v>1616</v>
+        <v>1571</v>
       </c>
       <c r="Y9" s="165"/>
       <c r="Z9" s="22"/>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A10" s="473"/>
-      <c r="B10" s="484"/>
-      <c r="C10" s="470"/>
+      <c r="A10" s="468"/>
+      <c r="B10" s="479"/>
+      <c r="C10" s="465"/>
       <c r="D10" s="389" t="s">
-        <v>1620</v>
+        <v>1575</v>
       </c>
       <c r="E10" s="165"/>
       <c r="F10" s="22"/>
-      <c r="G10" s="470"/>
+      <c r="G10" s="465"/>
       <c r="H10" s="389" t="s">
-        <v>1620</v>
+        <v>1575</v>
       </c>
       <c r="I10" s="165"/>
       <c r="J10" s="22"/>
-      <c r="K10" s="470"/>
+      <c r="K10" s="465"/>
       <c r="L10" s="391" t="s">
-        <v>1620</v>
+        <v>1575</v>
       </c>
       <c r="M10" s="396"/>
       <c r="N10" s="23"/>
-      <c r="O10" s="470"/>
+      <c r="O10" s="465"/>
       <c r="P10" s="389" t="s">
-        <v>1620</v>
+        <v>1575</v>
       </c>
       <c r="Q10" s="165"/>
       <c r="R10" s="22"/>
-      <c r="S10" s="470"/>
+      <c r="S10" s="465"/>
       <c r="T10" s="394" t="s">
-        <v>1620</v>
+        <v>1575</v>
       </c>
       <c r="U10" s="397"/>
       <c r="V10" s="24"/>
-      <c r="W10" s="470"/>
+      <c r="W10" s="465"/>
       <c r="X10" s="389" t="s">
-        <v>1620</v>
+        <v>1575</v>
       </c>
       <c r="Y10" s="165"/>
       <c r="Z10" s="22"/>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A11" s="473"/>
-      <c r="B11" s="484"/>
-      <c r="C11" s="470"/>
+      <c r="A11" s="468"/>
+      <c r="B11" s="479"/>
+      <c r="C11" s="465"/>
       <c r="D11" s="389" t="s">
-        <v>1610</v>
+        <v>1565</v>
       </c>
       <c r="E11" s="165"/>
       <c r="F11" s="22"/>
-      <c r="G11" s="470"/>
+      <c r="G11" s="465"/>
       <c r="H11" s="389" t="s">
-        <v>1610</v>
+        <v>1565</v>
       </c>
       <c r="I11" s="165"/>
       <c r="J11" s="22"/>
-      <c r="K11" s="470"/>
+      <c r="K11" s="465"/>
       <c r="L11" s="391" t="s">
-        <v>1610</v>
+        <v>1565</v>
       </c>
       <c r="M11" s="396"/>
       <c r="N11" s="23"/>
-      <c r="O11" s="470"/>
+      <c r="O11" s="465"/>
       <c r="P11" s="389" t="s">
-        <v>1610</v>
+        <v>1565</v>
       </c>
       <c r="Q11" s="165"/>
       <c r="R11" s="22"/>
-      <c r="S11" s="470"/>
+      <c r="S11" s="465"/>
       <c r="T11" s="394" t="s">
-        <v>1610</v>
+        <v>1565</v>
       </c>
       <c r="U11" s="397"/>
       <c r="V11" s="24"/>
-      <c r="W11" s="470"/>
+      <c r="W11" s="465"/>
       <c r="X11" s="389" t="s">
-        <v>1610</v>
+        <v>1565</v>
       </c>
       <c r="Y11" s="165"/>
       <c r="Z11" s="22"/>
     </row>
     <row r="12" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="495"/>
-      <c r="B12" s="513"/>
-      <c r="C12" s="475"/>
+      <c r="A12" s="490"/>
+      <c r="B12" s="508"/>
+      <c r="C12" s="470"/>
       <c r="D12" s="25" t="s">
-        <v>1612</v>
+        <v>1567</v>
       </c>
       <c r="E12" s="26"/>
       <c r="F12" s="27"/>
-      <c r="G12" s="475"/>
+      <c r="G12" s="470"/>
       <c r="H12" s="25" t="s">
-        <v>1612</v>
+        <v>1567</v>
       </c>
       <c r="I12" s="26"/>
       <c r="J12" s="27"/>
-      <c r="K12" s="475"/>
+      <c r="K12" s="470"/>
       <c r="L12" s="28" t="s">
-        <v>1612</v>
+        <v>1567</v>
       </c>
       <c r="M12" s="29"/>
       <c r="N12" s="30"/>
-      <c r="O12" s="475"/>
+      <c r="O12" s="470"/>
       <c r="P12" s="25" t="s">
-        <v>1612</v>
+        <v>1567</v>
       </c>
       <c r="Q12" s="26"/>
       <c r="R12" s="27"/>
-      <c r="S12" s="475"/>
+      <c r="S12" s="470"/>
       <c r="T12" s="31" t="s">
-        <v>1612</v>
+        <v>1567</v>
       </c>
       <c r="U12" s="32"/>
       <c r="V12" s="33"/>
-      <c r="W12" s="475"/>
+      <c r="W12" s="470"/>
       <c r="X12" s="25" t="s">
-        <v>1612</v>
+        <v>1567</v>
       </c>
       <c r="Y12" s="26"/>
       <c r="Z12" s="27"/>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A13" s="509" t="s">
+      <c r="A13" s="504" t="s">
         <v>1301</v>
       </c>
-      <c r="B13" s="465" t="s">
-        <v>1621</v>
-      </c>
-      <c r="C13" s="525">
+      <c r="B13" s="460" t="s">
+        <v>1576</v>
+      </c>
+      <c r="C13" s="520">
         <v>100170460</v>
       </c>
       <c r="D13" s="34" t="s">
-        <v>1622</v>
+        <v>1577</v>
       </c>
       <c r="E13" s="35">
         <v>10573076</v>
       </c>
       <c r="F13" s="36"/>
-      <c r="G13" s="511">
+      <c r="G13" s="506">
         <v>10949272</v>
       </c>
       <c r="H13" s="34" t="s">
-        <v>1622</v>
+        <v>1577</v>
       </c>
       <c r="I13" s="35">
         <v>10573076</v>
       </c>
       <c r="J13" s="36"/>
-      <c r="K13" s="511">
+      <c r="K13" s="506">
         <v>10949272</v>
       </c>
       <c r="L13" s="34" t="s">
-        <v>1622</v>
+        <v>1577</v>
       </c>
       <c r="M13" s="35">
         <v>10573076</v>
       </c>
       <c r="N13" s="36"/>
-      <c r="O13" s="525">
+      <c r="O13" s="520">
         <v>100170460</v>
       </c>
       <c r="P13" s="34" t="s">
-        <v>1622</v>
+        <v>1577</v>
       </c>
       <c r="Q13" s="35">
         <v>10573076</v>
       </c>
       <c r="R13" s="36"/>
-      <c r="S13" s="516"/>
+      <c r="S13" s="511"/>
       <c r="T13" s="37" t="s">
-        <v>1622</v>
+        <v>1577</v>
       </c>
       <c r="U13" s="37"/>
       <c r="V13" s="38"/>
-      <c r="W13" s="525"/>
+      <c r="W13" s="520"/>
       <c r="X13" s="34" t="s">
-        <v>1622</v>
+        <v>1577</v>
       </c>
       <c r="Y13" s="34"/>
       <c r="Z13" s="36"/>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A14" s="473"/>
-      <c r="B14" s="484"/>
-      <c r="C14" s="470"/>
+      <c r="A14" s="468"/>
+      <c r="B14" s="479"/>
+      <c r="C14" s="465"/>
       <c r="D14" s="165" t="s">
-        <v>1623</v>
+        <v>1578</v>
       </c>
       <c r="E14" s="7">
         <v>10561136</v>
       </c>
       <c r="F14" s="22"/>
-      <c r="G14" s="470"/>
+      <c r="G14" s="465"/>
       <c r="H14" s="165" t="s">
-        <v>1623</v>
+        <v>1578</v>
       </c>
       <c r="I14" s="7">
         <v>10561136</v>
       </c>
       <c r="J14" s="22"/>
-      <c r="K14" s="470"/>
+      <c r="K14" s="465"/>
       <c r="L14" s="165" t="s">
-        <v>1623</v>
+        <v>1578</v>
       </c>
       <c r="M14" s="7">
         <v>10561136</v>
       </c>
       <c r="N14" s="22"/>
-      <c r="O14" s="470"/>
+      <c r="O14" s="465"/>
       <c r="P14" s="165" t="s">
-        <v>1623</v>
+        <v>1578</v>
       </c>
       <c r="Q14" s="166">
         <v>10561136</v>
       </c>
       <c r="R14" s="22"/>
-      <c r="S14" s="470"/>
+      <c r="S14" s="465"/>
       <c r="T14" s="397" t="s">
-        <v>1623</v>
+        <v>1578</v>
       </c>
       <c r="U14" s="397"/>
       <c r="V14" s="24"/>
-      <c r="W14" s="470"/>
+      <c r="W14" s="465"/>
       <c r="X14" s="165" t="s">
-        <v>1623</v>
+        <v>1578</v>
       </c>
       <c r="Y14" s="165"/>
       <c r="Z14" s="22" t="s">
-        <v>1624</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A15" s="473"/>
-      <c r="B15" s="484"/>
-      <c r="C15" s="470"/>
+      <c r="A15" s="468"/>
+      <c r="B15" s="479"/>
+      <c r="C15" s="465"/>
       <c r="D15" s="165" t="s">
-        <v>1625</v>
+        <v>1580</v>
       </c>
       <c r="E15" s="166" t="s">
-        <v>1626</v>
+        <v>1581</v>
       </c>
       <c r="F15" s="22"/>
-      <c r="G15" s="470"/>
+      <c r="G15" s="465"/>
       <c r="H15" s="165" t="s">
-        <v>1625</v>
+        <v>1580</v>
       </c>
       <c r="I15" s="166" t="s">
-        <v>1626</v>
+        <v>1581</v>
       </c>
       <c r="J15" s="22"/>
-      <c r="K15" s="470"/>
+      <c r="K15" s="465"/>
       <c r="L15" s="165" t="s">
-        <v>1625</v>
+        <v>1580</v>
       </c>
       <c r="M15" s="166" t="s">
-        <v>1626</v>
+        <v>1581</v>
       </c>
       <c r="N15" s="22"/>
-      <c r="O15" s="470"/>
+      <c r="O15" s="465"/>
       <c r="P15" s="165" t="s">
-        <v>1625</v>
+        <v>1580</v>
       </c>
       <c r="Q15" s="7" t="s">
-        <v>1626</v>
+        <v>1581</v>
       </c>
       <c r="R15" s="22"/>
-      <c r="S15" s="470"/>
+      <c r="S15" s="465"/>
       <c r="T15" s="397" t="s">
-        <v>1625</v>
+        <v>1580</v>
       </c>
       <c r="U15" s="397"/>
       <c r="V15" s="24"/>
-      <c r="W15" s="470"/>
+      <c r="W15" s="465"/>
       <c r="X15" s="165" t="s">
-        <v>1625</v>
+        <v>1580</v>
       </c>
       <c r="Y15" s="165"/>
       <c r="Z15" s="22"/>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A16" s="473"/>
-      <c r="B16" s="446"/>
-      <c r="C16" s="471"/>
+      <c r="A16" s="468"/>
+      <c r="B16" s="441"/>
+      <c r="C16" s="466"/>
       <c r="D16" s="165" t="s">
-        <v>1441</v>
+        <v>1396</v>
       </c>
       <c r="E16" s="166">
         <v>102895</v>
       </c>
       <c r="F16" s="22"/>
-      <c r="G16" s="471"/>
+      <c r="G16" s="466"/>
       <c r="H16" s="165" t="s">
-        <v>1441</v>
+        <v>1396</v>
       </c>
       <c r="I16" s="404" t="s">
-        <v>1444</v>
+        <v>1399</v>
       </c>
       <c r="J16" s="40" t="s">
-        <v>1627</v>
-      </c>
-      <c r="K16" s="471"/>
+        <v>1582</v>
+      </c>
+      <c r="K16" s="466"/>
       <c r="L16" s="165" t="s">
-        <v>1441</v>
+        <v>1396</v>
       </c>
       <c r="M16" s="404" t="s">
-        <v>1445</v>
+        <v>1400</v>
       </c>
       <c r="N16" s="40" t="s">
-        <v>1627</v>
-      </c>
-      <c r="O16" s="471"/>
+        <v>1582</v>
+      </c>
+      <c r="O16" s="466"/>
       <c r="P16" s="165" t="s">
-        <v>1441</v>
+        <v>1396</v>
       </c>
       <c r="Q16" s="404" t="s">
-        <v>1628</v>
+        <v>1583</v>
       </c>
       <c r="R16" s="41" t="s">
-        <v>1629</v>
-      </c>
-      <c r="S16" s="471"/>
+        <v>1584</v>
+      </c>
+      <c r="S16" s="466"/>
       <c r="T16" s="397" t="s">
-        <v>1630</v>
+        <v>1585</v>
       </c>
       <c r="U16" s="397"/>
       <c r="V16" s="24"/>
-      <c r="W16" s="471"/>
+      <c r="W16" s="466"/>
       <c r="X16" s="165" t="s">
-        <v>1441</v>
+        <v>1396</v>
       </c>
       <c r="Y16" s="165"/>
       <c r="Z16" s="40" t="s">
-        <v>1627</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="17" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A17" s="473"/>
-      <c r="B17" s="512" t="s">
-        <v>1631</v>
-      </c>
-      <c r="C17" s="476">
+      <c r="A17" s="468"/>
+      <c r="B17" s="507" t="s">
+        <v>1586</v>
+      </c>
+      <c r="C17" s="471">
         <v>100170464</v>
       </c>
       <c r="D17" s="389" t="s">
-        <v>1622</v>
+        <v>1577</v>
       </c>
       <c r="E17" s="405">
         <v>10573076</v>
       </c>
       <c r="F17" s="22"/>
-      <c r="G17" s="496">
+      <c r="G17" s="491">
         <v>10949356</v>
       </c>
       <c r="H17" s="165" t="s">
-        <v>1622</v>
+        <v>1577</v>
       </c>
       <c r="I17" s="405">
         <v>10573076</v>
       </c>
       <c r="J17" s="22"/>
-      <c r="K17" s="496">
+      <c r="K17" s="491">
         <v>10949356</v>
       </c>
       <c r="L17" s="165" t="s">
-        <v>1622</v>
+        <v>1577</v>
       </c>
       <c r="M17" s="405">
         <v>10573076</v>
       </c>
       <c r="N17" s="22"/>
-      <c r="O17" s="476">
+      <c r="O17" s="471">
         <v>100170464</v>
       </c>
       <c r="P17" s="165" t="s">
-        <v>1622</v>
+        <v>1577</v>
       </c>
       <c r="Q17" s="9">
         <v>10573076</v>
       </c>
       <c r="R17" s="22"/>
-      <c r="S17" s="508"/>
+      <c r="S17" s="503"/>
       <c r="T17" s="397" t="s">
-        <v>1622</v>
+        <v>1577</v>
       </c>
       <c r="U17" s="397"/>
       <c r="V17" s="24"/>
-      <c r="W17" s="476"/>
+      <c r="W17" s="471"/>
       <c r="X17" s="165" t="s">
-        <v>1622</v>
+        <v>1577</v>
       </c>
       <c r="Y17" s="165"/>
       <c r="Z17" s="22"/>
     </row>
     <row r="18" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A18" s="473"/>
-      <c r="B18" s="484"/>
-      <c r="C18" s="470"/>
+      <c r="A18" s="468"/>
+      <c r="B18" s="479"/>
+      <c r="C18" s="465"/>
       <c r="D18" s="389" t="s">
-        <v>1623</v>
+        <v>1578</v>
       </c>
       <c r="E18" s="42">
         <v>10572700</v>
       </c>
       <c r="F18" s="22"/>
-      <c r="G18" s="470"/>
+      <c r="G18" s="465"/>
       <c r="H18" s="165" t="s">
-        <v>1623</v>
+        <v>1578</v>
       </c>
       <c r="I18" s="42">
         <v>10572700</v>
       </c>
       <c r="J18" s="22"/>
-      <c r="K18" s="470"/>
+      <c r="K18" s="465"/>
       <c r="L18" s="165" t="s">
-        <v>1623</v>
+        <v>1578</v>
       </c>
       <c r="M18" s="42">
         <v>10572700</v>
       </c>
       <c r="N18" s="22"/>
-      <c r="O18" s="470"/>
+      <c r="O18" s="465"/>
       <c r="P18" s="165" t="s">
-        <v>1623</v>
+        <v>1578</v>
       </c>
       <c r="Q18" s="406">
         <v>10572700</v>
       </c>
       <c r="R18" s="22" t="s">
-        <v>1632</v>
-      </c>
-      <c r="S18" s="470"/>
+        <v>1587</v>
+      </c>
+      <c r="S18" s="465"/>
       <c r="T18" s="397" t="s">
-        <v>1623</v>
+        <v>1578</v>
       </c>
       <c r="U18" s="397"/>
       <c r="V18" s="24"/>
-      <c r="W18" s="470"/>
+      <c r="W18" s="465"/>
       <c r="X18" s="165" t="s">
-        <v>1623</v>
+        <v>1578</v>
       </c>
       <c r="Y18" s="165"/>
       <c r="Z18" s="22"/>
     </row>
     <row r="19" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A19" s="473"/>
-      <c r="B19" s="484"/>
-      <c r="C19" s="470"/>
+      <c r="A19" s="468"/>
+      <c r="B19" s="479"/>
+      <c r="C19" s="465"/>
       <c r="D19" s="389" t="s">
-        <v>1625</v>
+        <v>1580</v>
       </c>
       <c r="E19" s="166" t="s">
-        <v>1633</v>
+        <v>1588</v>
       </c>
       <c r="F19" s="22"/>
-      <c r="G19" s="470"/>
+      <c r="G19" s="465"/>
       <c r="H19" s="165" t="s">
-        <v>1625</v>
+        <v>1580</v>
       </c>
       <c r="I19" s="166" t="s">
-        <v>1633</v>
+        <v>1588</v>
       </c>
       <c r="J19" s="22"/>
-      <c r="K19" s="470"/>
+      <c r="K19" s="465"/>
       <c r="L19" s="165" t="s">
-        <v>1625</v>
+        <v>1580</v>
       </c>
       <c r="M19" s="166" t="s">
-        <v>1633</v>
+        <v>1588</v>
       </c>
       <c r="N19" s="22"/>
-      <c r="O19" s="470"/>
+      <c r="O19" s="465"/>
       <c r="P19" s="165" t="s">
-        <v>1625</v>
+        <v>1580</v>
       </c>
       <c r="Q19" s="404" t="s">
-        <v>1634</v>
+        <v>1589</v>
       </c>
       <c r="R19" s="22" t="s">
-        <v>1635</v>
-      </c>
-      <c r="S19" s="470"/>
+        <v>1590</v>
+      </c>
+      <c r="S19" s="465"/>
       <c r="T19" s="397" t="s">
-        <v>1625</v>
+        <v>1580</v>
       </c>
       <c r="U19" s="407" t="s">
-        <v>1633</v>
+        <v>1588</v>
       </c>
       <c r="V19" s="24"/>
-      <c r="W19" s="470"/>
+      <c r="W19" s="465"/>
       <c r="X19" s="165" t="s">
-        <v>1625</v>
+        <v>1580</v>
       </c>
       <c r="Y19" s="166" t="s">
-        <v>1633</v>
+        <v>1588</v>
       </c>
       <c r="Z19" s="22"/>
     </row>
     <row r="20" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A20" s="473"/>
-      <c r="B20" s="513"/>
-      <c r="C20" s="471"/>
+      <c r="A20" s="468"/>
+      <c r="B20" s="508"/>
+      <c r="C20" s="466"/>
       <c r="D20" s="165" t="s">
-        <v>1441</v>
+        <v>1396</v>
       </c>
       <c r="E20" s="7">
         <v>102895</v>
       </c>
       <c r="F20" s="22"/>
-      <c r="G20" s="471"/>
+      <c r="G20" s="466"/>
       <c r="H20" s="165" t="s">
-        <v>1441</v>
+        <v>1396</v>
       </c>
       <c r="I20" s="404" t="s">
-        <v>1444</v>
+        <v>1399</v>
       </c>
       <c r="J20" s="40" t="s">
-        <v>1627</v>
-      </c>
-      <c r="K20" s="471"/>
+        <v>1582</v>
+      </c>
+      <c r="K20" s="466"/>
       <c r="L20" s="165" t="s">
-        <v>1441</v>
+        <v>1396</v>
       </c>
       <c r="M20" s="404" t="s">
-        <v>1445</v>
+        <v>1400</v>
       </c>
       <c r="N20" s="40" t="s">
-        <v>1627</v>
-      </c>
-      <c r="O20" s="471"/>
+        <v>1582</v>
+      </c>
+      <c r="O20" s="466"/>
       <c r="P20" s="165" t="s">
-        <v>1441</v>
+        <v>1396</v>
       </c>
       <c r="Q20" s="408">
         <v>102895</v>
       </c>
       <c r="R20" s="22"/>
-      <c r="S20" s="471"/>
+      <c r="S20" s="466"/>
       <c r="T20" s="397" t="s">
-        <v>1441</v>
+        <v>1396</v>
       </c>
       <c r="U20" s="397"/>
       <c r="V20" s="24"/>
-      <c r="W20" s="471"/>
+      <c r="W20" s="466"/>
       <c r="X20" s="165" t="s">
-        <v>1441</v>
+        <v>1396</v>
       </c>
       <c r="Y20" s="165"/>
       <c r="Z20" s="40" t="s">
-        <v>1627</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="21" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A21" s="473"/>
-      <c r="B21" s="512" t="s">
-        <v>1636</v>
-      </c>
-      <c r="C21" s="476" t="s">
-        <v>1637</v>
+      <c r="A21" s="468"/>
+      <c r="B21" s="507" t="s">
+        <v>1591</v>
+      </c>
+      <c r="C21" s="471" t="s">
+        <v>1592</v>
       </c>
       <c r="D21" s="389" t="s">
-        <v>1622</v>
+        <v>1577</v>
       </c>
       <c r="E21" s="396"/>
       <c r="F21" s="23"/>
-      <c r="G21" s="476" t="s">
-        <v>1637</v>
+      <c r="G21" s="471" t="s">
+        <v>1592</v>
       </c>
       <c r="H21" s="165" t="s">
-        <v>1622</v>
+        <v>1577</v>
       </c>
       <c r="I21" s="396"/>
       <c r="J21" s="23"/>
-      <c r="K21" s="476" t="s">
-        <v>1637</v>
+      <c r="K21" s="471" t="s">
+        <v>1592</v>
       </c>
       <c r="L21" s="165" t="s">
-        <v>1622</v>
+        <v>1577</v>
       </c>
       <c r="M21" s="396"/>
       <c r="N21" s="23"/>
-      <c r="O21" s="496">
+      <c r="O21" s="491">
         <v>10851208</v>
       </c>
       <c r="P21" s="165" t="s">
-        <v>1622</v>
+        <v>1577</v>
       </c>
       <c r="Q21" s="166">
         <v>10573076</v>
       </c>
       <c r="R21" s="22"/>
-      <c r="S21" s="508"/>
+      <c r="S21" s="503"/>
       <c r="T21" s="397" t="s">
-        <v>1622</v>
+        <v>1577</v>
       </c>
       <c r="U21" s="397"/>
       <c r="V21" s="24"/>
-      <c r="W21" s="476"/>
+      <c r="W21" s="471"/>
       <c r="X21" s="165" t="s">
-        <v>1622</v>
+        <v>1577</v>
       </c>
       <c r="Y21" s="396"/>
       <c r="Z21" s="23"/>
     </row>
     <row r="22" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A22" s="473"/>
-      <c r="B22" s="484"/>
-      <c r="C22" s="470"/>
+      <c r="A22" s="468"/>
+      <c r="B22" s="479"/>
+      <c r="C22" s="465"/>
       <c r="D22" s="389" t="s">
-        <v>1623</v>
+        <v>1578</v>
       </c>
       <c r="E22" s="396"/>
       <c r="F22" s="23"/>
-      <c r="G22" s="470"/>
+      <c r="G22" s="465"/>
       <c r="H22" s="165" t="s">
-        <v>1623</v>
+        <v>1578</v>
       </c>
       <c r="I22" s="396"/>
       <c r="J22" s="23"/>
-      <c r="K22" s="470"/>
+      <c r="K22" s="465"/>
       <c r="L22" s="165" t="s">
-        <v>1623</v>
+        <v>1578</v>
       </c>
       <c r="M22" s="396"/>
       <c r="N22" s="23"/>
-      <c r="O22" s="470"/>
+      <c r="O22" s="465"/>
       <c r="P22" s="165" t="s">
-        <v>1623</v>
+        <v>1578</v>
       </c>
       <c r="Q22" s="166">
         <v>10882275</v>
       </c>
       <c r="R22" s="22" t="s">
-        <v>1638</v>
-      </c>
-      <c r="S22" s="470"/>
+        <v>1593</v>
+      </c>
+      <c r="S22" s="465"/>
       <c r="T22" s="397" t="s">
-        <v>1623</v>
+        <v>1578</v>
       </c>
       <c r="U22" s="397"/>
       <c r="V22" s="24"/>
-      <c r="W22" s="470"/>
+      <c r="W22" s="465"/>
       <c r="X22" s="165" t="s">
-        <v>1623</v>
+        <v>1578</v>
       </c>
       <c r="Y22" s="396"/>
       <c r="Z22" s="23"/>
     </row>
     <row r="23" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A23" s="473"/>
-      <c r="B23" s="484"/>
-      <c r="C23" s="470"/>
+      <c r="A23" s="468"/>
+      <c r="B23" s="479"/>
+      <c r="C23" s="465"/>
       <c r="D23" s="389" t="s">
-        <v>1625</v>
+        <v>1580</v>
       </c>
       <c r="E23" s="396"/>
       <c r="F23" s="23"/>
-      <c r="G23" s="470"/>
+      <c r="G23" s="465"/>
       <c r="H23" s="165" t="s">
-        <v>1625</v>
+        <v>1580</v>
       </c>
       <c r="I23" s="396"/>
       <c r="J23" s="23"/>
-      <c r="K23" s="470"/>
+      <c r="K23" s="465"/>
       <c r="L23" s="165" t="s">
-        <v>1625</v>
+        <v>1580</v>
       </c>
       <c r="M23" s="396"/>
       <c r="N23" s="23"/>
-      <c r="O23" s="470"/>
+      <c r="O23" s="465"/>
       <c r="P23" s="165" t="s">
-        <v>1625</v>
+        <v>1580</v>
       </c>
       <c r="Q23" s="166" t="s">
-        <v>1639</v>
+        <v>1594</v>
       </c>
       <c r="R23" s="22"/>
-      <c r="S23" s="470"/>
+      <c r="S23" s="465"/>
       <c r="T23" s="397" t="s">
-        <v>1625</v>
+        <v>1580</v>
       </c>
       <c r="U23" s="397"/>
       <c r="V23" s="24"/>
-      <c r="W23" s="470"/>
+      <c r="W23" s="465"/>
       <c r="X23" s="165" t="s">
-        <v>1625</v>
+        <v>1580</v>
       </c>
       <c r="Y23" s="396"/>
       <c r="Z23" s="23"/>
     </row>
     <row r="24" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A24" s="473"/>
-      <c r="B24" s="513"/>
-      <c r="C24" s="471"/>
+      <c r="A24" s="468"/>
+      <c r="B24" s="508"/>
+      <c r="C24" s="466"/>
       <c r="D24" s="389" t="s">
-        <v>1630</v>
+        <v>1585</v>
       </c>
       <c r="E24" s="396"/>
       <c r="F24" s="23"/>
-      <c r="G24" s="471"/>
+      <c r="G24" s="466"/>
       <c r="H24" s="165" t="s">
-        <v>1630</v>
+        <v>1585</v>
       </c>
       <c r="I24" s="396"/>
       <c r="J24" s="23"/>
-      <c r="K24" s="471"/>
+      <c r="K24" s="466"/>
       <c r="L24" s="165" t="s">
-        <v>1630</v>
+        <v>1585</v>
       </c>
       <c r="M24" s="396"/>
       <c r="N24" s="23"/>
-      <c r="O24" s="471"/>
+      <c r="O24" s="466"/>
       <c r="P24" s="165" t="s">
-        <v>1441</v>
+        <v>1396</v>
       </c>
       <c r="Q24" s="404" t="s">
-        <v>1628</v>
+        <v>1583</v>
       </c>
       <c r="R24" s="41" t="s">
-        <v>1640</v>
-      </c>
-      <c r="S24" s="471"/>
+        <v>1595</v>
+      </c>
+      <c r="S24" s="466"/>
       <c r="T24" s="397" t="s">
-        <v>1630</v>
+        <v>1585</v>
       </c>
       <c r="U24" s="397"/>
       <c r="V24" s="24"/>
-      <c r="W24" s="471"/>
+      <c r="W24" s="466"/>
       <c r="X24" s="165" t="s">
-        <v>1630</v>
+        <v>1585</v>
       </c>
       <c r="Y24" s="396"/>
       <c r="Z24" s="23"/>
     </row>
     <row r="25" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A25" s="473"/>
-      <c r="B25" s="512" t="s">
-        <v>1641</v>
-      </c>
-      <c r="C25" s="476" t="s">
-        <v>1637</v>
+      <c r="A25" s="468"/>
+      <c r="B25" s="507" t="s">
+        <v>1596</v>
+      </c>
+      <c r="C25" s="471" t="s">
+        <v>1592</v>
       </c>
       <c r="D25" s="389" t="s">
-        <v>1622</v>
+        <v>1577</v>
       </c>
       <c r="E25" s="396"/>
       <c r="F25" s="23"/>
-      <c r="G25" s="476" t="s">
-        <v>1637</v>
+      <c r="G25" s="471" t="s">
+        <v>1592</v>
       </c>
       <c r="H25" s="165" t="s">
-        <v>1622</v>
+        <v>1577</v>
       </c>
       <c r="I25" s="396"/>
       <c r="J25" s="23"/>
-      <c r="K25" s="476" t="s">
-        <v>1637</v>
+      <c r="K25" s="471" t="s">
+        <v>1592</v>
       </c>
       <c r="L25" s="165" t="s">
-        <v>1622</v>
+        <v>1577</v>
       </c>
       <c r="M25" s="396"/>
       <c r="N25" s="23"/>
-      <c r="O25" s="526"/>
+      <c r="O25" s="521"/>
       <c r="P25" s="396" t="s">
-        <v>1622</v>
+        <v>1577</v>
       </c>
       <c r="Q25" s="396"/>
       <c r="R25" s="23"/>
-      <c r="S25" s="523"/>
+      <c r="S25" s="518"/>
       <c r="T25" s="397" t="s">
-        <v>1622</v>
+        <v>1577</v>
       </c>
       <c r="U25" s="397"/>
       <c r="V25" s="24"/>
-      <c r="W25" s="474"/>
+      <c r="W25" s="469"/>
       <c r="X25" s="165" t="s">
-        <v>1622</v>
+        <v>1577</v>
       </c>
       <c r="Y25" s="396"/>
       <c r="Z25" s="23"/>
     </row>
     <row r="26" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A26" s="473"/>
-      <c r="B26" s="484"/>
-      <c r="C26" s="470"/>
+      <c r="A26" s="468"/>
+      <c r="B26" s="479"/>
+      <c r="C26" s="465"/>
       <c r="D26" s="389" t="s">
-        <v>1623</v>
+        <v>1578</v>
       </c>
       <c r="E26" s="396"/>
       <c r="F26" s="23"/>
-      <c r="G26" s="470"/>
+      <c r="G26" s="465"/>
       <c r="H26" s="165" t="s">
-        <v>1623</v>
+        <v>1578</v>
       </c>
       <c r="I26" s="396"/>
       <c r="J26" s="23"/>
-      <c r="K26" s="470"/>
+      <c r="K26" s="465"/>
       <c r="L26" s="165" t="s">
-        <v>1623</v>
+        <v>1578</v>
       </c>
       <c r="M26" s="396"/>
       <c r="N26" s="23"/>
-      <c r="O26" s="470"/>
+      <c r="O26" s="465"/>
       <c r="P26" s="396" t="s">
-        <v>1623</v>
+        <v>1578</v>
       </c>
       <c r="Q26" s="396"/>
       <c r="R26" s="23"/>
-      <c r="S26" s="470"/>
+      <c r="S26" s="465"/>
       <c r="T26" s="397" t="s">
-        <v>1623</v>
+        <v>1578</v>
       </c>
       <c r="U26" s="397"/>
       <c r="V26" s="24"/>
-      <c r="W26" s="470"/>
+      <c r="W26" s="465"/>
       <c r="X26" s="165" t="s">
-        <v>1623</v>
+        <v>1578</v>
       </c>
       <c r="Y26" s="396"/>
       <c r="Z26" s="23"/>
     </row>
     <row r="27" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A27" s="473"/>
-      <c r="B27" s="484"/>
-      <c r="C27" s="470"/>
+      <c r="A27" s="468"/>
+      <c r="B27" s="479"/>
+      <c r="C27" s="465"/>
       <c r="D27" s="389" t="s">
-        <v>1625</v>
+        <v>1580</v>
       </c>
       <c r="E27" s="396"/>
       <c r="F27" s="23"/>
-      <c r="G27" s="470"/>
+      <c r="G27" s="465"/>
       <c r="H27" s="165" t="s">
-        <v>1625</v>
+        <v>1580</v>
       </c>
       <c r="I27" s="396"/>
       <c r="J27" s="23"/>
-      <c r="K27" s="470"/>
+      <c r="K27" s="465"/>
       <c r="L27" s="165" t="s">
-        <v>1625</v>
+        <v>1580</v>
       </c>
       <c r="M27" s="396"/>
       <c r="N27" s="23"/>
-      <c r="O27" s="470"/>
+      <c r="O27" s="465"/>
       <c r="P27" s="396" t="s">
-        <v>1625</v>
+        <v>1580</v>
       </c>
       <c r="Q27" s="396"/>
       <c r="R27" s="23"/>
-      <c r="S27" s="470"/>
+      <c r="S27" s="465"/>
       <c r="T27" s="397" t="s">
-        <v>1625</v>
+        <v>1580</v>
       </c>
       <c r="U27" s="397"/>
       <c r="V27" s="24"/>
-      <c r="W27" s="470"/>
+      <c r="W27" s="465"/>
       <c r="X27" s="165" t="s">
-        <v>1625</v>
+        <v>1580</v>
       </c>
       <c r="Y27" s="396"/>
       <c r="Z27" s="23"/>
     </row>
     <row r="28" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="510"/>
-      <c r="B28" s="513"/>
-      <c r="C28" s="471"/>
+      <c r="A28" s="505"/>
+      <c r="B28" s="508"/>
+      <c r="C28" s="466"/>
       <c r="D28" s="25" t="s">
-        <v>1630</v>
+        <v>1585</v>
       </c>
       <c r="E28" s="29"/>
       <c r="F28" s="30"/>
-      <c r="G28" s="471"/>
+      <c r="G28" s="466"/>
       <c r="H28" s="26" t="s">
-        <v>1630</v>
+        <v>1585</v>
       </c>
       <c r="I28" s="29"/>
       <c r="J28" s="30"/>
-      <c r="K28" s="471"/>
+      <c r="K28" s="466"/>
       <c r="L28" s="26" t="s">
-        <v>1630</v>
+        <v>1585</v>
       </c>
       <c r="M28" s="29"/>
       <c r="N28" s="30"/>
-      <c r="O28" s="475"/>
+      <c r="O28" s="470"/>
       <c r="P28" s="29" t="s">
-        <v>1441</v>
+        <v>1396</v>
       </c>
       <c r="Q28" s="29"/>
       <c r="R28" s="30"/>
-      <c r="S28" s="475"/>
+      <c r="S28" s="470"/>
       <c r="T28" s="32" t="s">
-        <v>1630</v>
+        <v>1585</v>
       </c>
       <c r="U28" s="32"/>
       <c r="V28" s="33"/>
-      <c r="W28" s="475"/>
+      <c r="W28" s="470"/>
       <c r="X28" s="26" t="s">
-        <v>1630</v>
+        <v>1585</v>
       </c>
       <c r="Y28" s="29"/>
       <c r="Z28" s="30"/>
     </row>
     <row r="29" spans="1:26" ht="101.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="494" t="s">
-        <v>1642</v>
-      </c>
-      <c r="B29" s="494" t="s">
-        <v>1643</v>
+      <c r="A29" s="489" t="s">
+        <v>1597</v>
+      </c>
+      <c r="B29" s="489" t="s">
+        <v>1598</v>
       </c>
       <c r="C29" s="44"/>
       <c r="D29" s="45" t="s">
-        <v>1644</v>
+        <v>1599</v>
       </c>
       <c r="E29" s="34" t="s">
-        <v>1448</v>
+        <v>1403</v>
       </c>
       <c r="F29" s="36"/>
       <c r="G29" s="44"/>
       <c r="H29" s="45" t="s">
-        <v>1644</v>
+        <v>1599</v>
       </c>
       <c r="I29" s="34" t="s">
-        <v>1448</v>
+        <v>1403</v>
       </c>
       <c r="J29" s="36"/>
       <c r="K29" s="44"/>
       <c r="L29" s="45" t="s">
-        <v>1644</v>
-      </c>
-      <c r="M29" s="520" t="s">
-        <v>1645</v>
-      </c>
-      <c r="N29" s="504"/>
+        <v>1599</v>
+      </c>
+      <c r="M29" s="515" t="s">
+        <v>1600</v>
+      </c>
+      <c r="N29" s="499"/>
       <c r="O29" s="44"/>
       <c r="P29" s="45" t="s">
-        <v>1644</v>
+        <v>1599</v>
       </c>
       <c r="Q29" s="34" t="s">
-        <v>1448</v>
+        <v>1403</v>
       </c>
       <c r="R29" s="36"/>
       <c r="S29" s="44"/>
       <c r="T29" s="45" t="s">
-        <v>1644</v>
+        <v>1599</v>
       </c>
       <c r="U29" s="34" t="s">
-        <v>1448</v>
+        <v>1403</v>
       </c>
       <c r="V29" s="36"/>
       <c r="W29" s="46"/>
       <c r="X29" s="45" t="s">
-        <v>1644</v>
+        <v>1599</v>
       </c>
       <c r="Y29" s="34" t="s">
-        <v>1646</v>
+        <v>1601</v>
       </c>
       <c r="Z29" s="47" t="s">
-        <v>1647</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="30" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A30" s="473"/>
-      <c r="B30" s="473"/>
+      <c r="A30" s="468"/>
+      <c r="B30" s="468"/>
       <c r="C30" s="48"/>
       <c r="D30" s="409" t="s">
-        <v>1648</v>
+        <v>1603</v>
       </c>
       <c r="E30" s="165" t="s">
-        <v>1454</v>
+        <v>1409</v>
       </c>
       <c r="F30" s="22"/>
       <c r="G30" s="48"/>
       <c r="H30" s="409" t="s">
-        <v>1648</v>
+        <v>1603</v>
       </c>
       <c r="I30" s="165" t="s">
-        <v>1454</v>
+        <v>1409</v>
       </c>
       <c r="J30" s="22"/>
       <c r="K30" s="48"/>
       <c r="L30" s="409" t="s">
-        <v>1648</v>
-      </c>
-      <c r="M30" s="521"/>
-      <c r="N30" s="485"/>
+        <v>1603</v>
+      </c>
+      <c r="M30" s="516"/>
+      <c r="N30" s="480"/>
       <c r="O30" s="48"/>
       <c r="P30" s="409" t="s">
-        <v>1648</v>
+        <v>1603</v>
       </c>
       <c r="Q30" s="165" t="s">
-        <v>1454</v>
+        <v>1409</v>
       </c>
       <c r="R30" s="22"/>
       <c r="S30" s="48"/>
       <c r="T30" s="409" t="s">
-        <v>1648</v>
+        <v>1603</v>
       </c>
       <c r="U30" s="165" t="s">
-        <v>1454</v>
+        <v>1409</v>
       </c>
       <c r="V30" s="22"/>
       <c r="W30" s="298"/>
       <c r="X30" s="409" t="s">
-        <v>1648</v>
+        <v>1603</v>
       </c>
       <c r="Y30" s="165" t="s">
-        <v>1649</v>
+        <v>1604</v>
       </c>
       <c r="Z30" s="22"/>
     </row>
     <row r="31" spans="1:26" ht="144.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="473"/>
-      <c r="B31" s="495"/>
+      <c r="A31" s="468"/>
+      <c r="B31" s="490"/>
       <c r="C31" s="48"/>
       <c r="D31" s="410" t="s">
-        <v>1650</v>
+        <v>1605</v>
       </c>
       <c r="E31" s="398" t="s">
-        <v>1651</v>
+        <v>1606</v>
       </c>
       <c r="F31" s="22"/>
       <c r="G31" s="48"/>
       <c r="H31" s="410" t="s">
-        <v>1650</v>
+        <v>1605</v>
       </c>
       <c r="I31" s="411" t="s">
-        <v>1652</v>
+        <v>1607</v>
       </c>
       <c r="J31" s="49" t="s">
-        <v>1653</v>
+        <v>1608</v>
       </c>
       <c r="K31" s="48"/>
       <c r="L31" s="410" t="s">
-        <v>1650</v>
-      </c>
-      <c r="M31" s="521"/>
-      <c r="N31" s="485"/>
+        <v>1605</v>
+      </c>
+      <c r="M31" s="516"/>
+      <c r="N31" s="480"/>
       <c r="O31" s="48"/>
       <c r="P31" s="410" t="s">
-        <v>1650</v>
+        <v>1605</v>
       </c>
       <c r="Q31" s="343" t="s">
-        <v>1651</v>
+        <v>1606</v>
       </c>
       <c r="R31" s="22"/>
       <c r="S31" s="48"/>
       <c r="T31" s="410" t="s">
-        <v>1650</v>
+        <v>1605</v>
       </c>
       <c r="U31" s="343" t="s">
-        <v>1651</v>
+        <v>1606</v>
       </c>
       <c r="V31" s="22"/>
       <c r="W31" s="298"/>
       <c r="X31" s="410" t="s">
-        <v>1650</v>
+        <v>1605</v>
       </c>
       <c r="Y31" s="412" t="s">
-        <v>1652</v>
+        <v>1607</v>
       </c>
       <c r="Z31" s="50" t="s">
-        <v>1653</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="32" spans="1:26" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="473"/>
+      <c r="A32" s="468"/>
       <c r="B32" s="16" t="s">
-        <v>1654</v>
+        <v>1609</v>
       </c>
       <c r="C32" s="48"/>
       <c r="D32" s="410" t="s">
-        <v>1502</v>
+        <v>1457</v>
       </c>
       <c r="E32" s="398" t="s">
-        <v>1501</v>
+        <v>1456</v>
       </c>
       <c r="F32" s="22"/>
       <c r="G32" s="48"/>
       <c r="H32" s="410" t="s">
-        <v>1502</v>
+        <v>1457</v>
       </c>
       <c r="I32" s="413" t="s">
-        <v>1503</v>
+        <v>1458</v>
       </c>
       <c r="J32" s="41" t="s">
-        <v>1655</v>
+        <v>1610</v>
       </c>
       <c r="K32" s="48"/>
       <c r="L32" s="410" t="s">
-        <v>1502</v>
-      </c>
-      <c r="M32" s="521"/>
-      <c r="N32" s="485"/>
+        <v>1457</v>
+      </c>
+      <c r="M32" s="516"/>
+      <c r="N32" s="480"/>
       <c r="O32" s="48"/>
       <c r="P32" s="410" t="s">
-        <v>1502</v>
+        <v>1457</v>
       </c>
       <c r="Q32" s="398" t="s">
-        <v>1501</v>
+        <v>1456</v>
       </c>
       <c r="R32" s="22"/>
       <c r="S32" s="48"/>
       <c r="T32" s="410" t="s">
-        <v>1502</v>
+        <v>1457</v>
       </c>
       <c r="U32" s="398" t="s">
-        <v>1501</v>
+        <v>1456</v>
       </c>
       <c r="V32" s="22"/>
       <c r="W32" s="298"/>
       <c r="X32" s="410" t="s">
-        <v>1502</v>
+        <v>1457</v>
       </c>
       <c r="Y32" s="165" t="s">
-        <v>1503</v>
+        <v>1458</v>
       </c>
       <c r="Z32" s="41" t="s">
-        <v>1655</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="33" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A33" s="473"/>
+      <c r="A33" s="468"/>
       <c r="B33" s="402" t="s">
-        <v>1656</v>
+        <v>1611</v>
       </c>
       <c r="C33" s="48"/>
       <c r="D33" s="409" t="s">
-        <v>1504</v>
+        <v>1459</v>
       </c>
       <c r="E33" s="165" t="s">
-        <v>1505</v>
+        <v>1460</v>
       </c>
       <c r="F33" s="22"/>
       <c r="G33" s="48"/>
       <c r="H33" s="409" t="s">
-        <v>1504</v>
+        <v>1459</v>
       </c>
       <c r="I33" s="165" t="s">
-        <v>1505</v>
+        <v>1460</v>
       </c>
       <c r="J33" s="22"/>
       <c r="K33" s="48"/>
       <c r="L33" s="409" t="s">
-        <v>1657</v>
-      </c>
-      <c r="M33" s="521"/>
-      <c r="N33" s="485"/>
+        <v>1612</v>
+      </c>
+      <c r="M33" s="516"/>
+      <c r="N33" s="480"/>
       <c r="O33" s="48"/>
       <c r="P33" s="409" t="s">
-        <v>1504</v>
+        <v>1459</v>
       </c>
       <c r="Q33" s="165" t="s">
-        <v>1505</v>
+        <v>1460</v>
       </c>
       <c r="R33" s="22"/>
       <c r="S33" s="48"/>
       <c r="T33" s="409" t="s">
-        <v>1504</v>
+        <v>1459</v>
       </c>
       <c r="U33" s="165" t="s">
-        <v>1505</v>
+        <v>1460</v>
       </c>
       <c r="V33" s="22"/>
       <c r="W33" s="298"/>
       <c r="X33" s="409" t="s">
-        <v>1504</v>
+        <v>1459</v>
       </c>
       <c r="Y33" s="165" t="s">
-        <v>1505</v>
+        <v>1460</v>
       </c>
       <c r="Z33" s="22"/>
     </row>
     <row r="34" spans="1:26" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="473"/>
-      <c r="B34" s="472" t="s">
-        <v>1658</v>
+      <c r="A34" s="468"/>
+      <c r="B34" s="467" t="s">
+        <v>1613</v>
       </c>
       <c r="C34" s="48"/>
       <c r="D34" s="409" t="s">
-        <v>1659</v>
+        <v>1614</v>
       </c>
       <c r="E34" s="165" t="s">
-        <v>1518</v>
+        <v>1473</v>
       </c>
       <c r="F34" s="22"/>
       <c r="G34" s="48"/>
       <c r="H34" s="409" t="s">
-        <v>1659</v>
+        <v>1614</v>
       </c>
       <c r="I34" s="413" t="s">
-        <v>1520</v>
-      </c>
-      <c r="J34" s="514" t="s">
-        <v>1653</v>
+        <v>1475</v>
+      </c>
+      <c r="J34" s="509" t="s">
+        <v>1608</v>
       </c>
       <c r="K34" s="48"/>
       <c r="L34" s="409" t="s">
-        <v>1659</v>
-      </c>
-      <c r="M34" s="521"/>
-      <c r="N34" s="485"/>
+        <v>1614</v>
+      </c>
+      <c r="M34" s="516"/>
+      <c r="N34" s="480"/>
       <c r="O34" s="48"/>
       <c r="P34" s="409" t="s">
-        <v>1659</v>
+        <v>1614</v>
       </c>
       <c r="Q34" s="165" t="s">
-        <v>1518</v>
+        <v>1473</v>
       </c>
       <c r="R34" s="22"/>
       <c r="S34" s="48"/>
       <c r="T34" s="409" t="s">
-        <v>1659</v>
+        <v>1614</v>
       </c>
       <c r="U34" s="165" t="s">
-        <v>1518</v>
+        <v>1473</v>
       </c>
       <c r="V34" s="22"/>
       <c r="W34" s="298"/>
       <c r="X34" s="409" t="s">
-        <v>1659</v>
+        <v>1614</v>
       </c>
       <c r="Y34" s="165" t="s">
-        <v>1520</v>
-      </c>
-      <c r="Z34" s="514" t="s">
-        <v>1653</v>
+        <v>1475</v>
+      </c>
+      <c r="Z34" s="509" t="s">
+        <v>1608</v>
       </c>
     </row>
     <row r="35" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A35" s="473"/>
-      <c r="B35" s="473"/>
+      <c r="A35" s="468"/>
+      <c r="B35" s="468"/>
       <c r="C35" s="48"/>
       <c r="D35" s="409" t="s">
-        <v>1660</v>
+        <v>1615</v>
       </c>
       <c r="E35" s="165" t="s">
-        <v>1515</v>
+        <v>1470</v>
       </c>
       <c r="F35" s="22"/>
       <c r="G35" s="48"/>
       <c r="H35" s="409" t="s">
-        <v>1660</v>
+        <v>1615</v>
       </c>
       <c r="I35" s="413" t="s">
-        <v>1516</v>
-      </c>
-      <c r="J35" s="515"/>
+        <v>1471</v>
+      </c>
+      <c r="J35" s="510"/>
       <c r="K35" s="48"/>
       <c r="L35" s="409" t="s">
-        <v>1660</v>
-      </c>
-      <c r="M35" s="521"/>
-      <c r="N35" s="485"/>
+        <v>1615</v>
+      </c>
+      <c r="M35" s="516"/>
+      <c r="N35" s="480"/>
       <c r="O35" s="48"/>
       <c r="P35" s="409" t="s">
-        <v>1660</v>
+        <v>1615</v>
       </c>
       <c r="Q35" s="165" t="s">
-        <v>1515</v>
+        <v>1470</v>
       </c>
       <c r="R35" s="22"/>
       <c r="S35" s="48"/>
       <c r="T35" s="409" t="s">
-        <v>1660</v>
+        <v>1615</v>
       </c>
       <c r="U35" s="165" t="s">
-        <v>1515</v>
+        <v>1470</v>
       </c>
       <c r="V35" s="22"/>
       <c r="W35" s="298"/>
       <c r="X35" s="409" t="s">
-        <v>1660</v>
+        <v>1615</v>
       </c>
       <c r="Y35" s="165" t="s">
-        <v>1516</v>
-      </c>
-      <c r="Z35" s="515"/>
+        <v>1471</v>
+      </c>
+      <c r="Z35" s="510"/>
     </row>
     <row r="36" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="495"/>
-      <c r="B36" s="473"/>
+      <c r="A36" s="490"/>
+      <c r="B36" s="468"/>
       <c r="C36" s="51"/>
       <c r="D36" s="414" t="s">
-        <v>1661</v>
+        <v>1616</v>
       </c>
       <c r="E36" s="167" t="s">
-        <v>1522</v>
+        <v>1477</v>
       </c>
       <c r="F36" s="52"/>
       <c r="G36" s="51"/>
       <c r="H36" s="414" t="s">
-        <v>1661</v>
+        <v>1616</v>
       </c>
       <c r="I36" s="415" t="s">
-        <v>1525</v>
-      </c>
-      <c r="J36" s="515"/>
+        <v>1480</v>
+      </c>
+      <c r="J36" s="510"/>
       <c r="K36" s="51"/>
       <c r="L36" s="414" t="s">
-        <v>1661</v>
-      </c>
-      <c r="M36" s="522"/>
-      <c r="N36" s="488"/>
+        <v>1616</v>
+      </c>
+      <c r="M36" s="517"/>
+      <c r="N36" s="483"/>
       <c r="O36" s="51"/>
       <c r="P36" s="414" t="s">
-        <v>1661</v>
+        <v>1616</v>
       </c>
       <c r="Q36" s="167" t="s">
-        <v>1522</v>
+        <v>1477</v>
       </c>
       <c r="R36" s="52"/>
       <c r="S36" s="51"/>
       <c r="T36" s="414" t="s">
-        <v>1661</v>
+        <v>1616</v>
       </c>
       <c r="U36" s="167" t="s">
-        <v>1522</v>
+        <v>1477</v>
       </c>
       <c r="V36" s="52"/>
       <c r="W36" s="375"/>
       <c r="X36" s="414" t="s">
-        <v>1661</v>
+        <v>1616</v>
       </c>
       <c r="Y36" s="167" t="s">
-        <v>1525</v>
-      </c>
-      <c r="Z36" s="515"/>
+        <v>1480</v>
+      </c>
+      <c r="Z36" s="510"/>
     </row>
     <row r="37" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="39" t="s">
-        <v>1662</v>
+        <v>1617</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>1663</v>
-      </c>
-      <c r="C37" s="479" t="s">
-        <v>1637</v>
-      </c>
-      <c r="D37" s="467"/>
-      <c r="E37" s="467"/>
-      <c r="F37" s="468"/>
-      <c r="G37" s="479" t="s">
-        <v>1637</v>
-      </c>
-      <c r="H37" s="467"/>
-      <c r="I37" s="467"/>
-      <c r="J37" s="468"/>
-      <c r="K37" s="490" t="s">
-        <v>1664</v>
-      </c>
-      <c r="L37" s="467"/>
-      <c r="M37" s="467"/>
-      <c r="N37" s="468"/>
-      <c r="O37" s="490" t="s">
-        <v>1665</v>
-      </c>
-      <c r="P37" s="467"/>
-      <c r="Q37" s="467"/>
-      <c r="R37" s="468"/>
-      <c r="S37" s="490" t="s">
-        <v>1666</v>
-      </c>
-      <c r="T37" s="467"/>
-      <c r="U37" s="467"/>
-      <c r="V37" s="468"/>
-      <c r="W37" s="490" t="s">
-        <v>1666</v>
-      </c>
-      <c r="X37" s="467"/>
-      <c r="Y37" s="467"/>
-      <c r="Z37" s="468"/>
+        <v>1618</v>
+      </c>
+      <c r="C37" s="474" t="s">
+        <v>1592</v>
+      </c>
+      <c r="D37" s="462"/>
+      <c r="E37" s="462"/>
+      <c r="F37" s="463"/>
+      <c r="G37" s="474" t="s">
+        <v>1592</v>
+      </c>
+      <c r="H37" s="462"/>
+      <c r="I37" s="462"/>
+      <c r="J37" s="463"/>
+      <c r="K37" s="485" t="s">
+        <v>1619</v>
+      </c>
+      <c r="L37" s="462"/>
+      <c r="M37" s="462"/>
+      <c r="N37" s="463"/>
+      <c r="O37" s="485" t="s">
+        <v>1620</v>
+      </c>
+      <c r="P37" s="462"/>
+      <c r="Q37" s="462"/>
+      <c r="R37" s="463"/>
+      <c r="S37" s="485" t="s">
+        <v>1621</v>
+      </c>
+      <c r="T37" s="462"/>
+      <c r="U37" s="462"/>
+      <c r="V37" s="463"/>
+      <c r="W37" s="485" t="s">
+        <v>1621</v>
+      </c>
+      <c r="X37" s="462"/>
+      <c r="Y37" s="462"/>
+      <c r="Z37" s="463"/>
     </row>
     <row r="38" spans="1:26" ht="87" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="494" t="s">
-        <v>1620</v>
-      </c>
-      <c r="B38" s="465" t="s">
-        <v>1667</v>
+      <c r="A38" s="489" t="s">
+        <v>1575</v>
+      </c>
+      <c r="B38" s="460" t="s">
+        <v>1622</v>
       </c>
       <c r="C38" s="44"/>
       <c r="D38" s="53" t="s">
-        <v>1668</v>
+        <v>1623</v>
       </c>
       <c r="E38" s="54" t="s">
-        <v>1669</v>
+        <v>1624</v>
       </c>
       <c r="F38" s="36"/>
       <c r="G38" s="44"/>
       <c r="H38" s="53" t="s">
-        <v>1668</v>
+        <v>1623</v>
       </c>
       <c r="I38" s="54" t="s">
-        <v>1669</v>
+        <v>1624</v>
       </c>
       <c r="J38" s="36"/>
       <c r="K38" s="44"/>
       <c r="L38" s="53" t="s">
-        <v>1668</v>
+        <v>1623</v>
       </c>
       <c r="M38" s="34"/>
       <c r="N38" s="36"/>
       <c r="O38" s="44"/>
       <c r="P38" s="53" t="s">
-        <v>1668</v>
+        <v>1623</v>
       </c>
       <c r="Q38" s="54" t="s">
-        <v>1669</v>
+        <v>1624</v>
       </c>
       <c r="R38" s="36"/>
       <c r="S38" s="44"/>
       <c r="T38" s="53" t="s">
-        <v>1668</v>
+        <v>1623</v>
       </c>
       <c r="U38" s="54" t="s">
-        <v>1669</v>
+        <v>1624</v>
       </c>
       <c r="V38" s="36"/>
       <c r="W38" s="44"/>
       <c r="X38" s="53" t="s">
-        <v>1668</v>
+        <v>1623</v>
       </c>
       <c r="Y38" s="34"/>
       <c r="Z38" s="36"/>
     </row>
     <row r="39" spans="1:26" ht="101.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="473"/>
-      <c r="B39" s="446"/>
+      <c r="A39" s="468"/>
+      <c r="B39" s="441"/>
       <c r="C39" s="48"/>
       <c r="D39" s="389" t="s">
-        <v>1670</v>
+        <v>1625</v>
       </c>
       <c r="E39" s="398" t="s">
-        <v>1671</v>
+        <v>1626</v>
       </c>
       <c r="F39" s="22"/>
       <c r="G39" s="48"/>
       <c r="H39" s="389" t="s">
-        <v>1670</v>
+        <v>1625</v>
       </c>
       <c r="I39" s="398" t="s">
-        <v>1671</v>
+        <v>1626</v>
       </c>
       <c r="J39" s="22"/>
       <c r="K39" s="48"/>
       <c r="L39" s="389" t="s">
-        <v>1670</v>
+        <v>1625</v>
       </c>
       <c r="M39" s="165"/>
       <c r="N39" s="22"/>
       <c r="O39" s="48"/>
       <c r="P39" s="389" t="s">
-        <v>1670</v>
+        <v>1625</v>
       </c>
       <c r="Q39" s="398" t="s">
-        <v>1671</v>
+        <v>1626</v>
       </c>
       <c r="R39" s="22"/>
       <c r="S39" s="48"/>
       <c r="T39" s="389" t="s">
-        <v>1670</v>
+        <v>1625</v>
       </c>
       <c r="U39" s="398" t="s">
-        <v>1671</v>
+        <v>1626</v>
       </c>
       <c r="V39" s="22"/>
       <c r="W39" s="48"/>
       <c r="X39" s="389" t="s">
-        <v>1670</v>
+        <v>1625</v>
       </c>
       <c r="Y39" s="165"/>
       <c r="Z39" s="22"/>
     </row>
     <row r="40" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A40" s="473"/>
-      <c r="B40" s="489" t="s">
-        <v>1672</v>
+      <c r="A40" s="468"/>
+      <c r="B40" s="484" t="s">
+        <v>1627</v>
       </c>
       <c r="C40" s="48"/>
       <c r="D40" s="389" t="s">
-        <v>1673</v>
+        <v>1628</v>
       </c>
       <c r="E40" s="416" t="s">
-        <v>1674</v>
+        <v>1629</v>
       </c>
       <c r="F40" s="22"/>
       <c r="G40" s="48"/>
       <c r="H40" s="389" t="s">
-        <v>1673</v>
+        <v>1628</v>
       </c>
       <c r="I40" s="416" t="s">
-        <v>1674</v>
+        <v>1629</v>
       </c>
       <c r="J40" s="22"/>
       <c r="K40" s="48"/>
       <c r="L40" s="389" t="s">
-        <v>1673</v>
+        <v>1628</v>
       </c>
       <c r="M40" s="165"/>
       <c r="N40" s="22"/>
       <c r="O40" s="48"/>
       <c r="P40" s="389" t="s">
-        <v>1673</v>
+        <v>1628</v>
       </c>
       <c r="Q40" s="416" t="s">
-        <v>1674</v>
+        <v>1629</v>
       </c>
       <c r="R40" s="22"/>
       <c r="S40" s="48"/>
       <c r="T40" s="389" t="s">
-        <v>1673</v>
+        <v>1628</v>
       </c>
       <c r="U40" s="416" t="s">
-        <v>1674</v>
+        <v>1629</v>
       </c>
       <c r="V40" s="22"/>
       <c r="W40" s="48"/>
       <c r="X40" s="389" t="s">
-        <v>1673</v>
+        <v>1628</v>
       </c>
       <c r="Y40" s="165"/>
       <c r="Z40" s="22"/>
     </row>
     <row r="41" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A41" s="473"/>
-      <c r="B41" s="483"/>
+      <c r="A41" s="468"/>
+      <c r="B41" s="478"/>
       <c r="C41" s="48"/>
       <c r="D41" s="389" t="s">
-        <v>1675</v>
+        <v>1630</v>
       </c>
       <c r="E41" s="165" t="s">
-        <v>1676</v>
+        <v>1631</v>
       </c>
       <c r="F41" s="22"/>
       <c r="G41" s="48"/>
       <c r="H41" s="389" t="s">
-        <v>1675</v>
+        <v>1630</v>
       </c>
       <c r="I41" s="165" t="s">
-        <v>1676</v>
+        <v>1631</v>
       </c>
       <c r="J41" s="22"/>
       <c r="K41" s="48"/>
       <c r="L41" s="389" t="s">
-        <v>1675</v>
+        <v>1630</v>
       </c>
       <c r="M41" s="165"/>
       <c r="N41" s="22"/>
       <c r="O41" s="48"/>
       <c r="P41" s="389" t="s">
-        <v>1675</v>
+        <v>1630</v>
       </c>
       <c r="Q41" s="165" t="s">
-        <v>1676</v>
+        <v>1631</v>
       </c>
       <c r="R41" s="22"/>
       <c r="S41" s="48"/>
       <c r="T41" s="389" t="s">
-        <v>1675</v>
+        <v>1630</v>
       </c>
       <c r="U41" s="165" t="s">
-        <v>1676</v>
+        <v>1631</v>
       </c>
       <c r="V41" s="22"/>
       <c r="W41" s="48"/>
       <c r="X41" s="389" t="s">
-        <v>1675</v>
+        <v>1630</v>
       </c>
       <c r="Y41" s="165"/>
       <c r="Z41" s="22"/>
     </row>
     <row r="42" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="495"/>
-      <c r="B42" s="486"/>
+      <c r="A42" s="490"/>
+      <c r="B42" s="481"/>
       <c r="C42" s="51"/>
       <c r="D42" s="417" t="s">
-        <v>1677</v>
+        <v>1632</v>
       </c>
       <c r="E42" s="167" t="s">
-        <v>1678</v>
+        <v>1633</v>
       </c>
       <c r="F42" s="27" t="s">
-        <v>1679</v>
+        <v>1634</v>
       </c>
       <c r="G42" s="55"/>
       <c r="H42" s="25" t="s">
-        <v>1677</v>
+        <v>1632</v>
       </c>
       <c r="I42" s="167" t="s">
-        <v>1678</v>
+        <v>1633</v>
       </c>
       <c r="J42" s="27" t="s">
-        <v>1679</v>
+        <v>1634</v>
       </c>
       <c r="K42" s="55"/>
       <c r="L42" s="25" t="s">
-        <v>1677</v>
+        <v>1632</v>
       </c>
       <c r="M42" s="26" t="s">
-        <v>1680</v>
+        <v>1635</v>
       </c>
       <c r="N42" s="27" t="s">
-        <v>1681</v>
+        <v>1636</v>
       </c>
       <c r="O42" s="55"/>
       <c r="P42" s="25" t="s">
-        <v>1677</v>
+        <v>1632</v>
       </c>
       <c r="Q42" s="167" t="s">
-        <v>1678</v>
+        <v>1633</v>
       </c>
       <c r="R42" s="27" t="s">
-        <v>1679</v>
+        <v>1634</v>
       </c>
       <c r="S42" s="55"/>
       <c r="T42" s="25" t="s">
-        <v>1677</v>
+        <v>1632</v>
       </c>
       <c r="U42" s="26" t="s">
-        <v>1680</v>
+        <v>1635</v>
       </c>
       <c r="V42" s="27" t="s">
-        <v>1681</v>
+        <v>1636</v>
       </c>
       <c r="W42" s="55"/>
       <c r="X42" s="25" t="s">
-        <v>1677</v>
+        <v>1632</v>
       </c>
       <c r="Y42" s="26" t="s">
-        <v>1680</v>
+        <v>1635</v>
       </c>
       <c r="Z42" s="27" t="s">
-        <v>1681</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="43" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A43" s="494" t="s">
-        <v>1682</v>
-      </c>
-      <c r="B43" s="465" t="s">
+      <c r="A43" s="489" t="s">
+        <v>1637</v>
+      </c>
+      <c r="B43" s="460" t="s">
         <v>601</v>
       </c>
-      <c r="C43" s="502" t="s">
-        <v>1683</v>
-      </c>
-      <c r="D43" s="503"/>
-      <c r="E43" s="503"/>
-      <c r="F43" s="504"/>
-      <c r="G43" s="502" t="s">
-        <v>1683</v>
-      </c>
-      <c r="H43" s="503"/>
-      <c r="I43" s="503"/>
-      <c r="J43" s="504"/>
-      <c r="K43" s="502" t="s">
-        <v>1684</v>
-      </c>
-      <c r="L43" s="503"/>
-      <c r="M43" s="503"/>
-      <c r="N43" s="504"/>
-      <c r="O43" s="502" t="s">
-        <v>1683</v>
-      </c>
-      <c r="P43" s="503"/>
-      <c r="Q43" s="503"/>
-      <c r="R43" s="504"/>
-      <c r="S43" s="502" t="s">
-        <v>1683</v>
-      </c>
-      <c r="T43" s="503"/>
-      <c r="U43" s="503"/>
-      <c r="V43" s="504"/>
-      <c r="W43" s="502" t="s">
-        <v>1684</v>
-      </c>
-      <c r="X43" s="503"/>
-      <c r="Y43" s="503"/>
-      <c r="Z43" s="504"/>
+      <c r="C43" s="497" t="s">
+        <v>1638</v>
+      </c>
+      <c r="D43" s="498"/>
+      <c r="E43" s="498"/>
+      <c r="F43" s="499"/>
+      <c r="G43" s="497" t="s">
+        <v>1638</v>
+      </c>
+      <c r="H43" s="498"/>
+      <c r="I43" s="498"/>
+      <c r="J43" s="499"/>
+      <c r="K43" s="497" t="s">
+        <v>1639</v>
+      </c>
+      <c r="L43" s="498"/>
+      <c r="M43" s="498"/>
+      <c r="N43" s="499"/>
+      <c r="O43" s="497" t="s">
+        <v>1638</v>
+      </c>
+      <c r="P43" s="498"/>
+      <c r="Q43" s="498"/>
+      <c r="R43" s="499"/>
+      <c r="S43" s="497" t="s">
+        <v>1638</v>
+      </c>
+      <c r="T43" s="498"/>
+      <c r="U43" s="498"/>
+      <c r="V43" s="499"/>
+      <c r="W43" s="497" t="s">
+        <v>1639</v>
+      </c>
+      <c r="X43" s="498"/>
+      <c r="Y43" s="498"/>
+      <c r="Z43" s="499"/>
     </row>
     <row r="44" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A44" s="473"/>
-      <c r="B44" s="446"/>
-      <c r="C44" s="505"/>
-      <c r="D44" s="446"/>
-      <c r="E44" s="446"/>
-      <c r="F44" s="506"/>
-      <c r="G44" s="505"/>
-      <c r="H44" s="446"/>
-      <c r="I44" s="446"/>
-      <c r="J44" s="506"/>
-      <c r="K44" s="505"/>
-      <c r="L44" s="446"/>
-      <c r="M44" s="446"/>
-      <c r="N44" s="506"/>
-      <c r="O44" s="505"/>
-      <c r="P44" s="446"/>
-      <c r="Q44" s="446"/>
-      <c r="R44" s="506"/>
-      <c r="S44" s="505"/>
-      <c r="T44" s="446"/>
-      <c r="U44" s="446"/>
-      <c r="V44" s="506"/>
-      <c r="W44" s="505"/>
-      <c r="X44" s="446"/>
-      <c r="Y44" s="446"/>
-      <c r="Z44" s="506"/>
+      <c r="A44" s="468"/>
+      <c r="B44" s="441"/>
+      <c r="C44" s="500"/>
+      <c r="D44" s="441"/>
+      <c r="E44" s="441"/>
+      <c r="F44" s="501"/>
+      <c r="G44" s="500"/>
+      <c r="H44" s="441"/>
+      <c r="I44" s="441"/>
+      <c r="J44" s="501"/>
+      <c r="K44" s="500"/>
+      <c r="L44" s="441"/>
+      <c r="M44" s="441"/>
+      <c r="N44" s="501"/>
+      <c r="O44" s="500"/>
+      <c r="P44" s="441"/>
+      <c r="Q44" s="441"/>
+      <c r="R44" s="501"/>
+      <c r="S44" s="500"/>
+      <c r="T44" s="441"/>
+      <c r="U44" s="441"/>
+      <c r="V44" s="501"/>
+      <c r="W44" s="500"/>
+      <c r="X44" s="441"/>
+      <c r="Y44" s="441"/>
+      <c r="Z44" s="501"/>
     </row>
     <row r="45" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A45" s="473"/>
-      <c r="B45" s="489" t="s">
-        <v>1685</v>
-      </c>
-      <c r="C45" s="480" t="s">
-        <v>1686</v>
-      </c>
-      <c r="D45" s="481"/>
-      <c r="E45" s="481"/>
-      <c r="F45" s="482"/>
-      <c r="G45" s="480" t="s">
-        <v>1686</v>
-      </c>
-      <c r="H45" s="481"/>
-      <c r="I45" s="481"/>
-      <c r="J45" s="482"/>
-      <c r="K45" s="517" t="s">
-        <v>1687</v>
-      </c>
-      <c r="L45" s="481"/>
-      <c r="M45" s="481"/>
-      <c r="N45" s="482"/>
-      <c r="O45" s="480" t="s">
-        <v>1686</v>
-      </c>
-      <c r="P45" s="481"/>
-      <c r="Q45" s="481"/>
-      <c r="R45" s="482"/>
-      <c r="S45" s="480" t="s">
-        <v>1686</v>
-      </c>
-      <c r="T45" s="481"/>
-      <c r="U45" s="481"/>
-      <c r="V45" s="482"/>
-      <c r="W45" s="517" t="s">
-        <v>1688</v>
-      </c>
-      <c r="X45" s="481"/>
-      <c r="Y45" s="481"/>
-      <c r="Z45" s="482"/>
+      <c r="A45" s="468"/>
+      <c r="B45" s="484" t="s">
+        <v>1640</v>
+      </c>
+      <c r="C45" s="475" t="s">
+        <v>1641</v>
+      </c>
+      <c r="D45" s="476"/>
+      <c r="E45" s="476"/>
+      <c r="F45" s="477"/>
+      <c r="G45" s="475" t="s">
+        <v>1641</v>
+      </c>
+      <c r="H45" s="476"/>
+      <c r="I45" s="476"/>
+      <c r="J45" s="477"/>
+      <c r="K45" s="512" t="s">
+        <v>1642</v>
+      </c>
+      <c r="L45" s="476"/>
+      <c r="M45" s="476"/>
+      <c r="N45" s="477"/>
+      <c r="O45" s="475" t="s">
+        <v>1641</v>
+      </c>
+      <c r="P45" s="476"/>
+      <c r="Q45" s="476"/>
+      <c r="R45" s="477"/>
+      <c r="S45" s="475" t="s">
+        <v>1641</v>
+      </c>
+      <c r="T45" s="476"/>
+      <c r="U45" s="476"/>
+      <c r="V45" s="477"/>
+      <c r="W45" s="512" t="s">
+        <v>1643</v>
+      </c>
+      <c r="X45" s="476"/>
+      <c r="Y45" s="476"/>
+      <c r="Z45" s="477"/>
     </row>
     <row r="46" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A46" s="473"/>
-      <c r="B46" s="483"/>
-      <c r="C46" s="483"/>
-      <c r="D46" s="484"/>
-      <c r="E46" s="484"/>
-      <c r="F46" s="485"/>
-      <c r="G46" s="483"/>
-      <c r="H46" s="484"/>
-      <c r="I46" s="484"/>
-      <c r="J46" s="485"/>
-      <c r="K46" s="483"/>
-      <c r="L46" s="484"/>
-      <c r="M46" s="484"/>
-      <c r="N46" s="485"/>
-      <c r="O46" s="483"/>
-      <c r="P46" s="484"/>
-      <c r="Q46" s="484"/>
-      <c r="R46" s="485"/>
-      <c r="S46" s="483"/>
-      <c r="T46" s="484"/>
-      <c r="U46" s="484"/>
-      <c r="V46" s="485"/>
-      <c r="W46" s="483"/>
-      <c r="X46" s="484"/>
-      <c r="Y46" s="484"/>
-      <c r="Z46" s="485"/>
+      <c r="A46" s="468"/>
+      <c r="B46" s="478"/>
+      <c r="C46" s="478"/>
+      <c r="D46" s="479"/>
+      <c r="E46" s="479"/>
+      <c r="F46" s="480"/>
+      <c r="G46" s="478"/>
+      <c r="H46" s="479"/>
+      <c r="I46" s="479"/>
+      <c r="J46" s="480"/>
+      <c r="K46" s="478"/>
+      <c r="L46" s="479"/>
+      <c r="M46" s="479"/>
+      <c r="N46" s="480"/>
+      <c r="O46" s="478"/>
+      <c r="P46" s="479"/>
+      <c r="Q46" s="479"/>
+      <c r="R46" s="480"/>
+      <c r="S46" s="478"/>
+      <c r="T46" s="479"/>
+      <c r="U46" s="479"/>
+      <c r="V46" s="480"/>
+      <c r="W46" s="478"/>
+      <c r="X46" s="479"/>
+      <c r="Y46" s="479"/>
+      <c r="Z46" s="480"/>
     </row>
     <row r="47" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="495"/>
-      <c r="B47" s="486"/>
-      <c r="C47" s="486"/>
-      <c r="D47" s="487"/>
-      <c r="E47" s="487"/>
-      <c r="F47" s="488"/>
-      <c r="G47" s="486"/>
-      <c r="H47" s="487"/>
-      <c r="I47" s="487"/>
-      <c r="J47" s="488"/>
-      <c r="K47" s="486"/>
-      <c r="L47" s="487"/>
-      <c r="M47" s="487"/>
-      <c r="N47" s="488"/>
-      <c r="O47" s="486"/>
-      <c r="P47" s="487"/>
-      <c r="Q47" s="487"/>
-      <c r="R47" s="488"/>
-      <c r="S47" s="486"/>
-      <c r="T47" s="487"/>
-      <c r="U47" s="487"/>
-      <c r="V47" s="488"/>
-      <c r="W47" s="486"/>
-      <c r="X47" s="487"/>
-      <c r="Y47" s="487"/>
-      <c r="Z47" s="488"/>
+      <c r="A47" s="490"/>
+      <c r="B47" s="481"/>
+      <c r="C47" s="481"/>
+      <c r="D47" s="482"/>
+      <c r="E47" s="482"/>
+      <c r="F47" s="483"/>
+      <c r="G47" s="481"/>
+      <c r="H47" s="482"/>
+      <c r="I47" s="482"/>
+      <c r="J47" s="483"/>
+      <c r="K47" s="481"/>
+      <c r="L47" s="482"/>
+      <c r="M47" s="482"/>
+      <c r="N47" s="483"/>
+      <c r="O47" s="481"/>
+      <c r="P47" s="482"/>
+      <c r="Q47" s="482"/>
+      <c r="R47" s="483"/>
+      <c r="S47" s="481"/>
+      <c r="T47" s="482"/>
+      <c r="U47" s="482"/>
+      <c r="V47" s="483"/>
+      <c r="W47" s="481"/>
+      <c r="X47" s="482"/>
+      <c r="Y47" s="482"/>
+      <c r="Z47" s="483"/>
     </row>
     <row r="48" spans="1:26" ht="29.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="56" t="s">
-        <v>1689</v>
+        <v>1644</v>
       </c>
       <c r="B48" s="57" t="s">
-        <v>1663</v>
-      </c>
-      <c r="C48" s="518" t="s">
-        <v>1690</v>
-      </c>
-      <c r="D48" s="467"/>
-      <c r="E48" s="467"/>
-      <c r="F48" s="468"/>
-      <c r="G48" s="518" t="s">
-        <v>1690</v>
-      </c>
-      <c r="H48" s="467"/>
-      <c r="I48" s="467"/>
-      <c r="J48" s="468"/>
-      <c r="K48" s="466" t="s">
-        <v>1691</v>
-      </c>
-      <c r="L48" s="467"/>
-      <c r="M48" s="467"/>
-      <c r="N48" s="468"/>
-      <c r="O48" s="518" t="s">
-        <v>1690</v>
-      </c>
-      <c r="P48" s="467"/>
-      <c r="Q48" s="467"/>
-      <c r="R48" s="468"/>
-      <c r="S48" s="518" t="s">
-        <v>1690</v>
-      </c>
-      <c r="T48" s="467"/>
-      <c r="U48" s="467"/>
-      <c r="V48" s="468"/>
-      <c r="W48" s="478" t="s">
-        <v>1692</v>
-      </c>
-      <c r="X48" s="467"/>
-      <c r="Y48" s="467"/>
-      <c r="Z48" s="468"/>
+        <v>1618</v>
+      </c>
+      <c r="C48" s="513" t="s">
+        <v>1645</v>
+      </c>
+      <c r="D48" s="462"/>
+      <c r="E48" s="462"/>
+      <c r="F48" s="463"/>
+      <c r="G48" s="513" t="s">
+        <v>1645</v>
+      </c>
+      <c r="H48" s="462"/>
+      <c r="I48" s="462"/>
+      <c r="J48" s="463"/>
+      <c r="K48" s="461" t="s">
+        <v>1646</v>
+      </c>
+      <c r="L48" s="462"/>
+      <c r="M48" s="462"/>
+      <c r="N48" s="463"/>
+      <c r="O48" s="513" t="s">
+        <v>1645</v>
+      </c>
+      <c r="P48" s="462"/>
+      <c r="Q48" s="462"/>
+      <c r="R48" s="463"/>
+      <c r="S48" s="513" t="s">
+        <v>1645</v>
+      </c>
+      <c r="T48" s="462"/>
+      <c r="U48" s="462"/>
+      <c r="V48" s="463"/>
+      <c r="W48" s="473" t="s">
+        <v>1647</v>
+      </c>
+      <c r="X48" s="462"/>
+      <c r="Y48" s="462"/>
+      <c r="Z48" s="463"/>
     </row>
     <row r="49" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="509" t="s">
-        <v>1693</v>
+      <c r="A49" s="504" t="s">
+        <v>1648</v>
       </c>
       <c r="B49" s="58" t="s">
-        <v>1694</v>
-      </c>
-      <c r="C49" s="502" t="s">
-        <v>1695</v>
-      </c>
-      <c r="D49" s="452"/>
-      <c r="E49" s="452"/>
-      <c r="F49" s="493"/>
-      <c r="G49" s="492" t="s">
-        <v>1696</v>
-      </c>
-      <c r="H49" s="452"/>
-      <c r="I49" s="452"/>
-      <c r="J49" s="493"/>
-      <c r="K49" s="492" t="s">
-        <v>1697</v>
-      </c>
-      <c r="L49" s="452"/>
-      <c r="M49" s="452"/>
-      <c r="N49" s="493"/>
-      <c r="O49" s="502" t="s">
-        <v>1695</v>
-      </c>
-      <c r="P49" s="452"/>
-      <c r="Q49" s="452"/>
-      <c r="R49" s="493"/>
-      <c r="S49" s="502" t="s">
-        <v>1695</v>
-      </c>
-      <c r="T49" s="452"/>
-      <c r="U49" s="452"/>
-      <c r="V49" s="493"/>
-      <c r="W49" s="492" t="s">
-        <v>1696</v>
-      </c>
-      <c r="X49" s="452"/>
-      <c r="Y49" s="452"/>
-      <c r="Z49" s="493"/>
+        <v>1649</v>
+      </c>
+      <c r="C49" s="497" t="s">
+        <v>1650</v>
+      </c>
+      <c r="D49" s="447"/>
+      <c r="E49" s="447"/>
+      <c r="F49" s="488"/>
+      <c r="G49" s="487" t="s">
+        <v>1651</v>
+      </c>
+      <c r="H49" s="447"/>
+      <c r="I49" s="447"/>
+      <c r="J49" s="488"/>
+      <c r="K49" s="487" t="s">
+        <v>1652</v>
+      </c>
+      <c r="L49" s="447"/>
+      <c r="M49" s="447"/>
+      <c r="N49" s="488"/>
+      <c r="O49" s="497" t="s">
+        <v>1650</v>
+      </c>
+      <c r="P49" s="447"/>
+      <c r="Q49" s="447"/>
+      <c r="R49" s="488"/>
+      <c r="S49" s="497" t="s">
+        <v>1650</v>
+      </c>
+      <c r="T49" s="447"/>
+      <c r="U49" s="447"/>
+      <c r="V49" s="488"/>
+      <c r="W49" s="487" t="s">
+        <v>1651</v>
+      </c>
+      <c r="X49" s="447"/>
+      <c r="Y49" s="447"/>
+      <c r="Z49" s="488"/>
     </row>
     <row r="50" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="510"/>
+      <c r="A50" s="505"/>
       <c r="B50" s="43" t="s">
-        <v>1698</v>
-      </c>
-      <c r="C50" s="499" t="s">
-        <v>1699</v>
-      </c>
-      <c r="D50" s="487"/>
-      <c r="E50" s="487"/>
-      <c r="F50" s="488"/>
-      <c r="G50" s="519" t="s">
-        <v>1699</v>
-      </c>
-      <c r="H50" s="487"/>
-      <c r="I50" s="487"/>
-      <c r="J50" s="488"/>
-      <c r="K50" s="519" t="s">
-        <v>1700</v>
-      </c>
-      <c r="L50" s="487"/>
-      <c r="M50" s="487"/>
-      <c r="N50" s="488"/>
-      <c r="O50" s="499" t="s">
-        <v>1699</v>
-      </c>
-      <c r="P50" s="487"/>
-      <c r="Q50" s="487"/>
-      <c r="R50" s="488"/>
-      <c r="S50" s="499" t="s">
-        <v>1699</v>
-      </c>
-      <c r="T50" s="487"/>
-      <c r="U50" s="487"/>
-      <c r="V50" s="488"/>
-      <c r="W50" s="499" t="s">
-        <v>1637</v>
-      </c>
-      <c r="X50" s="487"/>
-      <c r="Y50" s="487"/>
-      <c r="Z50" s="488"/>
+        <v>1653</v>
+      </c>
+      <c r="C50" s="494" t="s">
+        <v>1654</v>
+      </c>
+      <c r="D50" s="482"/>
+      <c r="E50" s="482"/>
+      <c r="F50" s="483"/>
+      <c r="G50" s="514" t="s">
+        <v>1654</v>
+      </c>
+      <c r="H50" s="482"/>
+      <c r="I50" s="482"/>
+      <c r="J50" s="483"/>
+      <c r="K50" s="514" t="s">
+        <v>1655</v>
+      </c>
+      <c r="L50" s="482"/>
+      <c r="M50" s="482"/>
+      <c r="N50" s="483"/>
+      <c r="O50" s="494" t="s">
+        <v>1654</v>
+      </c>
+      <c r="P50" s="482"/>
+      <c r="Q50" s="482"/>
+      <c r="R50" s="483"/>
+      <c r="S50" s="494" t="s">
+        <v>1654</v>
+      </c>
+      <c r="T50" s="482"/>
+      <c r="U50" s="482"/>
+      <c r="V50" s="483"/>
+      <c r="W50" s="494" t="s">
+        <v>1592</v>
+      </c>
+      <c r="X50" s="482"/>
+      <c r="Y50" s="482"/>
+      <c r="Z50" s="483"/>
     </row>
   </sheetData>
   <mergeCells count="100">
@@ -16423,10 +15773,10 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="418" t="s">
-        <v>1701</v>
+        <v>1656</v>
       </c>
       <c r="B2" s="418" t="s">
-        <v>1701</v>
+        <v>1656</v>
       </c>
       <c r="C2" s="179"/>
       <c r="D2" s="419"/>
@@ -16454,7 +15804,7 @@
     </row>
     <row r="4" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="59" t="s">
-        <v>1702</v>
+        <v>1657</v>
       </c>
       <c r="B4" s="9">
         <f ca="1">MATCH($D3, INDIRECT("'" &amp; $C3 &amp; "'!$B:$B"), 0)</f>
@@ -16475,7 +15825,7 @@
     </row>
     <row r="5" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="59" t="s">
-        <v>1703</v>
+        <v>1658</v>
       </c>
       <c r="B5" s="9">
         <f ca="1">MATCH(F$1,INDIRECT("'"&amp;$C3&amp;"'!$1:$1"),0)</f>
@@ -16493,7 +15843,7 @@
     </row>
     <row r="6" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="59" t="s">
-        <v>1704</v>
+        <v>1659</v>
       </c>
       <c r="B6" s="9" t="str">
         <f ca="1">ADDRESS(MATCH($D3,INDIRECT("'"&amp;$C3&amp;"'!$B:$B"),0),MATCH(F$1,INDIRECT("'"&amp;$C3&amp;"'!$1:$1"),0))</f>
@@ -16511,7 +15861,7 @@
     </row>
     <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="59" t="s">
-        <v>1705</v>
+        <v>1660</v>
       </c>
       <c r="B7" s="9" t="str">
         <f ca="1">CONCATENATE("'" &amp; $C3 &amp; "'!",ADDRESS(MATCH($D3, INDIRECT("'" &amp; $C3 &amp; "'!$B:$B"), 0),MATCH(F$1, INDIRECT("'" &amp; $C3 &amp; "'!$1:$1"), 0)))</f>
@@ -16529,7 +15879,7 @@
     </row>
     <row r="8" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="59" t="s">
-        <v>1706</v>
+        <v>1661</v>
       </c>
       <c r="B8" s="214" t="str">
         <f t="array" aca="1" ref="B8" ca="1">INDIRECT(CONCATENATE("'"&amp;$C3&amp;"'!",ADDRESS(MATCH($D3,INDIRECT("'"&amp;$C3&amp;"'!$B:$B"),0),MATCH(F$1,INDIRECT("'"&amp;$C3&amp;"'!$1:$1"),0))))</f>
@@ -16547,7 +15897,7 @@
     </row>
     <row r="9" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="59" t="s">
-        <v>1707</v>
+        <v>1662</v>
       </c>
       <c r="B9" s="214" t="str">
         <f>MID($D3,1,FIND("_",$D3)-1)</f>
@@ -16565,7 +15915,7 @@
     </row>
     <row r="10" spans="1:7" ht="165" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="59" t="s">
-        <v>1708</v>
+        <v>1663</v>
       </c>
       <c r="B10" s="215" t="str">
         <f t="array" aca="1" ref="B10" ca="1">CONCATENATE(Cartelle!$D$5,F$1,"/",$C3,"/",MID($D3,1,FIND("_",$D3)-1),"/",INDIRECT(CONCATENATE("'" &amp; $C3 &amp; "'!",ADDRESS(MATCH($D3, INDIRECT("'" &amp; $C3 &amp; "'!$B:$B"), 0),MATCH(F$1, INDIRECT("'" &amp; $C3 &amp; "'!$1:$1"), 0)))),".pdf#page=",F4)</f>
@@ -16589,7 +15939,7 @@
     </row>
     <row r="12" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="59" t="s">
-        <v>1709</v>
+        <v>1664</v>
       </c>
       <c r="B12" s="216" t="str">
         <f t="array" aca="1" ref="B12" ca="1">INDIRECT(CONCATENATE("'"&amp;$C7&amp;"'!",ADDRESS(MATCH($D3,INDIRECT("'"&amp;$C3&amp;"'!$B:$B"),0),3)))</f>
@@ -16611,7 +15961,7 @@
     </row>
     <row r="13" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="59" t="s">
-        <v>1710</v>
+        <v>1665</v>
       </c>
       <c r="B13" s="215" t="str">
         <f t="array" aca="1" ref="B13" ca="1">CONCATENATE(Cartelle!$D$5,F$1,"/",$C12,"/",MID($D12,1,FIND("_",$D12)-1),"/",INDIRECT(CONCATENATE("'" &amp; $C12 &amp; "'!",ADDRESS(MATCH($D12, INDIRECT("'" &amp; $C12 &amp; "'!$B:$B"), 0),MATCH(F$1, INDIRECT("'" &amp; $C12 &amp; "'!$1:$1"), 0)))),".",INDIRECT(CONCATENATE("'"&amp;$C12&amp;"'!",ADDRESS(MATCH($D12,INDIRECT("'"&amp;$C12&amp;"'!$B:$B"),0),3))),"#page=",F13)</f>
@@ -16623,14 +15973,14 @@
     </row>
     <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="219" t="s">
-        <v>1711</v>
+        <v>1666</v>
       </c>
       <c r="B14" s="220"/>
       <c r="C14" s="338" t="s">
         <v>25</v>
       </c>
       <c r="D14" s="338" t="s">
-        <v>1712</v>
+        <v>1667</v>
       </c>
       <c r="E14" s="339" t="s">
         <v>18</v>
@@ -16647,14 +15997,14 @@
     </row>
     <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="219" t="s">
-        <v>1711</v>
+        <v>1666</v>
       </c>
       <c r="B17" s="220"/>
       <c r="C17" s="338" t="s">
         <v>25</v>
       </c>
       <c r="D17" s="338" t="s">
-        <v>1712</v>
+        <v>1667</v>
       </c>
       <c r="E17" s="339" t="s">
         <v>18</v>
@@ -16671,10 +16021,10 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="418" t="s">
-        <v>1701</v>
+        <v>1656</v>
       </c>
       <c r="B19" s="418" t="s">
-        <v>1701</v>
+        <v>1656</v>
       </c>
       <c r="C19" s="179"/>
       <c r="D19" s="419"/>
@@ -16684,7 +16034,7 @@
     </row>
     <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="62" t="s">
-        <v>1713</v>
+        <v>1668</v>
       </c>
       <c r="B20" s="86" t="str">
         <f ca="1">ADDRESS(MATCH($D20, INDIRECT("'" &amp; $C20 &amp; "'!$B:$B"), 0),MATCH(G$1, INDIRECT("'" &amp; $C20 &amp; "'!$1:$1"), 0))</f>
@@ -16707,7 +16057,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="59" t="s">
-        <v>1714</v>
+        <v>1669</v>
       </c>
       <c r="B21" s="9" t="str">
         <f t="array" aca="1" ref="B21" ca="1">INDIRECT(CONCATENATE("'" &amp; $C20 &amp; "'!",ADDRESS(MATCH($D20, INDIRECT("'" &amp; $C20 &amp; "'!$B:$B"), 0),MATCH(G$1, INDIRECT("'" &amp; $C20 &amp; "'!$1:$1"), 0))))</f>
@@ -16815,7 +16165,7 @@
         <v>29</v>
       </c>
       <c r="C31" s="332" t="s">
-        <v>1715</v>
+        <v>1670</v>
       </c>
       <c r="D31" s="344" t="s">
         <v>341</v>
@@ -16842,118 +16192,118 @@
     <row r="1" spans="2:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C2" s="1" t="s">
-        <v>1716</v>
+        <v>1671</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>1717</v>
+        <v>1672</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>1718</v>
+        <v>1673</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>1719</v>
+        <v>1674</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>1720</v>
+        <v>1675</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>1178</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>1721</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="3" spans="2:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
-        <v>1722</v>
+        <v>1677</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="254" t="s">
-        <v>1723</v>
+        <v>1678</v>
       </c>
       <c r="E3" s="254" t="s">
-        <v>1723</v>
+        <v>1678</v>
       </c>
       <c r="F3" s="254" t="s">
-        <v>1723</v>
+        <v>1678</v>
       </c>
       <c r="G3" s="254"/>
       <c r="H3" s="254" t="s">
-        <v>1723</v>
+        <v>1678</v>
       </c>
       <c r="I3" s="254" t="s">
-        <v>1723</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="4" spans="2:9" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
-        <v>1724</v>
+        <v>1679</v>
       </c>
       <c r="C4" s="236"/>
       <c r="D4" s="233" t="s">
-        <v>1723</v>
+        <v>1678</v>
       </c>
       <c r="E4" s="233" t="s">
-        <v>1723</v>
+        <v>1678</v>
       </c>
       <c r="F4" s="233" t="s">
-        <v>1723</v>
+        <v>1678</v>
       </c>
       <c r="G4" s="233"/>
       <c r="H4" s="233" t="s">
-        <v>1723</v>
+        <v>1678</v>
       </c>
       <c r="I4" s="233" t="s">
-        <v>1723</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="5" spans="2:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
-        <v>1725</v>
+        <v>1680</v>
       </c>
       <c r="C5" s="236"/>
       <c r="D5" s="233" t="s">
-        <v>1723</v>
+        <v>1678</v>
       </c>
       <c r="E5" s="233" t="s">
-        <v>1723</v>
+        <v>1678</v>
       </c>
       <c r="F5" s="233" t="s">
-        <v>1723</v>
+        <v>1678</v>
       </c>
       <c r="G5" s="233"/>
       <c r="H5" s="233" t="s">
-        <v>1723</v>
+        <v>1678</v>
       </c>
       <c r="I5" s="233" t="s">
-        <v>1723</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
-        <v>1726</v>
+        <v>1681</v>
       </c>
       <c r="C6" s="236"/>
       <c r="D6" s="233" t="s">
-        <v>1723</v>
+        <v>1678</v>
       </c>
       <c r="E6" s="233" t="s">
-        <v>1723</v>
+        <v>1678</v>
       </c>
       <c r="F6" s="233" t="s">
-        <v>1723</v>
+        <v>1678</v>
       </c>
       <c r="G6" s="233"/>
       <c r="H6" s="233" t="s">
-        <v>1723</v>
+        <v>1678</v>
       </c>
       <c r="I6" s="233" t="s">
-        <v>1723</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
-        <v>1727</v>
+        <v>1682</v>
       </c>
       <c r="C7" s="236"/>
       <c r="D7" s="233"/>
@@ -16965,29 +16315,29 @@
     </row>
     <row r="8" spans="2:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
-        <v>1728</v>
+        <v>1683</v>
       </c>
       <c r="C8" s="236"/>
       <c r="D8" s="233" t="s">
-        <v>1723</v>
+        <v>1678</v>
       </c>
       <c r="E8" s="233" t="s">
-        <v>1723</v>
+        <v>1678</v>
       </c>
       <c r="F8" s="233" t="s">
-        <v>1723</v>
+        <v>1678</v>
       </c>
       <c r="G8" s="233"/>
       <c r="H8" s="233" t="s">
-        <v>1723</v>
+        <v>1678</v>
       </c>
       <c r="I8" s="233" t="s">
-        <v>1723</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="9" spans="2:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
-        <v>1729</v>
+        <v>1684</v>
       </c>
       <c r="C9" s="236"/>
       <c r="D9" s="233"/>
@@ -16999,29 +16349,29 @@
     </row>
     <row r="10" spans="2:9" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="3" t="s">
-        <v>1730</v>
+        <v>1685</v>
       </c>
       <c r="C10" s="236"/>
       <c r="D10" s="233" t="s">
-        <v>1723</v>
+        <v>1678</v>
       </c>
       <c r="E10" s="233" t="s">
-        <v>1723</v>
+        <v>1678</v>
       </c>
       <c r="F10" s="233" t="s">
-        <v>1723</v>
+        <v>1678</v>
       </c>
       <c r="G10" s="233"/>
       <c r="H10" s="233" t="s">
-        <v>1723</v>
+        <v>1678</v>
       </c>
       <c r="I10" s="233" t="s">
-        <v>1723</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="11" spans="2:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
-        <v>1731</v>
+        <v>1686</v>
       </c>
       <c r="C11" s="236"/>
       <c r="D11" s="233"/>
@@ -17033,7 +16383,7 @@
     </row>
     <row r="12" spans="2:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="1" t="s">
-        <v>1732</v>
+        <v>1687</v>
       </c>
       <c r="C12" s="298"/>
       <c r="D12" s="165"/>
@@ -17045,7 +16395,7 @@
     </row>
     <row r="13" spans="2:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
-        <v>1733</v>
+        <v>1688</v>
       </c>
       <c r="C13" s="298"/>
       <c r="D13" s="165"/>
@@ -17057,7 +16407,7 @@
     </row>
     <row r="14" spans="2:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
-        <v>1734</v>
+        <v>1689</v>
       </c>
       <c r="C14" s="298"/>
       <c r="D14" s="165"/>
@@ -17069,7 +16419,7 @@
     </row>
     <row r="15" spans="2:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="1" t="s">
-        <v>1735</v>
+        <v>1690</v>
       </c>
       <c r="C15" s="298"/>
       <c r="D15" s="165"/>
@@ -17081,7 +16431,7 @@
     </row>
     <row r="16" spans="2:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="1" t="s">
-        <v>1736</v>
+        <v>1691</v>
       </c>
       <c r="C16" s="298"/>
       <c r="D16" s="165"/>
@@ -17093,7 +16443,7 @@
     </row>
     <row r="17" spans="2:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="6" t="s">
-        <v>1737</v>
+        <v>1692</v>
       </c>
       <c r="C17" s="165"/>
       <c r="D17" s="165"/>
@@ -18646,97 +17996,97 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" s="61" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="440" t="s">
+      <c r="A1" s="435" t="s">
         <v>447</v>
       </c>
-      <c r="B1" s="440" t="s">
+      <c r="B1" s="435" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="440" t="s">
+      <c r="C1" s="435" t="s">
         <v>419</v>
       </c>
-      <c r="D1" s="437" t="s">
+      <c r="D1" s="432" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="435"/>
-      <c r="F1" s="436"/>
-      <c r="G1" s="438" t="s">
+      <c r="E1" s="430"/>
+      <c r="F1" s="431"/>
+      <c r="G1" s="433" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="439"/>
-      <c r="I1" s="439"/>
-      <c r="J1" s="437" t="s">
+      <c r="H1" s="434"/>
+      <c r="I1" s="434"/>
+      <c r="J1" s="432" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="435"/>
-      <c r="L1" s="436"/>
-      <c r="M1" s="445" t="s">
+      <c r="K1" s="430"/>
+      <c r="L1" s="431"/>
+      <c r="M1" s="440" t="s">
         <v>8</v>
       </c>
-      <c r="N1" s="446"/>
-      <c r="O1" s="446"/>
-      <c r="P1" s="437" t="s">
+      <c r="N1" s="441"/>
+      <c r="O1" s="441"/>
+      <c r="P1" s="432" t="s">
         <v>9</v>
       </c>
-      <c r="Q1" s="436"/>
-      <c r="R1" s="437" t="s">
+      <c r="Q1" s="431"/>
+      <c r="R1" s="432" t="s">
         <v>10</v>
       </c>
-      <c r="S1" s="436"/>
-      <c r="T1" s="437" t="s">
+      <c r="S1" s="431"/>
+      <c r="T1" s="432" t="s">
         <v>11</v>
       </c>
-      <c r="U1" s="436"/>
-      <c r="V1" s="437" t="s">
+      <c r="U1" s="431"/>
+      <c r="V1" s="432" t="s">
         <v>448</v>
       </c>
-      <c r="W1" s="436"/>
+      <c r="W1" s="431"/>
     </row>
     <row r="2" spans="1:23" s="61" customFormat="1" ht="41.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="441"/>
-      <c r="B2" s="441"/>
-      <c r="C2" s="441"/>
-      <c r="D2" s="434" t="s">
+      <c r="A2" s="436"/>
+      <c r="B2" s="436"/>
+      <c r="C2" s="436"/>
+      <c r="D2" s="429" t="s">
         <v>449</v>
       </c>
-      <c r="E2" s="435"/>
-      <c r="F2" s="436"/>
-      <c r="G2" s="443" t="s">
+      <c r="E2" s="430"/>
+      <c r="F2" s="431"/>
+      <c r="G2" s="438" t="s">
         <v>450</v>
       </c>
-      <c r="H2" s="439"/>
-      <c r="I2" s="439"/>
-      <c r="J2" s="434" t="s">
+      <c r="H2" s="434"/>
+      <c r="I2" s="434"/>
+      <c r="J2" s="429" t="s">
         <v>451</v>
       </c>
-      <c r="K2" s="435"/>
-      <c r="L2" s="436"/>
-      <c r="M2" s="447" t="s">
+      <c r="K2" s="430"/>
+      <c r="L2" s="431"/>
+      <c r="M2" s="442" t="s">
         <v>452</v>
       </c>
-      <c r="N2" s="446"/>
-      <c r="O2" s="446"/>
-      <c r="P2" s="434" t="s">
+      <c r="N2" s="441"/>
+      <c r="O2" s="441"/>
+      <c r="P2" s="429" t="s">
         <v>453</v>
       </c>
-      <c r="Q2" s="436"/>
-      <c r="R2" s="444" t="s">
+      <c r="Q2" s="431"/>
+      <c r="R2" s="439" t="s">
         <v>454</v>
       </c>
-      <c r="S2" s="436"/>
-      <c r="T2" s="434" t="s">
+      <c r="S2" s="431"/>
+      <c r="T2" s="429" t="s">
         <v>455</v>
       </c>
-      <c r="U2" s="436"/>
-      <c r="V2" s="434" t="s">
+      <c r="U2" s="431"/>
+      <c r="V2" s="429" t="s">
         <v>456</v>
       </c>
-      <c r="W2" s="436"/>
+      <c r="W2" s="431"/>
     </row>
     <row r="3" spans="1:23" s="61" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="442"/>
-      <c r="B3" s="442"/>
-      <c r="C3" s="442"/>
+      <c r="A3" s="437"/>
+      <c r="B3" s="437"/>
+      <c r="C3" s="437"/>
       <c r="D3" s="183" t="s">
         <v>457</v>
       </c>
@@ -24791,52 +24141,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" s="61" customFormat="1" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="440" t="s">
+      <c r="A1" s="435" t="s">
         <v>447</v>
       </c>
-      <c r="B1" s="449" t="s">
+      <c r="B1" s="444" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="440" t="s">
+      <c r="C1" s="435" t="s">
         <v>419</v>
       </c>
-      <c r="D1" s="448" t="s">
+      <c r="D1" s="443" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="439"/>
-      <c r="F1" s="437" t="s">
+      <c r="E1" s="434"/>
+      <c r="F1" s="432" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="436"/>
-      <c r="H1" s="448" t="s">
+      <c r="G1" s="431"/>
+      <c r="H1" s="443" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="439"/>
-      <c r="J1" s="437" t="s">
+      <c r="I1" s="434"/>
+      <c r="J1" s="432" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="436"/>
-      <c r="L1" s="448" t="s">
+      <c r="K1" s="431"/>
+      <c r="L1" s="443" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="439"/>
-      <c r="N1" s="437" t="s">
+      <c r="M1" s="434"/>
+      <c r="N1" s="432" t="s">
         <v>10</v>
       </c>
-      <c r="O1" s="436"/>
-      <c r="P1" s="448" t="s">
+      <c r="O1" s="431"/>
+      <c r="P1" s="443" t="s">
         <v>11</v>
       </c>
-      <c r="Q1" s="439"/>
-      <c r="R1" s="437" t="s">
+      <c r="Q1" s="434"/>
+      <c r="R1" s="432" t="s">
         <v>448</v>
       </c>
-      <c r="S1" s="436"/>
+      <c r="S1" s="431"/>
     </row>
     <row r="2" spans="1:19" s="61" customFormat="1" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="442"/>
-      <c r="B2" s="450"/>
-      <c r="C2" s="442"/>
+      <c r="A2" s="437"/>
+      <c r="B2" s="445"/>
+      <c r="C2" s="437"/>
       <c r="D2" s="183" t="s">
         <v>457</v>
       </c>
@@ -25800,64 +25150,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="440" t="s">
+      <c r="A1" s="435" t="s">
         <v>447</v>
       </c>
-      <c r="B1" s="449" t="s">
+      <c r="B1" s="444" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="449" t="s">
+      <c r="C1" s="444" t="s">
         <v>419</v>
       </c>
-      <c r="D1" s="455" t="s">
+      <c r="D1" s="450" t="s">
         <v>1176</v>
       </c>
-      <c r="E1" s="455" t="s">
+      <c r="E1" s="450" t="s">
         <v>1177</v>
       </c>
-      <c r="F1" s="451" t="s">
+      <c r="F1" s="446" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="452"/>
-      <c r="H1" s="452"/>
-      <c r="I1" s="453"/>
-      <c r="J1" s="451" t="s">
+      <c r="G1" s="447"/>
+      <c r="H1" s="447"/>
+      <c r="I1" s="448"/>
+      <c r="J1" s="446" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="452"/>
-      <c r="L1" s="452"/>
-      <c r="M1" s="453"/>
-      <c r="N1" s="454" t="s">
+      <c r="K1" s="447"/>
+      <c r="L1" s="447"/>
+      <c r="M1" s="448"/>
+      <c r="N1" s="449" t="s">
         <v>7</v>
       </c>
-      <c r="O1" s="452"/>
-      <c r="P1" s="452"/>
-      <c r="Q1" s="453"/>
-      <c r="R1" s="454" t="s">
+      <c r="O1" s="447"/>
+      <c r="P1" s="447"/>
+      <c r="Q1" s="448"/>
+      <c r="R1" s="449" t="s">
         <v>1178</v>
       </c>
-      <c r="S1" s="452"/>
-      <c r="T1" s="452"/>
-      <c r="U1" s="453"/>
-      <c r="V1" s="457" t="s">
+      <c r="S1" s="447"/>
+      <c r="T1" s="447"/>
+      <c r="U1" s="448"/>
+      <c r="V1" s="452" t="s">
         <v>9</v>
       </c>
-      <c r="W1" s="452"/>
-      <c r="X1" s="452"/>
-      <c r="Y1" s="453"/>
-      <c r="Z1" s="457" t="s">
+      <c r="W1" s="447"/>
+      <c r="X1" s="447"/>
+      <c r="Y1" s="448"/>
+      <c r="Z1" s="452" t="s">
         <v>10</v>
       </c>
-      <c r="AA1" s="452"/>
-      <c r="AB1" s="452"/>
-      <c r="AC1" s="453"/>
+      <c r="AA1" s="447"/>
+      <c r="AB1" s="447"/>
+      <c r="AC1" s="448"/>
     </row>
     <row r="2" spans="1:29" ht="29.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="442"/>
-      <c r="B2" s="450"/>
-      <c r="C2" s="450"/>
-      <c r="D2" s="456"/>
-      <c r="E2" s="456"/>
+      <c r="A2" s="437"/>
+      <c r="B2" s="445"/>
+      <c r="C2" s="445"/>
+      <c r="D2" s="451"/>
+      <c r="E2" s="451"/>
       <c r="F2" s="172" t="s">
         <v>1179</v>
       </c>
@@ -33019,52 +32369,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" s="61" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="440" t="s">
+      <c r="A1" s="435" t="s">
         <v>447</v>
       </c>
-      <c r="B1" s="449" t="s">
+      <c r="B1" s="444" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="449" t="s">
+      <c r="C1" s="444" t="s">
         <v>419</v>
       </c>
-      <c r="D1" s="448" t="s">
+      <c r="D1" s="443" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="439"/>
-      <c r="F1" s="437" t="s">
+      <c r="E1" s="434"/>
+      <c r="F1" s="432" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="436"/>
-      <c r="H1" s="448" t="s">
+      <c r="G1" s="431"/>
+      <c r="H1" s="443" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="439"/>
-      <c r="J1" s="437" t="s">
+      <c r="I1" s="434"/>
+      <c r="J1" s="432" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="436"/>
-      <c r="L1" s="448" t="s">
+      <c r="K1" s="431"/>
+      <c r="L1" s="443" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="439"/>
-      <c r="N1" s="437" t="s">
+      <c r="M1" s="434"/>
+      <c r="N1" s="432" t="s">
         <v>10</v>
       </c>
-      <c r="O1" s="436"/>
-      <c r="P1" s="448" t="s">
+      <c r="O1" s="431"/>
+      <c r="P1" s="443" t="s">
         <v>11</v>
       </c>
-      <c r="Q1" s="439"/>
-      <c r="R1" s="437" t="s">
+      <c r="Q1" s="434"/>
+      <c r="R1" s="432" t="s">
         <v>448</v>
       </c>
-      <c r="S1" s="436"/>
+      <c r="S1" s="431"/>
     </row>
     <row r="2" spans="1:19" s="61" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="442"/>
-      <c r="B2" s="450"/>
-      <c r="C2" s="450"/>
+      <c r="A2" s="437"/>
+      <c r="B2" s="445"/>
+      <c r="C2" s="445"/>
       <c r="D2" s="183" t="s">
         <v>457</v>
       </c>
@@ -33857,7 +33207,7 @@
       <c r="K16" s="350"/>
       <c r="L16" s="351"/>
     </row>
-    <row r="17" spans="1:12" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A17" s="336"/>
       <c r="B17" s="337"/>
       <c r="C17" s="338" t="s">
@@ -33889,7 +33239,7 @@
       <c r="K17" s="341"/>
       <c r="L17" s="338"/>
     </row>
-    <row r="18" spans="1:12" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A18" s="105"/>
       <c r="B18" s="106"/>
       <c r="C18" s="106"/>
@@ -33913,7 +33263,7 @@
       <c r="K18" s="343"/>
       <c r="L18" s="217"/>
     </row>
-    <row r="19" spans="1:12" ht="409.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" ht="409.5" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A19" s="105"/>
       <c r="B19" s="106"/>
       <c r="C19" s="106"/>
@@ -33949,7 +33299,7 @@
       <c r="K20" s="350"/>
       <c r="L20" s="351"/>
     </row>
-    <row r="21" spans="1:12" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A21" s="336"/>
       <c r="B21" s="337"/>
       <c r="C21" s="338" t="s">
@@ -33981,7 +33331,7 @@
       <c r="K21" s="341"/>
       <c r="L21" s="338"/>
     </row>
-    <row r="22" spans="1:12" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A22" s="105"/>
       <c r="B22" s="106"/>
       <c r="C22" s="106"/>
@@ -34005,7 +33355,7 @@
       <c r="K22" s="343"/>
       <c r="L22" s="217"/>
     </row>
-    <row r="23" spans="1:12" ht="360" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" ht="360" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A23" s="105"/>
       <c r="B23" s="106"/>
       <c r="C23" s="106"/>
@@ -34013,11 +33363,11 @@
       <c r="E23" s="230" t="s">
         <v>34</v>
       </c>
-      <c r="F23" s="430"/>
+      <c r="F23" s="428"/>
       <c r="G23" s="231"/>
-      <c r="H23" s="430"/>
-      <c r="I23" s="430"/>
-      <c r="J23" s="430"/>
+      <c r="H23" s="428"/>
+      <c r="I23" s="428"/>
+      <c r="J23" s="428"/>
       <c r="K23" s="230"/>
       <c r="L23" s="232"/>
     </row>
@@ -34041,7 +33391,7 @@
       <c r="K24" s="350"/>
       <c r="L24" s="351"/>
     </row>
-    <row r="25" spans="1:12" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A25" s="336"/>
       <c r="B25" s="337"/>
       <c r="C25" s="338" t="s">
@@ -34073,7 +33423,7 @@
       <c r="K25" s="341"/>
       <c r="L25" s="338"/>
     </row>
-    <row r="26" spans="1:12" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A26" s="105"/>
       <c r="B26" s="106"/>
       <c r="C26" s="106"/>
@@ -34097,7 +33447,7 @@
       <c r="K26" s="343"/>
       <c r="L26" s="217"/>
     </row>
-    <row r="27" spans="1:12" ht="409.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" ht="409.5" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A27" s="105"/>
       <c r="B27" s="106"/>
       <c r="C27" s="106"/>
@@ -34105,11 +33455,11 @@
       <c r="E27" s="230" t="s">
         <v>34</v>
       </c>
-      <c r="F27" s="430"/>
+      <c r="F27" s="428"/>
       <c r="G27" s="231"/>
-      <c r="H27" s="430"/>
-      <c r="I27" s="430"/>
-      <c r="J27" s="430"/>
+      <c r="H27" s="428"/>
+      <c r="I27" s="428"/>
+      <c r="J27" s="428"/>
       <c r="K27" s="230"/>
       <c r="L27" s="232"/>
     </row>

--- a/DB Flotte ETR1000 Ver_1.8_PROVA.xlsx
+++ b/DB Flotte ETR1000 Ver_1.8_PROVA.xlsx
@@ -3857,8 +3857,8 @@
   <cols>
     <col width="10.85546875" customWidth="1" style="8" min="1" max="2"/>
     <col width="59" customWidth="1" style="8" min="3" max="3"/>
-    <col width="8.7109375" customWidth="1" style="8" min="4" max="23"/>
-    <col width="8.7109375" customWidth="1" style="8" min="24" max="16384"/>
+    <col width="8.7109375" customWidth="1" style="8" min="4" max="24"/>
+    <col width="8.7109375" customWidth="1" style="8" min="25" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" s="107">
@@ -3988,8 +3988,8 @@
     <col width="14.85546875" customWidth="1" style="10" min="10" max="11"/>
     <col width="8.7109375" customWidth="1" style="59" min="12" max="12"/>
     <col width="33.140625" customWidth="1" style="59" min="13" max="13"/>
-    <col width="8.7109375" customWidth="1" style="59" min="14" max="27"/>
-    <col width="8.7109375" customWidth="1" style="59" min="28" max="16384"/>
+    <col width="8.7109375" customWidth="1" style="59" min="14" max="28"/>
+    <col width="8.7109375" customWidth="1" style="59" min="29" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" s="61">
@@ -4177,7 +4177,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1" s="480">
+    <row r="5" ht="60" customHeight="1" s="480">
       <c r="C5" s="525" t="inlineStr">
         <is>
           <t>2F_04.01.Zefiro-Europe.CONCEPT.775</t>
@@ -4254,20 +4254,14 @@
       </c>
       <c r="H5" s="527" t="inlineStr">
         <is>
-          <t>Description divergente tra VZI_Base e VZ_ES (similarita' 81%, score 0/100).
-Dettaglio differenze nella Description:
-  • VZI_Base: «selected» → VZ_ES: «used»
-  • presente solo in VZ_ES: «tcms depending»
-  • VZI_Base: «driver on» → VZ_ES: «country in which»</t>
+          <t>In VZ_ES la soglia di intervento e' 800 kPa contro i 750 kPa della VZI_Base.
+Differenze nel testo del requisito: Confrontando il testo dei due documenti si osserva che dove VZI_Base prescrive «selected», VZ_ES prescrive invece «used»; dove VZI_Base prescrive «driver on», VZ_ES prescrive invece «country in which»; dove VZI_Base prescrive «idu», VZ_ES prescrive invece «vehicle will operate»; infine VZ_ES aggiunge la prescrizione «tcms depending», assente in VZI_Base. Verificare quale delle due formulazioni si applica alla configurazione VZ_ES.</t>
         </is>
       </c>
       <c r="I5" s="527" t="inlineStr">
         <is>
-          <t>Description divergente tra VZI_Base e VZI-6_R1 (similarita' 70%, score 0/100).
-Dettaglio differenze nella Description:
-  • VZI_Base: «selected» → VZI-6_R1: «used»
-  • presente solo in VZI-6_R1: «tcms depending»
-  • VZI_Base: «driver on» → VZI-6_R1: «country in which»</t>
+          <t>In VZ_ES la soglia di intervento e' 800 kPa contro i 750 kPa della VZI_Base.
+Differenze nel testo del requisito: Confrontando il testo dei due documenti si osserva che dove VZI_Base prescrive «selected», VZI-6_R1 prescrive invece «used»; dove VZI_Base prescrive «driver on», VZI-6_R1 prescrive invece «country in which»; dove VZI_Base prescrive «idu», VZI-6_R1 prescrive invece «vehicle will operate»; la prescrizione «6 netherlands 7 spain 8 switzerland 0 not defined», presente in VZI_Base, non compare in VZI-6_R1; infine VZI-6_R1 aggiunge la prescrizione «tcms depending», assente in VZI_Base. Verificare quale delle due formulazioni si applica alla configurazione VZI-6_R1.</t>
         </is>
       </c>
     </row>
@@ -4357,7 +4351,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="45" customHeight="1" s="480">
+    <row r="7" ht="30" customHeight="1" s="480">
       <c r="C7" s="525" t="inlineStr">
         <is>
           <t>2F_04.01.Zefiro-Europe.CONCEPT.965</t>
@@ -4432,9 +4426,10 @@
           <t>MATCHED</t>
         </is>
       </c>
-      <c r="H7" s="526" t="inlineStr">
-        <is>
-          <t>MATCHED</t>
+      <c r="H7" s="527" t="inlineStr">
+        <is>
+          <t>In VZ_ES la soglia di intervento e' 800 kPa contro i 750 kPa della VZI_Base.
+Differenze nel testo del requisito: Confrontando il testo dei due documenti si osserva che dove VZI_Base prescrive «the driver shall get a feedback on idu from propulsion system that the system is prepared for operation in country or selected country-code. the driver has to c», VZ_ES prescrive invece «deleted.». Verificare quale delle due formulazioni si applica alla configurazione VZ_ES.</t>
         </is>
       </c>
       <c r="I7" s="526" t="inlineStr">
@@ -4504,14 +4499,14 @@
       </c>
       <c r="E8" s="525" t="inlineStr">
         <is>
-          <t>Description: _ It shall be possible to select the country which the train will be operated in from the IDU. Possible counties are:  Italy, Austria, Belgium, France, Germany, Netherlands, Spain and Switzerland. The country selection shall be used for country specific configurations such as:  selection of wide or narrow pantograph  levels of line voltage supervision  levels of line current harmonics.
+          <t>Description: It shall be possible to select the country which the train will be operated in from the IDU. Possible counties are:  Italy, Austria, Belgium, France, Germany, Netherlands, Spain and Switzerland. The country selection shall be used for country specific configurations such as:  selection of wide or narrow pantograph  levels of line voltage supervision  levels of line current harmonics.
 ————————————————————
 Safety level: SIL 2</t>
         </is>
       </c>
-      <c r="G8" s="527" t="inlineStr">
-        <is>
-          <t>Description divergente tra VZI_Base e VZ_FR (similarita' 89%, score 0/100).</t>
+      <c r="G8" s="526" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
         </is>
       </c>
       <c r="H8" s="527" t="inlineStr">
@@ -4521,15 +4516,12 @@
       </c>
       <c r="I8" s="527" t="inlineStr">
         <is>
-          <t>Description divergente tra VZI_Base e VZI-6_R1 (similarita' 77%, score 0/100).
-Dettaglio differenze nella Description:
-  • VZI_Base: «idu.» → VZI-6_R1: «tod.»
-  • VZI_Base: «counties» → VZI-6_R1: «countries»
-  • presente solo in VZI-6_R1: «only italy code is operative»</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="45" customHeight="1" s="480">
+          <t>In VZ_ES la soglia di intervento e' 800 kPa contro i 750 kPa della VZI_Base.
+Differenze nel testo del requisito: Confrontando il testo dei due documenti si osserva che dove VZI_Base prescrive «idu.», VZI-6_R1 prescrive invece «tod.»; dove VZI_Base prescrive «counties», VZI-6_R1 prescrive invece «countries»; VZI-6_R1 aggiunge la prescrizione «only italy code is operative», assente in VZI_Base; infine VZI-6_R1 aggiunge la prescrizione «selection of voltage system», assente in VZI_Base. Verificare quale delle due formulazioni si applica alla configurazione VZI-6_R1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1" s="480">
       <c r="C9" s="525" t="inlineStr">
         <is>
           <t>2F_04.01.Zefiro-Europe.CONCEPT.HR01</t>
@@ -4565,7 +4557,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="30" customHeight="1" s="480">
       <c r="C11" s="525" t="inlineStr">
         <is>
           <t>2F_04.01.Zefiro-Europe.CONCEPT.HR03</t>
@@ -4583,7 +4575,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="30" customHeight="1" s="480">
       <c r="C12" s="525" t="inlineStr">
         <is>
           <t>2F_04.01.Zefiro-Europe.CONCEPT.HR310</t>
@@ -4622,7 +4614,7 @@
       <c r="J13" s="350" t="n"/>
       <c r="K13" s="351" t="n"/>
     </row>
-    <row r="14" ht="60" customHeight="1" s="480">
+    <row r="14" ht="30" customHeight="1" s="480">
       <c r="A14" s="347" t="inlineStr">
         <is>
           <t>LV_Pantograph_Lowering</t>
@@ -5821,8 +5813,8 @@
     <col width="24.28515625" customWidth="1" style="10" min="3" max="3"/>
     <col width="18.7109375" bestFit="1" customWidth="1" style="10" min="4" max="4"/>
     <col width="16.5703125" customWidth="1" style="10" min="5" max="10"/>
-    <col width="8.7109375" customWidth="1" style="59" min="11" max="30"/>
-    <col width="8.7109375" customWidth="1" style="59" min="31" max="16384"/>
+    <col width="8.7109375" customWidth="1" style="59" min="11" max="31"/>
+    <col width="8.7109375" customWidth="1" style="59" min="32" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="31.5" customFormat="1" customHeight="1" s="61">
@@ -11903,8 +11895,8 @@
     <mergeCell ref="A43:A47"/>
     <mergeCell ref="W49:Z49"/>
     <mergeCell ref="O25:O28"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="K43:N44"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="S9:S12"/>
     <mergeCell ref="G3:G8"/>
     <mergeCell ref="C17:C20"/>
@@ -11934,8 +11926,8 @@
     <col width="28.42578125" bestFit="1" customWidth="1" style="8" min="4" max="4"/>
     <col width="21.42578125" customWidth="1" style="8" min="5" max="5"/>
     <col width="35.5703125" customWidth="1" style="8" min="6" max="7"/>
-    <col width="8.7109375" customWidth="1" style="8" min="8" max="27"/>
-    <col width="8.7109375" customWidth="1" style="8" min="28" max="16384"/>
+    <col width="8.7109375" customWidth="1" style="8" min="8" max="28"/>
+    <col width="8.7109375" customWidth="1" style="8" min="29" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" s="480">
@@ -12940,8 +12932,8 @@
     <col width="8.7109375" customWidth="1" style="9" min="3" max="3"/>
     <col width="120.7109375" customWidth="1" style="59" min="4" max="4"/>
     <col width="60.140625" customWidth="1" style="59" min="5" max="5"/>
-    <col width="8.7109375" customWidth="1" style="8" min="6" max="25"/>
-    <col width="8.7109375" customWidth="1" style="8" min="26" max="16384"/>
+    <col width="8.7109375" customWidth="1" style="8" min="6" max="26"/>
+    <col width="8.7109375" customWidth="1" style="8" min="27" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="23.45" customFormat="1" customHeight="1" s="109">
@@ -13293,8 +13285,8 @@
     <col width="6.5703125" bestFit="1" customWidth="1" style="8" min="3" max="3"/>
     <col width="139.42578125" bestFit="1" customWidth="1" style="60" min="4" max="4"/>
     <col width="8.7109375" customWidth="1" style="9" min="5" max="5"/>
-    <col width="8.7109375" customWidth="1" style="8" min="6" max="25"/>
-    <col width="8.7109375" customWidth="1" style="8" min="26" max="16384"/>
+    <col width="8.7109375" customWidth="1" style="8" min="6" max="26"/>
+    <col width="8.7109375" customWidth="1" style="8" min="27" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="21.6" customHeight="1" s="480">
@@ -14718,8 +14710,8 @@
     <col width="6.5703125" customWidth="1" style="10" min="21" max="21"/>
     <col width="6.5703125" bestFit="1" customWidth="1" style="10" min="22" max="22"/>
     <col width="6.5703125" customWidth="1" style="10" min="23" max="23"/>
-    <col width="8.7109375" customWidth="1" style="59" min="24" max="43"/>
-    <col width="8.7109375" customWidth="1" style="59" min="44" max="16384"/>
+    <col width="8.7109375" customWidth="1" style="59" min="24" max="44"/>
+    <col width="8.7109375" customWidth="1" style="59" min="45" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" s="61">
@@ -24091,8 +24083,8 @@
     <col width="6.5703125" customWidth="1" style="10" min="17" max="17"/>
     <col width="6.5703125" bestFit="1" customWidth="1" style="10" min="18" max="18"/>
     <col width="6.5703125" customWidth="1" style="10" min="19" max="19"/>
-    <col width="8.7109375" customWidth="1" style="59" min="20" max="39"/>
-    <col width="8.7109375" customWidth="1" style="59" min="40" max="16384"/>
+    <col width="8.7109375" customWidth="1" style="59" min="20" max="40"/>
+    <col width="8.7109375" customWidth="1" style="59" min="41" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="26.45" customFormat="1" customHeight="1" s="61">
@@ -25453,8 +25445,8 @@
     <col width="26.42578125" bestFit="1" customWidth="1" style="9" min="27" max="27"/>
     <col width="4.42578125" bestFit="1" customWidth="1" style="9" min="28" max="28"/>
     <col width="8.85546875" bestFit="1" customWidth="1" style="290" min="29" max="29"/>
-    <col width="8.7109375" customWidth="1" style="8" min="30" max="43"/>
-    <col width="8.7109375" customWidth="1" style="8" min="44" max="16384"/>
+    <col width="8.7109375" customWidth="1" style="8" min="30" max="44"/>
+    <col width="8.7109375" customWidth="1" style="8" min="45" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="29.45" customHeight="1" s="480">
@@ -33960,8 +33952,8 @@
     <col width="6.5703125" customWidth="1" style="10" min="17" max="17"/>
     <col width="6.5703125" bestFit="1" customWidth="1" style="10" min="18" max="18"/>
     <col width="6.5703125" customWidth="1" style="10" min="19" max="19"/>
-    <col width="8.7109375" customWidth="1" style="59" min="20" max="39"/>
-    <col width="8.7109375" customWidth="1" style="59" min="40" max="16384"/>
+    <col width="8.7109375" customWidth="1" style="59" min="20" max="40"/>
+    <col width="8.7109375" customWidth="1" style="59" min="41" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="21.6" customFormat="1" customHeight="1" s="61">
@@ -34569,8 +34561,8 @@
     <col width="14.85546875" customWidth="1" style="10" min="11" max="12"/>
     <col width="8.7109375" customWidth="1" style="59" min="13" max="13"/>
     <col width="33.140625" customWidth="1" style="59" min="14" max="14"/>
-    <col width="8.7109375" customWidth="1" style="59" min="15" max="34"/>
-    <col width="8.7109375" customWidth="1" style="59" min="35" max="16384"/>
+    <col width="8.7109375" customWidth="1" style="59" min="15" max="35"/>
+    <col width="8.7109375" customWidth="1" style="59" min="36" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customFormat="1" customHeight="1" s="61">
@@ -35273,11 +35265,11 @@
           <t>Funzioni AI</t>
         </is>
       </c>
-      <c r="F23" s="429" t="n"/>
+      <c r="F23" s="428" t="n"/>
       <c r="G23" s="231" t="n"/>
-      <c r="H23" s="429" t="n"/>
-      <c r="I23" s="429" t="n"/>
-      <c r="J23" s="429" t="n"/>
+      <c r="H23" s="428" t="n"/>
+      <c r="I23" s="428" t="n"/>
+      <c r="J23" s="428" t="n"/>
       <c r="K23" s="230" t="n"/>
       <c r="L23" s="232" t="n"/>
     </row>
